--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1679,7 +1684,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2011,12 +2021,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2435,12 +2440,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2783,12 +2788,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2870,7 +2875,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3104,12 +3114,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4432,12 +4442,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4693,12 +4698,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4780,12 +4785,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4867,12 +4872,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5215,12 +5220,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5465,12 +5470,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6074,12 +6074,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7281,12 +7281,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7455,12 +7455,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7542,12 +7537,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8042,12 +8037,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8216,12 +8211,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8901,12 +8891,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9488,12 +9478,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -9749,12 +9739,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -9836,12 +9826,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -10184,7 +10174,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -12071,12 +12066,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -13017,12 +13012,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -13104,12 +13094,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -13767,12 +13752,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -14688,12 +14673,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -14775,12 +14760,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -16384,7 +16369,12 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -16598,12 +16588,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -17011,12 +16996,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -17837,12 +17817,12 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SULCA NUÑEZ, DAVID ALEJANDRO</t>
+          <t>NAVARRO ORGONE, ALFREDO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>994 101 509</t>
+          <t>991892546</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -18663,12 +18643,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -19261,12 +19236,12 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -19435,7 +19410,12 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -19604,7 +19584,12 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>CHUMPITAZ VARGAS, GEORGE BENSON</t>
+          <t>CHIPANA QUISPE, CHRISTIAN ALONSO</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>953 450 482</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -19675,7 +19660,12 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>CHUMPITAZ VARGAS, GEORGE BENSON</t>
+          <t>CHIPANA QUISPE, CHRISTIAN ALONSO</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>953 450 482</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -23706,12 +23696,12 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -24304,12 +24294,12 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -24728,12 +24718,12 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -25044,12 +25034,12 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -25729,12 +25719,12 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -25816,12 +25806,12 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>SULCA NUÑEZ, DAVID ALEJANDRO</t>
+          <t>NAVARRO ORGONE, ALFREDO</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>994 101 509</t>
+          <t>991892546</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -26127,12 +26117,12 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SULCA NUÑEZ, DAVID ALEJANDRO</t>
+          <t>NAVARRO ORGONE, ALFREDO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>994 101 509</t>
+          <t>991892546</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -26203,7 +26193,12 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -26285,7 +26280,12 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -26530,12 +26530,12 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SULCA NUÑEZ, DAVID ALEJANDRO</t>
+          <t>NAVARRO ORGONE, ALFREDO</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>994 101 509</t>
+          <t>991892546</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -27117,7 +27117,12 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -27286,7 +27291,12 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -27787,7 +27797,12 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -27956,12 +27971,12 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -29576,12 +29591,12 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>SULCA NUÑEZ, DAVID ALEJANDRO</t>
+          <t>NAVARRO ORGONE, ALFREDO</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>994 101 509</t>
+          <t>991892546</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -29739,12 +29754,12 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SULCA NUÑEZ, DAVID ALEJANDRO</t>
+          <t>NAVARRO ORGONE, ALFREDO</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>994 101 509</t>
+          <t>991892546</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -30065,12 +30080,12 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -31143,7 +31158,12 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -31225,7 +31245,12 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -31557,12 +31582,12 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -35374,7 +35399,12 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -36473,12 +36503,12 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>SULCA NUÑEZ, DAVID ALEJANDRO</t>
+          <t>NAVARRO ORGONE, ALFREDO</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>994 101 509</t>
+          <t>991892546</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -37653,12 +37683,12 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -38088,12 +38118,12 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>SULCA NUÑEZ, DAVID ALEJANDRO</t>
+          <t>NAVARRO ORGONE, ALFREDO</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>994 101 509</t>
+          <t>991892546</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -38235,12 +38265,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H458" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -38322,12 +38347,12 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -38746,12 +38771,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H464" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -39181,12 +39201,12 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -39355,12 +39375,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H471" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -39616,12 +39631,12 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -39703,7 +39718,12 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -39785,12 +39805,12 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -41001,12 +41021,12 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -41262,12 +41282,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H494" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -43002,7 +43017,12 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -43606,12 +43626,12 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -43943,12 +43963,12 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -44204,12 +44224,12 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -44291,12 +44311,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H529" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -45074,12 +45089,7 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H538" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -45161,12 +45171,12 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -45248,12 +45258,7 @@
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H540" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -45498,12 +45503,12 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -45585,12 +45590,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H544" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -45835,12 +45835,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H547" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -46618,7 +46613,12 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>CHUMPITAZ VARGAS, GEORGE BENSON</t>
+          <t>CHIPANA QUISPE, CHRISTIAN ALONSO</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>953 450 482</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -46950,12 +46950,12 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -47548,12 +47548,12 @@
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -47635,7 +47635,12 @@
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -48152,12 +48157,12 @@
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -48750,12 +48755,12 @@
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -49598,12 +49603,7 @@
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H591" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -50109,12 +50109,12 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -51207,12 +51207,12 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -51381,12 +51381,12 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -51555,7 +51555,12 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -51637,12 +51642,12 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -51724,7 +51729,12 @@
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -52241,12 +52251,12 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -54111,12 +54121,12 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -56828,12 +56838,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H677" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -56915,7 +56920,12 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -57334,12 +57344,12 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -58530,12 +58540,12 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -58617,12 +58627,12 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -59139,12 +59149,7 @@
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H704" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -59487,7 +59492,12 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -59743,12 +59753,12 @@
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -60167,7 +60177,12 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -60510,7 +60525,12 @@
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -60679,12 +60699,12 @@
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -61625,7 +61645,12 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -61794,12 +61819,12 @@
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -62142,7 +62167,12 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -62485,12 +62515,12 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -62572,12 +62602,12 @@
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -63165,12 +63195,12 @@
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -64622,7 +64652,12 @@
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -65400,12 +65435,12 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -65922,12 +65957,12 @@
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -66694,7 +66729,12 @@
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -67211,12 +67251,12 @@
       </c>
       <c r="G798" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -67298,12 +67338,12 @@
       </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -68244,7 +68284,12 @@
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -68500,12 +68545,12 @@
       </c>
       <c r="G813" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -68674,12 +68719,7 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H815" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -68761,7 +68801,12 @@
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -69626,12 +69671,7 @@
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H826" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
@@ -70496,12 +70536,12 @@
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
@@ -71268,12 +71308,7 @@
       </c>
       <c r="G845" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H845" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -72127,12 +72162,12 @@
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -72562,12 +72597,7 @@
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H860" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -73062,12 +73092,12 @@
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
@@ -73660,12 +73690,12 @@
       </c>
       <c r="G873" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -73747,12 +73777,12 @@
       </c>
       <c r="G874" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
@@ -74356,12 +74386,12 @@
       </c>
       <c r="G881" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -74617,12 +74647,7 @@
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H884" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
@@ -74791,7 +74816,12 @@
       </c>
       <c r="G886" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -75047,12 +75077,12 @@
       </c>
       <c r="G889" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -75569,12 +75599,12 @@
       </c>
       <c r="G895" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
@@ -75917,12 +75947,7 @@
       </c>
       <c r="G899" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H899" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
@@ -76439,12 +76464,7 @@
       </c>
       <c r="G905" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H905" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
@@ -76526,12 +76546,12 @@
       </c>
       <c r="G906" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
@@ -76787,12 +76807,12 @@
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -76961,7 +76981,12 @@
       </c>
       <c r="G911" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I911" t="inlineStr">
@@ -77478,12 +77503,12 @@
       </c>
       <c r="G917" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
@@ -78239,12 +78264,12 @@
       </c>
       <c r="G926" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">
@@ -78587,12 +78612,7 @@
       </c>
       <c r="G930" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H930" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I930" t="inlineStr">
@@ -78674,12 +78694,7 @@
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H931" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I931" t="inlineStr">
@@ -78761,12 +78776,7 @@
       </c>
       <c r="G932" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H932" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I932" t="inlineStr">
@@ -79022,7 +79032,12 @@
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I935" t="inlineStr">
@@ -79278,12 +79293,12 @@
       </c>
       <c r="G938" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H938" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I938" t="inlineStr">
@@ -79865,12 +79880,12 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I945" t="inlineStr">
@@ -80898,7 +80913,12 @@
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I957" t="inlineStr">
@@ -81056,12 +81076,12 @@
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H959" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I959" t="inlineStr">
@@ -81475,12 +81495,12 @@
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H964" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I964" t="inlineStr">
@@ -81736,12 +81756,12 @@
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I967" t="inlineStr">
@@ -82073,12 +82093,7 @@
       </c>
       <c r="G971" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H971" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I971" t="inlineStr">
@@ -82334,12 +82349,7 @@
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H974" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I974" t="inlineStr">
@@ -83280,7 +83290,12 @@
       </c>
       <c r="G985" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I985" t="inlineStr">
@@ -83449,12 +83464,12 @@
       </c>
       <c r="G987" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H987" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I987" t="inlineStr">
@@ -83873,12 +83888,7 @@
       </c>
       <c r="G992" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H992" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I992" t="inlineStr">
@@ -84297,12 +84307,12 @@
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H997" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I997" t="inlineStr">
@@ -86091,12 +86101,7 @@
       </c>
       <c r="G1018" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H1018" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I1018" t="inlineStr">
@@ -86863,12 +86868,12 @@
       </c>
       <c r="G1027" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H1027" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I1027" t="inlineStr">
@@ -86950,12 +86955,12 @@
       </c>
       <c r="G1028" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H1028" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I1028" t="inlineStr">
@@ -87124,12 +87129,12 @@
       </c>
       <c r="G1030" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H1030" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I1030" t="inlineStr">
@@ -88581,7 +88586,12 @@
       </c>
       <c r="G1047" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I1047" t="inlineStr">
@@ -89261,12 +89271,12 @@
       </c>
       <c r="G1055" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1055" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1055" t="inlineStr">
@@ -90120,12 +90130,7 @@
       </c>
       <c r="G1065" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H1065" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I1065" t="inlineStr">
@@ -90207,12 +90212,12 @@
       </c>
       <c r="G1066" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H1066" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I1066" t="inlineStr">
@@ -93360,12 +93365,12 @@
       </c>
       <c r="G1103" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1103" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1103" t="inlineStr">
@@ -93447,12 +93452,7 @@
       </c>
       <c r="G1104" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H1104" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I1104" t="inlineStr">
@@ -93784,12 +93784,7 @@
       </c>
       <c r="G1108" t="inlineStr">
         <is>
-          <t>CUEVA ORBEGOZO, ALFONSO ENRIQUE</t>
-        </is>
-      </c>
-      <c r="H1108" t="inlineStr">
-        <is>
-          <t>987 635 519</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="I1108" t="inlineStr">
@@ -94480,12 +94475,12 @@
       </c>
       <c r="G1116" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1116" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1116" t="inlineStr">
@@ -94567,12 +94562,12 @@
       </c>
       <c r="G1117" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1117" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1117" t="inlineStr">
@@ -94654,12 +94649,12 @@
       </c>
       <c r="G1118" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1118" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1118" t="inlineStr">
@@ -94828,12 +94823,12 @@
       </c>
       <c r="G1120" t="inlineStr">
         <is>
-          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
+          <t>ARIZAPANA CORONACION, ANGELO ALESSANDRO</t>
         </is>
       </c>
       <c r="H1120" t="inlineStr">
         <is>
-          <t>987 635 804</t>
+          <t>907 474 380</t>
         </is>
       </c>
       <c r="I1120" t="inlineStr">
@@ -94915,12 +94910,12 @@
       </c>
       <c r="G1121" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H1121" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I1121" t="inlineStr">
@@ -95176,12 +95171,12 @@
       </c>
       <c r="G1124" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1124" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1124" t="inlineStr">
@@ -95263,12 +95258,12 @@
       </c>
       <c r="G1125" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1125" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1125" t="inlineStr">
@@ -95350,12 +95345,12 @@
       </c>
       <c r="G1126" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1126" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1126" t="inlineStr">
@@ -95524,7 +95519,12 @@
       </c>
       <c r="G1128" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I1128" t="inlineStr">
@@ -97661,7 +97661,12 @@
       </c>
       <c r="G1153" t="inlineStr">
         <is>
-          <t>Franco Maravi</t>
+          <t>PONCE BENITO, MOISES WALTHER</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>968 965 845</t>
         </is>
       </c>
       <c r="I1153" t="inlineStr">
@@ -97743,12 +97748,12 @@
       </c>
       <c r="G1154" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1154" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1154" t="inlineStr">
@@ -97917,12 +97922,12 @@
       </c>
       <c r="G1156" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1156" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1156" t="inlineStr">
@@ -98439,12 +98444,12 @@
       </c>
       <c r="G1162" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1162" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1162" t="inlineStr">
@@ -98700,12 +98705,12 @@
       </c>
       <c r="G1165" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H1165" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I1165" t="inlineStr">
@@ -98787,12 +98792,12 @@
       </c>
       <c r="G1166" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1166" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1166" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1022,17 +1022,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1041,17 +1041,6 @@
       <c r="P7" t="n">
         <v>-77.05877</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-12.0784</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-77.05877</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1196,17 +1185,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1215,17 +1204,6 @@
       <c r="P9" t="n">
         <v>-77.04321</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-12.06433</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-77.04321</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1614,12 +1592,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1629,14 +1607,14 @@
         <v>-76.85301</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.29456</v>
+        <v>-12.254973</v>
       </c>
       <c r="R14" t="n">
-        <v>-76.85301</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1940,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1977,14 +1955,14 @@
         <v>-76.85357</v>
       </c>
       <c r="Q18" t="n">
-        <v>-12.29034</v>
+        <v>-12.254973</v>
       </c>
       <c r="R18" t="n">
-        <v>-76.85357</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2190,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2222,14 +2200,14 @@
         <v>-77.09954</v>
       </c>
       <c r="Q21" t="n">
-        <v>-12.05567</v>
+        <v>-12.0596747</v>
       </c>
       <c r="R21" t="n">
-        <v>-77.09954</v>
+        <v>-77.10685359999999</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2864,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -2896,14 +2874,14 @@
         <v>-76.94418</v>
       </c>
       <c r="Q29" t="n">
-        <v>-12.10059</v>
+        <v>-12.1011044</v>
       </c>
       <c r="R29" t="n">
-        <v>-76.94418</v>
+        <v>-76.9495994</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -2968,12 +2946,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -2983,14 +2961,14 @@
         <v>-76.83973</v>
       </c>
       <c r="Q30" t="n">
-        <v>-12.27591</v>
+        <v>-12.254973</v>
       </c>
       <c r="R30" t="n">
-        <v>-76.83973</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -3632,17 +3610,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O38" t="n">
@@ -3651,17 +3629,6 @@
       <c r="P38" t="n">
         <v>-77.06435</v>
       </c>
-      <c r="Q38" t="n">
-        <v>-12.0734</v>
-      </c>
-      <c r="R38" t="n">
-        <v>-77.06435</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4318,12 +4285,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -4333,14 +4300,14 @@
         <v>-76.86939</v>
       </c>
       <c r="Q46" t="n">
-        <v>-12.27683</v>
+        <v>-12.254973</v>
       </c>
       <c r="R46" t="n">
-        <v>-76.86939</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5046,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O55" t="n">
@@ -5089,14 +5056,14 @@
         <v>-77.09782</v>
       </c>
       <c r="Q55" t="n">
-        <v>-12.06121</v>
+        <v>-12.0596747</v>
       </c>
       <c r="R55" t="n">
-        <v>-77.09782</v>
+        <v>-77.10685359999999</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -5324,12 +5291,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O58" t="n">
@@ -5339,14 +5306,14 @@
         <v>-76.8381</v>
       </c>
       <c r="Q58" t="n">
-        <v>-12.30896</v>
+        <v>-12.254973</v>
       </c>
       <c r="R58" t="n">
-        <v>-76.8381</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -5564,17 +5531,17 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -5583,17 +5550,6 @@
       <c r="P61" t="n">
         <v>-77.05634999999999</v>
       </c>
-      <c r="Q61" t="n">
-        <v>-12.07325</v>
-      </c>
-      <c r="R61" t="n">
-        <v>-77.05634999999999</v>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6227,17 +6183,17 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O69" t="n">
@@ -6246,17 +6202,6 @@
       <c r="P69" t="n">
         <v>-77.05798</v>
       </c>
-      <c r="Q69" t="n">
-        <v>-12.07688</v>
-      </c>
-      <c r="R69" t="n">
-        <v>-77.05798</v>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7651,12 +7596,12 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O86" t="n">
@@ -7666,14 +7611,14 @@
         <v>-76.85405</v>
       </c>
       <c r="Q86" t="n">
-        <v>-12.29277</v>
+        <v>-12.254973</v>
       </c>
       <c r="R86" t="n">
-        <v>-76.85405</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8036,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O91" t="n">
@@ -8101,14 +8046,14 @@
         <v>-77.02034</v>
       </c>
       <c r="Q91" t="n">
-        <v>-12.11084</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R91" t="n">
-        <v>-77.02034</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -9114,12 +9059,12 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -9129,14 +9074,14 @@
         <v>-76.87018999999999</v>
       </c>
       <c r="Q103" t="n">
-        <v>-12.27793</v>
+        <v>-12.254973</v>
       </c>
       <c r="R103" t="n">
-        <v>-76.87018999999999</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9575,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O109" t="n">
@@ -9640,14 +9585,14 @@
         <v>-77.04510999999999</v>
       </c>
       <c r="Q109" t="n">
-        <v>-12.09216</v>
+        <v>-12.0764541</v>
       </c>
       <c r="R109" t="n">
-        <v>-77.04510999999999</v>
+        <v>-77.0112151</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -9891,7 +9836,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O112" t="n">
@@ -9901,14 +9846,14 @@
         <v>-77.05880999999999</v>
       </c>
       <c r="Q112" t="n">
-        <v>-12.10267</v>
+        <v>-12.0765143</v>
       </c>
       <c r="R112" t="n">
-        <v>-77.05880999999999</v>
+        <v>-77.0118501</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -10403,17 +10348,17 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O118" t="n">
@@ -10422,17 +10367,6 @@
       <c r="P118" t="n">
         <v>-77.03766</v>
       </c>
-      <c r="Q118" t="n">
-        <v>-12.05661</v>
-      </c>
-      <c r="R118" t="n">
-        <v>-77.03766</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10500,7 +10434,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O119" t="n">
@@ -10510,14 +10444,14 @@
         <v>-77.07504</v>
       </c>
       <c r="Q119" t="n">
-        <v>-12.09094</v>
+        <v>-12.0780896</v>
       </c>
       <c r="R119" t="n">
-        <v>-77.07504</v>
+        <v>-77.0131758</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -11087,7 +11021,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O126" t="n">
@@ -11097,14 +11031,14 @@
         <v>-77.00254</v>
       </c>
       <c r="Q126" t="n">
-        <v>-12.11689</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R126" t="n">
-        <v>-77.00254</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11108,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -11184,14 +11118,14 @@
         <v>-77.00254</v>
       </c>
       <c r="Q127" t="n">
-        <v>-12.11689</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R127" t="n">
-        <v>-77.00254</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -11588,17 +11522,17 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O132" t="n">
@@ -11607,17 +11541,6 @@
       <c r="P132" t="n">
         <v>-77.05754</v>
       </c>
-      <c r="Q132" t="n">
-        <v>-12.07036</v>
-      </c>
-      <c r="R132" t="n">
-        <v>-77.05754</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11772,7 +11695,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O134" t="n">
@@ -11782,14 +11705,14 @@
         <v>-77.13114</v>
       </c>
       <c r="Q134" t="n">
-        <v>-11.9523366</v>
+        <v>-12.0344931</v>
       </c>
       <c r="R134" t="n">
-        <v>-77.1322583</v>
+        <v>-76.9896052</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>LLEGADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11869,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O136" t="n">
@@ -11956,14 +11879,14 @@
         <v>-77.02728</v>
       </c>
       <c r="Q136" t="n">
-        <v>-12.10915</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R136" t="n">
-        <v>-77.02728</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -12632,17 +12555,17 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O144" t="n">
@@ -12651,17 +12574,6 @@
       <c r="P144" t="n">
         <v>-77.05391</v>
       </c>
-      <c r="Q144" t="n">
-        <v>-12.07063</v>
-      </c>
-      <c r="R144" t="n">
-        <v>-77.05391</v>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13431,12 +13343,12 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O154" t="n">
@@ -13446,14 +13358,14 @@
         <v>-76.86939</v>
       </c>
       <c r="Q154" t="n">
-        <v>-12.27683</v>
+        <v>-12.254973</v>
       </c>
       <c r="R154" t="n">
-        <v>-76.86939</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -14749,17 +14661,17 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O171" t="n">
@@ -14768,17 +14680,6 @@
       <c r="P171" t="n">
         <v>-77.06335</v>
       </c>
-      <c r="Q171" t="n">
-        <v>-12.07021</v>
-      </c>
-      <c r="R171" t="n">
-        <v>-77.06335</v>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -15102,12 +15003,12 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O175" t="n">
@@ -15117,14 +15018,14 @@
         <v>-76.87074</v>
       </c>
       <c r="Q175" t="n">
-        <v>-12.27634</v>
+        <v>-12.254973</v>
       </c>
       <c r="R175" t="n">
-        <v>-76.87074</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -15189,12 +15090,12 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O176" t="n">
@@ -15204,14 +15105,14 @@
         <v>-76.87087</v>
       </c>
       <c r="Q176" t="n">
-        <v>-12.27473</v>
+        <v>-12.254973</v>
       </c>
       <c r="R176" t="n">
-        <v>-76.87087</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -15537,12 +15438,12 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O180" t="n">
@@ -15552,14 +15453,14 @@
         <v>-76.85375999999999</v>
       </c>
       <c r="Q180" t="n">
-        <v>-12.29477</v>
+        <v>-12.254973</v>
       </c>
       <c r="R180" t="n">
-        <v>-76.85375999999999</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -15619,17 +15520,17 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O181" t="n">
@@ -15638,17 +15539,6 @@
       <c r="P181" t="n">
         <v>-77.05853</v>
       </c>
-      <c r="Q181" t="n">
-        <v>-12.06815</v>
-      </c>
-      <c r="R181" t="n">
-        <v>-77.05853</v>
-      </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15879,7 +15769,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O184" t="n">
@@ -15889,14 +15779,14 @@
         <v>-76.88070999999999</v>
       </c>
       <c r="Q184" t="n">
-        <v>-12.033935</v>
+        <v>-12.0153</v>
       </c>
       <c r="R184" t="n">
-        <v>-76.8822033</v>
+        <v>-76.8848033</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>LLEGADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -16140,7 +16030,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O187" t="n">
@@ -16150,14 +16040,14 @@
         <v>-76.97439</v>
       </c>
       <c r="Q187" t="n">
-        <v>-12.15522</v>
+        <v>-12.04532</v>
       </c>
       <c r="R187" t="n">
-        <v>-76.97439</v>
+        <v>-76.938125</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -16599,12 +16489,12 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O193" t="n">
@@ -16614,14 +16504,14 @@
         <v>-76.86957</v>
       </c>
       <c r="Q193" t="n">
-        <v>-12.27496</v>
+        <v>-12.254973</v>
       </c>
       <c r="R193" t="n">
-        <v>-76.86957</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -16773,12 +16663,12 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O195" t="n">
@@ -16788,14 +16678,14 @@
         <v>-76.85383</v>
       </c>
       <c r="Q195" t="n">
-        <v>-12.29151</v>
+        <v>-12.254973</v>
       </c>
       <c r="R195" t="n">
-        <v>-76.85383</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -17181,12 +17071,12 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O200" t="n">
@@ -17196,14 +17086,14 @@
         <v>-76.86821</v>
       </c>
       <c r="Q200" t="n">
-        <v>-12.2725</v>
+        <v>-12.254973</v>
       </c>
       <c r="R200" t="n">
-        <v>-76.86821</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -17616,12 +17506,12 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O205" t="n">
@@ -17631,14 +17521,14 @@
         <v>-76.85363</v>
       </c>
       <c r="Q205" t="n">
-        <v>-12.29459</v>
+        <v>-12.254973</v>
       </c>
       <c r="R205" t="n">
-        <v>-76.85363</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -17866,12 +17756,12 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O208" t="n">
@@ -17881,14 +17771,14 @@
         <v>-76.86933000000001</v>
       </c>
       <c r="Q208" t="n">
-        <v>-12.27687</v>
+        <v>-12.254973</v>
       </c>
       <c r="R208" t="n">
-        <v>-76.86933000000001</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -18274,17 +18164,17 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O213" t="n">
@@ -18293,17 +18183,6 @@
       <c r="P213" t="n">
         <v>-77.05492</v>
       </c>
-      <c r="Q213" t="n">
-        <v>-12.06652</v>
-      </c>
-      <c r="R213" t="n">
-        <v>-77.05492</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -18366,12 +18245,12 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O214" t="n">
@@ -18381,14 +18260,14 @@
         <v>-76.84092</v>
       </c>
       <c r="Q214" t="n">
-        <v>-12.2766</v>
+        <v>-12.254973</v>
       </c>
       <c r="R214" t="n">
-        <v>-76.84092</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -18453,12 +18332,12 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O215" t="n">
@@ -18468,14 +18347,14 @@
         <v>-76.83899</v>
       </c>
       <c r="Q215" t="n">
-        <v>-12.30755</v>
+        <v>-12.254973</v>
       </c>
       <c r="R215" t="n">
-        <v>-76.83899</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18424,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O216" t="n">
@@ -18555,14 +18434,14 @@
         <v>-76.98461</v>
       </c>
       <c r="Q216" t="n">
-        <v>-12.07433</v>
+        <v>-12.07804</v>
       </c>
       <c r="R216" t="n">
-        <v>-76.98461</v>
+        <v>-76.9843267</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -18698,12 +18577,12 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O218" t="n">
@@ -18713,14 +18592,14 @@
         <v>-76.85265</v>
       </c>
       <c r="Q218" t="n">
-        <v>-12.28946</v>
+        <v>-12.254973</v>
       </c>
       <c r="R218" t="n">
-        <v>-76.85265</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -18780,17 +18659,17 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O219" t="n">
@@ -18799,17 +18678,6 @@
       <c r="P219" t="n">
         <v>-77.03857000000001</v>
       </c>
-      <c r="Q219" t="n">
-        <v>-12.07071</v>
-      </c>
-      <c r="R219" t="n">
-        <v>-77.03857000000001</v>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -18877,7 +18745,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O220" t="n">
@@ -18887,14 +18755,14 @@
         <v>-77.0239</v>
       </c>
       <c r="Q220" t="n">
-        <v>-12.10615</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R220" t="n">
-        <v>-77.0239</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -19291,17 +19159,17 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O225" t="n">
@@ -19310,17 +19178,6 @@
       <c r="P225" t="n">
         <v>-77.05725</v>
       </c>
-      <c r="Q225" t="n">
-        <v>-12.06944</v>
-      </c>
-      <c r="R225" t="n">
-        <v>-77.05725</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -22756,12 +22613,12 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O270" t="n">
@@ -22771,14 +22628,14 @@
         <v>-76.85398000000001</v>
       </c>
       <c r="Q270" t="n">
-        <v>-12.29238</v>
+        <v>-12.254973</v>
       </c>
       <c r="R270" t="n">
-        <v>-76.85398000000001</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -22838,17 +22695,17 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O271" t="n">
@@ -22857,17 +22714,6 @@
       <c r="P271" t="n">
         <v>-77.03292999999999</v>
       </c>
-      <c r="Q271" t="n">
-        <v>-12.07283</v>
-      </c>
-      <c r="R271" t="n">
-        <v>-77.03292999999999</v>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -23452,12 +23298,12 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O278" t="n">
@@ -23467,14 +23313,14 @@
         <v>-76.83991</v>
       </c>
       <c r="Q278" t="n">
-        <v>-12.27673</v>
+        <v>-12.254973</v>
       </c>
       <c r="R278" t="n">
-        <v>-76.83991</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -23539,12 +23385,12 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O279" t="n">
@@ -23554,14 +23400,14 @@
         <v>-76.84050000000001</v>
       </c>
       <c r="Q279" t="n">
-        <v>-12.27656</v>
+        <v>-12.254973</v>
       </c>
       <c r="R279" t="n">
-        <v>-76.84050000000001</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -23870,7 +23716,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O283" t="n">
@@ -23880,14 +23726,14 @@
         <v>-77.07719</v>
       </c>
       <c r="Q283" t="n">
-        <v>-12.08775</v>
+        <v>-12.0765169</v>
       </c>
       <c r="R283" t="n">
-        <v>-77.07719</v>
+        <v>-77.0122461</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -24534,17 +24380,17 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O291" t="n">
@@ -24553,17 +24399,6 @@
       <c r="P291" t="n">
         <v>-77.03814</v>
       </c>
-      <c r="Q291" t="n">
-        <v>-12.06995</v>
-      </c>
-      <c r="R291" t="n">
-        <v>-77.03814</v>
-      </c>
-      <c r="S291" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -24794,7 +24629,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O294" t="n">
@@ -24804,14 +24639,14 @@
         <v>-77.02001</v>
       </c>
       <c r="Q294" t="n">
-        <v>-12.10884</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R294" t="n">
-        <v>-77.02001</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -25094,12 +24929,12 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O298" t="n">
@@ -25109,14 +24944,14 @@
         <v>-76.85091</v>
       </c>
       <c r="Q298" t="n">
-        <v>-12.29745</v>
+        <v>-12.254973</v>
       </c>
       <c r="R298" t="n">
-        <v>-76.85091</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -25263,17 +25098,17 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O300" t="n">
@@ -25282,17 +25117,6 @@
       <c r="P300" t="n">
         <v>-77.03708</v>
       </c>
-      <c r="Q300" t="n">
-        <v>-12.07546</v>
-      </c>
-      <c r="R300" t="n">
-        <v>-77.03708</v>
-      </c>
-      <c r="S300" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -26758,7 +26582,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O318" t="n">
@@ -26768,14 +26592,14 @@
         <v>-77.03337999999999</v>
       </c>
       <c r="Q318" t="n">
-        <v>-12.11775</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R318" t="n">
-        <v>-77.03337999999999</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -26927,12 +26751,12 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O320" t="n">
@@ -26942,14 +26766,14 @@
         <v>-76.83796</v>
       </c>
       <c r="Q320" t="n">
-        <v>-12.30898</v>
+        <v>-12.254973</v>
       </c>
       <c r="R320" t="n">
-        <v>-76.83796</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -27019,7 +26843,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O321" t="n">
@@ -27029,14 +26853,14 @@
         <v>-77.068</v>
       </c>
       <c r="Q321" t="n">
-        <v>-11.88283</v>
+        <v>-11.599975</v>
       </c>
       <c r="R321" t="n">
-        <v>-77.068</v>
+        <v>-77.2482385</v>
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -27280,7 +27104,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O324" t="n">
@@ -27290,14 +27114,14 @@
         <v>-76.9508</v>
       </c>
       <c r="Q324" t="n">
-        <v>-12.07324</v>
+        <v>-12.0757877</v>
       </c>
       <c r="R324" t="n">
-        <v>-76.9508</v>
+        <v>-76.9634274</v>
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -27438,7 +27262,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O326" t="n">
@@ -27448,14 +27272,14 @@
         <v>-77.13114</v>
       </c>
       <c r="Q326" t="n">
-        <v>-11.9523366</v>
+        <v>-12.0344931</v>
       </c>
       <c r="R326" t="n">
-        <v>-77.1322583</v>
+        <v>-76.9896052</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>LLEGADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -27699,7 +27523,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O329" t="n">
@@ -27709,14 +27533,14 @@
         <v>-76.97565</v>
       </c>
       <c r="Q329" t="n">
-        <v>-12.16703</v>
+        <v>-12.04532</v>
       </c>
       <c r="R329" t="n">
-        <v>-76.97565</v>
+        <v>-76.938125</v>
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -27786,7 +27610,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O330" t="n">
@@ -27796,14 +27620,14 @@
         <v>-76.95854</v>
       </c>
       <c r="Q330" t="n">
-        <v>-12.0728</v>
+        <v>-12.0998048</v>
       </c>
       <c r="R330" t="n">
-        <v>-76.95854</v>
+        <v>-76.950164</v>
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -28129,12 +27953,12 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O334" t="n">
@@ -28144,14 +27968,14 @@
         <v>-76.83852</v>
       </c>
       <c r="Q334" t="n">
-        <v>-12.30826</v>
+        <v>-12.254973</v>
       </c>
       <c r="R334" t="n">
-        <v>-76.83852</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -28216,12 +28040,12 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O335" t="n">
@@ -28231,14 +28055,14 @@
         <v>-76.83891</v>
       </c>
       <c r="Q335" t="n">
-        <v>-12.30767</v>
+        <v>-12.254973</v>
       </c>
       <c r="R335" t="n">
-        <v>-76.83891</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -28624,17 +28448,17 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O340" t="n">
@@ -28643,17 +28467,6 @@
       <c r="P340" t="n">
         <v>-77.05456</v>
       </c>
-      <c r="Q340" t="n">
-        <v>-12.07062</v>
-      </c>
-      <c r="R340" t="n">
-        <v>-77.05456</v>
-      </c>
-      <c r="S340" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -29058,7 +28871,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O345" t="n">
@@ -29068,14 +28881,14 @@
         <v>-77.07906</v>
       </c>
       <c r="Q345" t="n">
-        <v>-12.08951</v>
+        <v>-12.077346</v>
       </c>
       <c r="R345" t="n">
-        <v>-77.07906</v>
+        <v>-77.01499990000001</v>
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -29135,17 +28948,17 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O346" t="n">
@@ -29154,17 +28967,6 @@
       <c r="P346" t="n">
         <v>-77.06431000000001</v>
       </c>
-      <c r="Q346" t="n">
-        <v>-12.06898</v>
-      </c>
-      <c r="R346" t="n">
-        <v>-77.06431000000001</v>
-      </c>
-      <c r="S346" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -29232,7 +29034,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O347" t="n">
@@ -29242,14 +29044,14 @@
         <v>-77.07239</v>
       </c>
       <c r="Q347" t="n">
-        <v>-12.09052</v>
+        <v>-12.0778712</v>
       </c>
       <c r="R347" t="n">
-        <v>-77.07239</v>
+        <v>-77.0130621</v>
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -29319,7 +29121,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O348" t="n">
@@ -29329,14 +29131,14 @@
         <v>-77.00042999999999</v>
       </c>
       <c r="Q348" t="n">
-        <v>-12.07683</v>
+        <v>-12.0787955</v>
       </c>
       <c r="R348" t="n">
-        <v>-77.00042999999999</v>
+        <v>-77.0081964</v>
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -29483,17 +29285,17 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O350" t="n">
@@ -29502,17 +29304,6 @@
       <c r="P350" t="n">
         <v>-77.03801</v>
       </c>
-      <c r="Q350" t="n">
-        <v>-12.07252</v>
-      </c>
-      <c r="R350" t="n">
-        <v>-77.03801</v>
-      </c>
-      <c r="S350" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -29656,7 +29447,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O352" t="n">
@@ -29666,14 +29457,14 @@
         <v>-77.02297</v>
       </c>
       <c r="Q352" t="n">
-        <v>-12.08134</v>
+        <v>-12.0768636</v>
       </c>
       <c r="R352" t="n">
-        <v>-77.02297</v>
+        <v>-77.0068694</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -29906,7 +29697,7 @@
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O355" t="n">
@@ -29916,14 +29707,14 @@
         <v>-77.0232</v>
       </c>
       <c r="Q355" t="n">
-        <v>-12.10709</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R355" t="n">
-        <v>-77.0232</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -30146,17 +29937,17 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O358" t="n">
@@ -30165,17 +29956,6 @@
       <c r="P358" t="n">
         <v>-77.05710999999999</v>
       </c>
-      <c r="Q358" t="n">
-        <v>-12.07584</v>
-      </c>
-      <c r="R358" t="n">
-        <v>-77.05710999999999</v>
-      </c>
-      <c r="S358" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -30309,17 +30089,17 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O360" t="n">
@@ -30328,17 +30108,6 @@
       <c r="P360" t="n">
         <v>-77.03982000000001</v>
       </c>
-      <c r="Q360" t="n">
-        <v>-12.07603</v>
-      </c>
-      <c r="R360" t="n">
-        <v>-77.03982000000001</v>
-      </c>
-      <c r="S360" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -30472,17 +30241,17 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O362" t="n">
@@ -30491,17 +30260,6 @@
       <c r="P362" t="n">
         <v>-77.04886</v>
       </c>
-      <c r="Q362" t="n">
-        <v>-12.07889</v>
-      </c>
-      <c r="R362" t="n">
-        <v>-77.04886</v>
-      </c>
-      <c r="S362" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -31103,7 +30861,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O370" t="n">
@@ -31113,14 +30871,14 @@
         <v>-76.94338</v>
       </c>
       <c r="Q370" t="n">
-        <v>-12.10215</v>
+        <v>-12.1005671</v>
       </c>
       <c r="R370" t="n">
-        <v>-76.94338</v>
+        <v>-76.9440192</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -31364,7 +31122,7 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O373" t="n">
@@ -31374,14 +31132,14 @@
         <v>-76.92298</v>
       </c>
       <c r="Q373" t="n">
-        <v>-12.02529</v>
+        <v>-12.0249533</v>
       </c>
       <c r="R373" t="n">
-        <v>-76.92298</v>
+        <v>-76.9242433</v>
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -31701,7 +31459,7 @@
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O377" t="n">
@@ -31711,14 +31469,14 @@
         <v>-77.13114</v>
       </c>
       <c r="Q377" t="n">
-        <v>-11.9523366</v>
+        <v>-12.0344931</v>
       </c>
       <c r="R377" t="n">
-        <v>-77.1322583</v>
+        <v>-76.9896052</v>
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>LLEGADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -34585,17 +34343,17 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O414" t="n">
@@ -34604,17 +34362,6 @@
       <c r="P414" t="n">
         <v>-77.05834</v>
       </c>
-      <c r="Q414" t="n">
-        <v>-12.07799</v>
-      </c>
-      <c r="R414" t="n">
-        <v>-77.05834</v>
-      </c>
-      <c r="S414" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -35177,12 +34924,12 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O421" t="n">
@@ -35192,14 +34939,14 @@
         <v>-76.85348999999999</v>
       </c>
       <c r="Q421" t="n">
-        <v>-12.29004</v>
+        <v>-12.254973</v>
       </c>
       <c r="R421" t="n">
-        <v>-76.85348999999999</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -36341,17 +36088,17 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O435" t="n">
@@ -36360,17 +36107,6 @@
       <c r="P435" t="n">
         <v>-77.03252999999999</v>
       </c>
-      <c r="Q435" t="n">
-        <v>-12.0751</v>
-      </c>
-      <c r="R435" t="n">
-        <v>-77.03252999999999</v>
-      </c>
-      <c r="S435" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -36846,12 +36582,12 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O441" t="n">
@@ -36861,14 +36597,14 @@
         <v>-76.84094</v>
       </c>
       <c r="Q441" t="n">
-        <v>-12.30933</v>
+        <v>-12.254973</v>
       </c>
       <c r="R441" t="n">
-        <v>-76.84094</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -37444,7 +37180,7 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O448" t="n">
@@ -37454,14 +37190,14 @@
         <v>-76.91614</v>
       </c>
       <c r="Q448" t="n">
-        <v>-12.02428</v>
+        <v>-12.0244933</v>
       </c>
       <c r="R448" t="n">
-        <v>-76.91614</v>
+        <v>-76.9169033</v>
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -37607,7 +37343,7 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O450" t="n">
@@ -37617,14 +37353,14 @@
         <v>-77.10656</v>
       </c>
       <c r="Q450" t="n">
-        <v>-12.05938</v>
+        <v>-12.0596747</v>
       </c>
       <c r="R450" t="n">
-        <v>-77.10656</v>
+        <v>-77.10685359999999</v>
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -38020,7 +37756,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O455" t="n">
@@ -38030,14 +37766,14 @@
         <v>-76.96644000000001</v>
       </c>
       <c r="Q455" t="n">
-        <v>-12.16459</v>
+        <v>-12.04532</v>
       </c>
       <c r="R455" t="n">
-        <v>-76.96644000000001</v>
+        <v>-76.938125</v>
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -38907,7 +38643,7 @@
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O466" t="n">
@@ -38917,14 +38653,14 @@
         <v>-77.13114</v>
       </c>
       <c r="Q466" t="n">
-        <v>-11.9523366</v>
+        <v>-12.0344931</v>
       </c>
       <c r="R466" t="n">
-        <v>-77.1322583</v>
+        <v>-76.9896052</v>
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>LLEGADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -39081,7 +38817,7 @@
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O468" t="n">
@@ -39091,14 +38827,14 @@
         <v>-76.96912</v>
       </c>
       <c r="Q468" t="n">
-        <v>-12.16744</v>
+        <v>-12.0453267</v>
       </c>
       <c r="R468" t="n">
-        <v>-76.96912</v>
+        <v>-76.9381017</v>
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -39897,12 +39633,12 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O478" t="n">
@@ -39912,14 +39648,14 @@
         <v>-76.86912</v>
       </c>
       <c r="Q478" t="n">
-        <v>-12.27283</v>
+        <v>-12.254973</v>
       </c>
       <c r="R478" t="n">
-        <v>-76.86912</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -40509,7 +40245,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O486" t="n">
@@ -40519,14 +40255,14 @@
         <v>-76.98283000000001</v>
       </c>
       <c r="Q486" t="n">
-        <v>-12.15373</v>
+        <v>-12.04532</v>
       </c>
       <c r="R486" t="n">
-        <v>-76.98283000000001</v>
+        <v>-76.938125</v>
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -41255,17 +40991,17 @@
       </c>
       <c r="L495" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O495" t="n">
@@ -41274,17 +41010,6 @@
       <c r="P495" t="n">
         <v>-77.045</v>
       </c>
-      <c r="Q495" t="n">
-        <v>-12.05469</v>
-      </c>
-      <c r="R495" t="n">
-        <v>-77.045</v>
-      </c>
-      <c r="S495" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -41429,17 +41154,17 @@
       </c>
       <c r="L497" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O497" t="n">
@@ -41448,17 +41173,6 @@
       <c r="P497" t="n">
         <v>-77.03489</v>
       </c>
-      <c r="Q497" t="n">
-        <v>-12.06753</v>
-      </c>
-      <c r="R497" t="n">
-        <v>-77.03489</v>
-      </c>
-      <c r="S497" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -41690,17 +41404,17 @@
       </c>
       <c r="L500" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O500" t="n">
@@ -41709,17 +41423,6 @@
       <c r="P500" t="n">
         <v>-77.03818</v>
       </c>
-      <c r="Q500" t="n">
-        <v>-12.06987</v>
-      </c>
-      <c r="R500" t="n">
-        <v>-77.03818</v>
-      </c>
-      <c r="S500" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -41787,7 +41490,7 @@
       </c>
       <c r="N501" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O501" t="n">
@@ -41797,14 +41500,14 @@
         <v>-77.13114</v>
       </c>
       <c r="Q501" t="n">
-        <v>-11.9523366</v>
+        <v>-12.0344931</v>
       </c>
       <c r="R501" t="n">
-        <v>-77.1322583</v>
+        <v>-76.9896052</v>
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>LLEGADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -41874,7 +41577,7 @@
       </c>
       <c r="N502" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O502" t="n">
@@ -41884,14 +41587,14 @@
         <v>-77.02019</v>
       </c>
       <c r="Q502" t="n">
-        <v>-12.11726</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R502" t="n">
-        <v>-77.02019</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -41951,17 +41654,17 @@
       </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M503" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N503" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O503" t="n">
@@ -41970,17 +41673,6 @@
       <c r="P503" t="n">
         <v>-77.03742</v>
       </c>
-      <c r="Q503" t="n">
-        <v>-12.05671</v>
-      </c>
-      <c r="R503" t="n">
-        <v>-77.03742</v>
-      </c>
-      <c r="S503" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -42038,17 +41730,17 @@
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M504" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N504" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O504" t="n">
@@ -42057,17 +41749,6 @@
       <c r="P504" t="n">
         <v>-77.06337000000001</v>
       </c>
-      <c r="Q504" t="n">
-        <v>-12.07111</v>
-      </c>
-      <c r="R504" t="n">
-        <v>-77.06337000000001</v>
-      </c>
-      <c r="S504" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -44587,7 +44268,7 @@
       </c>
       <c r="N534" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O534" t="n">
@@ -44597,14 +44278,14 @@
         <v>-76.95578999999999</v>
       </c>
       <c r="Q534" t="n">
-        <v>-12.16216</v>
+        <v>-12.04532</v>
       </c>
       <c r="R534" t="n">
-        <v>-76.95578999999999</v>
+        <v>-76.938125</v>
       </c>
       <c r="S534" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -45480,12 +45161,12 @@
       </c>
       <c r="M545" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N545" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O545" t="n">
@@ -45495,14 +45176,14 @@
         <v>-76.86920000000001</v>
       </c>
       <c r="Q545" t="n">
-        <v>-12.27309</v>
+        <v>-12.254973</v>
       </c>
       <c r="R545" t="n">
-        <v>-76.86920000000001</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S545" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -45572,7 +45253,7 @@
       </c>
       <c r="N546" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O546" t="n">
@@ -45582,14 +45263,14 @@
         <v>-77.10687</v>
       </c>
       <c r="Q546" t="n">
-        <v>-12.05974</v>
+        <v>-12.0596747</v>
       </c>
       <c r="R546" t="n">
-        <v>-77.10687</v>
+        <v>-77.10685359999999</v>
       </c>
       <c r="S546" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -46078,7 +45759,7 @@
       </c>
       <c r="N552" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O552" t="n">
@@ -46088,14 +45769,14 @@
         <v>-76.97454</v>
       </c>
       <c r="Q552" t="n">
-        <v>-12.15826</v>
+        <v>-12.04532</v>
       </c>
       <c r="R552" t="n">
-        <v>-76.97454</v>
+        <v>-76.938125</v>
       </c>
       <c r="S552" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -46992,17 +46673,17 @@
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M563" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N563" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O563" t="n">
@@ -47011,17 +46692,6 @@
       <c r="P563" t="n">
         <v>-77.05593</v>
       </c>
-      <c r="Q563" t="n">
-        <v>-12.06828</v>
-      </c>
-      <c r="R563" t="n">
-        <v>-77.05593</v>
-      </c>
-      <c r="S563" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -47502,7 +47172,7 @@
       </c>
       <c r="N569" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O569" t="n">
@@ -47512,14 +47182,14 @@
         <v>-77.02545000000001</v>
       </c>
       <c r="Q569" t="n">
-        <v>-12.11827</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R569" t="n">
-        <v>-77.02545000000001</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S569" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -47753,17 +47423,17 @@
       </c>
       <c r="L572" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M572" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N572" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O572" t="n">
@@ -47772,17 +47442,6 @@
       <c r="P572" t="n">
         <v>-77.03605</v>
       </c>
-      <c r="Q572" t="n">
-        <v>-12.05289</v>
-      </c>
-      <c r="R572" t="n">
-        <v>-77.03605</v>
-      </c>
-      <c r="S572" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -47850,7 +47509,7 @@
       </c>
       <c r="N573" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O573" t="n">
@@ -47860,14 +47519,14 @@
         <v>-76.98314000000001</v>
       </c>
       <c r="Q573" t="n">
-        <v>-12.15399</v>
+        <v>-12.04532</v>
       </c>
       <c r="R573" t="n">
-        <v>-76.98314000000001</v>
+        <v>-76.938125</v>
       </c>
       <c r="S573" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -48774,7 +48433,7 @@
       </c>
       <c r="N584" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O584" t="n">
@@ -48784,14 +48443,14 @@
         <v>-76.96606</v>
       </c>
       <c r="Q584" t="n">
-        <v>-12.16277</v>
+        <v>-12.04532</v>
       </c>
       <c r="R584" t="n">
-        <v>-76.96606</v>
+        <v>-76.938125</v>
       </c>
       <c r="S584" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -49253,17 +48912,17 @@
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M590" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O590" t="n">
@@ -49272,17 +48931,6 @@
       <c r="P590" t="n">
         <v>-77.04147</v>
       </c>
-      <c r="Q590" t="n">
-        <v>-12.07513</v>
-      </c>
-      <c r="R590" t="n">
-        <v>-77.04147</v>
-      </c>
-      <c r="S590" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -49416,12 +49064,12 @@
       </c>
       <c r="M592" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N592" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O592" t="n">
@@ -49431,14 +49079,14 @@
         <v>-76.86981</v>
       </c>
       <c r="Q592" t="n">
-        <v>-12.27478</v>
+        <v>-12.254973</v>
       </c>
       <c r="R592" t="n">
-        <v>-76.86981</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S592" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -50792,17 +50440,17 @@
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M608" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O608" t="n">
@@ -50811,17 +50459,6 @@
       <c r="P608" t="n">
         <v>-77.03837</v>
       </c>
-      <c r="Q608" t="n">
-        <v>-12.07469</v>
-      </c>
-      <c r="R608" t="n">
-        <v>-77.03837</v>
-      </c>
-      <c r="S608" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -51542,17 +51179,17 @@
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M617" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O617" t="n">
@@ -51561,17 +51198,6 @@
       <c r="P617" t="n">
         <v>-77.05370000000001</v>
       </c>
-      <c r="Q617" t="n">
-        <v>-12.07056</v>
-      </c>
-      <c r="R617" t="n">
-        <v>-77.05370000000001</v>
-      </c>
-      <c r="S617" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -51705,17 +51331,17 @@
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M619" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N619" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O619" t="n">
@@ -51724,17 +51350,6 @@
       <c r="P619" t="n">
         <v>-77.04037</v>
       </c>
-      <c r="Q619" t="n">
-        <v>-12.07505</v>
-      </c>
-      <c r="R619" t="n">
-        <v>-77.04037</v>
-      </c>
-      <c r="S619" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -51802,7 +51417,7 @@
       </c>
       <c r="N620" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O620" t="n">
@@ -51812,14 +51427,14 @@
         <v>-76.97772000000001</v>
       </c>
       <c r="Q620" t="n">
-        <v>-12.0748617</v>
+        <v>-12.0749812</v>
       </c>
       <c r="R620" t="n">
-        <v>-76.977465</v>
+        <v>-76.9781342</v>
       </c>
       <c r="S620" t="inlineStr">
         <is>
-          <t>LLEGADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -52477,17 +52092,17 @@
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M628" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N628" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O628" t="n">
@@ -52496,17 +52111,6 @@
       <c r="P628" t="n">
         <v>-77.05663</v>
       </c>
-      <c r="Q628" t="n">
-        <v>-12.07833</v>
-      </c>
-      <c r="R628" t="n">
-        <v>-77.05663</v>
-      </c>
-      <c r="S628" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -52651,17 +52255,17 @@
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M630" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N630" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O630" t="n">
@@ -52670,17 +52274,6 @@
       <c r="P630" t="n">
         <v>-77.0568</v>
       </c>
-      <c r="Q630" t="n">
-        <v>-12.06701</v>
-      </c>
-      <c r="R630" t="n">
-        <v>-77.0568</v>
-      </c>
-      <c r="S630" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -52738,17 +52331,17 @@
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M631" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N631" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O631" t="n">
@@ -52757,17 +52350,6 @@
       <c r="P631" t="n">
         <v>-77.03702</v>
       </c>
-      <c r="Q631" t="n">
-        <v>-12.07586</v>
-      </c>
-      <c r="R631" t="n">
-        <v>-77.03702</v>
-      </c>
-      <c r="S631" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -53183,7 +52765,7 @@
       </c>
       <c r="N636" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O636" t="n">
@@ -53193,14 +52775,14 @@
         <v>-77.10657999999999</v>
       </c>
       <c r="Q636" t="n">
-        <v>-12.05938</v>
+        <v>-12.0596747</v>
       </c>
       <c r="R636" t="n">
-        <v>-77.10657999999999</v>
+        <v>-77.10685359999999</v>
       </c>
       <c r="S636" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -53357,7 +52939,7 @@
       </c>
       <c r="N638" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O638" t="n">
@@ -53367,14 +52949,14 @@
         <v>-76.92731999999999</v>
       </c>
       <c r="Q638" t="n">
-        <v>-12.02762</v>
+        <v>-12.0452871</v>
       </c>
       <c r="R638" t="n">
-        <v>-76.92731999999999</v>
+        <v>-76.93811770000001</v>
       </c>
       <c r="S638" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -53444,7 +53026,7 @@
       </c>
       <c r="N639" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O639" t="n">
@@ -53454,14 +53036,14 @@
         <v>-77.10680000000001</v>
       </c>
       <c r="Q639" t="n">
-        <v>-12.05967</v>
+        <v>-12.0596747</v>
       </c>
       <c r="R639" t="n">
-        <v>-77.10680000000001</v>
+        <v>-77.10685359999999</v>
       </c>
       <c r="S639" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -54368,7 +53950,7 @@
       </c>
       <c r="N650" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O650" t="n">
@@ -54378,14 +53960,14 @@
         <v>-76.91849999999999</v>
       </c>
       <c r="Q650" t="n">
-        <v>-12.02469</v>
+        <v>-12.02485</v>
       </c>
       <c r="R650" t="n">
-        <v>-76.91849999999999</v>
+        <v>-76.9188233</v>
       </c>
       <c r="S650" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -55129,7 +54711,7 @@
       </c>
       <c r="N659" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O659" t="n">
@@ -55139,14 +54721,14 @@
         <v>-76.9807</v>
       </c>
       <c r="Q659" t="n">
-        <v>-12.0748</v>
+        <v>-12.0778367</v>
       </c>
       <c r="R659" t="n">
-        <v>-76.9807</v>
+        <v>-76.98472</v>
       </c>
       <c r="S659" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -56434,17 +56016,17 @@
       </c>
       <c r="L675" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M675" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N675" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O675" t="n">
@@ -56453,17 +56035,6 @@
       <c r="P675" t="n">
         <v>-77.06349</v>
       </c>
-      <c r="Q675" t="n">
-        <v>-12.07109</v>
-      </c>
-      <c r="R675" t="n">
-        <v>-77.06349</v>
-      </c>
-      <c r="S675" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -56755,17 +56326,17 @@
       </c>
       <c r="L679" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M679" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N679" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O679" t="n">
@@ -56774,17 +56345,6 @@
       <c r="P679" t="n">
         <v>-77.05869</v>
       </c>
-      <c r="Q679" t="n">
-        <v>-12.06731</v>
-      </c>
-      <c r="R679" t="n">
-        <v>-77.05869</v>
-      </c>
-      <c r="S679" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -57179,17 +56739,17 @@
       </c>
       <c r="L684" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N684" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O684" t="n">
@@ -57198,17 +56758,6 @@
       <c r="P684" t="n">
         <v>-77.05204000000001</v>
       </c>
-      <c r="Q684" t="n">
-        <v>-12.07071</v>
-      </c>
-      <c r="R684" t="n">
-        <v>-77.05204000000001</v>
-      </c>
-      <c r="S684" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -57266,17 +56815,17 @@
       </c>
       <c r="L685" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M685" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N685" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O685" t="n">
@@ -57285,17 +56834,6 @@
       <c r="P685" t="n">
         <v>-77.03849</v>
       </c>
-      <c r="Q685" t="n">
-        <v>-12.06998</v>
-      </c>
-      <c r="R685" t="n">
-        <v>-77.03849</v>
-      </c>
-      <c r="S685" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -57972,7 +57510,7 @@
       </c>
       <c r="N693" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O693" t="n">
@@ -57982,14 +57520,14 @@
         <v>-76.98455</v>
       </c>
       <c r="Q693" t="n">
-        <v>-12.07421</v>
+        <v>-12.07804</v>
       </c>
       <c r="R693" t="n">
-        <v>-76.98455</v>
+        <v>-76.9843267</v>
       </c>
       <c r="S693" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -58636,17 +58174,17 @@
       </c>
       <c r="L701" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N701" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O701" t="n">
@@ -58655,17 +58193,6 @@
       <c r="P701" t="n">
         <v>-77.03788</v>
       </c>
-      <c r="Q701" t="n">
-        <v>-12.06143</v>
-      </c>
-      <c r="R701" t="n">
-        <v>-77.03788</v>
-      </c>
-      <c r="S701" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -59902,7 +59429,7 @@
       </c>
       <c r="N716" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O716" t="n">
@@ -59912,14 +59439,14 @@
         <v>-76.94309</v>
       </c>
       <c r="Q716" t="n">
-        <v>-12.10248</v>
+        <v>-12.1001793</v>
       </c>
       <c r="R716" t="n">
-        <v>-76.94309</v>
+        <v>-76.95003</v>
       </c>
       <c r="S716" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -60076,7 +59603,7 @@
       </c>
       <c r="N718" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O718" t="n">
@@ -60086,14 +59613,14 @@
         <v>-77.02545000000001</v>
       </c>
       <c r="Q718" t="n">
-        <v>-12.11827</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R718" t="n">
-        <v>-77.02545000000001</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S718" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -60326,7 +59853,7 @@
       </c>
       <c r="N721" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O721" t="n">
@@ -60336,14 +59863,14 @@
         <v>-77.07359</v>
       </c>
       <c r="Q721" t="n">
-        <v>-12.09017</v>
+        <v>-12.078013</v>
       </c>
       <c r="R721" t="n">
-        <v>-77.07359</v>
+        <v>-77.0131365</v>
       </c>
       <c r="S721" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -60652,7 +60179,7 @@
       </c>
       <c r="N725" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O725" t="n">
@@ -60662,14 +60189,14 @@
         <v>-76.96732</v>
       </c>
       <c r="Q725" t="n">
-        <v>-12.15869</v>
+        <v>-12.04532</v>
       </c>
       <c r="R725" t="n">
-        <v>-76.96732</v>
+        <v>-76.938125</v>
       </c>
       <c r="S725" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -61142,17 +60669,17 @@
       </c>
       <c r="L731" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M731" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N731" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O731" t="n">
@@ -61161,17 +60688,6 @@
       <c r="P731" t="n">
         <v>-77.03977</v>
       </c>
-      <c r="Q731" t="n">
-        <v>-12.06283</v>
-      </c>
-      <c r="R731" t="n">
-        <v>-77.03977</v>
-      </c>
-      <c r="S731" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -61403,17 +60919,17 @@
       </c>
       <c r="L734" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M734" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N734" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O734" t="n">
@@ -61422,17 +60938,6 @@
       <c r="P734" t="n">
         <v>-77.06403</v>
       </c>
-      <c r="Q734" t="n">
-        <v>-12.06893</v>
-      </c>
-      <c r="R734" t="n">
-        <v>-77.06403</v>
-      </c>
-      <c r="S734" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -62533,7 +62038,7 @@
       </c>
       <c r="N747" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O747" t="n">
@@ -62543,14 +62048,14 @@
         <v>-76.91607</v>
       </c>
       <c r="Q747" t="n">
-        <v>-12.02431</v>
+        <v>-12.0244967</v>
       </c>
       <c r="R747" t="n">
-        <v>-76.91607</v>
+        <v>-76.9169333</v>
       </c>
       <c r="S747" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -62789,7 +62294,7 @@
       </c>
       <c r="N750" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O750" t="n">
@@ -62799,14 +62304,14 @@
         <v>-76.97756</v>
       </c>
       <c r="Q750" t="n">
-        <v>-12.1533</v>
+        <v>-12.04532</v>
       </c>
       <c r="R750" t="n">
-        <v>-76.97756</v>
+        <v>-76.938125</v>
       </c>
       <c r="S750" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -63116,17 +62621,17 @@
       </c>
       <c r="L754" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M754" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N754" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O754" t="n">
@@ -63135,17 +62640,6 @@
       <c r="P754" t="n">
         <v>-77.03276</v>
       </c>
-      <c r="Q754" t="n">
-        <v>-12.06327</v>
-      </c>
-      <c r="R754" t="n">
-        <v>-77.03276</v>
-      </c>
-      <c r="S754" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -64050,7 +63544,7 @@
       </c>
       <c r="N765" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O765" t="n">
@@ -64060,14 +63554,14 @@
         <v>-77.07571</v>
       </c>
       <c r="Q765" t="n">
-        <v>-12.09275</v>
+        <v>-12.0765146</v>
       </c>
       <c r="R765" t="n">
-        <v>-77.07571</v>
+        <v>-77.0121007</v>
       </c>
       <c r="S765" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -65181,7 +64675,7 @@
       </c>
       <c r="N778" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O778" t="n">
@@ -65191,14 +64685,14 @@
         <v>-76.97477000000001</v>
       </c>
       <c r="Q778" t="n">
-        <v>-12.15931</v>
+        <v>-12.04532</v>
       </c>
       <c r="R778" t="n">
-        <v>-76.97477000000001</v>
+        <v>-76.938125</v>
       </c>
       <c r="S778" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -65769,17 +65263,17 @@
       </c>
       <c r="L785" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M785" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N785" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O785" t="n">
@@ -65788,17 +65282,6 @@
       <c r="P785" t="n">
         <v>-77.05725</v>
       </c>
-      <c r="Q785" t="n">
-        <v>-12.06944</v>
-      </c>
-      <c r="R785" t="n">
-        <v>-77.05725</v>
-      </c>
-      <c r="S785" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -65856,17 +65339,17 @@
       </c>
       <c r="L786" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M786" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N786" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O786" t="n">
@@ -65875,17 +65358,6 @@
       <c r="P786" t="n">
         <v>-77.03466</v>
       </c>
-      <c r="Q786" t="n">
-        <v>-12.06751</v>
-      </c>
-      <c r="R786" t="n">
-        <v>-77.03466</v>
-      </c>
-      <c r="S786" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -66291,17 +65763,17 @@
       </c>
       <c r="L791" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M791" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N791" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O791" t="n">
@@ -66310,17 +65782,6 @@
       <c r="P791" t="n">
         <v>-77.05835999999999</v>
       </c>
-      <c r="Q791" t="n">
-        <v>-12.06959</v>
-      </c>
-      <c r="R791" t="n">
-        <v>-77.05835999999999</v>
-      </c>
-      <c r="S791" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -66552,17 +66013,17 @@
       </c>
       <c r="L794" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M794" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N794" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O794" t="n">
@@ -66571,17 +66032,6 @@
       <c r="P794" t="n">
         <v>-77.05282</v>
       </c>
-      <c r="Q794" t="n">
-        <v>-12.07255</v>
-      </c>
-      <c r="R794" t="n">
-        <v>-77.05282</v>
-      </c>
-      <c r="S794" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -66812,7 +66262,7 @@
       </c>
       <c r="N797" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O797" t="n">
@@ -66822,14 +66272,14 @@
         <v>-77.03042000000001</v>
       </c>
       <c r="Q797" t="n">
-        <v>-12.11827</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R797" t="n">
-        <v>-77.03042000000001</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S797" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -67063,17 +66513,17 @@
       </c>
       <c r="L800" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M800" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N800" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O800" t="n">
@@ -67082,17 +66532,6 @@
       <c r="P800" t="n">
         <v>-77.03139</v>
       </c>
-      <c r="Q800" t="n">
-        <v>-12.07408</v>
-      </c>
-      <c r="R800" t="n">
-        <v>-77.03139</v>
-      </c>
-      <c r="S800" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -67247,7 +66686,7 @@
       </c>
       <c r="N802" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O802" t="n">
@@ -67257,14 +66696,14 @@
         <v>-76.9689</v>
       </c>
       <c r="Q802" t="n">
-        <v>-12.16855</v>
+        <v>-12.0453267</v>
       </c>
       <c r="R802" t="n">
-        <v>-76.9689</v>
+        <v>-76.9381017</v>
       </c>
       <c r="S802" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -67563,17 +67002,17 @@
       </c>
       <c r="L806" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M806" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N806" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O806" t="n">
@@ -67582,17 +67021,6 @@
       <c r="P806" t="n">
         <v>-77.06223</v>
       </c>
-      <c r="Q806" t="n">
-        <v>-12.07038</v>
-      </c>
-      <c r="R806" t="n">
-        <v>-77.06223</v>
-      </c>
-      <c r="S806" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -67660,7 +67088,7 @@
       </c>
       <c r="N807" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O807" t="n">
@@ -67670,14 +67098,14 @@
         <v>-76.98032000000001</v>
       </c>
       <c r="Q807" t="n">
-        <v>-12.15476</v>
+        <v>-12.04532</v>
       </c>
       <c r="R807" t="n">
-        <v>-76.98032000000001</v>
+        <v>-76.938125</v>
       </c>
       <c r="S807" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -67742,12 +67170,12 @@
       </c>
       <c r="M808" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N808" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O808" t="n">
@@ -67757,14 +67185,14 @@
         <v>-76.85115</v>
       </c>
       <c r="Q808" t="n">
-        <v>-12.29837</v>
+        <v>-12.254973</v>
       </c>
       <c r="R808" t="n">
-        <v>-76.85115</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S808" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -68503,7 +67931,7 @@
       </c>
       <c r="N817" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O817" t="n">
@@ -68513,14 +67941,14 @@
         <v>-77.06476000000001</v>
       </c>
       <c r="Q817" t="n">
-        <v>-12.08907</v>
+        <v>-12.0770618</v>
       </c>
       <c r="R817" t="n">
-        <v>-77.06476000000001</v>
+        <v>-77.0156137</v>
       </c>
       <c r="S817" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -69025,7 +68453,7 @@
       </c>
       <c r="N823" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O823" t="n">
@@ -69035,14 +68463,14 @@
         <v>-77.07359</v>
       </c>
       <c r="Q823" t="n">
-        <v>-12.09017</v>
+        <v>-12.078013</v>
       </c>
       <c r="R823" t="n">
-        <v>-77.07359</v>
+        <v>-77.0131365</v>
       </c>
       <c r="S823" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -69357,7 +68785,7 @@
       </c>
       <c r="N827" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O827" t="n">
@@ -69367,14 +68795,14 @@
         <v>-77.03492</v>
       </c>
       <c r="Q827" t="n">
-        <v>-12.11703</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R827" t="n">
-        <v>-77.03492</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S827" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -70619,17 +70047,17 @@
       </c>
       <c r="L842" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M842" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N842" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O842" t="n">
@@ -70638,17 +70066,6 @@
       <c r="P842" t="n">
         <v>-77.06332</v>
       </c>
-      <c r="Q842" t="n">
-        <v>-12.06848</v>
-      </c>
-      <c r="R842" t="n">
-        <v>-77.06332</v>
-      </c>
-      <c r="S842" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -70793,17 +70210,17 @@
       </c>
       <c r="L844" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M844" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N844" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O844" t="n">
@@ -70812,17 +70229,6 @@
       <c r="P844" t="n">
         <v>-77.03216</v>
       </c>
-      <c r="Q844" t="n">
-        <v>-12.07129</v>
-      </c>
-      <c r="R844" t="n">
-        <v>-77.03216</v>
-      </c>
-      <c r="S844" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -71048,7 +70454,7 @@
       </c>
       <c r="N847" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O847" t="n">
@@ -71058,14 +70464,14 @@
         <v>-77.02302</v>
       </c>
       <c r="Q847" t="n">
-        <v>-12.0815</v>
+        <v>-12.0768636</v>
       </c>
       <c r="R847" t="n">
-        <v>-77.02302</v>
+        <v>-77.0068694</v>
       </c>
       <c r="S847" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -71212,17 +70618,17 @@
       </c>
       <c r="L849" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M849" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N849" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O849" t="n">
@@ -71231,17 +70637,6 @@
       <c r="P849" t="n">
         <v>-77.04037</v>
       </c>
-      <c r="Q849" t="n">
-        <v>-12.07505</v>
-      </c>
-      <c r="R849" t="n">
-        <v>-77.04037</v>
-      </c>
-      <c r="S849" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -71483,7 +70878,7 @@
       </c>
       <c r="N852" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O852" t="n">
@@ -71493,14 +70888,14 @@
         <v>-77.07695</v>
       </c>
       <c r="Q852" t="n">
-        <v>-12.08432</v>
+        <v>-12.0771591</v>
       </c>
       <c r="R852" t="n">
-        <v>-77.07695</v>
+        <v>-77.01541210000001</v>
       </c>
       <c r="S852" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -72206,7 +71601,7 @@
       </c>
       <c r="N861" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O861" t="n">
@@ -72216,14 +71611,14 @@
         <v>-76.96832999999999</v>
       </c>
       <c r="Q861" t="n">
-        <v>-12.16167</v>
+        <v>-12.04532</v>
       </c>
       <c r="R861" t="n">
-        <v>-76.96832999999999</v>
+        <v>-76.938125</v>
       </c>
       <c r="S861" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -72532,7 +71927,7 @@
       </c>
       <c r="N865" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O865" t="n">
@@ -72542,14 +71937,14 @@
         <v>-77.0665</v>
       </c>
       <c r="Q865" t="n">
-        <v>-12.08725</v>
+        <v>-12.0765979</v>
       </c>
       <c r="R865" t="n">
-        <v>-77.0665</v>
+        <v>-77.01262509999999</v>
       </c>
       <c r="S865" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -73707,17 +73102,17 @@
       </c>
       <c r="L879" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M879" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N879" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O879" t="n">
@@ -73726,17 +73121,6 @@
       <c r="P879" t="n">
         <v>-77.03491</v>
       </c>
-      <c r="Q879" t="n">
-        <v>-12.07423</v>
-      </c>
-      <c r="R879" t="n">
-        <v>-77.03491</v>
-      </c>
-      <c r="S879" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -74065,7 +73449,7 @@
       </c>
       <c r="N883" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O883" t="n">
@@ -74075,14 +73459,14 @@
         <v>-77.05844999999999</v>
       </c>
       <c r="Q883" t="n">
-        <v>-12.09494</v>
+        <v>-12.0777859</v>
       </c>
       <c r="R883" t="n">
-        <v>-77.05844999999999</v>
+        <v>-77.0130362</v>
       </c>
       <c r="S883" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -74637,17 +74021,17 @@
       </c>
       <c r="L890" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M890" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N890" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O890" t="n">
@@ -74656,17 +74040,6 @@
       <c r="P890" t="n">
         <v>-77.06519</v>
       </c>
-      <c r="Q890" t="n">
-        <v>-12.07311</v>
-      </c>
-      <c r="R890" t="n">
-        <v>-77.06519</v>
-      </c>
-      <c r="S890" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -74898,17 +74271,17 @@
       </c>
       <c r="L893" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M893" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N893" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O893" t="n">
@@ -74917,17 +74290,6 @@
       <c r="P893" t="n">
         <v>-77.03251</v>
       </c>
-      <c r="Q893" t="n">
-        <v>-12.07378</v>
-      </c>
-      <c r="R893" t="n">
-        <v>-77.03251</v>
-      </c>
-      <c r="S893" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -75169,7 +74531,7 @@
       </c>
       <c r="N896" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O896" t="n">
@@ -75179,14 +74541,14 @@
         <v>-76.97823</v>
       </c>
       <c r="Q896" t="n">
-        <v>-12.0749705</v>
+        <v>-12.0743619</v>
       </c>
       <c r="R896" t="n">
-        <v>-76.9781266</v>
+        <v>-76.9777342</v>
       </c>
       <c r="S896" t="inlineStr">
         <is>
-          <t>LLEGADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -75343,7 +74705,7 @@
       </c>
       <c r="N898" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O898" t="n">
@@ -75353,14 +74715,14 @@
         <v>-76.97583</v>
       </c>
       <c r="Q898" t="n">
-        <v>-12.15313</v>
+        <v>-12.04532</v>
       </c>
       <c r="R898" t="n">
-        <v>-76.97583</v>
+        <v>-76.938125</v>
       </c>
       <c r="S898" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -75578,17 +74940,17 @@
       </c>
       <c r="L901" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M901" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N901" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O901" t="n">
@@ -75597,17 +74959,6 @@
       <c r="P901" t="n">
         <v>-77.06511</v>
       </c>
-      <c r="Q901" t="n">
-        <v>-12.06774</v>
-      </c>
-      <c r="R901" t="n">
-        <v>-77.06511</v>
-      </c>
-      <c r="S901" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
@@ -76431,7 +75782,7 @@
       </c>
       <c r="N911" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O911" t="n">
@@ -76441,14 +75792,14 @@
         <v>-76.95146</v>
       </c>
       <c r="Q911" t="n">
-        <v>-12.09071</v>
+        <v>-12.0986005</v>
       </c>
       <c r="R911" t="n">
-        <v>-76.95146</v>
+        <v>-76.95073050000001</v>
       </c>
       <c r="S911" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -76595,17 +75946,17 @@
       </c>
       <c r="L913" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M913" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N913" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O913" t="n">
@@ -76614,17 +75965,6 @@
       <c r="P913" t="n">
         <v>-77.06505</v>
       </c>
-      <c r="Q913" t="n">
-        <v>-12.06956</v>
-      </c>
-      <c r="R913" t="n">
-        <v>-77.06505</v>
-      </c>
-      <c r="S913" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -76692,7 +76032,7 @@
       </c>
       <c r="N914" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O914" t="n">
@@ -76702,14 +76042,14 @@
         <v>-77.00691</v>
       </c>
       <c r="Q914" t="n">
-        <v>-12.0767</v>
+        <v>-12.0768636</v>
       </c>
       <c r="R914" t="n">
-        <v>-77.00691</v>
+        <v>-77.0068694</v>
       </c>
       <c r="S914" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -77350,12 +76690,12 @@
       </c>
       <c r="M922" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N922" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O922" t="n">
@@ -77365,14 +76705,14 @@
         <v>-76.83991</v>
       </c>
       <c r="Q922" t="n">
-        <v>-12.27673</v>
+        <v>-12.254973</v>
       </c>
       <c r="R922" t="n">
-        <v>-76.83991</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S922" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -78221,17 +77561,17 @@
       </c>
       <c r="L933" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M933" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N933" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O933" t="n">
@@ -78240,17 +77580,6 @@
       <c r="P933" t="n">
         <v>-77.03241</v>
       </c>
-      <c r="Q933" t="n">
-        <v>-12.07498</v>
-      </c>
-      <c r="R933" t="n">
-        <v>-77.03241</v>
-      </c>
-      <c r="S933" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -78318,7 +77647,7 @@
       </c>
       <c r="N934" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O934" t="n">
@@ -78328,14 +77657,14 @@
         <v>-76.961</v>
       </c>
       <c r="Q934" t="n">
-        <v>-12.16737</v>
+        <v>-12.04532</v>
       </c>
       <c r="R934" t="n">
-        <v>-76.961</v>
+        <v>-76.938125</v>
       </c>
       <c r="S934" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -78405,7 +77734,7 @@
       </c>
       <c r="N935" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O935" t="n">
@@ -78415,14 +77744,14 @@
         <v>-76.94358</v>
       </c>
       <c r="Q935" t="n">
-        <v>-12.10216</v>
+        <v>-12.1005897</v>
       </c>
       <c r="R935" t="n">
-        <v>-76.94358</v>
+        <v>-76.9440336</v>
       </c>
       <c r="S935" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -78742,7 +78071,7 @@
       </c>
       <c r="N939" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O939" t="n">
@@ -78752,14 +78081,14 @@
         <v>-76.91612000000001</v>
       </c>
       <c r="Q939" t="n">
-        <v>-12.02408</v>
+        <v>-12.0244633</v>
       </c>
       <c r="R939" t="n">
-        <v>-76.91612000000001</v>
+        <v>-76.9167333</v>
       </c>
       <c r="S939" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -78829,7 +78158,7 @@
       </c>
       <c r="N940" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O940" t="n">
@@ -78839,14 +78168,14 @@
         <v>-77.10590999999999</v>
       </c>
       <c r="Q940" t="n">
-        <v>-12.0591</v>
+        <v>-12.0596747</v>
       </c>
       <c r="R940" t="n">
-        <v>-77.10590999999999</v>
+        <v>-77.10685359999999</v>
       </c>
       <c r="S940" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -79145,17 +78474,17 @@
       </c>
       <c r="L944" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M944" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N944" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O944" t="n">
@@ -79164,17 +78493,6 @@
       <c r="P944" t="n">
         <v>-77.03716</v>
       </c>
-      <c r="Q944" t="n">
-        <v>-12.07435</v>
-      </c>
-      <c r="R944" t="n">
-        <v>-77.03716</v>
-      </c>
-      <c r="S944" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -79405,7 +78723,7 @@
       </c>
       <c r="N947" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O947" t="n">
@@ -79415,14 +78733,14 @@
         <v>-77.07736</v>
       </c>
       <c r="Q947" t="n">
-        <v>-12.09018</v>
+        <v>-12.0772523</v>
       </c>
       <c r="R947" t="n">
-        <v>-77.07736</v>
+        <v>-77.01521099999999</v>
       </c>
       <c r="S947" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -79574,12 +78892,12 @@
       </c>
       <c r="M949" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N949" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O949" t="n">
@@ -79589,14 +78907,14 @@
         <v>-76.86931</v>
       </c>
       <c r="Q949" t="n">
-        <v>-12.27211</v>
+        <v>-12.254973</v>
       </c>
       <c r="R949" t="n">
-        <v>-76.86931</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S949" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -79992,7 +79310,7 @@
       </c>
       <c r="N954" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O954" t="n">
@@ -80002,14 +79320,14 @@
         <v>-76.92701</v>
       </c>
       <c r="Q954" t="n">
-        <v>-12.02753</v>
+        <v>-12.0452851</v>
       </c>
       <c r="R954" t="n">
-        <v>-76.92701</v>
+        <v>-76.938118</v>
       </c>
       <c r="S954" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -80079,7 +79397,7 @@
       </c>
       <c r="N955" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O955" t="n">
@@ -80089,14 +79407,14 @@
         <v>-77.10557</v>
       </c>
       <c r="Q955" t="n">
-        <v>-12.06271</v>
+        <v>-12.0596747</v>
       </c>
       <c r="R955" t="n">
-        <v>-77.10557</v>
+        <v>-77.10685359999999</v>
       </c>
       <c r="S955" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -80335,12 +79653,12 @@
       </c>
       <c r="M958" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N958" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O958" t="n">
@@ -80350,14 +79668,14 @@
         <v>-76.86912</v>
       </c>
       <c r="Q958" t="n">
-        <v>-12.27283</v>
+        <v>-12.254973</v>
       </c>
       <c r="R958" t="n">
-        <v>-76.86912</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S958" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -81260,17 +80578,17 @@
       </c>
       <c r="L969" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M969" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N969" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O969" t="n">
@@ -81279,17 +80597,6 @@
       <c r="P969" t="n">
         <v>-77.06316</v>
       </c>
-      <c r="Q969" t="n">
-        <v>-12.07402</v>
-      </c>
-      <c r="R969" t="n">
-        <v>-77.06316</v>
-      </c>
-      <c r="S969" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
@@ -81847,7 +81154,7 @@
       </c>
       <c r="N976" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O976" t="n">
@@ -81857,14 +81164,14 @@
         <v>-76.98478</v>
       </c>
       <c r="Q976" t="n">
-        <v>-12.07418</v>
+        <v>-12.0781267</v>
       </c>
       <c r="R976" t="n">
-        <v>-76.98478</v>
+        <v>-76.984155</v>
       </c>
       <c r="S976" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -82521,7 +81828,7 @@
       </c>
       <c r="N984" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O984" t="n">
@@ -82531,14 +81838,14 @@
         <v>-77.07001</v>
       </c>
       <c r="Q984" t="n">
-        <v>-12.08696</v>
+        <v>-12.0764361</v>
       </c>
       <c r="R984" t="n">
-        <v>-77.07001</v>
+        <v>-77.0125262</v>
       </c>
       <c r="S984" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -82608,7 +81915,7 @@
       </c>
       <c r="N985" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O985" t="n">
@@ -82618,14 +81925,14 @@
         <v>-76.94349</v>
       </c>
       <c r="Q985" t="n">
-        <v>-12.10216</v>
+        <v>-12.0992428</v>
       </c>
       <c r="R985" t="n">
-        <v>-76.94349</v>
+        <v>-76.9504314</v>
       </c>
       <c r="S985" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -82695,7 +82002,7 @@
       </c>
       <c r="N986" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O986" t="n">
@@ -82705,14 +82012,14 @@
         <v>-77.0312</v>
       </c>
       <c r="Q986" t="n">
-        <v>-12.11602</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R986" t="n">
-        <v>-77.0312</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S986" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -83734,17 +83041,17 @@
       </c>
       <c r="L999" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M999" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N999" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O999" t="n">
@@ -83753,17 +83060,6 @@
       <c r="P999" t="n">
         <v>-77.06746</v>
       </c>
-      <c r="Q999" t="n">
-        <v>-12.06783</v>
-      </c>
-      <c r="R999" t="n">
-        <v>-77.06746</v>
-      </c>
-      <c r="S999" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
@@ -84685,12 +83981,12 @@
       </c>
       <c r="M1010" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1010" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1010" t="n">
@@ -84700,14 +83996,14 @@
         <v>-76.87054000000001</v>
       </c>
       <c r="Q1010" t="n">
-        <v>-12.27539</v>
+        <v>-12.254973</v>
       </c>
       <c r="R1010" t="n">
-        <v>-76.87054000000001</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S1010" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -85027,7 +84323,7 @@
       </c>
       <c r="N1014" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1014" t="n">
@@ -85037,14 +84333,14 @@
         <v>-77.07671999999999</v>
       </c>
       <c r="Q1014" t="n">
-        <v>-11.86698</v>
+        <v>-11.599975</v>
       </c>
       <c r="R1014" t="n">
-        <v>-77.07671999999999</v>
+        <v>-77.2482385</v>
       </c>
       <c r="S1014" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -85201,7 +84497,7 @@
       </c>
       <c r="N1016" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1016" t="n">
@@ -85211,14 +84507,14 @@
         <v>-77.01066</v>
       </c>
       <c r="Q1016" t="n">
-        <v>-12.10782</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R1016" t="n">
-        <v>-77.01066</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S1016" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -85685,7 +84981,7 @@
       </c>
       <c r="N1022" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1022" t="n">
@@ -85695,14 +84991,14 @@
         <v>-76.97662</v>
       </c>
       <c r="Q1022" t="n">
-        <v>-12.15225</v>
+        <v>-12.04532</v>
       </c>
       <c r="R1022" t="n">
-        <v>-76.97662</v>
+        <v>-76.938125</v>
       </c>
       <c r="S1022" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -85849,17 +85145,17 @@
       </c>
       <c r="L1024" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1024" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1024" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1024" t="n">
@@ -85868,17 +85164,6 @@
       <c r="P1024" t="n">
         <v>-77.0498</v>
       </c>
-      <c r="Q1024" t="n">
-        <v>-12.07322</v>
-      </c>
-      <c r="R1024" t="n">
-        <v>-77.0498</v>
-      </c>
-      <c r="S1024" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
@@ -86452,12 +85737,12 @@
       </c>
       <c r="M1031" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1031" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1031" t="n">
@@ -86467,14 +85752,14 @@
         <v>-76.86897</v>
       </c>
       <c r="Q1031" t="n">
-        <v>-12.27699</v>
+        <v>-12.254973</v>
       </c>
       <c r="R1031" t="n">
-        <v>-76.86897</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S1031" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -86968,7 +86253,7 @@
       </c>
       <c r="N1037" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1037" t="n">
@@ -86978,14 +86263,14 @@
         <v>-77.07437</v>
       </c>
       <c r="Q1037" t="n">
-        <v>-12.08584</v>
+        <v>-12.0764921</v>
       </c>
       <c r="R1037" t="n">
-        <v>-77.07437</v>
+        <v>-77.0123866</v>
       </c>
       <c r="S1037" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -87055,7 +86340,7 @@
       </c>
       <c r="N1038" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1038" t="n">
@@ -87065,14 +86350,14 @@
         <v>-77.00385</v>
       </c>
       <c r="Q1038" t="n">
-        <v>-12.07676</v>
+        <v>-12.076624</v>
       </c>
       <c r="R1038" t="n">
-        <v>-77.00385</v>
+        <v>-77.0040527</v>
       </c>
       <c r="S1038" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -87142,7 +86427,7 @@
       </c>
       <c r="N1039" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1039" t="n">
@@ -87152,14 +86437,14 @@
         <v>-77.10558</v>
       </c>
       <c r="Q1039" t="n">
-        <v>-12.05908</v>
+        <v>-12.0596747</v>
       </c>
       <c r="R1039" t="n">
-        <v>-77.10558</v>
+        <v>-77.10685359999999</v>
       </c>
       <c r="S1039" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -87393,17 +86678,17 @@
       </c>
       <c r="L1042" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1042" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1042" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1042" t="n">
@@ -87412,17 +86697,6 @@
       <c r="P1042" t="n">
         <v>-77.05525</v>
       </c>
-      <c r="Q1042" t="n">
-        <v>-12.07704</v>
-      </c>
-      <c r="R1042" t="n">
-        <v>-77.05525</v>
-      </c>
-      <c r="S1042" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
@@ -87480,17 +86754,17 @@
       </c>
       <c r="L1043" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1043" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1043" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1043" t="n">
@@ -87499,17 +86773,6 @@
       <c r="P1043" t="n">
         <v>-77.05146999999999</v>
       </c>
-      <c r="Q1043" t="n">
-        <v>-12.07707</v>
-      </c>
-      <c r="R1043" t="n">
-        <v>-77.05146999999999</v>
-      </c>
-      <c r="S1043" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
@@ -87816,7 +87079,7 @@
       </c>
       <c r="N1047" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1047" t="n">
@@ -87826,14 +87089,14 @@
         <v>-76.94316000000001</v>
       </c>
       <c r="Q1047" t="n">
-        <v>-12.102</v>
+        <v>-12.1006131</v>
       </c>
       <c r="R1047" t="n">
-        <v>-76.94316000000001</v>
+        <v>-76.9440725</v>
       </c>
       <c r="S1047" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -87903,7 +87166,7 @@
       </c>
       <c r="N1048" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1048" t="n">
@@ -87913,14 +87176,14 @@
         <v>-77.11721</v>
       </c>
       <c r="Q1048" t="n">
-        <v>-12.06354</v>
+        <v>-12.0596747</v>
       </c>
       <c r="R1048" t="n">
-        <v>-77.11721</v>
+        <v>-77.10685359999999</v>
       </c>
       <c r="S1048" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -89561,7 +88824,7 @@
       </c>
       <c r="N1068" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1068" t="n">
@@ -89571,14 +88834,14 @@
         <v>-76.92753</v>
       </c>
       <c r="Q1068" t="n">
-        <v>-12.02761</v>
+        <v>-12.0452961</v>
       </c>
       <c r="R1068" t="n">
-        <v>-76.92753</v>
+        <v>-76.93812</v>
       </c>
       <c r="S1068" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -89638,17 +88901,17 @@
       </c>
       <c r="L1069" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1069" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1069" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1069" t="n">
@@ -89657,17 +88920,6 @@
       <c r="P1069" t="n">
         <v>-77.06232</v>
       </c>
-      <c r="Q1069" t="n">
-        <v>-12.06894</v>
-      </c>
-      <c r="R1069" t="n">
-        <v>-77.06232</v>
-      </c>
-      <c r="S1069" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
@@ -90333,7 +89585,7 @@
       </c>
       <c r="N1077" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1077" t="n">
@@ -90343,14 +89595,14 @@
         <v>-77.07677</v>
       </c>
       <c r="Q1077" t="n">
-        <v>-12.09358</v>
+        <v>-12.0765186</v>
       </c>
       <c r="R1077" t="n">
-        <v>-77.07677</v>
+        <v>-77.0119789</v>
       </c>
       <c r="S1077" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -90507,7 +89759,7 @@
       </c>
       <c r="N1079" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1079" t="n">
@@ -90517,14 +89769,14 @@
         <v>-76.92295</v>
       </c>
       <c r="Q1079" t="n">
-        <v>-12.02529</v>
+        <v>-12.0249483</v>
       </c>
       <c r="R1079" t="n">
-        <v>-76.92295</v>
+        <v>-76.9241933</v>
       </c>
       <c r="S1079" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -90584,17 +89836,17 @@
       </c>
       <c r="L1080" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1080" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1080" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1080" t="n">
@@ -90603,17 +89855,6 @@
       <c r="P1080" t="n">
         <v>-77.05114</v>
       </c>
-      <c r="Q1080" t="n">
-        <v>-12.05487</v>
-      </c>
-      <c r="R1080" t="n">
-        <v>-77.05114</v>
-      </c>
-      <c r="S1080" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
@@ -90676,12 +89917,12 @@
       </c>
       <c r="M1081" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1081" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1081" t="n">
@@ -90691,14 +89932,14 @@
         <v>-76.87044</v>
       </c>
       <c r="Q1081" t="n">
-        <v>-12.27826</v>
+        <v>-12.254973</v>
       </c>
       <c r="R1081" t="n">
-        <v>-76.87044</v>
+        <v>-76.9235359</v>
       </c>
       <c r="S1081" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -90855,7 +90096,7 @@
       </c>
       <c r="N1083" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1083" t="n">
@@ -90865,14 +90106,14 @@
         <v>-77.02427</v>
       </c>
       <c r="Q1083" t="n">
-        <v>-12.11842</v>
+        <v>-12.1108821</v>
       </c>
       <c r="R1083" t="n">
-        <v>-77.02427</v>
+        <v>-76.98695379999999</v>
       </c>
       <c r="S1083" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -93389,7 +92630,7 @@
       </c>
       <c r="N1113" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1113" t="n">
@@ -93399,14 +92640,14 @@
         <v>-77.05880999999999</v>
       </c>
       <c r="Q1113" t="n">
-        <v>-12.10267</v>
+        <v>-12.0765143</v>
       </c>
       <c r="R1113" t="n">
-        <v>-77.05880999999999</v>
+        <v>-77.0118501</v>
       </c>
       <c r="S1113" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -93476,7 +92717,7 @@
       </c>
       <c r="N1114" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1114" t="n">
@@ -93486,14 +92727,14 @@
         <v>-77.05880999999999</v>
       </c>
       <c r="Q1114" t="n">
-        <v>-12.10267</v>
+        <v>-12.0765143</v>
       </c>
       <c r="R1114" t="n">
-        <v>-77.05880999999999</v>
+        <v>-77.0118501</v>
       </c>
       <c r="S1114" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -94683,7 +93924,7 @@
       </c>
       <c r="N1128" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1128" t="n">
@@ -94693,14 +93934,14 @@
         <v>-76.94342</v>
       </c>
       <c r="Q1128" t="n">
-        <v>-12.10227</v>
+        <v>-12.1002076</v>
       </c>
       <c r="R1128" t="n">
-        <v>-76.94342</v>
+        <v>-76.9435829</v>
       </c>
       <c r="S1128" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -95400,7 +94641,7 @@
       </c>
       <c r="N1137" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1137" t="n">
@@ -95410,14 +94651,14 @@
         <v>-76.92152</v>
       </c>
       <c r="Q1137" t="n">
-        <v>-12.0256</v>
+        <v>-12.0249883</v>
       </c>
       <c r="R1137" t="n">
-        <v>-76.92152</v>
+        <v>-76.92443</v>
       </c>
       <c r="S1137" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -95912,17 +95153,17 @@
       </c>
       <c r="L1143" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1143" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1143" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1143" t="n">
@@ -95931,17 +95172,6 @@
       <c r="P1143" t="n">
         <v>-77.04891000000001</v>
       </c>
-      <c r="Q1143" t="n">
-        <v>-12.06767</v>
-      </c>
-      <c r="R1143" t="n">
-        <v>-77.04891000000001</v>
-      </c>
-      <c r="S1143" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
@@ -96596,7 +95826,7 @@
       </c>
       <c r="N1151" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1151" t="n">
@@ -96606,14 +95836,14 @@
         <v>-76.97866</v>
       </c>
       <c r="Q1151" t="n">
-        <v>-12.16232</v>
+        <v>-12.04532</v>
       </c>
       <c r="R1151" t="n">
-        <v>-76.97866</v>
+        <v>-76.938125</v>
       </c>
       <c r="S1151" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -97205,7 +96435,7 @@
       </c>
       <c r="N1158" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1158" t="n">
@@ -97215,14 +96445,14 @@
         <v>-77.07644000000001</v>
       </c>
       <c r="Q1158" t="n">
-        <v>-11.86557</v>
+        <v>-11.599975</v>
       </c>
       <c r="R1158" t="n">
-        <v>-77.07644000000001</v>
+        <v>-77.2482385</v>
       </c>
       <c r="S1158" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>
@@ -97379,7 +96609,7 @@
       </c>
       <c r="N1160" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1160" t="n">
@@ -97389,14 +96619,14 @@
         <v>-76.97978999999999</v>
       </c>
       <c r="Q1160" t="n">
-        <v>-12.15172</v>
+        <v>-12.04532</v>
       </c>
       <c r="R1160" t="n">
-        <v>-76.97978999999999</v>
+        <v>-76.938125</v>
       </c>
       <c r="S1160" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>PARTIDA</t>
         </is>
       </c>
     </row>

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3114,7 +3114,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -3124,14 +3124,14 @@
         <v>-76.96469</v>
       </c>
       <c r="Q32" t="n">
-        <v>-12.19928</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R32" t="n">
-        <v>-76.96469</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -4719,14 +4719,14 @@
         <v>-76.96563999999999</v>
       </c>
       <c r="Q51" t="n">
-        <v>-12.19864</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R51" t="n">
-        <v>-76.96563999999999</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O53" t="n">
@@ -4882,14 +4882,14 @@
         <v>-76.93325</v>
       </c>
       <c r="Q53" t="n">
-        <v>-12.21237</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R53" t="n">
-        <v>-76.93325</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O67" t="n">
@@ -6040,14 +6040,14 @@
         <v>-76.97469</v>
       </c>
       <c r="Q67" t="n">
-        <v>-12.1663</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R67" t="n">
-        <v>-76.97469</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -7203,14 +7203,14 @@
         <v>-76.9652</v>
       </c>
       <c r="Q81" t="n">
-        <v>-12.19873</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R81" t="n">
-        <v>-76.9652</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O84" t="n">
@@ -7437,14 +7437,14 @@
         <v>-76.97461</v>
       </c>
       <c r="Q84" t="n">
-        <v>-12.16657</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R84" t="n">
-        <v>-76.97461</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O90" t="n">
@@ -7959,14 +7959,14 @@
         <v>-76.93334</v>
       </c>
       <c r="Q90" t="n">
-        <v>-12.21236</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R90" t="n">
-        <v>-76.93334</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -9672,14 +9672,14 @@
         <v>-76.94197</v>
       </c>
       <c r="Q110" t="n">
-        <v>-12.20527</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R110" t="n">
-        <v>-76.94197</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O111" t="n">
@@ -9759,14 +9759,14 @@
         <v>-76.96566</v>
       </c>
       <c r="Q111" t="n">
-        <v>-12.19893</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R111" t="n">
-        <v>-76.96566</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -19082,7 +19082,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O224" t="n">
@@ -19092,14 +19092,14 @@
         <v>-76.97469</v>
       </c>
       <c r="Q224" t="n">
-        <v>-12.16625</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R224" t="n">
-        <v>-76.97469</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -24140,7 +24140,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O288" t="n">
@@ -24150,14 +24150,14 @@
         <v>-76.97104</v>
       </c>
       <c r="Q288" t="n">
-        <v>-12.15277</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R288" t="n">
-        <v>-76.97104</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O293" t="n">
@@ -24552,14 +24552,14 @@
         <v>-76.965</v>
       </c>
       <c r="Q293" t="n">
-        <v>-12.19852</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R293" t="n">
-        <v>-76.965</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O305" t="n">
@@ -25531,14 +25531,14 @@
         <v>-76.98195</v>
       </c>
       <c r="Q305" t="n">
-        <v>-12.19703</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R305" t="n">
-        <v>-76.98195</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -38904,7 +38904,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O469" t="n">
@@ -38914,14 +38914,14 @@
         <v>-76.96469</v>
       </c>
       <c r="Q469" t="n">
-        <v>-12.19928</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R469" t="n">
-        <v>-76.96469</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -43186,7 +43186,7 @@
       </c>
       <c r="N521" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O521" t="n">
@@ -43196,14 +43196,14 @@
         <v>-76.98220000000001</v>
       </c>
       <c r="Q521" t="n">
-        <v>-12.1968</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R521" t="n">
-        <v>-76.98220000000001</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S521" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -43512,7 +43512,7 @@
       </c>
       <c r="N525" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O525" t="n">
@@ -43522,14 +43522,14 @@
         <v>-76.96444</v>
       </c>
       <c r="Q525" t="n">
-        <v>-12.19844</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R525" t="n">
-        <v>-76.96444</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S525" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -45008,7 +45008,7 @@
       </c>
       <c r="N543" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O543" t="n">
@@ -45018,14 +45018,14 @@
         <v>-76.96535</v>
       </c>
       <c r="Q543" t="n">
-        <v>-12.19837</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R543" t="n">
-        <v>-76.96535</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S543" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -47596,7 +47596,7 @@
       </c>
       <c r="N574" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O574" t="n">
@@ -47606,14 +47606,14 @@
         <v>-76.97109</v>
       </c>
       <c r="Q574" t="n">
-        <v>-12.15221</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R574" t="n">
-        <v>-76.97109</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S574" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -49493,7 +49493,7 @@
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O597" t="n">
@@ -49503,14 +49503,14 @@
         <v>-76.93340000000001</v>
       </c>
       <c r="Q597" t="n">
-        <v>-12.21205</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R597" t="n">
-        <v>-76.93340000000001</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S597" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -51591,7 +51591,7 @@
       </c>
       <c r="N622" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O622" t="n">
@@ -51601,14 +51601,14 @@
         <v>-76.93331000000001</v>
       </c>
       <c r="Q622" t="n">
-        <v>-12.21218</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R622" t="n">
-        <v>-76.93331000000001</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S622" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -56662,7 +56662,7 @@
       </c>
       <c r="N683" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O683" t="n">
@@ -56672,14 +56672,14 @@
         <v>-76.93334</v>
       </c>
       <c r="Q683" t="n">
-        <v>-12.21236</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R683" t="n">
-        <v>-76.93334</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S683" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -57847,7 +57847,7 @@
       </c>
       <c r="N697" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O697" t="n">
@@ -57857,14 +57857,14 @@
         <v>-76.93331000000001</v>
       </c>
       <c r="Q697" t="n">
-        <v>-12.21214</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R697" t="n">
-        <v>-76.93331000000001</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S697" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -57934,7 +57934,7 @@
       </c>
       <c r="N698" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O698" t="n">
@@ -57944,14 +57944,14 @@
         <v>-76.93331000000001</v>
       </c>
       <c r="Q698" t="n">
-        <v>-12.21214</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R698" t="n">
-        <v>-76.93331000000001</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S698" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -61005,7 +61005,7 @@
       </c>
       <c r="N735" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O735" t="n">
@@ -61015,14 +61015,14 @@
         <v>-76.94222000000001</v>
       </c>
       <c r="Q735" t="n">
-        <v>-12.20574</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R735" t="n">
-        <v>-76.94222000000001</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S735" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -61777,7 +61777,7 @@
       </c>
       <c r="N744" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O744" t="n">
@@ -61787,14 +61787,14 @@
         <v>-76.94197</v>
       </c>
       <c r="Q744" t="n">
-        <v>-12.20527</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R744" t="n">
-        <v>-76.94197</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S744" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -64588,7 +64588,7 @@
       </c>
       <c r="N777" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O777" t="n">
@@ -64598,14 +64598,14 @@
         <v>-76.93356</v>
       </c>
       <c r="Q777" t="n">
-        <v>-12.21213</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R777" t="n">
-        <v>-76.93356</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S777" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -66349,7 +66349,7 @@
       </c>
       <c r="N798" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O798" t="n">
@@ -66359,14 +66359,14 @@
         <v>-76.97104</v>
       </c>
       <c r="Q798" t="n">
-        <v>-12.15277</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R798" t="n">
-        <v>-76.97104</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S798" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -66436,7 +66436,7 @@
       </c>
       <c r="N799" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O799" t="n">
@@ -66446,14 +66446,14 @@
         <v>-76.93368</v>
       </c>
       <c r="Q799" t="n">
-        <v>-12.2119</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R799" t="n">
-        <v>-76.93368</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S799" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -72014,7 +72014,7 @@
       </c>
       <c r="N866" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O866" t="n">
@@ -72024,14 +72024,14 @@
         <v>-76.94240000000001</v>
       </c>
       <c r="Q866" t="n">
-        <v>-12.20561</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R866" t="n">
-        <v>-76.94240000000001</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S866" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -74444,7 +74444,7 @@
       </c>
       <c r="N895" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O895" t="n">
@@ -74454,14 +74454,14 @@
         <v>-76.93368</v>
       </c>
       <c r="Q895" t="n">
-        <v>-12.2119</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R895" t="n">
-        <v>-76.93368</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S895" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -75608,7 +75608,7 @@
       </c>
       <c r="N909" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O909" t="n">
@@ -75618,14 +75618,14 @@
         <v>-76.97469</v>
       </c>
       <c r="Q909" t="n">
-        <v>-12.1663</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R909" t="n">
-        <v>-76.97469</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S909" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -77021,7 +77021,7 @@
       </c>
       <c r="N926" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O926" t="n">
@@ -77031,14 +77031,14 @@
         <v>-76.98220000000001</v>
       </c>
       <c r="Q926" t="n">
-        <v>-12.1968</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R926" t="n">
-        <v>-76.98220000000001</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S926" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -79745,7 +79745,7 @@
       </c>
       <c r="N959" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O959" t="n">
@@ -79755,14 +79755,14 @@
         <v>-76.97104</v>
       </c>
       <c r="Q959" t="n">
-        <v>-12.15277</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R959" t="n">
-        <v>-76.97104</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S959" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -80164,7 +80164,7 @@
       </c>
       <c r="N964" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O964" t="n">
@@ -80174,14 +80174,14 @@
         <v>-76.97132999999999</v>
       </c>
       <c r="Q964" t="n">
-        <v>-12.15213</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R964" t="n">
-        <v>-76.97132999999999</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S964" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -80414,7 +80414,7 @@
       </c>
       <c r="N967" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O967" t="n">
@@ -80424,14 +80424,14 @@
         <v>-76.93331000000001</v>
       </c>
       <c r="Q967" t="n">
-        <v>-12.21218</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R967" t="n">
-        <v>-76.93331000000001</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S967" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -87742,7 +87742,7 @@
       </c>
       <c r="N1055" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1055" t="n">
@@ -87752,14 +87752,14 @@
         <v>-76.94225</v>
       </c>
       <c r="Q1055" t="n">
-        <v>-12.206</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1055" t="n">
-        <v>-76.94225</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1055" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -91803,7 +91803,7 @@
       </c>
       <c r="N1103" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1103" t="n">
@@ -91813,14 +91813,14 @@
         <v>-76.97096999999999</v>
       </c>
       <c r="Q1103" t="n">
-        <v>-12.15275</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1103" t="n">
-        <v>-76.97096999999999</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1103" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -92891,7 +92891,7 @@
       </c>
       <c r="N1116" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1116" t="n">
@@ -92901,14 +92901,14 @@
         <v>-76.97084</v>
       </c>
       <c r="Q1116" t="n">
-        <v>-12.15242</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1116" t="n">
-        <v>-76.97084</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1116" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -92978,7 +92978,7 @@
       </c>
       <c r="N1117" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1117" t="n">
@@ -92988,14 +92988,14 @@
         <v>-76.97461</v>
       </c>
       <c r="Q1117" t="n">
-        <v>-12.16657</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1117" t="n">
-        <v>-76.97461</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1117" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -93065,7 +93065,7 @@
       </c>
       <c r="N1118" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1118" t="n">
@@ -93075,14 +93075,14 @@
         <v>-76.93356</v>
       </c>
       <c r="Q1118" t="n">
-        <v>-12.21213</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1118" t="n">
-        <v>-76.93356</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1118" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -93576,7 +93576,7 @@
       </c>
       <c r="N1124" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1124" t="n">
@@ -93586,14 +93586,14 @@
         <v>-76.97076</v>
       </c>
       <c r="Q1124" t="n">
-        <v>-12.15257</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1124" t="n">
-        <v>-76.97076</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1124" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -93663,7 +93663,7 @@
       </c>
       <c r="N1125" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1125" t="n">
@@ -93673,14 +93673,14 @@
         <v>-76.97096999999999</v>
       </c>
       <c r="Q1125" t="n">
-        <v>-12.15275</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1125" t="n">
-        <v>-76.97096999999999</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1125" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -93750,7 +93750,7 @@
       </c>
       <c r="N1126" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1126" t="n">
@@ -93760,14 +93760,14 @@
         <v>-76.97109</v>
       </c>
       <c r="Q1126" t="n">
-        <v>-12.15221</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1126" t="n">
-        <v>-76.97109</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1126" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -96087,7 +96087,7 @@
       </c>
       <c r="N1154" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1154" t="n">
@@ -96097,14 +96097,14 @@
         <v>-76.97076</v>
       </c>
       <c r="Q1154" t="n">
-        <v>-12.15257</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1154" t="n">
-        <v>-76.97076</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1154" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -96261,7 +96261,7 @@
       </c>
       <c r="N1156" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1156" t="n">
@@ -96271,14 +96271,14 @@
         <v>-76.97104</v>
       </c>
       <c r="Q1156" t="n">
-        <v>-12.15277</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1156" t="n">
-        <v>-76.97104</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1156" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -96783,7 +96783,7 @@
       </c>
       <c r="N1162" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1162" t="n">
@@ -96793,14 +96793,14 @@
         <v>-76.97109</v>
       </c>
       <c r="Q1162" t="n">
-        <v>-12.15221</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1162" t="n">
-        <v>-76.97109</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1162" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>
@@ -97120,7 +97120,7 @@
       </c>
       <c r="N1166" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1166" t="n">
@@ -97130,14 +97130,14 @@
         <v>-76.93331000000001</v>
       </c>
       <c r="Q1166" t="n">
-        <v>-12.21214</v>
+        <v>-12.2065895</v>
       </c>
       <c r="R1166" t="n">
-        <v>-76.93331000000001</v>
+        <v>-76.9366375</v>
       </c>
       <c r="S1166" t="inlineStr">
         <is>
-          <t>PARADA</t>
+          <t>LLEGADA</t>
         </is>
       </c>
     </row>

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1434,7 +1434,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O71" t="n">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O104" t="n">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O105" t="n">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O113" t="n">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O117" t="n">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O123" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O135" t="n">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O143" t="n">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O146" t="n">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O151" t="n">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O167" t="n">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O177" t="n">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O182" t="n">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O199" t="n">
@@ -17424,7 +17424,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O204" t="n">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O216" t="n">
@@ -18990,7 +18990,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O314" t="n">
@@ -30769,7 +30769,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -31204,7 +31204,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -32945,7 +32945,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O397" t="n">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O404" t="n">
@@ -33929,7 +33929,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O409" t="n">
@@ -34424,7 +34424,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -35935,7 +35935,7 @@
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O433" t="n">
@@ -36674,7 +36674,7 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O442" t="n">
@@ -38404,7 +38404,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -38725,7 +38725,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -39133,7 +39133,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -39225,7 +39225,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O473" t="n">
@@ -39551,7 +39551,7 @@
       </c>
       <c r="N477" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O477" t="n">
@@ -39801,7 +39801,7 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O480" t="n">
@@ -41327,7 +41327,7 @@
       </c>
       <c r="N499" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O499" t="n">
@@ -42664,7 +42664,7 @@
       </c>
       <c r="N515" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O515" t="n">
@@ -42746,7 +42746,7 @@
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N516" t="inlineStr">
@@ -43344,7 +43344,7 @@
       </c>
       <c r="M523" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N523" t="inlineStr">
@@ -44094,7 +44094,7 @@
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O532" t="n">
@@ -45498,7 +45498,7 @@
       </c>
       <c r="N549" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O549" t="n">
@@ -45672,7 +45672,7 @@
       </c>
       <c r="N551" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O551" t="n">
@@ -45841,7 +45841,7 @@
       </c>
       <c r="M553" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N553" t="inlineStr">
@@ -47857,7 +47857,7 @@
       </c>
       <c r="N577" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O577" t="n">
@@ -49667,7 +49667,7 @@
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O599" t="n">
@@ -49841,7 +49841,7 @@
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O601" t="n">
@@ -50271,7 +50271,7 @@
       </c>
       <c r="M606" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N606" t="inlineStr">
@@ -51504,7 +51504,7 @@
       </c>
       <c r="N621" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O621" t="n">
@@ -51928,7 +51928,7 @@
       </c>
       <c r="N626" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O626" t="n">
@@ -52178,7 +52178,7 @@
       </c>
       <c r="N629" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O629" t="n">
@@ -54298,7 +54298,7 @@
       </c>
       <c r="N654" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O654" t="n">
@@ -54532,7 +54532,7 @@
       </c>
       <c r="M657" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N657" t="inlineStr">
@@ -54624,7 +54624,7 @@
       </c>
       <c r="N658" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O658" t="n">
@@ -54711,7 +54711,7 @@
       </c>
       <c r="N659" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O659" t="n">
@@ -54957,7 +54957,7 @@
       </c>
       <c r="N662" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O662" t="n">
@@ -55121,7 +55121,7 @@
       </c>
       <c r="N664" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O664" t="n">
@@ -55285,7 +55285,7 @@
       </c>
       <c r="N666" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O666" t="n">
@@ -55449,7 +55449,7 @@
       </c>
       <c r="N668" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O668" t="n">
@@ -55531,7 +55531,7 @@
       </c>
       <c r="N669" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O669" t="n">
@@ -56575,7 +56575,7 @@
       </c>
       <c r="N682" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O682" t="n">
@@ -56901,7 +56901,7 @@
       </c>
       <c r="N686" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O686" t="n">
@@ -57510,7 +57510,7 @@
       </c>
       <c r="N693" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O693" t="n">
@@ -59266,7 +59266,7 @@
       </c>
       <c r="N714" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O714" t="n">
@@ -59516,7 +59516,7 @@
       </c>
       <c r="N717" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O717" t="n">
@@ -60500,7 +60500,7 @@
       </c>
       <c r="M729" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N729" t="inlineStr">
@@ -60592,7 +60592,7 @@
       </c>
       <c r="N730" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O730" t="n">
@@ -60755,7 +60755,7 @@
       </c>
       <c r="N732" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O732" t="n">
@@ -61440,7 +61440,7 @@
       </c>
       <c r="N740" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O740" t="n">
@@ -61864,7 +61864,7 @@
       </c>
       <c r="N745" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O745" t="n">
@@ -62207,7 +62207,7 @@
       </c>
       <c r="N749" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O749" t="n">
@@ -62544,7 +62544,7 @@
       </c>
       <c r="N753" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O753" t="n">
@@ -63892,7 +63892,7 @@
       </c>
       <c r="N769" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O769" t="n">
@@ -65936,7 +65936,7 @@
       </c>
       <c r="N793" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O793" t="n">
@@ -68018,7 +68018,7 @@
       </c>
       <c r="N818" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O818" t="n">
@@ -68279,7 +68279,7 @@
       </c>
       <c r="N821" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O821" t="n">
@@ -70133,7 +70133,7 @@
       </c>
       <c r="N843" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O843" t="n">
@@ -72351,7 +72351,7 @@
       </c>
       <c r="N870" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O870" t="n">
@@ -74858,7 +74858,7 @@
       </c>
       <c r="M900" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N900" t="inlineStr">
@@ -76206,7 +76206,7 @@
       </c>
       <c r="N916" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O916" t="n">
@@ -76608,7 +76608,7 @@
       </c>
       <c r="N921" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O921" t="n">
@@ -77108,7 +77108,7 @@
       </c>
       <c r="N927" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O927" t="n">
@@ -77816,7 +77816,7 @@
       </c>
       <c r="M936" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N936" t="inlineStr">
@@ -77903,7 +77903,7 @@
       </c>
       <c r="M937" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N937" t="inlineStr">
@@ -81154,7 +81154,7 @@
       </c>
       <c r="N976" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O976" t="n">
@@ -82176,7 +82176,7 @@
       </c>
       <c r="N988" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O988" t="n">
@@ -83122,7 +83122,7 @@
       </c>
       <c r="M1000" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1000" t="inlineStr">
@@ -83557,7 +83557,7 @@
       </c>
       <c r="M1005" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1005" t="inlineStr">
@@ -85231,7 +85231,7 @@
       </c>
       <c r="N1025" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1025" t="n">
@@ -85829,7 +85829,7 @@
       </c>
       <c r="N1032" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1032" t="n">
@@ -87329,7 +87329,7 @@
       </c>
       <c r="N1050" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1050" t="n">
@@ -87503,7 +87503,7 @@
       </c>
       <c r="N1052" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1052" t="n">
@@ -88003,7 +88003,7 @@
       </c>
       <c r="N1058" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1058" t="n">
@@ -88090,7 +88090,7 @@
       </c>
       <c r="N1059" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1059" t="n">
@@ -88416,7 +88416,7 @@
       </c>
       <c r="N1063" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1063" t="n">
@@ -88503,7 +88503,7 @@
       </c>
       <c r="N1064" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1064" t="n">
@@ -88737,7 +88737,7 @@
       </c>
       <c r="N1067" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1067" t="n">
@@ -89063,7 +89063,7 @@
       </c>
       <c r="N1071" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1071" t="n">
@@ -89319,7 +89319,7 @@
       </c>
       <c r="M1074" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1074" t="inlineStr">
@@ -90004,7 +90004,7 @@
       </c>
       <c r="M1082" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1082" t="inlineStr">
@@ -91216,7 +91216,7 @@
       </c>
       <c r="N1096" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1096" t="n">
@@ -92369,7 +92369,7 @@
       </c>
       <c r="N1110" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1110" t="n">
@@ -93147,7 +93147,7 @@
       </c>
       <c r="M1119" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1119" t="inlineStr">
@@ -93837,7 +93837,7 @@
       </c>
       <c r="N1127" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1127" t="n">
@@ -94473,7 +94473,7 @@
       </c>
       <c r="M1135" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1135" t="inlineStr">
@@ -95489,7 +95489,7 @@
       </c>
       <c r="N1147" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1147" t="n">
@@ -95734,7 +95734,7 @@
       </c>
       <c r="M1150" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1150" t="inlineStr">
@@ -96174,7 +96174,7 @@
       </c>
       <c r="N1155" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1155" t="n">
@@ -96691,7 +96691,7 @@
       </c>
       <c r="M1161" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1161" t="inlineStr">
@@ -96870,7 +96870,7 @@
       </c>
       <c r="N1163" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1163" t="n">
@@ -96957,7 +96957,7 @@
       </c>
       <c r="N1164" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1164" t="n">
@@ -97202,7 +97202,7 @@
       </c>
       <c r="M1167" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1167" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1848,17 +1848,17 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1867,17 +1867,6 @@
       <c r="P17" t="n">
         <v>-77.11427</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R17" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2093,17 +2082,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>RECHAZADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -2112,17 +2101,6 @@
       <c r="P20" t="n">
         <v>-77.09956</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-12.05593</v>
-      </c>
-      <c r="R20" t="n">
-        <v>-77.09956</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2180,17 +2158,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2199,17 +2177,6 @@
       <c r="P21" t="n">
         <v>-77.09954</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-12.0596747</v>
-      </c>
-      <c r="R21" t="n">
-        <v>-77.10685359999999</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3932,17 +3899,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3951,17 +3918,6 @@
       <c r="P42" t="n">
         <v>-77.11277</v>
       </c>
-      <c r="Q42" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R42" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4106,17 +4062,17 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -4125,17 +4081,6 @@
       <c r="P44" t="n">
         <v>-76.99592</v>
       </c>
-      <c r="Q44" t="n">
-        <v>-12.1609738</v>
-      </c>
-      <c r="R44" t="n">
-        <v>-76.9960928</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5036,17 +4981,17 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O55" t="n">
@@ -5055,17 +5000,6 @@
       <c r="P55" t="n">
         <v>-77.09782</v>
       </c>
-      <c r="Q55" t="n">
-        <v>-12.0596747</v>
-      </c>
-      <c r="R55" t="n">
-        <v>-77.10685359999999</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8184,17 +8118,17 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O93" t="n">
@@ -8203,17 +8137,6 @@
       <c r="P93" t="n">
         <v>-76.9905</v>
       </c>
-      <c r="Q93" t="n">
-        <v>-12.1667765</v>
-      </c>
-      <c r="R93" t="n">
-        <v>-76.99035120000001</v>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -12294,17 +12217,17 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O141" t="n">
@@ -12313,17 +12236,6 @@
       <c r="P141" t="n">
         <v>-77.10402999999999</v>
       </c>
-      <c r="Q141" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R141" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14824,17 +14736,17 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O173" t="n">
@@ -14843,17 +14755,6 @@
       <c r="P173" t="n">
         <v>-77.11046</v>
       </c>
-      <c r="Q173" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R173" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16107,17 +16008,17 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O188" t="n">
@@ -16126,17 +16027,6 @@
       <c r="P188" t="n">
         <v>-76.99652</v>
       </c>
-      <c r="Q188" t="n">
-        <v>-12.1102148</v>
-      </c>
-      <c r="R188" t="n">
-        <v>-76.97817310000001</v>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -17914,17 +17804,17 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O210" t="n">
@@ -17933,17 +17823,6 @@
       <c r="P210" t="n">
         <v>-77.11121</v>
       </c>
-      <c r="Q210" t="n">
-        <v>-12.047711</v>
-      </c>
-      <c r="R210" t="n">
-        <v>-77.11145380000001</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -18822,17 +18701,17 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O221" t="n">
@@ -18841,17 +18720,6 @@
       <c r="P221" t="n">
         <v>-76.99204</v>
       </c>
-      <c r="Q221" t="n">
-        <v>-12.1080578</v>
-      </c>
-      <c r="R221" t="n">
-        <v>-76.9781351</v>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -25250,17 +25118,17 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O302" t="n">
@@ -25269,17 +25137,6 @@
       <c r="P302" t="n">
         <v>-76.98878000000001</v>
       </c>
-      <c r="Q302" t="n">
-        <v>-12.1658382</v>
-      </c>
-      <c r="R302" t="n">
-        <v>-76.9887645</v>
-      </c>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -28698,17 +28555,17 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O343" t="n">
@@ -28717,17 +28574,6 @@
       <c r="P343" t="n">
         <v>-77.10548</v>
       </c>
-      <c r="Q343" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R343" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S343" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -34006,17 +33852,17 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O410" t="n">
@@ -34025,17 +33871,6 @@
       <c r="P410" t="n">
         <v>-76.99829</v>
       </c>
-      <c r="Q410" t="n">
-        <v>-12.1670349</v>
-      </c>
-      <c r="R410" t="n">
-        <v>-76.9982043</v>
-      </c>
-      <c r="S410" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -34256,17 +34091,17 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O413" t="n">
@@ -34275,17 +34110,6 @@
       <c r="P413" t="n">
         <v>-77.10868000000001</v>
       </c>
-      <c r="Q413" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R413" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S413" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -37333,17 +37157,17 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O450" t="n">
@@ -37352,17 +37176,6 @@
       <c r="P450" t="n">
         <v>-77.10656</v>
       </c>
-      <c r="Q450" t="n">
-        <v>-12.0596747</v>
-      </c>
-      <c r="R450" t="n">
-        <v>-77.10685359999999</v>
-      </c>
-      <c r="S450" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -38225,17 +38038,17 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O461" t="n">
@@ -38244,17 +38057,6 @@
       <c r="P461" t="n">
         <v>-76.99236000000001</v>
       </c>
-      <c r="Q461" t="n">
-        <v>-12.1613204</v>
-      </c>
-      <c r="R461" t="n">
-        <v>-76.9924092</v>
-      </c>
-      <c r="S461" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -40409,17 +40211,17 @@
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O488" t="n">
@@ -40428,17 +40230,6 @@
       <c r="P488" t="n">
         <v>-77.11113</v>
       </c>
-      <c r="Q488" t="n">
-        <v>-12.047711</v>
-      </c>
-      <c r="R488" t="n">
-        <v>-77.11145380000001</v>
-      </c>
-      <c r="S488" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -41230,17 +41021,17 @@
       </c>
       <c r="L498" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O498" t="n">
@@ -41249,17 +41040,6 @@
       <c r="P498" t="n">
         <v>-76.99384999999999</v>
       </c>
-      <c r="Q498" t="n">
-        <v>-12.1080578</v>
-      </c>
-      <c r="R498" t="n">
-        <v>-76.9781351</v>
-      </c>
-      <c r="S498" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -42143,17 +41923,17 @@
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M509" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N509" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O509" t="n">
@@ -42162,17 +41942,6 @@
       <c r="P509" t="n">
         <v>-77.11139</v>
       </c>
-      <c r="Q509" t="n">
-        <v>-12.047711</v>
-      </c>
-      <c r="R509" t="n">
-        <v>-77.11145380000001</v>
-      </c>
-      <c r="S509" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -42480,17 +42249,17 @@
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M513" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N513" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O513" t="n">
@@ -42499,17 +42268,6 @@
       <c r="P513" t="n">
         <v>-77.11145999999999</v>
       </c>
-      <c r="Q513" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R513" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S513" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -43665,17 +43423,17 @@
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M527" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N527" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O527" t="n">
@@ -43684,17 +43442,6 @@
       <c r="P527" t="n">
         <v>-76.99041</v>
       </c>
-      <c r="Q527" t="n">
-        <v>-12.1080578</v>
-      </c>
-      <c r="R527" t="n">
-        <v>-76.9781351</v>
-      </c>
-      <c r="S527" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -44171,17 +43918,17 @@
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M533" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N533" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O533" t="n">
@@ -44190,17 +43937,6 @@
       <c r="P533" t="n">
         <v>-77.11408</v>
       </c>
-      <c r="Q533" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R533" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S533" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -44345,17 +44081,17 @@
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M535" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N535" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O535" t="n">
@@ -44364,17 +44100,6 @@
       <c r="P535" t="n">
         <v>-77.10566</v>
       </c>
-      <c r="Q535" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R535" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S535" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -44432,17 +44157,17 @@
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M536" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N536" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O536" t="n">
@@ -44451,17 +44176,6 @@
       <c r="P536" t="n">
         <v>-76.99198</v>
       </c>
-      <c r="Q536" t="n">
-        <v>-12.1080578</v>
-      </c>
-      <c r="R536" t="n">
-        <v>-76.9781351</v>
-      </c>
-      <c r="S536" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -45243,17 +44957,17 @@
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M546" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N546" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O546" t="n">
@@ -45262,17 +44976,6 @@
       <c r="P546" t="n">
         <v>-77.10687</v>
       </c>
-      <c r="Q546" t="n">
-        <v>-12.0596747</v>
-      </c>
-      <c r="R546" t="n">
-        <v>-77.10685359999999</v>
-      </c>
-      <c r="S546" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -49309,17 +49012,17 @@
       </c>
       <c r="L595" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M595" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N595" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O595" t="n">
@@ -49328,17 +49031,6 @@
       <c r="P595" t="n">
         <v>-77.11121</v>
       </c>
-      <c r="Q595" t="n">
-        <v>-12.047711</v>
-      </c>
-      <c r="R595" t="n">
-        <v>-77.11145380000001</v>
-      </c>
-      <c r="S595" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -50179,17 +49871,17 @@
       </c>
       <c r="L605" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O605" t="n">
@@ -50198,17 +49890,6 @@
       <c r="P605" t="n">
         <v>-76.99381</v>
       </c>
-      <c r="Q605" t="n">
-        <v>-12.1080578</v>
-      </c>
-      <c r="R605" t="n">
-        <v>-76.9781351</v>
-      </c>
-      <c r="S605" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -50668,17 +50349,17 @@
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M611" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t>RECHAZADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O611" t="n">
@@ -50687,17 +50368,6 @@
       <c r="P611" t="n">
         <v>-76.98933</v>
       </c>
-      <c r="Q611" t="n">
-        <v>-12.1113699</v>
-      </c>
-      <c r="R611" t="n">
-        <v>-76.97793710000001</v>
-      </c>
-      <c r="S611" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -52005,17 +51675,17 @@
       </c>
       <c r="L627" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M627" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N627" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O627" t="n">
@@ -52024,17 +51694,6 @@
       <c r="P627" t="n">
         <v>-77.11136</v>
       </c>
-      <c r="Q627" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R627" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S627" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -52755,17 +52414,17 @@
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M636" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N636" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O636" t="n">
@@ -52774,17 +52433,6 @@
       <c r="P636" t="n">
         <v>-77.10657999999999</v>
       </c>
-      <c r="Q636" t="n">
-        <v>-12.0596747</v>
-      </c>
-      <c r="R636" t="n">
-        <v>-77.10685359999999</v>
-      </c>
-      <c r="S636" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -52842,17 +52490,17 @@
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M637" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N637" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O637" t="n">
@@ -52861,17 +52509,6 @@
       <c r="P637" t="n">
         <v>-76.98838000000001</v>
       </c>
-      <c r="Q637" t="n">
-        <v>-12.1699914</v>
-      </c>
-      <c r="R637" t="n">
-        <v>-76.9998638</v>
-      </c>
-      <c r="S637" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -53016,17 +52653,17 @@
       </c>
       <c r="L639" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M639" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N639" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O639" t="n">
@@ -53035,17 +52672,6 @@
       <c r="P639" t="n">
         <v>-77.10680000000001</v>
       </c>
-      <c r="Q639" t="n">
-        <v>-12.0596747</v>
-      </c>
-      <c r="R639" t="n">
-        <v>-77.10685359999999</v>
-      </c>
-      <c r="S639" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -53103,17 +52729,17 @@
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M640" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N640" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O640" t="n">
@@ -53122,17 +52748,6 @@
       <c r="P640" t="n">
         <v>-76.99759</v>
       </c>
-      <c r="Q640" t="n">
-        <v>-12.1699952</v>
-      </c>
-      <c r="R640" t="n">
-        <v>-76.9998702</v>
-      </c>
-      <c r="S640" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -53190,17 +52805,17 @@
       </c>
       <c r="L641" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M641" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N641" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O641" t="n">
@@ -53209,17 +52824,6 @@
       <c r="P641" t="n">
         <v>-76.99066000000001</v>
       </c>
-      <c r="Q641" t="n">
-        <v>-12.174435</v>
-      </c>
-      <c r="R641" t="n">
-        <v>-76.99113939999999</v>
-      </c>
-      <c r="S641" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -55929,17 +55533,17 @@
       </c>
       <c r="L674" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M674" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N674" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O674" t="n">
@@ -55948,17 +55552,6 @@
       <c r="P674" t="n">
         <v>-76.99532000000001</v>
       </c>
-      <c r="Q674" t="n">
-        <v>-12.1080578</v>
-      </c>
-      <c r="R674" t="n">
-        <v>-76.9781351</v>
-      </c>
-      <c r="S674" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -57239,17 +56832,17 @@
       </c>
       <c r="L690" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M690" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N690" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O690" t="n">
@@ -57258,17 +56851,6 @@
       <c r="P690" t="n">
         <v>-76.99256</v>
       </c>
-      <c r="Q690" t="n">
-        <v>-12.1672571</v>
-      </c>
-      <c r="R690" t="n">
-        <v>-76.99452239999999</v>
-      </c>
-      <c r="S690" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -57326,17 +56908,17 @@
       </c>
       <c r="L691" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M691" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N691" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O691" t="n">
@@ -57345,17 +56927,6 @@
       <c r="P691" t="n">
         <v>-76.99314</v>
       </c>
-      <c r="Q691" t="n">
-        <v>-12.1672613</v>
-      </c>
-      <c r="R691" t="n">
-        <v>-76.9945256</v>
-      </c>
-      <c r="S691" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -59082,17 +58653,17 @@
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M712" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N712" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O712" t="n">
@@ -59101,17 +58672,6 @@
       <c r="P712" t="n">
         <v>-76.99127</v>
       </c>
-      <c r="Q712" t="n">
-        <v>-12.1684457</v>
-      </c>
-      <c r="R712" t="n">
-        <v>-76.99123160000001</v>
-      </c>
-      <c r="S712" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -62115,17 +61675,17 @@
       </c>
       <c r="L748" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M748" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N748" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O748" t="n">
@@ -62134,17 +61694,6 @@
       <c r="P748" t="n">
         <v>-77.10686</v>
       </c>
-      <c r="Q748" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R748" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S748" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -62773,17 +62322,17 @@
       </c>
       <c r="L756" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M756" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N756" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O756" t="n">
@@ -62792,17 +62341,6 @@
       <c r="P756" t="n">
         <v>-76.9984</v>
       </c>
-      <c r="Q756" t="n">
-        <v>-12.1102148</v>
-      </c>
-      <c r="R756" t="n">
-        <v>-76.97817310000001</v>
-      </c>
-      <c r="S756" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -63197,17 +62735,17 @@
       </c>
       <c r="L761" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M761" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N761" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O761" t="n">
@@ -63216,17 +62754,6 @@
       <c r="P761" t="n">
         <v>-76.99162</v>
       </c>
-      <c r="Q761" t="n">
-        <v>-12.1080578</v>
-      </c>
-      <c r="R761" t="n">
-        <v>-76.9781351</v>
-      </c>
-      <c r="S761" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -64317,17 +63844,17 @@
       </c>
       <c r="L774" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M774" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N774" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O774" t="n">
@@ -64336,17 +63863,6 @@
       <c r="P774" t="n">
         <v>-77.10979</v>
       </c>
-      <c r="Q774" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R774" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S774" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -65013,17 +64529,17 @@
       </c>
       <c r="L782" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M782" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N782" t="inlineStr">
         <is>
-          <t>RECHAZADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O782" t="n">
@@ -65032,17 +64548,6 @@
       <c r="P782" t="n">
         <v>-76.99907</v>
       </c>
-      <c r="Q782" t="n">
-        <v>-12.1116465</v>
-      </c>
-      <c r="R782" t="n">
-        <v>-76.97791049999999</v>
-      </c>
-      <c r="S782" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -65589,17 +65094,17 @@
       </c>
       <c r="L789" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M789" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N789" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O789" t="n">
@@ -65608,17 +65113,6 @@
       <c r="P789" t="n">
         <v>-76.99053000000001</v>
       </c>
-      <c r="Q789" t="n">
-        <v>-12.1667775</v>
-      </c>
-      <c r="R789" t="n">
-        <v>-76.99034450000001</v>
-      </c>
-      <c r="S789" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -66589,17 +66083,17 @@
       </c>
       <c r="L801" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M801" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N801" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O801" t="n">
@@ -66608,17 +66102,6 @@
       <c r="P801" t="n">
         <v>-76.99223000000001</v>
       </c>
-      <c r="Q801" t="n">
-        <v>-12.1080578</v>
-      </c>
-      <c r="R801" t="n">
-        <v>-76.9781351</v>
-      </c>
-      <c r="S801" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -67252,17 +66735,17 @@
       </c>
       <c r="L809" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M809" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N809" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O809" t="n">
@@ -67271,17 +66754,6 @@
       <c r="P809" t="n">
         <v>-77.10389000000001</v>
       </c>
-      <c r="Q809" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R809" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S809" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -67502,17 +66974,17 @@
       </c>
       <c r="L812" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M812" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N812" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O812" t="n">
@@ -67521,17 +66993,6 @@
       <c r="P812" t="n">
         <v>-76.99997999999999</v>
       </c>
-      <c r="Q812" t="n">
-        <v>-12.1705177</v>
-      </c>
-      <c r="R812" t="n">
-        <v>-76.9980997</v>
-      </c>
-      <c r="S812" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -68095,17 +67556,17 @@
       </c>
       <c r="L819" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M819" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N819" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O819" t="n">
@@ -68114,17 +67575,6 @@
       <c r="P819" t="n">
         <v>-76.9922</v>
       </c>
-      <c r="Q819" t="n">
-        <v>-12.1080578</v>
-      </c>
-      <c r="R819" t="n">
-        <v>-76.9781351</v>
-      </c>
-      <c r="S819" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -68182,17 +67632,17 @@
       </c>
       <c r="L820" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M820" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N820" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O820" t="n">
@@ -68201,17 +67651,6 @@
       <c r="P820" t="n">
         <v>-76.9897</v>
       </c>
-      <c r="Q820" t="n">
-        <v>-12.1668298</v>
-      </c>
-      <c r="R820" t="n">
-        <v>-76.9896591</v>
-      </c>
-      <c r="S820" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -68530,17 +67969,17 @@
       </c>
       <c r="L824" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M824" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N824" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O824" t="n">
@@ -68549,17 +67988,6 @@
       <c r="P824" t="n">
         <v>-76.99189</v>
       </c>
-      <c r="Q824" t="n">
-        <v>-12.1080578</v>
-      </c>
-      <c r="R824" t="n">
-        <v>-76.9781351</v>
-      </c>
-      <c r="S824" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -68617,17 +68045,17 @@
       </c>
       <c r="L825" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M825" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N825" t="inlineStr">
         <is>
-          <t>RECHAZADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O825" t="n">
@@ -68636,17 +68064,6 @@
       <c r="P825" t="n">
         <v>-76.99198</v>
       </c>
-      <c r="Q825" t="n">
-        <v>-12.1102148</v>
-      </c>
-      <c r="R825" t="n">
-        <v>-76.97817310000001</v>
-      </c>
-      <c r="S825" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -69112,17 +68529,17 @@
       </c>
       <c r="L831" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M831" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N831" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O831" t="n">
@@ -69131,17 +68548,6 @@
       <c r="P831" t="n">
         <v>-76.99218999999999</v>
       </c>
-      <c r="Q831" t="n">
-        <v>-12.1612695</v>
-      </c>
-      <c r="R831" t="n">
-        <v>-76.99257420000001</v>
-      </c>
-      <c r="S831" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -69199,17 +68605,17 @@
       </c>
       <c r="L832" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M832" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N832" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O832" t="n">
@@ -69218,17 +68624,6 @@
       <c r="P832" t="n">
         <v>-76.99651</v>
       </c>
-      <c r="Q832" t="n">
-        <v>-12.1102148</v>
-      </c>
-      <c r="R832" t="n">
-        <v>-76.97817310000001</v>
-      </c>
-      <c r="S832" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
@@ -70531,17 +69926,17 @@
       </c>
       <c r="L848" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M848" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N848" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O848" t="n">
@@ -70550,17 +69945,6 @@
       <c r="P848" t="n">
         <v>-76.98891</v>
       </c>
-      <c r="Q848" t="n">
-        <v>-12.166258</v>
-      </c>
-      <c r="R848" t="n">
-        <v>-76.9890417</v>
-      </c>
-      <c r="S848" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -74097,17 +73481,17 @@
       </c>
       <c r="L891" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M891" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N891" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O891" t="n">
@@ -74116,17 +73500,6 @@
       <c r="P891" t="n">
         <v>-77.11476</v>
       </c>
-      <c r="Q891" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R891" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S891" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -74184,17 +73557,17 @@
       </c>
       <c r="L892" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M892" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N892" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O892" t="n">
@@ -74203,17 +73576,6 @@
       <c r="P892" t="n">
         <v>-76.99454</v>
       </c>
-      <c r="Q892" t="n">
-        <v>-12.1672452</v>
-      </c>
-      <c r="R892" t="n">
-        <v>-76.99450280000001</v>
-      </c>
-      <c r="S892" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
@@ -74608,17 +73970,17 @@
       </c>
       <c r="L897" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M897" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N897" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O897" t="n">
@@ -74627,17 +73989,6 @@
       <c r="P897" t="n">
         <v>-76.99979</v>
       </c>
-      <c r="Q897" t="n">
-        <v>-12.1699983</v>
-      </c>
-      <c r="R897" t="n">
-        <v>-76.9998724</v>
-      </c>
-      <c r="S897" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
@@ -75424,17 +74775,17 @@
       </c>
       <c r="L907" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M907" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N907" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O907" t="n">
@@ -75443,17 +74794,6 @@
       <c r="P907" t="n">
         <v>-77.11139</v>
       </c>
-      <c r="Q907" t="n">
-        <v>-12.047711</v>
-      </c>
-      <c r="R907" t="n">
-        <v>-77.11145380000001</v>
-      </c>
-      <c r="S907" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
@@ -78148,17 +77488,17 @@
       </c>
       <c r="L940" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M940" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N940" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O940" t="n">
@@ -78167,17 +77507,6 @@
       <c r="P940" t="n">
         <v>-77.10590999999999</v>
       </c>
-      <c r="Q940" t="n">
-        <v>-12.0596747</v>
-      </c>
-      <c r="R940" t="n">
-        <v>-77.10685359999999</v>
-      </c>
-      <c r="S940" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
@@ -78626,17 +77955,17 @@
       </c>
       <c r="L946" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M946" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N946" t="inlineStr">
         <is>
-          <t>RECHAZADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O946" t="n">
@@ -78645,17 +77974,6 @@
       <c r="P946" t="n">
         <v>-76.99225</v>
       </c>
-      <c r="Q946" t="n">
-        <v>-12.1102148</v>
-      </c>
-      <c r="R946" t="n">
-        <v>-76.97817310000001</v>
-      </c>
-      <c r="S946" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
@@ -79387,17 +78705,17 @@
       </c>
       <c r="L955" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M955" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N955" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O955" t="n">
@@ -79406,17 +78724,6 @@
       <c r="P955" t="n">
         <v>-77.10557</v>
       </c>
-      <c r="Q955" t="n">
-        <v>-12.0596747</v>
-      </c>
-      <c r="R955" t="n">
-        <v>-77.10685359999999</v>
-      </c>
-      <c r="S955" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
@@ -80241,17 +79548,17 @@
       </c>
       <c r="L965" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M965" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N965" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O965" t="n">
@@ -80260,17 +79567,6 @@
       <c r="P965" t="n">
         <v>-76.99829</v>
       </c>
-      <c r="Q965" t="n">
-        <v>-12.1670349</v>
-      </c>
-      <c r="R965" t="n">
-        <v>-76.9982043</v>
-      </c>
-      <c r="S965" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
@@ -82166,17 +81462,17 @@
       </c>
       <c r="L988" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M988" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N988" t="inlineStr">
         <is>
-          <t>RECHAZADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O988" t="n">
@@ -82185,17 +81481,6 @@
       <c r="P988" t="n">
         <v>-77.10914</v>
       </c>
-      <c r="Q988" t="n">
-        <v>-12.04995</v>
-      </c>
-      <c r="R988" t="n">
-        <v>-77.10914</v>
-      </c>
-      <c r="S988" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
@@ -83378,17 +82663,17 @@
       </c>
       <c r="L1003" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1003" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1003" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1003" t="n">
@@ -83397,17 +82682,6 @@
       <c r="P1003" t="n">
         <v>-76.99092</v>
       </c>
-      <c r="Q1003" t="n">
-        <v>-12.1676755</v>
-      </c>
-      <c r="R1003" t="n">
-        <v>-76.9907917</v>
-      </c>
-      <c r="S1003" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
@@ -86069,17 +85343,17 @@
       </c>
       <c r="L1035" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1035" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1035" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1035" t="n">
@@ -86088,17 +85362,6 @@
       <c r="P1035" t="n">
         <v>-76.99127</v>
       </c>
-      <c r="Q1035" t="n">
-        <v>-12.1684457</v>
-      </c>
-      <c r="R1035" t="n">
-        <v>-76.99123160000001</v>
-      </c>
-      <c r="S1035" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
@@ -86156,17 +85419,17 @@
       </c>
       <c r="L1036" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1036" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1036" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1036" t="n">
@@ -86175,17 +85438,6 @@
       <c r="P1036" t="n">
         <v>-76.99127</v>
       </c>
-      <c r="Q1036" t="n">
-        <v>-12.1684457</v>
-      </c>
-      <c r="R1036" t="n">
-        <v>-76.99123160000001</v>
-      </c>
-      <c r="S1036" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
@@ -86417,17 +85669,17 @@
       </c>
       <c r="L1039" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1039" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1039" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1039" t="n">
@@ -86436,17 +85688,6 @@
       <c r="P1039" t="n">
         <v>-77.10558</v>
       </c>
-      <c r="Q1039" t="n">
-        <v>-12.0596747</v>
-      </c>
-      <c r="R1039" t="n">
-        <v>-77.10685359999999</v>
-      </c>
-      <c r="S1039" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
@@ -87156,17 +86397,17 @@
       </c>
       <c r="L1048" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1048" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1048" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1048" t="n">
@@ -87175,17 +86416,6 @@
       <c r="P1048" t="n">
         <v>-77.11721</v>
       </c>
-      <c r="Q1048" t="n">
-        <v>-12.0596747</v>
-      </c>
-      <c r="R1048" t="n">
-        <v>-77.10685359999999</v>
-      </c>
-      <c r="S1048" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
@@ -88167,17 +87397,17 @@
       </c>
       <c r="L1060" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1060" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1060" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1060" t="n">
@@ -88186,17 +87416,6 @@
       <c r="P1060" t="n">
         <v>-76.99755</v>
       </c>
-      <c r="Q1060" t="n">
-        <v>-12.1699952</v>
-      </c>
-      <c r="R1060" t="n">
-        <v>-76.9998702</v>
-      </c>
-      <c r="S1060" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
@@ -89488,17 +88707,17 @@
       </c>
       <c r="L1076" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1076" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1076" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1076" t="n">
@@ -89507,17 +88726,6 @@
       <c r="P1076" t="n">
         <v>-77.09353</v>
       </c>
-      <c r="Q1076" t="n">
-        <v>-12.0632387</v>
-      </c>
-      <c r="R1076" t="n">
-        <v>-77.1171495</v>
-      </c>
-      <c r="S1076" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
@@ -89662,17 +88870,17 @@
       </c>
       <c r="L1078" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1078" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1078" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1078" t="n">
@@ -89681,17 +88889,6 @@
       <c r="P1078" t="n">
         <v>-76.99807</v>
       </c>
-      <c r="Q1078" t="n">
-        <v>-12.170565</v>
-      </c>
-      <c r="R1078" t="n">
-        <v>-76.9982428</v>
-      </c>
-      <c r="S1078" t="inlineStr">
-        <is>
-          <t>PARTIDA</t>
-        </is>
-      </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
@@ -90945,17 +90142,17 @@
       </c>
       <c r="L1093" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1093" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1093" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1093" t="n">
@@ -90964,17 +90161,6 @@
       <c r="P1093" t="n">
         <v>-76.99793</v>
       </c>
-      <c r="Q1093" t="n">
-        <v>-12.1080578</v>
-      </c>
-      <c r="R1093" t="n">
-        <v>-76.9781351</v>
-      </c>
-      <c r="S1093" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
-      </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
@@ -94892,17 +94078,17 @@
       </c>
       <c r="L1140" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1140" t="inlineStr">
         <is>
-          <t>CONECTADO</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1140" t="inlineStr">
         <is>
-          <t>ENTREGADO</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1140" t="n">
@@ -94910,17 +94096,6 @@
       </c>
       <c r="P1140" t="n">
         <v>-76.99563000000001</v>
-      </c>
-      <c r="Q1140" t="n">
-        <v>-12.1699952</v>
-      </c>
-      <c r="R1140" t="n">
-        <v>-76.9998702</v>
-      </c>
-      <c r="S1140" t="inlineStr">
-        <is>
-          <t>LLEGADA</t>
-        </is>
       </c>
     </row>
     <row r="1141">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -7932,7 +7932,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -27345,7 +27345,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -29052,7 +29052,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -50517,7 +50517,7 @@
       </c>
       <c r="M592" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N592" t="inlineStr">
@@ -50604,7 +50604,7 @@
       </c>
       <c r="M593" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N593" t="inlineStr">
@@ -58212,7 +58212,7 @@
       </c>
       <c r="M686" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N686" t="inlineStr">
@@ -58473,7 +58473,7 @@
       </c>
       <c r="M689" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N689" t="inlineStr">
@@ -59071,7 +59071,7 @@
       </c>
       <c r="M696" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N696" t="inlineStr">
@@ -61708,7 +61708,7 @@
       </c>
       <c r="M727" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N727" t="inlineStr">
@@ -63502,7 +63502,7 @@
       </c>
       <c r="M748" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N748" t="inlineStr">
@@ -73411,7 +73411,7 @@
       </c>
       <c r="M864" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N864" t="inlineStr">
@@ -74526,7 +74526,7 @@
       </c>
       <c r="M877" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N877" t="inlineStr">
@@ -82264,7 +82264,7 @@
       </c>
       <c r="M967" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N967" t="inlineStr">
@@ -85728,7 +85728,7 @@
       </c>
       <c r="M1007" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1007" t="inlineStr">
@@ -89442,7 +89442,7 @@
       </c>
       <c r="M1050" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1050" t="inlineStr">
@@ -95301,7 +95301,7 @@
       </c>
       <c r="M1118" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1118" t="inlineStr">
@@ -95388,7 +95388,7 @@
       </c>
       <c r="M1119" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1119" t="inlineStr">
@@ -95986,7 +95986,7 @@
       </c>
       <c r="M1126" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1126" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -11723,7 +11723,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -22704,7 +22704,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -27258,7 +27258,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -32241,7 +32241,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -36878,7 +36878,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -41706,7 +41706,7 @@
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O488" t="n">
@@ -46922,7 +46922,7 @@
       </c>
       <c r="M550" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N550" t="inlineStr">
@@ -47270,7 +47270,7 @@
       </c>
       <c r="M554" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N554" t="inlineStr">
@@ -60528,7 +60528,7 @@
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N713" t="inlineStr">
@@ -61284,7 +61284,7 @@
       </c>
       <c r="M722" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N722" t="inlineStr">
@@ -62317,7 +62317,7 @@
       </c>
       <c r="M734" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N734" t="inlineStr">
@@ -67330,7 +67330,7 @@
       </c>
       <c r="M793" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N793" t="inlineStr">
@@ -67417,7 +67417,7 @@
       </c>
       <c r="M794" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N794" t="inlineStr">
@@ -71181,7 +71181,7 @@
       </c>
       <c r="M838" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N838" t="inlineStr">
@@ -71268,7 +71268,7 @@
       </c>
       <c r="M839" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N839" t="inlineStr">
@@ -72889,7 +72889,7 @@
       </c>
       <c r="M858" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N858" t="inlineStr">
@@ -89790,7 +89790,7 @@
       </c>
       <c r="M1054" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1054" t="inlineStr">
@@ -90138,7 +90138,7 @@
       </c>
       <c r="M1058" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1058" t="inlineStr">
@@ -90225,7 +90225,7 @@
       </c>
       <c r="M1059" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1059" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4006,7 +4006,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -23139,7 +23139,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -24847,7 +24847,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -39053,7 +39053,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -43299,7 +43299,7 @@
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N507" t="inlineStr">
@@ -52811,7 +52811,7 @@
       </c>
       <c r="M619" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N619" t="inlineStr">
@@ -53072,7 +53072,7 @@
       </c>
       <c r="M622" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N622" t="inlineStr">
@@ -59495,7 +59495,7 @@
       </c>
       <c r="M701" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N701" t="inlineStr">
@@ -60615,7 +60615,7 @@
       </c>
       <c r="M714" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N714" t="inlineStr">
@@ -62404,7 +62404,7 @@
       </c>
       <c r="M735" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N735" t="inlineStr">
@@ -62491,7 +62491,7 @@
       </c>
       <c r="M736" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N736" t="inlineStr">
@@ -66813,7 +66813,7 @@
       </c>
       <c r="M787" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N787" t="inlineStr">
@@ -68543,7 +68543,7 @@
       </c>
       <c r="M807" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N807" t="inlineStr">
@@ -71529,7 +71529,7 @@
       </c>
       <c r="M842" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N842" t="inlineStr">
@@ -73672,7 +73672,7 @@
       </c>
       <c r="M867" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N867" t="inlineStr">
@@ -82177,7 +82177,7 @@
       </c>
       <c r="M966" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N966" t="inlineStr">
@@ -83656,7 +83656,7 @@
       </c>
       <c r="M983" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N983" t="inlineStr">
@@ -85130,7 +85130,7 @@
       </c>
       <c r="M1000" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1000" t="inlineStr">
@@ -87539,7 +87539,7 @@
       </c>
       <c r="M1028" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1028" t="inlineStr">
@@ -87702,7 +87702,7 @@
       </c>
       <c r="M1030" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1030" t="inlineStr">
@@ -89355,7 +89355,7 @@
       </c>
       <c r="M1049" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1049" t="inlineStr">
@@ -89703,7 +89703,7 @@
       </c>
       <c r="M1053" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1053" t="inlineStr">
@@ -93245,7 +93245,7 @@
       </c>
       <c r="M1094" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1094" t="inlineStr">
@@ -94023,7 +94023,7 @@
       </c>
       <c r="M1103" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1103" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3832,7 +3832,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -19022,7 +19022,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -20055,7 +20055,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -26246,7 +26246,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -28628,7 +28628,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -29220,7 +29220,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O339" t="n">
@@ -31306,7 +31306,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -37144,7 +37144,7 @@
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O435" t="n">
@@ -40336,7 +40336,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -42136,7 +42136,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -43968,7 +43968,7 @@
       </c>
       <c r="M515" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N515" t="inlineStr">
@@ -44479,7 +44479,7 @@
       </c>
       <c r="M521" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N521" t="inlineStr">
@@ -45403,7 +45403,7 @@
       </c>
       <c r="M532" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N532" t="inlineStr">
@@ -47531,7 +47531,7 @@
       </c>
       <c r="M557" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N557" t="inlineStr">
@@ -51365,7 +51365,7 @@
       </c>
       <c r="M602" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N602" t="inlineStr">
@@ -62143,7 +62143,7 @@
       </c>
       <c r="M732" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N732" t="inlineStr">
@@ -63415,7 +63415,7 @@
       </c>
       <c r="M747" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N747" t="inlineStr">
@@ -64165,7 +64165,7 @@
       </c>
       <c r="M756" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N756" t="inlineStr">
@@ -75744,7 +75744,7 @@
       </c>
       <c r="M891" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N891" t="inlineStr">
@@ -76685,7 +76685,7 @@
       </c>
       <c r="M902" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N902" t="inlineStr">
@@ -77544,7 +77544,7 @@
       </c>
       <c r="M912" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N912" t="inlineStr">
@@ -84091,7 +84091,7 @@
       </c>
       <c r="M988" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N988" t="inlineStr">
@@ -87789,7 +87789,7 @@
       </c>
       <c r="M1031" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1031" t="inlineStr">
@@ -90834,7 +90834,7 @@
       </c>
       <c r="M1066" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1066" t="inlineStr">
@@ -92559,7 +92559,7 @@
       </c>
       <c r="M1086" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1086" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -7497,7 +7497,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -28367,7 +28367,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -34741,7 +34741,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -35002,7 +35002,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -40423,7 +40423,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -46661,7 +46661,7 @@
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N547" t="inlineStr">
@@ -47792,7 +47792,7 @@
       </c>
       <c r="M560" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N560" t="inlineStr">
@@ -47966,7 +47966,7 @@
       </c>
       <c r="M562" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N562" t="inlineStr">
@@ -52039,7 +52039,7 @@
       </c>
       <c r="M610" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N610" t="inlineStr">
@@ -59930,7 +59930,7 @@
       </c>
       <c r="M706" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N706" t="inlineStr">
@@ -61458,7 +61458,7 @@
       </c>
       <c r="M724" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N724" t="inlineStr">
@@ -68200,7 +68200,7 @@
       </c>
       <c r="M803" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N803" t="inlineStr">
@@ -85048,7 +85048,7 @@
       </c>
       <c r="N999" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O999" t="n">
@@ -86337,7 +86337,7 @@
       </c>
       <c r="M1014" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1014" t="inlineStr">
@@ -88920,7 +88920,7 @@
       </c>
       <c r="M1044" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1044" t="inlineStr">
@@ -91868,7 +91868,7 @@
       </c>
       <c r="M1078" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1078" t="inlineStr">
@@ -92303,7 +92303,7 @@
       </c>
       <c r="N1083" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1083" t="n">
@@ -94605,7 +94605,7 @@
       </c>
       <c r="M1110" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1110" t="inlineStr">
@@ -95214,7 +95214,7 @@
       </c>
       <c r="M1117" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1117" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -6061,7 +6061,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -17297,7 +17297,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -17727,7 +17727,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -19446,7 +19446,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -25108,7 +25108,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -26333,7 +26333,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -28802,7 +28802,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -29634,7 +29634,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -29721,7 +29721,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -30145,7 +30145,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -30958,7 +30958,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -32154,7 +32154,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -33438,7 +33438,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -33612,7 +33612,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -34567,7 +34567,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -36965,7 +36965,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -37487,7 +37487,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -38096,7 +38096,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -38357,7 +38357,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -40162,7 +40162,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -40597,7 +40597,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -40934,7 +40934,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -42473,7 +42473,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -44653,7 +44653,7 @@
       </c>
       <c r="M523" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N523" t="inlineStr">
@@ -45664,7 +45664,7 @@
       </c>
       <c r="M535" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N535" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="M548" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N548" t="inlineStr">
@@ -47705,7 +47705,7 @@
       </c>
       <c r="M559" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N559" t="inlineStr">
@@ -48989,12 +48989,12 @@
       </c>
       <c r="M574" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N574" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O574" t="n">
@@ -49734,7 +49734,7 @@
       </c>
       <c r="M583" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N583" t="inlineStr">
@@ -51452,7 +51452,7 @@
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N603" t="inlineStr">
@@ -51800,7 +51800,7 @@
       </c>
       <c r="M607" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N607" t="inlineStr">
@@ -53594,7 +53594,7 @@
       </c>
       <c r="M628" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N628" t="inlineStr">
@@ -56659,7 +56659,7 @@
       </c>
       <c r="M666" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N666" t="inlineStr">
@@ -57007,7 +57007,7 @@
       </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N670" t="inlineStr">
@@ -57094,7 +57094,7 @@
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N671" t="inlineStr">
@@ -58984,7 +58984,7 @@
       </c>
       <c r="M695" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N695" t="inlineStr">
@@ -59582,7 +59582,7 @@
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N702" t="inlineStr">
@@ -59669,7 +59669,7 @@
       </c>
       <c r="M703" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N703" t="inlineStr">
@@ -60104,7 +60104,7 @@
       </c>
       <c r="M708" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N708" t="inlineStr">
@@ -61023,7 +61023,7 @@
       </c>
       <c r="M719" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N719" t="inlineStr">
@@ -64948,7 +64948,7 @@
       </c>
       <c r="M765" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N765" t="inlineStr">
@@ -65209,7 +65209,7 @@
       </c>
       <c r="M768" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N768" t="inlineStr">
@@ -66726,7 +66726,7 @@
       </c>
       <c r="M786" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N786" t="inlineStr">
@@ -66982,7 +66982,7 @@
       </c>
       <c r="M789" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N789" t="inlineStr">
@@ -69577,7 +69577,7 @@
       </c>
       <c r="M819" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N819" t="inlineStr">
@@ -70257,7 +70257,7 @@
       </c>
       <c r="M827" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N827" t="inlineStr">
@@ -73498,7 +73498,7 @@
       </c>
       <c r="M865" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N865" t="inlineStr">
@@ -78403,7 +78403,7 @@
       </c>
       <c r="M922" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N922" t="inlineStr">
@@ -80099,7 +80099,7 @@
       </c>
       <c r="M942" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N942" t="inlineStr">
@@ -82873,7 +82873,7 @@
       </c>
       <c r="M974" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N974" t="inlineStr">
@@ -82960,7 +82960,7 @@
       </c>
       <c r="M975" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N975" t="inlineStr">
@@ -83743,7 +83743,7 @@
       </c>
       <c r="M984" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N984" t="inlineStr">
@@ -88746,7 +88746,7 @@
       </c>
       <c r="M1042" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1042" t="inlineStr">
@@ -89529,7 +89529,7 @@
       </c>
       <c r="M1051" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1051" t="inlineStr">
@@ -90051,7 +90051,7 @@
       </c>
       <c r="M1057" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1057" t="inlineStr">
@@ -90399,7 +90399,7 @@
       </c>
       <c r="M1061" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1061" t="inlineStr">
@@ -90486,7 +90486,7 @@
       </c>
       <c r="M1062" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1062" t="inlineStr">
@@ -90747,7 +90747,7 @@
       </c>
       <c r="M1065" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1065" t="inlineStr">
@@ -91008,7 +91008,7 @@
       </c>
       <c r="M1068" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1068" t="inlineStr">
@@ -91356,7 +91356,7 @@
       </c>
       <c r="M1072" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1072" t="inlineStr">
@@ -92810,7 +92810,7 @@
       </c>
       <c r="M1089" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1089" t="inlineStr">
@@ -94518,7 +94518,7 @@
       </c>
       <c r="M1109" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1109" t="inlineStr">
@@ -94866,7 +94866,7 @@
       </c>
       <c r="M1113" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1113" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -6322,7 +6322,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -26083,7 +26083,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -26420,7 +26420,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -26997,7 +26997,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -32415,7 +32415,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -35339,7 +35339,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -38183,7 +38183,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -39988,7 +39988,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -41614,7 +41614,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -45920,7 +45920,7 @@
       </c>
       <c r="M538" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N538" t="inlineStr">
@@ -48467,7 +48467,7 @@
       </c>
       <c r="M568" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N568" t="inlineStr">
@@ -50082,7 +50082,7 @@
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N587" t="inlineStr">
@@ -50256,7 +50256,7 @@
       </c>
       <c r="M589" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N589" t="inlineStr">
@@ -50691,7 +50691,7 @@
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N594" t="inlineStr">
@@ -53246,7 +53246,7 @@
       </c>
       <c r="M624" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N624" t="inlineStr">
@@ -54426,7 +54426,7 @@
       </c>
       <c r="M638" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N638" t="inlineStr">
@@ -54579,7 +54579,7 @@
       </c>
       <c r="M640" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N640" t="inlineStr">
@@ -54732,7 +54732,7 @@
       </c>
       <c r="M642" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N642" t="inlineStr">
@@ -55027,7 +55027,7 @@
       </c>
       <c r="M646" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N646" t="inlineStr">
@@ -55109,7 +55109,7 @@
       </c>
       <c r="M647" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N647" t="inlineStr">
@@ -55191,7 +55191,7 @@
       </c>
       <c r="M648" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N648" t="inlineStr">
@@ -55273,7 +55273,7 @@
       </c>
       <c r="M649" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N649" t="inlineStr">
@@ -55355,7 +55355,7 @@
       </c>
       <c r="M650" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N650" t="inlineStr">
@@ -55508,7 +55508,7 @@
       </c>
       <c r="M652" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N652" t="inlineStr">
@@ -55590,7 +55590,7 @@
       </c>
       <c r="M653" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N653" t="inlineStr">
@@ -55814,7 +55814,7 @@
       </c>
       <c r="M656" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N656" t="inlineStr">
@@ -55896,7 +55896,7 @@
       </c>
       <c r="M657" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N657" t="inlineStr">
@@ -55978,7 +55978,7 @@
       </c>
       <c r="M658" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N658" t="inlineStr">
@@ -56060,7 +56060,7 @@
       </c>
       <c r="M659" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N659" t="inlineStr">
@@ -56142,7 +56142,7 @@
       </c>
       <c r="M660" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N660" t="inlineStr">
@@ -56224,7 +56224,7 @@
       </c>
       <c r="M661" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N661" t="inlineStr">
@@ -56833,7 +56833,7 @@
       </c>
       <c r="M668" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N668" t="inlineStr">
@@ -61795,7 +61795,7 @@
       </c>
       <c r="M728" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N728" t="inlineStr">
@@ -65122,7 +65122,7 @@
       </c>
       <c r="M767" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N767" t="inlineStr">
@@ -66052,7 +66052,7 @@
       </c>
       <c r="M778" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N778" t="inlineStr">
@@ -67156,7 +67156,7 @@
       </c>
       <c r="M791" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N791" t="inlineStr">
@@ -67852,7 +67852,7 @@
       </c>
       <c r="M799" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N799" t="inlineStr">
@@ -72204,7 +72204,7 @@
       </c>
       <c r="M850" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N850" t="inlineStr">
@@ -72291,7 +72291,7 @@
       </c>
       <c r="M851" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N851" t="inlineStr">
@@ -72378,7 +72378,7 @@
       </c>
       <c r="M852" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N852" t="inlineStr">
@@ -72976,7 +72976,7 @@
       </c>
       <c r="M859" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N859" t="inlineStr">
@@ -74700,7 +74700,7 @@
       </c>
       <c r="M879" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N879" t="inlineStr">
@@ -75570,7 +75570,7 @@
       </c>
       <c r="M889" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N889" t="inlineStr">
@@ -76424,7 +76424,7 @@
       </c>
       <c r="M899" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N899" t="inlineStr">
@@ -77370,7 +77370,7 @@
       </c>
       <c r="M910" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N910" t="inlineStr">
@@ -80273,7 +80273,7 @@
       </c>
       <c r="M944" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N944" t="inlineStr">
@@ -82438,7 +82438,7 @@
       </c>
       <c r="M969" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N969" t="inlineStr">
@@ -82878,7 +82878,7 @@
       </c>
       <c r="N974" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O974" t="n">
@@ -82965,7 +82965,7 @@
       </c>
       <c r="N975" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O975" t="n">
@@ -85478,7 +85478,7 @@
       </c>
       <c r="M1004" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1004" t="inlineStr">
@@ -86685,7 +86685,7 @@
       </c>
       <c r="M1018" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1018" t="inlineStr">
@@ -87017,7 +87017,7 @@
       </c>
       <c r="M1022" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1022" t="inlineStr">
@@ -88050,7 +88050,7 @@
       </c>
       <c r="M1034" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1034" t="inlineStr">
@@ -88833,7 +88833,7 @@
       </c>
       <c r="M1043" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1043" t="inlineStr">
@@ -89616,7 +89616,7 @@
       </c>
       <c r="M1052" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1052" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1207,17 +1207,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1226,17 +1226,6 @@
       <c r="P9" t="n">
         <v>-77.00993</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-12.08737</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-77.00993</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7083,7 +7072,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O80" t="n">
@@ -10521,7 +10510,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O120" t="n">
@@ -14393,17 +14382,17 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O165" t="n">
@@ -14412,17 +14401,6 @@
       <c r="P165" t="n">
         <v>-76.99289</v>
       </c>
-      <c r="Q165" t="n">
-        <v>-12.06688</v>
-      </c>
-      <c r="R165" t="n">
-        <v>-76.99289</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14490,7 +14468,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O166" t="n">
@@ -17466,17 +17444,17 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O201" t="n">
@@ -17485,17 +17463,6 @@
       <c r="P201" t="n">
         <v>-77.02302</v>
       </c>
-      <c r="Q201" t="n">
-        <v>-12.0815</v>
-      </c>
-      <c r="R201" t="n">
-        <v>-77.02302</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -18582,17 +18549,17 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O214" t="n">
@@ -18601,17 +18568,6 @@
       <c r="P214" t="n">
         <v>-77.01217</v>
       </c>
-      <c r="Q214" t="n">
-        <v>-12.08802</v>
-      </c>
-      <c r="R214" t="n">
-        <v>-77.01217</v>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -23972,17 +23928,17 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O277" t="n">
@@ -23991,17 +23947,6 @@
       <c r="P277" t="n">
         <v>-77.00991</v>
       </c>
-      <c r="Q277" t="n">
-        <v>-12.08747</v>
-      </c>
-      <c r="R277" t="n">
-        <v>-77.00991</v>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -28188,17 +28133,17 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O327" t="n">
@@ -28207,17 +28152,6 @@
       <c r="P327" t="n">
         <v>-77.00452</v>
       </c>
-      <c r="Q327" t="n">
-        <v>-12.08392</v>
-      </c>
-      <c r="R327" t="n">
-        <v>-77.00452</v>
-      </c>
-      <c r="S327" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -29542,17 +29476,17 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O343" t="n">
@@ -29561,17 +29495,6 @@
       <c r="P343" t="n">
         <v>-77.02297</v>
       </c>
-      <c r="Q343" t="n">
-        <v>-12.08134</v>
-      </c>
-      <c r="R343" t="n">
-        <v>-77.02297</v>
-      </c>
-      <c r="S343" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -30866,17 +30789,17 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O360" t="n">
@@ -30885,17 +30808,6 @@
       <c r="P360" t="n">
         <v>-77.00749</v>
       </c>
-      <c r="Q360" t="n">
-        <v>-12.0844</v>
-      </c>
-      <c r="R360" t="n">
-        <v>-77.00749</v>
-      </c>
-      <c r="S360" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -31888,17 +31800,17 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O372" t="n">
@@ -31907,17 +31819,6 @@
       <c r="P372" t="n">
         <v>-77.01300000000001</v>
       </c>
-      <c r="Q372" t="n">
-        <v>-12.08877</v>
-      </c>
-      <c r="R372" t="n">
-        <v>-77.01300000000001</v>
-      </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -32323,17 +32224,17 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O377" t="n">
@@ -32342,17 +32243,6 @@
       <c r="P377" t="n">
         <v>-77.02305</v>
       </c>
-      <c r="Q377" t="n">
-        <v>-12.08015</v>
-      </c>
-      <c r="R377" t="n">
-        <v>-77.02305</v>
-      </c>
-      <c r="S377" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -32671,17 +32561,17 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O381" t="n">
@@ -32690,17 +32580,6 @@
       <c r="P381" t="n">
         <v>-77.00818</v>
       </c>
-      <c r="Q381" t="n">
-        <v>-12.07877</v>
-      </c>
-      <c r="R381" t="n">
-        <v>-77.00818</v>
-      </c>
-      <c r="S381" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -35942,7 +35821,7 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O421" t="n">
@@ -36362,17 +36241,17 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O426" t="n">
@@ -36381,17 +36260,6 @@
       <c r="P426" t="n">
         <v>-77.00418000000001</v>
       </c>
-      <c r="Q426" t="n">
-        <v>-12.08429</v>
-      </c>
-      <c r="R426" t="n">
-        <v>-77.00418000000001</v>
-      </c>
-      <c r="S426" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -36623,17 +36491,17 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O429" t="n">
@@ -36642,17 +36510,6 @@
       <c r="P429" t="n">
         <v>-77.01667</v>
       </c>
-      <c r="Q429" t="n">
-        <v>-12.08067</v>
-      </c>
-      <c r="R429" t="n">
-        <v>-77.01667</v>
-      </c>
-      <c r="S429" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -37569,17 +37426,17 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O440" t="n">
@@ -37588,17 +37445,6 @@
       <c r="P440" t="n">
         <v>-77.00411</v>
       </c>
-      <c r="Q440" t="n">
-        <v>-12.07975</v>
-      </c>
-      <c r="R440" t="n">
-        <v>-77.00411</v>
-      </c>
-      <c r="S440" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -38265,17 +38111,17 @@
       </c>
       <c r="L448" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O448" t="n">
@@ -38284,17 +38130,6 @@
       <c r="P448" t="n">
         <v>-77.00226000000001</v>
       </c>
-      <c r="Q448" t="n">
-        <v>-12.07811</v>
-      </c>
-      <c r="R448" t="n">
-        <v>-77.00226000000001</v>
-      </c>
-      <c r="S448" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -40679,17 +40514,17 @@
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O476" t="n">
@@ -40698,17 +40533,6 @@
       <c r="P476" t="n">
         <v>-77.01801</v>
       </c>
-      <c r="Q476" t="n">
-        <v>-12.08406</v>
-      </c>
-      <c r="R476" t="n">
-        <v>-77.01801</v>
-      </c>
-      <c r="S476" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -40766,17 +40590,17 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O477" t="n">
@@ -40785,17 +40609,6 @@
       <c r="P477" t="n">
         <v>-77.00617</v>
       </c>
-      <c r="Q477" t="n">
-        <v>-12.08138</v>
-      </c>
-      <c r="R477" t="n">
-        <v>-77.00617</v>
-      </c>
-      <c r="S477" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -44985,17 +44798,17 @@
       </c>
       <c r="L527" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M527" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N527" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O527" t="n">
@@ -45004,17 +44817,6 @@
       <c r="P527" t="n">
         <v>-76.99309</v>
       </c>
-      <c r="Q527" t="n">
-        <v>-12.07172</v>
-      </c>
-      <c r="R527" t="n">
-        <v>-76.99309</v>
-      </c>
-      <c r="S527" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -45833,17 +45635,17 @@
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M537" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N537" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O537" t="n">
@@ -45852,17 +45654,6 @@
       <c r="P537" t="n">
         <v>-77.00461</v>
       </c>
-      <c r="Q537" t="n">
-        <v>-12.08394</v>
-      </c>
-      <c r="R537" t="n">
-        <v>-77.00461</v>
-      </c>
-      <c r="S537" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -46830,17 +46621,17 @@
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M549" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N549" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O549" t="n">
@@ -46849,17 +46640,6 @@
       <c r="P549" t="n">
         <v>-77.00866000000001</v>
       </c>
-      <c r="Q549" t="n">
-        <v>-12.0877</v>
-      </c>
-      <c r="R549" t="n">
-        <v>-77.00866000000001</v>
-      </c>
-      <c r="S549" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -47091,17 +46871,17 @@
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M552" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N552" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O552" t="n">
@@ -47110,17 +46890,6 @@
       <c r="P552" t="n">
         <v>-77.00691</v>
       </c>
-      <c r="Q552" t="n">
-        <v>-12.0767</v>
-      </c>
-      <c r="R552" t="n">
-        <v>-77.00691</v>
-      </c>
-      <c r="S552" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -49327,17 +49096,17 @@
       </c>
       <c r="L578" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M578" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N578" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O578" t="n">
@@ -49346,17 +49115,6 @@
       <c r="P578" t="n">
         <v>-77.02043999999999</v>
       </c>
-      <c r="Q578" t="n">
-        <v>-12.07816</v>
-      </c>
-      <c r="R578" t="n">
-        <v>-77.02043999999999</v>
-      </c>
-      <c r="S578" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -49642,17 +49400,17 @@
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M582" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N582" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O582" t="n">
@@ -49661,17 +49419,6 @@
       <c r="P582" t="n">
         <v>-77.00020000000001</v>
       </c>
-      <c r="Q582" t="n">
-        <v>-12.0769</v>
-      </c>
-      <c r="R582" t="n">
-        <v>-77.00020000000001</v>
-      </c>
-      <c r="S582" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -51110,17 +50857,17 @@
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O599" t="n">
@@ -51129,17 +50876,6 @@
       <c r="P599" t="n">
         <v>-77.01769</v>
       </c>
-      <c r="Q599" t="n">
-        <v>-12.08091</v>
-      </c>
-      <c r="R599" t="n">
-        <v>-77.01769</v>
-      </c>
-      <c r="S599" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -58294,17 +58030,17 @@
       </c>
       <c r="L687" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M687" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O687" t="n">
@@ -58313,17 +58049,6 @@
       <c r="P687" t="n">
         <v>-77.02009</v>
       </c>
-      <c r="Q687" t="n">
-        <v>-12.08897</v>
-      </c>
-      <c r="R687" t="n">
-        <v>-77.02009</v>
-      </c>
-      <c r="S687" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -59240,17 +58965,17 @@
       </c>
       <c r="L698" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M698" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N698" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O698" t="n">
@@ -59259,17 +58984,6 @@
       <c r="P698" t="n">
         <v>-77.00734</v>
       </c>
-      <c r="Q698" t="n">
-        <v>-12.07936</v>
-      </c>
-      <c r="R698" t="n">
-        <v>-77.00734</v>
-      </c>
-      <c r="S698" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -60262,17 +59976,17 @@
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N710" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O710" t="n">
@@ -60281,17 +59995,6 @@
       <c r="P710" t="n">
         <v>-77.00385</v>
       </c>
-      <c r="Q710" t="n">
-        <v>-12.07676</v>
-      </c>
-      <c r="R710" t="n">
-        <v>-77.00385</v>
-      </c>
-      <c r="S710" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -62235,7 +61938,7 @@
       </c>
       <c r="N733" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O733" t="n">
@@ -64595,17 +64298,17 @@
       </c>
       <c r="L761" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M761" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N761" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O761" t="n">
@@ -64614,17 +64317,6 @@
       <c r="P761" t="n">
         <v>-77.00476999999999</v>
       </c>
-      <c r="Q761" t="n">
-        <v>-12.08443</v>
-      </c>
-      <c r="R761" t="n">
-        <v>-77.00476999999999</v>
-      </c>
-      <c r="S761" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -69229,17 +68921,17 @@
       </c>
       <c r="L815" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M815" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N815" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O815" t="n">
@@ -69248,17 +68940,6 @@
       <c r="P815" t="n">
         <v>-77.02007999999999</v>
       </c>
-      <c r="Q815" t="n">
-        <v>-12.08901</v>
-      </c>
-      <c r="R815" t="n">
-        <v>-77.02007999999999</v>
-      </c>
-      <c r="S815" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -72460,17 +72141,17 @@
       </c>
       <c r="L853" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M853" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N853" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O853" t="n">
@@ -72479,17 +72160,6 @@
       <c r="P853" t="n">
         <v>-77.04507</v>
       </c>
-      <c r="Q853" t="n">
-        <v>-12.03313</v>
-      </c>
-      <c r="R853" t="n">
-        <v>-77.04507</v>
-      </c>
-      <c r="S853" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -78408,7 +78078,7 @@
       </c>
       <c r="N922" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O922" t="n">
@@ -79170,17 +78840,17 @@
       </c>
       <c r="L931" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M931" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N931" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O931" t="n">
@@ -79189,17 +78859,6 @@
       <c r="P931" t="n">
         <v>-77.00830000000001</v>
       </c>
-      <c r="Q931" t="n">
-        <v>-12.08218</v>
-      </c>
-      <c r="R931" t="n">
-        <v>-77.00830000000001</v>
-      </c>
-      <c r="S931" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
@@ -83912,17 +83571,17 @@
       </c>
       <c r="L986" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M986" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N986" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O986" t="n">
@@ -83931,17 +83590,6 @@
       <c r="P986" t="n">
         <v>-77.00483</v>
       </c>
-      <c r="Q986" t="n">
-        <v>-12.07629</v>
-      </c>
-      <c r="R986" t="n">
-        <v>-77.00483</v>
-      </c>
-      <c r="S986" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
@@ -84434,17 +84082,17 @@
       </c>
       <c r="L992" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M992" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N992" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O992" t="n">
@@ -84453,17 +84101,6 @@
       <c r="P992" t="n">
         <v>-77.00042999999999</v>
       </c>
-      <c r="Q992" t="n">
-        <v>-12.07683</v>
-      </c>
-      <c r="R992" t="n">
-        <v>-77.00042999999999</v>
-      </c>
-      <c r="S992" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
@@ -91704,7 +91341,7 @@
       </c>
       <c r="N1076" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1076" t="n">
@@ -92979,17 +92616,17 @@
       </c>
       <c r="L1091" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1091" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1091" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1091" t="n">
@@ -92998,17 +92635,6 @@
       <c r="P1091" t="n">
         <v>-77.01428</v>
       </c>
-      <c r="Q1091" t="n">
-        <v>-12.07767</v>
-      </c>
-      <c r="R1091" t="n">
-        <v>-77.01428</v>
-      </c>
-      <c r="S1091" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
@@ -93757,17 +93383,17 @@
       </c>
       <c r="L1100" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1100" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1100" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1100" t="n">
@@ -93776,17 +93402,6 @@
       <c r="P1100" t="n">
         <v>-76.99200999999999</v>
       </c>
-      <c r="Q1100" t="n">
-        <v>-12.07845</v>
-      </c>
-      <c r="R1100" t="n">
-        <v>-76.99200999999999</v>
-      </c>
-      <c r="S1100" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
@@ -95644,17 +95259,17 @@
       </c>
       <c r="L1122" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1122" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1122" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1122" t="n">
@@ -95662,17 +95277,6 @@
       </c>
       <c r="P1122" t="n">
         <v>-77.00296</v>
-      </c>
-      <c r="Q1122" t="n">
-        <v>-12.07554</v>
-      </c>
-      <c r="R1122" t="n">
-        <v>-77.00296</v>
-      </c>
-      <c r="S1122" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
       </c>
     </row>
     <row r="1123">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4077,17 +4077,17 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -4096,17 +4096,6 @@
       <c r="P45" t="n">
         <v>-77.10357</v>
       </c>
-      <c r="Q45" t="n">
-        <v>-12.08084</v>
-      </c>
-      <c r="R45" t="n">
-        <v>-77.10357</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5800,7 +5789,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7655,17 +7644,17 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O87" t="n">
@@ -7674,17 +7663,6 @@
       <c r="P87" t="n">
         <v>-77.08365000000001</v>
       </c>
-      <c r="Q87" t="n">
-        <v>-12.07615</v>
-      </c>
-      <c r="R87" t="n">
-        <v>-77.08365000000001</v>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9569,7 +9547,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -10761,17 +10739,17 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O123" t="n">
@@ -10780,17 +10758,6 @@
       <c r="P123" t="n">
         <v>-77.10689000000001</v>
       </c>
-      <c r="Q123" t="n">
-        <v>-12.07752</v>
-      </c>
-      <c r="R123" t="n">
-        <v>-77.10689000000001</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10924,17 +10891,17 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -10943,17 +10910,6 @@
       <c r="P125" t="n">
         <v>-77.07767</v>
       </c>
-      <c r="Q125" t="n">
-        <v>-12.06563</v>
-      </c>
-      <c r="R125" t="n">
-        <v>-77.07767</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12229,17 +12185,17 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O140" t="n">
@@ -12248,17 +12204,6 @@
       <c r="P140" t="n">
         <v>-77.09137</v>
       </c>
-      <c r="Q140" t="n">
-        <v>-12.0786</v>
-      </c>
-      <c r="R140" t="n">
-        <v>-77.09137</v>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14208,17 +14153,17 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O163" t="n">
@@ -14227,17 +14172,6 @@
       <c r="P163" t="n">
         <v>-77.10714</v>
       </c>
-      <c r="Q163" t="n">
-        <v>-12.07675</v>
-      </c>
-      <c r="R163" t="n">
-        <v>-77.10714</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15204,17 +15138,17 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O175" t="n">
@@ -15223,17 +15157,6 @@
       <c r="P175" t="n">
         <v>-77.09225000000001</v>
       </c>
-      <c r="Q175" t="n">
-        <v>-12.07399</v>
-      </c>
-      <c r="R175" t="n">
-        <v>-77.09225000000001</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -16927,7 +16850,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -18211,7 +18134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -20604,17 +20527,17 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O238" t="n">
@@ -20623,17 +20546,6 @@
       <c r="P238" t="n">
         <v>-77.07472</v>
       </c>
-      <c r="Q238" t="n">
-        <v>-12.07748</v>
-      </c>
-      <c r="R238" t="n">
-        <v>-77.07472</v>
-      </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -20778,17 +20690,17 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O240" t="n">
@@ -20797,17 +20709,6 @@
       <c r="P240" t="n">
         <v>-77.10749</v>
       </c>
-      <c r="Q240" t="n">
-        <v>-12.07741</v>
-      </c>
-      <c r="R240" t="n">
-        <v>-77.10749</v>
-      </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -21566,7 +21467,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -22175,7 +22076,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -24265,17 +24166,17 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O281" t="n">
@@ -24284,17 +24185,6 @@
       <c r="P281" t="n">
         <v>-77.08498</v>
       </c>
-      <c r="Q281" t="n">
-        <v>-12.08418</v>
-      </c>
-      <c r="R281" t="n">
-        <v>-77.08498</v>
-      </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -27540,7 +27430,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -41601,7 +41491,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -44205,7 +44095,7 @@
       </c>
       <c r="M520" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N520" t="inlineStr">
@@ -47382,17 +47272,17 @@
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N558" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O558" t="n">
@@ -47401,17 +47291,6 @@
       <c r="P558" t="n">
         <v>-77.0852</v>
       </c>
-      <c r="Q558" t="n">
-        <v>-12.07735</v>
-      </c>
-      <c r="R558" t="n">
-        <v>-77.0852</v>
-      </c>
-      <c r="S558" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -48144,17 +48023,17 @@
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M567" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N567" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O567" t="n">
@@ -48163,17 +48042,6 @@
       <c r="P567" t="n">
         <v>-77.10238</v>
       </c>
-      <c r="Q567" t="n">
-        <v>-12.08164</v>
-      </c>
-      <c r="R567" t="n">
-        <v>-77.10238</v>
-      </c>
-      <c r="S567" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -49563,17 +49431,17 @@
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M584" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N584" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O584" t="n">
@@ -49582,17 +49450,6 @@
       <c r="P584" t="n">
         <v>-77.10504</v>
       </c>
-      <c r="Q584" t="n">
-        <v>-12.08005</v>
-      </c>
-      <c r="R584" t="n">
-        <v>-77.10504</v>
-      </c>
-      <c r="S584" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -58459,7 +58316,7 @@
       </c>
       <c r="M692" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N692" t="inlineStr">
@@ -59465,17 +59322,17 @@
       </c>
       <c r="L704" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M704" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N704" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O704" t="n">
@@ -59484,17 +59341,6 @@
       <c r="P704" t="n">
         <v>-77.10986</v>
       </c>
-      <c r="Q704" t="n">
-        <v>-12.07814</v>
-      </c>
-      <c r="R704" t="n">
-        <v>-77.10986</v>
-      </c>
-      <c r="S704" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -59823,7 +59669,7 @@
       </c>
       <c r="N708" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O708" t="n">
@@ -64374,17 +64220,17 @@
       </c>
       <c r="L762" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M762" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N762" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O762" t="n">
@@ -64393,17 +64239,6 @@
       <c r="P762" t="n">
         <v>-77.10257</v>
       </c>
-      <c r="Q762" t="n">
-        <v>-12.0754</v>
-      </c>
-      <c r="R762" t="n">
-        <v>-77.10257</v>
-      </c>
-      <c r="S762" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -64466,7 +64301,7 @@
       </c>
       <c r="M763" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N763" t="inlineStr">
@@ -65489,17 +65324,17 @@
       </c>
       <c r="L775" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M775" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N775" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O775" t="n">
@@ -65508,17 +65343,6 @@
       <c r="P775" t="n">
         <v>-77.10424999999999</v>
       </c>
-      <c r="Q775" t="n">
-        <v>-12.08244</v>
-      </c>
-      <c r="R775" t="n">
-        <v>-77.10424999999999</v>
-      </c>
-      <c r="S775" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -70020,17 +69844,17 @@
       </c>
       <c r="L828" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M828" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N828" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O828" t="n">
@@ -70039,17 +69863,6 @@
       <c r="P828" t="n">
         <v>-77.09690999999999</v>
       </c>
-      <c r="Q828" t="n">
-        <v>-12.08262</v>
-      </c>
-      <c r="R828" t="n">
-        <v>-77.09690999999999</v>
-      </c>
-      <c r="S828" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -72989,17 +72802,17 @@
       </c>
       <c r="L863" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M863" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N863" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O863" t="n">
@@ -73008,17 +72821,6 @@
       <c r="P863" t="n">
         <v>-77.10423</v>
       </c>
-      <c r="Q863" t="n">
-        <v>-12.07996</v>
-      </c>
-      <c r="R863" t="n">
-        <v>-77.10423</v>
-      </c>
-      <c r="S863" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -73434,7 +73236,7 @@
       </c>
       <c r="N868" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O868" t="n">
@@ -74887,17 +74689,17 @@
       </c>
       <c r="L885" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M885" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N885" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O885" t="n">
@@ -74906,17 +74708,6 @@
       <c r="P885" t="n">
         <v>-77.10286000000001</v>
       </c>
-      <c r="Q885" t="n">
-        <v>-12.07287</v>
-      </c>
-      <c r="R885" t="n">
-        <v>-77.10286000000001</v>
-      </c>
-      <c r="S885" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -74974,17 +74765,17 @@
       </c>
       <c r="L886" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M886" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N886" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O886" t="n">
@@ -74993,17 +74784,6 @@
       <c r="P886" t="n">
         <v>-77.10441</v>
       </c>
-      <c r="Q886" t="n">
-        <v>-12.08229</v>
-      </c>
-      <c r="R886" t="n">
-        <v>-77.10441</v>
-      </c>
-      <c r="S886" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -75583,17 +75363,17 @@
       </c>
       <c r="L893" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M893" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N893" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O893" t="n">
@@ -75602,17 +75382,6 @@
       <c r="P893" t="n">
         <v>-77.10702999999999</v>
       </c>
-      <c r="Q893" t="n">
-        <v>-12.07693</v>
-      </c>
-      <c r="R893" t="n">
-        <v>-77.10702999999999</v>
-      </c>
-      <c r="S893" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -76268,7 +76037,7 @@
       </c>
       <c r="M901" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N901" t="inlineStr">
@@ -76605,7 +76374,7 @@
       </c>
       <c r="M905" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N905" t="inlineStr">
@@ -77470,17 +77239,17 @@
       </c>
       <c r="L915" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M915" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N915" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O915" t="n">
@@ -77489,17 +77258,6 @@
       <c r="P915" t="n">
         <v>-77.10256</v>
       </c>
-      <c r="Q915" t="n">
-        <v>-12.07972</v>
-      </c>
-      <c r="R915" t="n">
-        <v>-77.10256</v>
-      </c>
-      <c r="S915" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
@@ -77731,17 +77489,17 @@
       </c>
       <c r="L918" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M918" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N918" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O918" t="n">
@@ -77750,17 +77508,6 @@
       <c r="P918" t="n">
         <v>-77.09225000000001</v>
       </c>
-      <c r="Q918" t="n">
-        <v>-12.07399</v>
-      </c>
-      <c r="R918" t="n">
-        <v>-77.09225000000001</v>
-      </c>
-      <c r="S918" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
@@ -78155,17 +77902,17 @@
       </c>
       <c r="L923" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M923" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N923" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O923" t="n">
@@ -78174,17 +77921,6 @@
       <c r="P923" t="n">
         <v>-77.08147</v>
       </c>
-      <c r="Q923" t="n">
-        <v>-12.08202</v>
-      </c>
-      <c r="R923" t="n">
-        <v>-77.08147</v>
-      </c>
-      <c r="S923" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
@@ -78329,17 +78065,17 @@
       </c>
       <c r="L925" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M925" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N925" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O925" t="n">
@@ -78348,17 +78084,6 @@
       <c r="P925" t="n">
         <v>-77.10612999999999</v>
       </c>
-      <c r="Q925" t="n">
-        <v>-12.08133</v>
-      </c>
-      <c r="R925" t="n">
-        <v>-77.10612999999999</v>
-      </c>
-      <c r="S925" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
@@ -80270,17 +79995,17 @@
       </c>
       <c r="L948" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M948" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N948" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O948" t="n">
@@ -80289,17 +80014,6 @@
       <c r="P948" t="n">
         <v>-77.08226999999999</v>
       </c>
-      <c r="Q948" t="n">
-        <v>-12.08099</v>
-      </c>
-      <c r="R948" t="n">
-        <v>-77.08226999999999</v>
-      </c>
-      <c r="S948" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
@@ -80439,17 +80153,17 @@
       </c>
       <c r="L950" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M950" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N950" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O950" t="n">
@@ -80458,17 +80172,6 @@
       <c r="P950" t="n">
         <v>-77.10048</v>
       </c>
-      <c r="Q950" t="n">
-        <v>-12.07571</v>
-      </c>
-      <c r="R950" t="n">
-        <v>-77.10048</v>
-      </c>
-      <c r="S950" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
@@ -81749,7 +81452,7 @@
       </c>
       <c r="M965" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N965" t="inlineStr">
@@ -82967,7 +82670,7 @@
       </c>
       <c r="M979" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N979" t="inlineStr">
@@ -84936,17 +84639,17 @@
       </c>
       <c r="L1002" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1002" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1002" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1002" t="n">
@@ -84955,17 +84658,6 @@
       <c r="P1002" t="n">
         <v>-77.10102000000001</v>
       </c>
-      <c r="Q1002" t="n">
-        <v>-12.0774</v>
-      </c>
-      <c r="R1002" t="n">
-        <v>-77.10102000000001</v>
-      </c>
-      <c r="S1002" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
@@ -88900,17 +88592,17 @@
       </c>
       <c r="L1048" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1048" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1048" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1048" t="n">
@@ -88919,17 +88611,6 @@
       <c r="P1048" t="n">
         <v>-77.1044</v>
       </c>
-      <c r="Q1048" t="n">
-        <v>-12.08234</v>
-      </c>
-      <c r="R1048" t="n">
-        <v>-77.1044</v>
-      </c>
-      <c r="S1048" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
@@ -89949,7 +89630,7 @@
       </c>
       <c r="M1060" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1060" t="inlineStr">
@@ -90292,17 +89973,17 @@
       </c>
       <c r="L1064" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1064" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1064" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1064" t="n">
@@ -90311,17 +89992,6 @@
       <c r="P1064" t="n">
         <v>-77.08602999999999</v>
       </c>
-      <c r="Q1064" t="n">
-        <v>-12.08106</v>
-      </c>
-      <c r="R1064" t="n">
-        <v>-77.08602999999999</v>
-      </c>
-      <c r="S1064" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
@@ -92022,7 +91692,7 @@
       </c>
       <c r="M1084" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1084" t="inlineStr">
@@ -93127,7 +92797,7 @@
       </c>
       <c r="M1097" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1097" t="inlineStr">
@@ -93720,17 +93390,17 @@
       </c>
       <c r="L1104" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1104" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1104" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1104" t="n">
@@ -93739,17 +93409,6 @@
       <c r="P1104" t="n">
         <v>-77.10800999999999</v>
       </c>
-      <c r="Q1104" t="n">
-        <v>-12.07707</v>
-      </c>
-      <c r="R1104" t="n">
-        <v>-77.10800999999999</v>
-      </c>
-      <c r="S1104" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
@@ -95498,17 +95157,17 @@
       </c>
       <c r="L1125" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1125" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1125" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1125" t="n">
@@ -95516,17 +95175,6 @@
       </c>
       <c r="P1125" t="n">
         <v>-77.09063</v>
-      </c>
-      <c r="Q1125" t="n">
-        <v>-12.08669</v>
-      </c>
-      <c r="R1125" t="n">
-        <v>-77.09063</v>
-      </c>
-      <c r="S1125" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
       </c>
     </row>
     <row r="1126">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -696,17 +696,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -715,17 +715,6 @@
       <c r="P3" t="n">
         <v>-77.01393</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-12.14636</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-77.01393</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4756,7 +4745,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4919,7 +4908,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5006,7 +4995,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5175,17 +5164,17 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O58" t="n">
@@ -5194,17 +5183,6 @@
       <c r="P58" t="n">
         <v>-77.01746</v>
       </c>
-      <c r="Q58" t="n">
-        <v>-12.14595</v>
-      </c>
-      <c r="R58" t="n">
-        <v>-77.01746</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5349,17 +5327,17 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O60" t="n">
@@ -5368,17 +5346,6 @@
       <c r="P60" t="n">
         <v>-77.02386</v>
       </c>
-      <c r="Q60" t="n">
-        <v>-12.14305</v>
-      </c>
-      <c r="R60" t="n">
-        <v>-77.02386</v>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5702,7 +5669,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6469,17 +6436,17 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O73" t="n">
@@ -6488,17 +6455,6 @@
       <c r="P73" t="n">
         <v>-77.01347</v>
       </c>
-      <c r="Q73" t="n">
-        <v>-12.14592</v>
-      </c>
-      <c r="R73" t="n">
-        <v>-77.01347</v>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7138,17 +7094,17 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -7157,17 +7113,6 @@
       <c r="P81" t="n">
         <v>-77.02047</v>
       </c>
-      <c r="Q81" t="n">
-        <v>-12.13699</v>
-      </c>
-      <c r="R81" t="n">
-        <v>-77.02047</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7725,7 +7670,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -7812,7 +7757,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -8242,7 +8187,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -8329,7 +8274,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -8498,17 +8443,17 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -8517,17 +8462,6 @@
       <c r="P97" t="n">
         <v>-77.01656</v>
       </c>
-      <c r="Q97" t="n">
-        <v>-12.14533</v>
-      </c>
-      <c r="R97" t="n">
-        <v>-77.01656</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8846,17 +8780,17 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O101" t="n">
@@ -8865,17 +8799,6 @@
       <c r="P101" t="n">
         <v>-77.02287</v>
       </c>
-      <c r="Q101" t="n">
-        <v>-12.14562</v>
-      </c>
-      <c r="R101" t="n">
-        <v>-77.02287</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11059,7 +10982,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -12440,7 +12363,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -13044,17 +12967,17 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O150" t="n">
@@ -13063,17 +12986,6 @@
       <c r="P150" t="n">
         <v>-77.01568</v>
       </c>
-      <c r="Q150" t="n">
-        <v>-12.14178</v>
-      </c>
-      <c r="R150" t="n">
-        <v>-77.01568</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15475,17 +15387,17 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O179" t="n">
@@ -15494,17 +15406,6 @@
       <c r="P179" t="n">
         <v>-77.01438</v>
       </c>
-      <c r="Q179" t="n">
-        <v>-12.13868</v>
-      </c>
-      <c r="R179" t="n">
-        <v>-77.01438</v>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15736,17 +15637,17 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O182" t="n">
@@ -15755,17 +15656,6 @@
       <c r="P182" t="n">
         <v>-77.01797999999999</v>
       </c>
-      <c r="Q182" t="n">
-        <v>-12.13947</v>
-      </c>
-      <c r="R182" t="n">
-        <v>-77.01797999999999</v>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -16252,7 +16142,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -16676,12 +16566,12 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O193" t="n">
@@ -17280,17 +17170,17 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O200" t="n">
@@ -17299,17 +17189,6 @@
       <c r="P200" t="n">
         <v>-77.02064</v>
       </c>
-      <c r="Q200" t="n">
-        <v>-12.13929</v>
-      </c>
-      <c r="R200" t="n">
-        <v>-77.02064</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -19499,7 +19378,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -19847,7 +19726,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -20021,7 +19900,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -20271,7 +20150,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -20940,17 +20819,17 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O243" t="n">
@@ -20959,17 +20838,6 @@
       <c r="P243" t="n">
         <v>-77.01356</v>
       </c>
-      <c r="Q243" t="n">
-        <v>-12.14598</v>
-      </c>
-      <c r="R243" t="n">
-        <v>-77.01356</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -21027,17 +20895,17 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O244" t="n">
@@ -21046,17 +20914,6 @@
       <c r="P244" t="n">
         <v>-77.01369</v>
       </c>
-      <c r="Q244" t="n">
-        <v>-12.1459</v>
-      </c>
-      <c r="R244" t="n">
-        <v>-77.01369</v>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -21815,7 +21672,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -21902,7 +21759,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -21989,7 +21846,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -23001,7 +22858,7 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O267" t="n">
@@ -25183,7 +25040,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -25270,7 +25127,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -26576,12 +26433,12 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O310" t="n">
@@ -26745,7 +26602,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -27849,17 +27706,17 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O325" t="n">
@@ -27868,17 +27725,6 @@
       <c r="P325" t="n">
         <v>-77.01631999999999</v>
       </c>
-      <c r="Q325" t="n">
-        <v>-12.14494</v>
-      </c>
-      <c r="R325" t="n">
-        <v>-77.01631999999999</v>
-      </c>
-      <c r="S325" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -28099,17 +27945,17 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O328" t="n">
@@ -28118,17 +27964,6 @@
       <c r="P328" t="n">
         <v>-77.02001</v>
       </c>
-      <c r="Q328" t="n">
-        <v>-12.14167</v>
-      </c>
-      <c r="R328" t="n">
-        <v>-77.02001</v>
-      </c>
-      <c r="S328" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -28789,7 +28624,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -29279,17 +29114,17 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O342" t="n">
@@ -29298,17 +29133,6 @@
       <c r="P342" t="n">
         <v>-77.01537999999999</v>
       </c>
-      <c r="Q342" t="n">
-        <v>-12.14707</v>
-      </c>
-      <c r="R342" t="n">
-        <v>-77.01537999999999</v>
-      </c>
-      <c r="S342" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -30847,7 +30671,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -30934,7 +30758,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -31277,17 +31101,17 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O367" t="n">
@@ -31296,17 +31120,6 @@
       <c r="P367" t="n">
         <v>-77.01656</v>
       </c>
-      <c r="Q367" t="n">
-        <v>-12.14533</v>
-      </c>
-      <c r="R367" t="n">
-        <v>-77.01656</v>
-      </c>
-      <c r="S367" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -31445,7 +31258,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -32869,7 +32682,7 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O386" t="n">
@@ -35271,7 +35084,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -36462,7 +36275,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -38517,7 +38330,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -38865,7 +38678,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -38952,7 +38765,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -39121,17 +38934,17 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O461" t="n">
@@ -39140,17 +38953,6 @@
       <c r="P461" t="n">
         <v>-77.01618000000001</v>
       </c>
-      <c r="Q461" t="n">
-        <v>-12.14219</v>
-      </c>
-      <c r="R461" t="n">
-        <v>-77.01618000000001</v>
-      </c>
-      <c r="S461" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -39218,7 +39020,7 @@
       </c>
       <c r="N462" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O462" t="n">
@@ -40719,17 +40521,17 @@
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O480" t="n">
@@ -40738,17 +40540,6 @@
       <c r="P480" t="n">
         <v>-77.01946</v>
       </c>
-      <c r="Q480" t="n">
-        <v>-12.14153</v>
-      </c>
-      <c r="R480" t="n">
-        <v>-77.01946</v>
-      </c>
-      <c r="S480" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -41665,7 +41456,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -41752,7 +41543,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -42508,17 +42299,17 @@
       </c>
       <c r="L501" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O501" t="n">
@@ -42527,17 +42318,6 @@
       <c r="P501" t="n">
         <v>-77.02133000000001</v>
       </c>
-      <c r="Q501" t="n">
-        <v>-12.1484</v>
-      </c>
-      <c r="R501" t="n">
-        <v>-77.02133000000001</v>
-      </c>
-      <c r="S501" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -43089,7 +42869,7 @@
       </c>
       <c r="M508" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N508" t="inlineStr">
@@ -43921,7 +43701,7 @@
       </c>
       <c r="M518" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N518" t="inlineStr">
@@ -44269,7 +44049,7 @@
       </c>
       <c r="M522" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N522" t="inlineStr">
@@ -44361,7 +44141,7 @@
       </c>
       <c r="N523" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O523" t="n">
@@ -44530,7 +44310,7 @@
       </c>
       <c r="M525" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N525" t="inlineStr">
@@ -44769,7 +44549,7 @@
       </c>
       <c r="M528" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N528" t="inlineStr">
@@ -45917,7 +45697,7 @@
       </c>
       <c r="M542" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N542" t="inlineStr">
@@ -46255,7 +46035,7 @@
       </c>
       <c r="M546" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N546" t="inlineStr">
@@ -47859,7 +47639,7 @@
       </c>
       <c r="M565" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N565" t="inlineStr">
@@ -48273,17 +48053,17 @@
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N570" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O570" t="n">
@@ -48292,17 +48072,6 @@
       <c r="P570" t="n">
         <v>-77.02200999999999</v>
       </c>
-      <c r="Q570" t="n">
-        <v>-12.14235</v>
-      </c>
-      <c r="R570" t="n">
-        <v>-77.02200999999999</v>
-      </c>
-      <c r="S570" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -48718,7 +48487,7 @@
       </c>
       <c r="N575" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O575" t="n">
@@ -50034,7 +49803,7 @@
       </c>
       <c r="M591" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N591" t="inlineStr">
@@ -50795,7 +50564,7 @@
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N600" t="inlineStr">
@@ -51127,17 +50896,17 @@
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M604" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O604" t="n">
@@ -51146,17 +50915,6 @@
       <c r="P604" t="n">
         <v>-77.01908</v>
       </c>
-      <c r="Q604" t="n">
-        <v>-12.13946</v>
-      </c>
-      <c r="R604" t="n">
-        <v>-77.01908</v>
-      </c>
-      <c r="S604" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -52230,7 +51988,7 @@
       </c>
       <c r="M617" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N617" t="inlineStr">
@@ -52926,7 +52684,7 @@
       </c>
       <c r="M625" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N625" t="inlineStr">
@@ -53513,7 +53271,7 @@
       </c>
       <c r="M632" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N632" t="inlineStr">
@@ -53600,7 +53358,7 @@
       </c>
       <c r="M633" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N633" t="inlineStr">
@@ -55899,17 +55657,17 @@
       </c>
       <c r="L662" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M662" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N662" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O662" t="n">
@@ -55918,17 +55676,6 @@
       <c r="P662" t="n">
         <v>-77.01773</v>
       </c>
-      <c r="Q662" t="n">
-        <v>-12.14574</v>
-      </c>
-      <c r="R662" t="n">
-        <v>-77.01773</v>
-      </c>
-      <c r="S662" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -56513,7 +56260,7 @@
       </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N669" t="inlineStr">
@@ -58403,7 +58150,7 @@
       </c>
       <c r="M693" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N693" t="inlineStr">
@@ -58735,17 +58482,17 @@
       </c>
       <c r="L697" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M697" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N697" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O697" t="n">
@@ -58754,17 +58501,6 @@
       <c r="P697" t="n">
         <v>-77.01767</v>
       </c>
-      <c r="Q697" t="n">
-        <v>-12.13771</v>
-      </c>
-      <c r="R697" t="n">
-        <v>-77.01767</v>
-      </c>
-      <c r="S697" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -59403,7 +59139,7 @@
       </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N705" t="inlineStr">
@@ -61431,7 +61167,7 @@
       </c>
       <c r="M729" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N729" t="inlineStr">
@@ -62725,7 +62461,7 @@
       </c>
       <c r="M744" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N744" t="inlineStr">
@@ -63801,7 +63537,7 @@
       </c>
       <c r="M757" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N757" t="inlineStr">
@@ -65155,12 +64891,12 @@
       </c>
       <c r="M773" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N773" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O773" t="n">
@@ -65237,17 +64973,17 @@
       </c>
       <c r="L774" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M774" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N774" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O774" t="n">
@@ -65256,17 +64992,6 @@
       <c r="P774" t="n">
         <v>-77.01566</v>
       </c>
-      <c r="Q774" t="n">
-        <v>-12.14169</v>
-      </c>
-      <c r="R774" t="n">
-        <v>-77.01566</v>
-      </c>
-      <c r="S774" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -66068,12 +65793,12 @@
       </c>
       <c r="M784" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N784" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O784" t="n">
@@ -66585,7 +66310,7 @@
       </c>
       <c r="M790" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N790" t="inlineStr">
@@ -67450,17 +67175,17 @@
       </c>
       <c r="L800" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M800" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N800" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O800" t="n">
@@ -67469,17 +67194,6 @@
       <c r="P800" t="n">
         <v>-77.01835</v>
       </c>
-      <c r="Q800" t="n">
-        <v>-12.14348</v>
-      </c>
-      <c r="R800" t="n">
-        <v>-77.01835</v>
-      </c>
-      <c r="S800" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -68571,17 +68285,17 @@
       </c>
       <c r="L813" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M813" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N813" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O813" t="n">
@@ -68590,17 +68304,6 @@
       <c r="P813" t="n">
         <v>-77.02464999999999</v>
       </c>
-      <c r="Q813" t="n">
-        <v>-12.13968</v>
-      </c>
-      <c r="R813" t="n">
-        <v>-77.02464999999999</v>
-      </c>
-      <c r="S813" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -68658,17 +68361,17 @@
       </c>
       <c r="L814" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M814" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N814" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O814" t="n">
@@ -68677,17 +68380,6 @@
       <c r="P814" t="n">
         <v>-77.02207</v>
       </c>
-      <c r="Q814" t="n">
-        <v>-12.14131</v>
-      </c>
-      <c r="R814" t="n">
-        <v>-77.02207</v>
-      </c>
-      <c r="S814" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -69087,7 +68779,7 @@
       </c>
       <c r="N819" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O819" t="n">
@@ -69920,17 +69612,17 @@
       </c>
       <c r="L829" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M829" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N829" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O829" t="n">
@@ -69939,17 +69631,6 @@
       <c r="P829" t="n">
         <v>-77.01576</v>
       </c>
-      <c r="Q829" t="n">
-        <v>-12.14194</v>
-      </c>
-      <c r="R829" t="n">
-        <v>-77.01576</v>
-      </c>
-      <c r="S829" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -70431,17 +70112,17 @@
       </c>
       <c r="L835" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M835" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N835" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O835" t="n">
@@ -70450,17 +70131,6 @@
       <c r="P835" t="n">
         <v>-77.02198</v>
       </c>
-      <c r="Q835" t="n">
-        <v>-12.13555</v>
-      </c>
-      <c r="R835" t="n">
-        <v>-77.02198</v>
-      </c>
-      <c r="S835" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -71279,7 +70949,7 @@
       </c>
       <c r="M845" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N845" t="inlineStr">
@@ -71530,17 +71200,17 @@
       </c>
       <c r="L848" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M848" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N848" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O848" t="n">
@@ -71549,17 +71219,6 @@
       <c r="P848" t="n">
         <v>-77.01918999999999</v>
       </c>
-      <c r="Q848" t="n">
-        <v>-12.13773</v>
-      </c>
-      <c r="R848" t="n">
-        <v>-77.01918999999999</v>
-      </c>
-      <c r="S848" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -72035,7 +71694,7 @@
       </c>
       <c r="M854" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N854" t="inlineStr">
@@ -73389,17 +73048,17 @@
       </c>
       <c r="L870" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M870" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N870" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O870" t="n">
@@ -73408,17 +73067,6 @@
       <c r="P870" t="n">
         <v>-77.02212</v>
       </c>
-      <c r="Q870" t="n">
-        <v>-12.14597</v>
-      </c>
-      <c r="R870" t="n">
-        <v>-77.02212</v>
-      </c>
-      <c r="S870" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -74259,7 +73907,7 @@
       </c>
       <c r="M880" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N880" t="inlineStr">
@@ -74607,7 +74255,7 @@
       </c>
       <c r="M884" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N884" t="inlineStr">
@@ -74928,17 +74576,17 @@
       </c>
       <c r="L888" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M888" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N888" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O888" t="n">
@@ -74947,17 +74595,6 @@
       <c r="P888" t="n">
         <v>-77.02077</v>
       </c>
-      <c r="Q888" t="n">
-        <v>-12.13767</v>
-      </c>
-      <c r="R888" t="n">
-        <v>-77.02077</v>
-      </c>
-      <c r="S888" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
@@ -75439,17 +75076,17 @@
       </c>
       <c r="L894" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M894" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N894" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O894" t="n">
@@ -75458,17 +75095,6 @@
       <c r="P894" t="n">
         <v>-77.01837</v>
       </c>
-      <c r="Q894" t="n">
-        <v>-12.14305</v>
-      </c>
-      <c r="R894" t="n">
-        <v>-77.01837</v>
-      </c>
-      <c r="S894" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -75526,17 +75152,17 @@
       </c>
       <c r="L895" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M895" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N895" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O895" t="n">
@@ -75545,17 +75171,6 @@
       <c r="P895" t="n">
         <v>-77.01568</v>
       </c>
-      <c r="Q895" t="n">
-        <v>-12.14178</v>
-      </c>
-      <c r="R895" t="n">
-        <v>-77.01568</v>
-      </c>
-      <c r="S895" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
@@ -76548,7 +76163,7 @@
       </c>
       <c r="M907" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N907" t="inlineStr">
@@ -77320,7 +76935,7 @@
       </c>
       <c r="M916" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N916" t="inlineStr">
@@ -78141,17 +77756,17 @@
       </c>
       <c r="L926" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M926" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N926" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O926" t="n">
@@ -78160,17 +77775,6 @@
       <c r="P926" t="n">
         <v>-77.02077</v>
       </c>
-      <c r="Q926" t="n">
-        <v>-12.13767</v>
-      </c>
-      <c r="R926" t="n">
-        <v>-77.02077</v>
-      </c>
-      <c r="S926" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
@@ -78396,7 +78000,7 @@
       </c>
       <c r="M929" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N929" t="inlineStr">
@@ -78804,17 +78408,17 @@
       </c>
       <c r="L934" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M934" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N934" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O934" t="n">
@@ -78823,17 +78427,6 @@
       <c r="P934" t="n">
         <v>-77.02065</v>
       </c>
-      <c r="Q934" t="n">
-        <v>-12.13786</v>
-      </c>
-      <c r="R934" t="n">
-        <v>-77.02065</v>
-      </c>
-      <c r="S934" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -78891,17 +78484,17 @@
       </c>
       <c r="L935" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M935" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N935" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O935" t="n">
@@ -78910,17 +78503,6 @@
       <c r="P935" t="n">
         <v>-77.02087</v>
       </c>
-      <c r="Q935" t="n">
-        <v>-12.13745</v>
-      </c>
-      <c r="R935" t="n">
-        <v>-77.02087</v>
-      </c>
-      <c r="S935" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -79831,7 +79413,7 @@
       </c>
       <c r="M946" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N946" t="inlineStr">
@@ -80076,7 +79658,7 @@
       </c>
       <c r="N949" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O949" t="n">
@@ -80234,7 +79816,7 @@
       </c>
       <c r="M951" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N951" t="inlineStr">
@@ -80582,7 +80164,7 @@
       </c>
       <c r="M955" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N955" t="inlineStr">
@@ -81104,7 +80686,7 @@
       </c>
       <c r="M961" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N961" t="inlineStr">
@@ -81365,12 +80947,12 @@
       </c>
       <c r="M964" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N964" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O964" t="n">
@@ -83529,7 +83111,7 @@
       </c>
       <c r="M989" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N989" t="inlineStr">
@@ -83611,17 +83193,17 @@
       </c>
       <c r="L990" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M990" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N990" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O990" t="n">
@@ -83630,17 +83212,6 @@
       <c r="P990" t="n">
         <v>-77.02198</v>
       </c>
-      <c r="Q990" t="n">
-        <v>-12.14103</v>
-      </c>
-      <c r="R990" t="n">
-        <v>-77.02198</v>
-      </c>
-      <c r="S990" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
@@ -83953,7 +83524,7 @@
       </c>
       <c r="M994" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N994" t="inlineStr">
@@ -84035,17 +83606,17 @@
       </c>
       <c r="L995" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M995" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N995" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O995" t="n">
@@ -84054,17 +83625,6 @@
       <c r="P995" t="n">
         <v>-77.02240999999999</v>
       </c>
-      <c r="Q995" t="n">
-        <v>-12.13723</v>
-      </c>
-      <c r="R995" t="n">
-        <v>-77.02240999999999</v>
-      </c>
-      <c r="S995" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
@@ -84557,7 +84117,7 @@
       </c>
       <c r="M1001" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1001" t="inlineStr">
@@ -85144,7 +84704,7 @@
       </c>
       <c r="M1008" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1008" t="inlineStr">
@@ -86602,17 +86162,17 @@
       </c>
       <c r="L1025" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1025" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1025" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1025" t="n">
@@ -86621,17 +86181,6 @@
       <c r="P1025" t="n">
         <v>-77.01566</v>
       </c>
-      <c r="Q1025" t="n">
-        <v>-12.14169</v>
-      </c>
-      <c r="R1025" t="n">
-        <v>-77.01566</v>
-      </c>
-      <c r="S1025" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
@@ -86781,7 +86330,7 @@
       </c>
       <c r="M1027" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1027" t="inlineStr">
@@ -87640,7 +87189,7 @@
       </c>
       <c r="M1037" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1037" t="inlineStr">
@@ -87727,7 +87276,7 @@
       </c>
       <c r="M1038" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1038" t="inlineStr">
@@ -87814,7 +87363,7 @@
       </c>
       <c r="M1039" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1039" t="inlineStr">
@@ -88336,7 +87885,7 @@
       </c>
       <c r="M1045" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1045" t="inlineStr">
@@ -88423,7 +87972,7 @@
       </c>
       <c r="M1046" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1046" t="inlineStr">
@@ -90402,7 +89951,7 @@
       </c>
       <c r="M1069" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1069" t="inlineStr">
@@ -90832,17 +90381,17 @@
       </c>
       <c r="L1074" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1074" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1074" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1074" t="n">
@@ -90851,17 +90400,6 @@
       <c r="P1074" t="n">
         <v>-77.02121</v>
       </c>
-      <c r="Q1074" t="n">
-        <v>-12.14803</v>
-      </c>
-      <c r="R1074" t="n">
-        <v>-77.02121</v>
-      </c>
-      <c r="S1074" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
@@ -91262,7 +90800,7 @@
       </c>
       <c r="M1079" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1079" t="inlineStr">
@@ -91349,12 +90887,12 @@
       </c>
       <c r="M1080" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1080" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1080" t="n">
@@ -92362,17 +91900,17 @@
       </c>
       <c r="L1092" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1092" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1092" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1092" t="n">
@@ -92381,17 +91919,6 @@
       <c r="P1092" t="n">
         <v>-77.01602</v>
       </c>
-      <c r="Q1092" t="n">
-        <v>-12.14362</v>
-      </c>
-      <c r="R1092" t="n">
-        <v>-77.01602</v>
-      </c>
-      <c r="S1092" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
@@ -94749,7 +94276,7 @@
       </c>
       <c r="M1120" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1120" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -749,12 +749,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5728,12 +5728,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -8496,12 +8496,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -13270,12 +13270,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -14118,12 +14118,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -14205,12 +14205,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>ROMAN MUÑOZ, ALEXIS ARTURO</t>
+          <t>CHIPANA QUISPE, CHRISTIAN ALONSO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>987 635 995</t>
+          <t>953 450 482</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -16712,12 +16712,12 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -16799,12 +16799,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -17223,12 +17223,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -17985,12 +17985,12 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -18328,12 +18328,12 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -18665,12 +18665,12 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -19176,12 +19176,12 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -19263,12 +19263,12 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -19524,12 +19524,12 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -20209,12 +20209,12 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -21035,12 +21035,12 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>939 147 798</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -21122,12 +21122,12 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DELGADO VELASQUEZ JOHN ANTHONY</t>
+          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>987 636 091</t>
+          <t>939 147 798</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -21296,12 +21296,12 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -21383,12 +21383,12 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -21905,12 +21905,12 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -23239,12 +23239,12 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -23326,12 +23326,12 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -23663,12 +23663,12 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -23826,12 +23826,12 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -24598,12 +24598,12 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -24772,12 +24772,12 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -25660,12 +25660,12 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -27259,12 +27259,12 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -27846,12 +27846,12 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -29167,12 +29167,12 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -29754,12 +29754,12 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -30480,12 +30480,12 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -30817,12 +30817,12 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -31480,12 +31480,12 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -31643,12 +31643,12 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -31904,12 +31904,12 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -32241,12 +32241,12 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -33166,12 +33166,12 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -34121,12 +34121,12 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -34208,12 +34208,12 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -35143,12 +35143,12 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -35578,12 +35578,12 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -35921,12 +35921,12 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -36171,12 +36171,12 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -36497,12 +36497,12 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -37106,12 +37106,12 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -37791,12 +37791,12 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -39661,12 +39661,12 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -40183,12 +40183,12 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -40259,12 +40259,12 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -40656,12 +40656,12 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -40743,12 +40743,12 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -41254,12 +41254,12 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -43847,12 +43847,12 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -44445,12 +44445,12 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>ROMAN MUÑOZ, ALEXIS ARTURO</t>
+          <t>CHIPANA QUISPE, CHRISTIAN ALONSO</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>987 635 995</t>
+          <t>953 450 482</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -45282,12 +45282,12 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -46181,12 +46181,12 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -46268,12 +46268,12 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -46431,12 +46431,12 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -46518,12 +46518,12 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -48710,12 +48710,12 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -49253,12 +49253,12 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -49688,12 +49688,12 @@
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -50123,12 +50123,12 @@
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -50460,12 +50460,12 @@
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -52221,12 +52221,12 @@
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -57611,12 +57611,12 @@
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -58035,12 +58035,12 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -58535,12 +58535,12 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -58948,12 +58948,12 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -59535,12 +59535,12 @@
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -63009,12 +63009,12 @@
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -63857,12 +63857,12 @@
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -64009,12 +64009,12 @@
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -65504,12 +65504,12 @@
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -65939,12 +65939,12 @@
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -66195,12 +66195,12 @@
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -67571,12 +67571,12 @@
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -68414,12 +68414,12 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -68996,12 +68996,12 @@
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
@@ -69426,12 +69426,12 @@
       </c>
       <c r="G827" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
@@ -71590,12 +71590,12 @@
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>ROMAN MUÑOZ, ALEXIS ARTURO</t>
+          <t>CHIPANA QUISPE, CHRISTIAN ALONSO</t>
         </is>
       </c>
       <c r="H853" t="inlineStr">
         <is>
-          <t>987 635 995</t>
+          <t>953 450 482</t>
         </is>
       </c>
       <c r="I853" t="inlineStr">
@@ -73357,12 +73357,12 @@
       </c>
       <c r="G874" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
@@ -73444,12 +73444,12 @@
       </c>
       <c r="G875" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I875" t="inlineStr">
@@ -74716,12 +74716,12 @@
       </c>
       <c r="G890" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -75624,12 +75624,12 @@
       </c>
       <c r="G901" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
@@ -75961,12 +75961,12 @@
       </c>
       <c r="G905" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
@@ -76309,12 +76309,12 @@
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -78146,12 +78146,12 @@
       </c>
       <c r="G931" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H931" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I931" t="inlineStr">
@@ -78863,12 +78863,12 @@
       </c>
       <c r="G940" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H940" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I940" t="inlineStr">
@@ -79298,12 +79298,12 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H945" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I945" t="inlineStr">
@@ -80310,12 +80310,12 @@
       </c>
       <c r="G957" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H957" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I957" t="inlineStr">
@@ -81006,12 +81006,12 @@
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I965" t="inlineStr">
@@ -81441,12 +81441,12 @@
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H970" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I970" t="inlineStr">
@@ -82224,12 +82224,12 @@
       </c>
       <c r="G979" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I979" t="inlineStr">
@@ -82659,12 +82659,12 @@
       </c>
       <c r="G984" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
@@ -82833,12 +82833,12 @@
       </c>
       <c r="G986" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H986" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I986" t="inlineStr">
@@ -83333,12 +83333,12 @@
       </c>
       <c r="G992" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H992" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I992" t="inlineStr">
@@ -83409,12 +83409,12 @@
       </c>
       <c r="G993" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H993" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I993" t="inlineStr">
@@ -85715,12 +85715,12 @@
       </c>
       <c r="G1020" t="inlineStr">
         <is>
-          <t>BOZA MARTINEZ, WILHELM ALFREDO KNOX</t>
+          <t>HUARANGA CHAVEZ STEVE ESTEFANO</t>
         </is>
       </c>
       <c r="H1020" t="inlineStr">
         <is>
-          <t>939 147 798</t>
+          <t>974060903</t>
         </is>
       </c>
       <c r="I1020" t="inlineStr">
@@ -86726,12 +86726,12 @@
       </c>
       <c r="G1032" t="inlineStr">
         <is>
-          <t>CHIROQUE FERNANDEZ HENRY JOEL</t>
+          <t>YATACO VALENZUELA, ROBERT</t>
         </is>
       </c>
       <c r="H1032" t="inlineStr">
         <is>
-          <t>974 060 557</t>
+          <t>987635902</t>
         </is>
       </c>
       <c r="I1032" t="inlineStr">
@@ -88890,12 +88890,12 @@
       </c>
       <c r="G1057" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1057" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1057" t="inlineStr">
@@ -89151,12 +89151,12 @@
       </c>
       <c r="G1060" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H1060" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I1060" t="inlineStr">
@@ -89238,12 +89238,12 @@
       </c>
       <c r="G1061" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1061" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1061" t="inlineStr">
@@ -89325,12 +89325,12 @@
       </c>
       <c r="G1062" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1062" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1062" t="inlineStr">
@@ -89575,12 +89575,12 @@
       </c>
       <c r="G1065" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1065" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1065" t="inlineStr">
@@ -89836,12 +89836,12 @@
       </c>
       <c r="G1068" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1068" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1068" t="inlineStr">
@@ -90184,12 +90184,12 @@
       </c>
       <c r="G1072" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1072" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1072" t="inlineStr">
@@ -91202,12 +91202,12 @@
       </c>
       <c r="G1084" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H1084" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I1084" t="inlineStr">
@@ -91627,12 +91627,12 @@
       </c>
       <c r="G1089" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1089" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1089" t="inlineStr">
@@ -91801,12 +91801,12 @@
       </c>
       <c r="G1091" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H1091" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I1091" t="inlineStr">
@@ -92296,12 +92296,12 @@
       </c>
       <c r="G1097" t="inlineStr">
         <is>
-          <t>YATACO VALENZUELA, ROBERT</t>
+          <t>MONTOYA CARRIZO JOSE DANIEL</t>
         </is>
       </c>
       <c r="H1097" t="inlineStr">
         <is>
-          <t>987635902</t>
+          <t>968 965 493</t>
         </is>
       </c>
       <c r="I1097" t="inlineStr">
@@ -92557,12 +92557,12 @@
       </c>
       <c r="G1100" t="inlineStr">
         <is>
-          <t>ROMAN MUÑOZ, ALEXIS ARTURO</t>
+          <t>CHIPANA QUISPE, CHRISTIAN ALONSO</t>
         </is>
       </c>
       <c r="H1100" t="inlineStr">
         <is>
-          <t>987 635 995</t>
+          <t>953 450 482</t>
         </is>
       </c>
       <c r="I1100" t="inlineStr">
@@ -93037,7 +93037,7 @@
       </c>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>CAN-838</t>
+          <t>CLP-822</t>
         </is>
       </c>
       <c r="D1106" t="inlineStr">
@@ -93639,12 +93639,12 @@
       </c>
       <c r="G1113" t="inlineStr">
         <is>
-          <t>CARI PEREZ, JUAN PABLO</t>
+          <t>GUERRERO CUETO, JEFFERSON PAOLO</t>
         </is>
       </c>
       <c r="H1113" t="inlineStr">
         <is>
-          <t>987 635 469</t>
+          <t>987 635 804</t>
         </is>
       </c>
       <c r="I1113" t="inlineStr">
@@ -94422,12 +94422,12 @@
       </c>
       <c r="G1122" t="inlineStr">
         <is>
-          <t>VELA MOZOMBITE NEYTON</t>
+          <t>VASQUEZ CANEVARO MARLON</t>
         </is>
       </c>
       <c r="H1122" t="inlineStr">
         <is>
-          <t>968 965 515</t>
+          <t>942635971</t>
         </is>
       </c>
       <c r="I1122" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3636,7 +3636,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -16229,7 +16229,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O292" t="n">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -32432,7 +32432,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -34062,7 +34062,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -36612,7 +36612,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -40444,7 +40444,7 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O479" t="n">
@@ -51564,7 +51564,7 @@
       </c>
       <c r="M612" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N612" t="inlineStr">
@@ -51830,7 +51830,7 @@
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O615" t="n">
@@ -53189,7 +53189,7 @@
       </c>
       <c r="N631" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O631" t="n">
@@ -72379,7 +72379,7 @@
       </c>
       <c r="M862" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N862" t="inlineStr">
@@ -73129,7 +73129,7 @@
       </c>
       <c r="M871" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N871" t="inlineStr">
@@ -73559,7 +73559,7 @@
       </c>
       <c r="M876" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N876" t="inlineStr">
@@ -73994,7 +73994,7 @@
       </c>
       <c r="M881" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N881" t="inlineStr">
@@ -82339,7 +82339,7 @@
       </c>
       <c r="M980" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N980" t="inlineStr">
@@ -84530,7 +84530,7 @@
       </c>
       <c r="M1006" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1006" t="inlineStr">
@@ -85487,7 +85487,7 @@
       </c>
       <c r="M1017" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1017" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O76" t="n">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O149" t="n">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -23267,7 +23267,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -25688,7 +25688,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O348" t="n">
@@ -30845,7 +30845,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -35606,7 +35606,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -40771,7 +40771,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -65532,7 +65532,7 @@
       </c>
       <c r="M781" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N781" t="inlineStr">
@@ -66837,7 +66837,7 @@
       </c>
       <c r="N796" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O796" t="n">
@@ -69024,7 +69024,7 @@
       </c>
       <c r="M822" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N822" t="inlineStr">
@@ -71036,7 +71036,7 @@
       </c>
       <c r="N846" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O846" t="n">
@@ -73385,7 +73385,7 @@
       </c>
       <c r="M874" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N874" t="inlineStr">
@@ -73472,7 +73472,7 @@
       </c>
       <c r="M875" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N875" t="inlineStr">
@@ -74744,7 +74744,7 @@
       </c>
       <c r="M890" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N890" t="inlineStr">
@@ -76337,7 +76337,7 @@
       </c>
       <c r="M909" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N909" t="inlineStr">
@@ -78891,7 +78891,7 @@
       </c>
       <c r="M940" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N940" t="inlineStr">
@@ -79326,7 +79326,7 @@
       </c>
       <c r="M945" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N945" t="inlineStr">
@@ -81469,7 +81469,7 @@
       </c>
       <c r="M970" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N970" t="inlineStr">
@@ -83437,7 +83437,7 @@
       </c>
       <c r="M993" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N993" t="inlineStr">
@@ -86754,7 +86754,7 @@
       </c>
       <c r="M1032" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1032" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -7507,7 +7507,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -15218,7 +15218,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -17327,7 +17327,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O286" t="n">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -35862,7 +35862,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -36873,7 +36873,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -37210,7 +37210,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -38417,7 +38417,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -39178,7 +39178,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -41885,7 +41885,7 @@
       </c>
       <c r="N496" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O496" t="n">
@@ -43114,7 +43114,7 @@
       </c>
       <c r="M511" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N511" t="inlineStr">
@@ -43282,7 +43282,7 @@
       </c>
       <c r="N513" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O513" t="n">
@@ -44223,7 +44223,7 @@
       </c>
       <c r="M524" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N524" t="inlineStr">
@@ -50977,7 +50977,7 @@
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N605" t="inlineStr">
@@ -60906,7 +60906,7 @@
       </c>
       <c r="M726" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N726" t="inlineStr">
@@ -62037,7 +62037,7 @@
       </c>
       <c r="M739" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N739" t="inlineStr">
@@ -63276,7 +63276,7 @@
       </c>
       <c r="M754" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N754" t="inlineStr">
@@ -63363,7 +63363,7 @@
       </c>
       <c r="M755" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N755" t="inlineStr">
@@ -63711,7 +63711,7 @@
       </c>
       <c r="M759" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N759" t="inlineStr">
@@ -65130,7 +65130,7 @@
       </c>
       <c r="M776" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N776" t="inlineStr">
@@ -66484,7 +66484,7 @@
       </c>
       <c r="M792" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N792" t="inlineStr">
@@ -67006,7 +67006,7 @@
       </c>
       <c r="M798" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N798" t="inlineStr">
@@ -67256,7 +67256,7 @@
       </c>
       <c r="M801" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N801" t="inlineStr">
@@ -67343,7 +67343,7 @@
       </c>
       <c r="M802" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N802" t="inlineStr">
@@ -67691,7 +67691,7 @@
       </c>
       <c r="N806" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O806" t="n">
@@ -68692,7 +68692,7 @@
       </c>
       <c r="N818" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O818" t="n">
@@ -72292,7 +72292,7 @@
       </c>
       <c r="M861" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N861" t="inlineStr">
@@ -75391,7 +75391,7 @@
       </c>
       <c r="M898" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N898" t="inlineStr">
@@ -77185,7 +77185,7 @@
       </c>
       <c r="M919" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N919" t="inlineStr">
@@ -82426,7 +82426,7 @@
       </c>
       <c r="M981" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N981" t="inlineStr">
@@ -82937,7 +82937,7 @@
       </c>
       <c r="M987" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N987" t="inlineStr">
@@ -86080,7 +86080,7 @@
       </c>
       <c r="M1024" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1024" t="inlineStr">
@@ -87450,7 +87450,7 @@
       </c>
       <c r="M1040" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1040" t="inlineStr">
@@ -88064,7 +88064,7 @@
       </c>
       <c r="N1047" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1047" t="n">
@@ -91568,7 +91568,7 @@
       </c>
       <c r="M1088" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1088" t="inlineStr">
@@ -93493,7 +93493,7 @@
       </c>
       <c r="M1111" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1111" t="inlineStr">
@@ -94363,7 +94363,7 @@
       </c>
       <c r="M1121" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1121" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -5587,7 +5587,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O63" t="n">
@@ -7226,6 +7226,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -10130,6 +10135,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -10386,6 +10396,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr">
         <is>
           <t>B6C</t>
@@ -17819,6 +17834,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr">
         <is>
           <t>B6E</t>
@@ -18249,6 +18269,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I213" t="inlineStr">
         <is>
           <t>B6D</t>
@@ -23160,6 +23185,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I271" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -24933,6 +24963,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I292" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -26495,6 +26530,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I311" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -32657,6 +32697,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I386" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -32739,6 +32784,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I387" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -35668,6 +35718,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I423" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -35693,7 +35748,7 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O423" t="n">
@@ -39955,7 +40010,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O473" t="n">
@@ -40129,7 +40184,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O475" t="n">
@@ -40577,6 +40632,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I481" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -42931,6 +42991,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I509" t="inlineStr">
         <is>
           <t>B6S</t>
@@ -47532,6 +47597,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I564" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -47701,6 +47771,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I566" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -48544,6 +48619,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I576" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -48569,7 +48649,7 @@
       </c>
       <c r="N576" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O576" t="n">
@@ -60313,7 +60393,7 @@
       </c>
       <c r="N719" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O719" t="n">
@@ -64129,7 +64209,7 @@
       </c>
       <c r="N764" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O764" t="n">
@@ -64621,6 +64701,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I770" t="inlineStr">
         <is>
           <t>B6E</t>
@@ -66116,6 +66201,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I788" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -67492,6 +67582,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I804" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -68183,6 +68278,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I812" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -68667,6 +68767,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I818" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -69347,6 +69452,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I826" t="inlineStr">
         <is>
           <t>B6L</t>
@@ -70755,6 +70865,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I843" t="inlineStr">
         <is>
           <t>B6L</t>
@@ -71011,6 +71126,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I846" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -73278,6 +73398,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I873" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -75284,6 +75409,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I897" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -79475,6 +79605,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I947" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -79633,6 +79768,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I949" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -81996,7 +82136,7 @@
       </c>
       <c r="N976" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O976" t="n">
@@ -83749,6 +83889,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I997" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -85636,6 +85781,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I1019" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -90524,6 +90674,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I1076" t="inlineStr">
         <is>
           <t>B6B</t>
@@ -90606,6 +90761,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I1077" t="inlineStr">
         <is>
           <t>B6K</t>
@@ -90949,6 +91109,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I1081" t="inlineStr">
         <is>
           <t>B6L</t>
@@ -92130,6 +92295,11 @@
           <t>SALINAS LINARES ADRIW SMITH</t>
         </is>
       </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
+        </is>
+      </c>
       <c r="I1095" t="inlineStr">
         <is>
           <t>B4R</t>
@@ -93324,7 +93494,7 @@
       </c>
       <c r="N1109" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1109" t="n">
@@ -94825,6 +94995,11 @@
       <c r="G1127" t="inlineStr">
         <is>
           <t>SALINAS LINARES ADRIW SMITH</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>906 591 184</t>
         </is>
       </c>
       <c r="I1127" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -27245,7 +27245,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O319" t="n">
@@ -38390,7 +38390,7 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O454" t="n">
@@ -48214,7 +48214,7 @@
       </c>
       <c r="N571" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O571" t="n">
@@ -93581,7 +93581,7 @@
       </c>
       <c r="N1110" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1110" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -26908,7 +26908,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O315" t="n">
@@ -30977,7 +30977,7 @@
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O365" t="n">
@@ -37020,7 +37020,7 @@
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O438" t="n">
@@ -47290,7 +47290,7 @@
       </c>
       <c r="N560" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O560" t="n">
@@ -58398,7 +58398,7 @@
       </c>
       <c r="N695" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O695" t="n">
@@ -58974,7 +58974,7 @@
       </c>
       <c r="N702" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O702" t="n">
@@ -91139,7 +91139,7 @@
       </c>
       <c r="N1081" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1081" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4234,12 +4234,12 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O69" t="n">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O75" t="n">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O105" t="n">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -11084,12 +11084,12 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O128" t="n">
@@ -14983,12 +14983,12 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O174" t="n">
@@ -20349,12 +20349,12 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O237" t="n">
@@ -20675,12 +20675,12 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O241" t="n">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -27414,7 +27414,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -32983,12 +32983,12 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O389" t="n">
@@ -35395,12 +35395,12 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O419" t="n">
@@ -42114,7 +42114,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -45926,7 +45926,7 @@
       </c>
       <c r="M544" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N544" t="inlineStr">
@@ -48046,12 +48046,12 @@
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N569" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O569" t="n">
@@ -49203,7 +49203,7 @@
       </c>
       <c r="N583" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O583" t="n">
@@ -51557,12 +51557,12 @@
       </c>
       <c r="M611" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O611" t="n">
@@ -53443,7 +53443,7 @@
       </c>
       <c r="N633" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O633" t="n">
@@ -56519,7 +56519,7 @@
       </c>
       <c r="N671" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O671" t="n">
@@ -65704,12 +65704,12 @@
       </c>
       <c r="M782" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N782" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O782" t="n">
@@ -69390,12 +69390,12 @@
       </c>
       <c r="M825" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N825" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O825" t="n">
@@ -71069,7 +71069,7 @@
       </c>
       <c r="N845" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O845" t="n">
@@ -74619,12 +74619,12 @@
       </c>
       <c r="M887" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N887" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O887" t="n">
@@ -76902,12 +76902,12 @@
       </c>
       <c r="M914" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N914" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O914" t="n">
@@ -78771,7 +78771,7 @@
       </c>
       <c r="M937" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N937" t="inlineStr">
@@ -78858,12 +78858,12 @@
       </c>
       <c r="M938" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N938" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O938" t="n">
@@ -80130,12 +80130,12 @@
       </c>
       <c r="M953" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N953" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O953" t="n">
@@ -81870,12 +81870,12 @@
       </c>
       <c r="M973" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N973" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O973" t="n">
@@ -82218,7 +82218,7 @@
       </c>
       <c r="M977" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N977" t="inlineStr">
@@ -84425,12 +84425,12 @@
       </c>
       <c r="M1003" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1003" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1003" t="n">
@@ -84854,7 +84854,7 @@
       </c>
       <c r="N1008" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1008" t="n">
@@ -84936,12 +84936,12 @@
       </c>
       <c r="M1009" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1009" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1009" t="n">
@@ -85284,12 +85284,12 @@
       </c>
       <c r="M1013" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1013" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1013" t="n">
@@ -88894,12 +88894,12 @@
       </c>
       <c r="M1055" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1055" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1055" t="n">
@@ -88981,12 +88981,12 @@
       </c>
       <c r="M1056" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1056" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1056" t="n">
@@ -89590,12 +89590,12 @@
       </c>
       <c r="M1063" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1063" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1063" t="n">
@@ -90188,12 +90188,12 @@
       </c>
       <c r="M1070" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1070" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1070" t="n">
@@ -90275,12 +90275,12 @@
       </c>
       <c r="M1071" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1071" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1071" t="n">
@@ -90791,7 +90791,7 @@
       </c>
       <c r="N1077" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1077" t="n">
@@ -91221,12 +91221,12 @@
       </c>
       <c r="M1082" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1082" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1082" t="n">
@@ -92918,12 +92918,12 @@
       </c>
       <c r="M1102" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1102" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1102" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -11437,7 +11437,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O132" t="n">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O134" t="n">
@@ -31890,7 +31890,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O376" t="n">
@@ -41434,7 +41434,7 @@
       </c>
       <c r="N490" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O490" t="n">
@@ -46442,7 +46442,7 @@
       </c>
       <c r="N550" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O550" t="n">
@@ -46779,7 +46779,7 @@
       </c>
       <c r="N554" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O554" t="n">
@@ -46953,7 +46953,7 @@
       </c>
       <c r="N556" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O556" t="n">
@@ -48388,7 +48388,7 @@
       </c>
       <c r="N573" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O573" t="n">
@@ -48736,7 +48736,7 @@
       </c>
       <c r="N577" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O577" t="n">
@@ -56432,7 +56432,7 @@
       </c>
       <c r="N670" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O670" t="n">
@@ -61687,7 +61687,7 @@
       </c>
       <c r="N734" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O734" t="n">
@@ -66231,7 +66231,7 @@
       </c>
       <c r="N788" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O788" t="n">
@@ -66753,7 +66753,7 @@
       </c>
       <c r="N794" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O794" t="n">
@@ -70547,7 +70547,7 @@
       </c>
       <c r="N839" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O839" t="n">
@@ -89845,7 +89845,7 @@
       </c>
       <c r="N1066" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1066" t="n">
@@ -92412,7 +92412,7 @@
       </c>
       <c r="N1096" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1096" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O173" t="n">
@@ -16407,7 +16407,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O204" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -21175,7 +21175,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -23036,7 +23036,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O334" t="n">
@@ -29316,7 +29316,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O344" t="n">
@@ -36841,7 +36841,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -38124,7 +38124,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -39657,7 +39657,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -45288,7 +45288,7 @@
       </c>
       <c r="M536" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N536" t="inlineStr">
@@ -50481,7 +50481,7 @@
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N598" t="inlineStr">
@@ -51144,7 +51144,7 @@
       </c>
       <c r="M606" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N606" t="inlineStr">
@@ -52856,7 +52856,7 @@
       </c>
       <c r="N626" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O626" t="n">
@@ -52938,7 +52938,7 @@
       </c>
       <c r="M627" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N627" t="inlineStr">
@@ -56693,7 +56693,7 @@
       </c>
       <c r="N673" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O673" t="n">
@@ -59719,7 +59719,7 @@
       </c>
       <c r="M711" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N711" t="inlineStr">
@@ -61334,7 +61334,7 @@
       </c>
       <c r="M730" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N730" t="inlineStr">
@@ -63704,7 +63704,7 @@
       </c>
       <c r="M758" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N758" t="inlineStr">
@@ -64639,7 +64639,7 @@
       </c>
       <c r="M769" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N769" t="inlineStr">
@@ -66666,7 +66666,7 @@
       </c>
       <c r="N793" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O793" t="n">
@@ -68705,7 +68705,7 @@
       </c>
       <c r="M817" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N817" t="inlineStr">
@@ -70460,7 +70460,7 @@
       </c>
       <c r="N838" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O838" t="n">
@@ -71977,7 +71977,7 @@
       </c>
       <c r="M856" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N856" t="inlineStr">
@@ -73858,7 +73858,7 @@
       </c>
       <c r="M878" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N878" t="inlineStr">
@@ -75043,7 +75043,7 @@
       </c>
       <c r="M892" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N892" t="inlineStr">
@@ -76815,7 +76815,7 @@
       </c>
       <c r="M913" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N913" t="inlineStr">
@@ -77967,7 +77967,7 @@
       </c>
       <c r="M927" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N927" t="inlineStr">
@@ -80217,7 +80217,7 @@
       </c>
       <c r="M954" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N954" t="inlineStr">
@@ -80565,7 +80565,7 @@
       </c>
       <c r="M958" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N958" t="inlineStr">
@@ -84001,7 +84001,7 @@
       </c>
       <c r="M998" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N998" t="inlineStr">
@@ -85458,7 +85458,7 @@
       </c>
       <c r="M1015" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1015" t="inlineStr">
@@ -87252,7 +87252,7 @@
       </c>
       <c r="M1036" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1036" t="inlineStr">
@@ -89927,7 +89927,7 @@
       </c>
       <c r="M1067" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1067" t="inlineStr">
@@ -93750,7 +93750,7 @@
       </c>
       <c r="M1112" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1112" t="inlineStr">
@@ -94011,7 +94011,7 @@
       </c>
       <c r="M1115" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1115" t="inlineStr">
@@ -94538,7 +94538,7 @@
       </c>
       <c r="N1121" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1121" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -869,7 +869,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O52" t="n">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O55" t="n">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O100" t="n">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O113" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O133" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O136" t="n">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O142" t="n">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O146" t="n">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O189" t="n">
@@ -17021,7 +17021,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O198" t="n">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O203" t="n">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O211" t="n">
@@ -18462,7 +18462,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O215" t="n">
@@ -20180,7 +20180,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O235" t="n">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O248" t="n">
@@ -21528,7 +21528,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O251" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O252" t="n">
@@ -25396,7 +25396,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O297" t="n">
@@ -32390,7 +32390,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O382" t="n">
@@ -39662,7 +39662,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O469" t="n">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="N518" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O518" t="n">
@@ -48301,7 +48301,7 @@
       </c>
       <c r="N572" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O572" t="n">
@@ -50649,7 +50649,7 @@
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O600" t="n">
@@ -59724,7 +59724,7 @@
       </c>
       <c r="N711" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O711" t="n">
@@ -63709,7 +63709,7 @@
       </c>
       <c r="N758" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O758" t="n">
@@ -69482,7 +69482,7 @@
       </c>
       <c r="N826" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O826" t="n">
@@ -72504,7 +72504,7 @@
       </c>
       <c r="N862" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O862" t="n">
@@ -73863,7 +73863,7 @@
       </c>
       <c r="N878" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O878" t="n">
@@ -75048,7 +75048,7 @@
       </c>
       <c r="N892" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O892" t="n">
@@ -76820,7 +76820,7 @@
       </c>
       <c r="N913" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O913" t="n">
@@ -77972,7 +77972,7 @@
       </c>
       <c r="N927" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O927" t="n">
@@ -84006,7 +84006,7 @@
       </c>
       <c r="N998" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O998" t="n">
@@ -94016,7 +94016,7 @@
       </c>
       <c r="N1115" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1115" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4147,7 +4147,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O171" t="n">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -21436,7 +21436,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -22116,7 +22116,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O258" t="n">
@@ -23384,7 +23384,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -31711,7 +31711,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -35221,7 +35221,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -40744,7 +40744,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -44119,7 +44119,7 @@
       </c>
       <c r="N522" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O522" t="n">
@@ -46524,7 +46524,7 @@
       </c>
       <c r="M551" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N551" t="inlineStr">
@@ -49361,7 +49361,7 @@
       </c>
       <c r="M585" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N585" t="inlineStr">
@@ -49796,7 +49796,7 @@
       </c>
       <c r="M590" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N590" t="inlineStr">
@@ -50231,7 +50231,7 @@
       </c>
       <c r="M595" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N595" t="inlineStr">
@@ -52329,7 +52329,7 @@
       </c>
       <c r="M620" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N620" t="inlineStr">
@@ -54015,7 +54015,7 @@
       </c>
       <c r="N640" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O640" t="n">
@@ -54168,7 +54168,7 @@
       </c>
       <c r="N642" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O642" t="n">
@@ -54463,7 +54463,7 @@
       </c>
       <c r="N646" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O646" t="n">
@@ -54545,7 +54545,7 @@
       </c>
       <c r="N647" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O647" t="n">
@@ -55250,7 +55250,7 @@
       </c>
       <c r="N656" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O656" t="n">
@@ -55414,7 +55414,7 @@
       </c>
       <c r="N658" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O658" t="n">
@@ -55578,7 +55578,7 @@
       </c>
       <c r="N660" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O660" t="n">
@@ -58235,7 +58235,7 @@
       </c>
       <c r="N693" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O693" t="n">
@@ -58887,7 +58887,7 @@
       </c>
       <c r="N701" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O701" t="n">
@@ -61078,7 +61078,7 @@
       </c>
       <c r="N727" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O727" t="n">
@@ -61948,7 +61948,7 @@
       </c>
       <c r="N737" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O737" t="n">
@@ -63117,7 +63117,7 @@
       </c>
       <c r="M751" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N751" t="inlineStr">
@@ -67694,7 +67694,7 @@
       </c>
       <c r="M805" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N805" t="inlineStr">
@@ -80478,7 +80478,7 @@
       </c>
       <c r="M957" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N957" t="inlineStr">
@@ -84767,7 +84767,7 @@
       </c>
       <c r="N1007" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1007" t="n">
@@ -85893,7 +85893,7 @@
       </c>
       <c r="M1020" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1020" t="inlineStr">
@@ -88464,7 +88464,7 @@
       </c>
       <c r="N1050" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1050" t="n">
@@ -91651,7 +91651,7 @@
       </c>
       <c r="N1087" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1087" t="n">
@@ -94364,7 +94364,7 @@
       </c>
       <c r="N1119" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1119" t="n">
@@ -94940,7 +94940,7 @@
       </c>
       <c r="N1126" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1126" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4413,7 +4413,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O49" t="n">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O119" t="n">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O154" t="n">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O206" t="n">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O217" t="n">
@@ -29490,7 +29490,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O346" t="n">
@@ -31716,7 +31716,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O374" t="n">
@@ -31803,7 +31803,7 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O375" t="n">
@@ -37444,7 +37444,7 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O443" t="n">
@@ -37705,7 +37705,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O446" t="n">
@@ -38738,7 +38738,7 @@
       </c>
       <c r="N458" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O458" t="n">
@@ -42282,7 +42282,7 @@
       </c>
       <c r="N500" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O500" t="n">
@@ -45206,7 +45206,7 @@
       </c>
       <c r="N535" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O535" t="n">
@@ -52073,7 +52073,7 @@
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O617" t="n">
@@ -53030,7 +53030,7 @@
       </c>
       <c r="N628" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O628" t="n">
@@ -64731,7 +64731,7 @@
       </c>
       <c r="N770" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O770" t="n">
@@ -72243,7 +72243,7 @@
       </c>
       <c r="N859" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O859" t="n">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="N889" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O889" t="n">
@@ -80483,7 +80483,7 @@
       </c>
       <c r="N957" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O957" t="n">
@@ -81005,7 +81005,7 @@
       </c>
       <c r="N963" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O963" t="n">
@@ -81527,7 +81527,7 @@
       </c>
       <c r="N969" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O969" t="n">
@@ -85724,7 +85724,7 @@
       </c>
       <c r="N1018" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1018" t="n">
@@ -87866,7 +87866,7 @@
       </c>
       <c r="N1043" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1043" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4750,7 +4750,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O53" t="n">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O117" t="n">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -12041,12 +12041,12 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O139" t="n">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O143" t="n">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O213" t="n">
@@ -22796,7 +22796,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O266" t="n">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O300" t="n">
@@ -28153,12 +28153,12 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O330" t="n">
@@ -29403,7 +29403,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O345" t="n">
@@ -31385,7 +31385,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -41081,7 +41081,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -41173,7 +41173,7 @@
       </c>
       <c r="N487" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O487" t="n">
@@ -45027,12 +45027,12 @@
       </c>
       <c r="M533" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N533" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O533" t="n">
@@ -46861,7 +46861,7 @@
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N555" t="inlineStr">
@@ -47040,7 +47040,7 @@
       </c>
       <c r="N557" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O557" t="n">
@@ -49448,7 +49448,7 @@
       </c>
       <c r="M586" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N586" t="inlineStr">
@@ -52682,7 +52682,7 @@
       </c>
       <c r="N624" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O624" t="n">
@@ -53530,7 +53530,7 @@
       </c>
       <c r="N634" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O634" t="n">
@@ -55992,7 +55992,7 @@
       </c>
       <c r="M665" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N665" t="inlineStr">
@@ -58719,7 +58719,7 @@
       </c>
       <c r="M699" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N699" t="inlineStr">
@@ -61774,7 +61774,7 @@
       </c>
       <c r="N735" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O735" t="n">
@@ -77152,7 +77152,7 @@
       </c>
       <c r="M917" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N917" t="inlineStr">
@@ -80043,12 +80043,12 @@
       </c>
       <c r="M952" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N952" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O952" t="n">
@@ -80913,7 +80913,7 @@
       </c>
       <c r="M962" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N962" t="inlineStr">
@@ -85023,12 +85023,12 @@
       </c>
       <c r="M1010" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1010" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1010" t="n">
@@ -85110,7 +85110,7 @@
       </c>
       <c r="M1011" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1011" t="inlineStr">
@@ -86143,7 +86143,7 @@
       </c>
       <c r="M1023" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1023" t="inlineStr">
@@ -94772,7 +94772,7 @@
       </c>
       <c r="M1124" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1124" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -42032,7 +42032,7 @@
       </c>
       <c r="N497" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O497" t="n">
@@ -50899,7 +50899,7 @@
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O603" t="n">
@@ -62546,7 +62546,7 @@
       </c>
       <c r="N744" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O744" t="n">
@@ -68308,7 +68308,7 @@
       </c>
       <c r="N812" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O812" t="n">
@@ -79200,7 +79200,7 @@
       </c>
       <c r="N942" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O942" t="n">
@@ -81788,7 +81788,7 @@
       </c>
       <c r="N972" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O972" t="n">
@@ -94451,7 +94451,7 @@
       </c>
       <c r="N1120" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1120" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -5848,7 +5848,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O66" t="n">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O114" t="n">
@@ -24226,7 +24226,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O283" t="n">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O287" t="n">
@@ -32227,7 +32227,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O380" t="n">
@@ -34726,7 +34726,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O411" t="n">
@@ -36085,7 +36085,7 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O427" t="n">
@@ -36335,7 +36335,7 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O430" t="n">
@@ -37955,7 +37955,7 @@
       </c>
       <c r="N449" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O449" t="n">
@@ -42847,7 +42847,7 @@
       </c>
       <c r="N507" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O507" t="n">
@@ -43608,7 +43608,7 @@
       </c>
       <c r="N516" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O516" t="n">
@@ -51149,7 +51149,7 @@
       </c>
       <c r="N606" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O606" t="n">
@@ -53780,7 +53780,7 @@
       </c>
       <c r="N637" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O637" t="n">
@@ -58724,7 +58724,7 @@
       </c>
       <c r="N699" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O699" t="n">
@@ -61339,7 +61339,7 @@
       </c>
       <c r="N730" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O730" t="n">
@@ -64644,7 +64644,7 @@
       </c>
       <c r="N769" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O769" t="n">
@@ -67014,7 +67014,7 @@
       </c>
       <c r="N797" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O797" t="n">
@@ -68221,7 +68221,7 @@
       </c>
       <c r="N811" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O811" t="n">
@@ -71982,7 +71982,7 @@
       </c>
       <c r="N856" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O856" t="n">
@@ -72841,7 +72841,7 @@
       </c>
       <c r="N866" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O866" t="n">
@@ -74211,7 +74211,7 @@
       </c>
       <c r="N882" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O882" t="n">
@@ -81701,7 +81701,7 @@
       </c>
       <c r="N971" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O971" t="n">
@@ -87170,7 +87170,7 @@
       </c>
       <c r="N1035" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1035" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -9045,7 +9045,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O104" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3989,7 +3989,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O85" t="n">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O88" t="n">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O116" t="n">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O122" t="n">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O160" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O278" t="n">
@@ -28071,7 +28071,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O329" t="n">
@@ -37531,7 +37531,7 @@
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O444" t="n">
@@ -47464,7 +47464,7 @@
       </c>
       <c r="N562" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O562" t="n">
@@ -51475,7 +51475,7 @@
       </c>
       <c r="N610" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O610" t="n">
@@ -60828,7 +60828,7 @@
       </c>
       <c r="N724" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O724" t="n">
@@ -75613,7 +75613,7 @@
       </c>
       <c r="N899" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O899" t="n">
@@ -85376,7 +85376,7 @@
       </c>
       <c r="N1014" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1014" t="n">
@@ -85811,7 +85811,7 @@
       </c>
       <c r="N1019" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1019" t="n">
@@ -88551,7 +88551,7 @@
       </c>
       <c r="N1051" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1051" t="n">
@@ -90965,7 +90965,7 @@
       </c>
       <c r="N1079" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1079" t="n">
@@ -94190,7 +94190,7 @@
       </c>
       <c r="N1117" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1117" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -28756,7 +28756,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O337" t="n">
@@ -32640,7 +32640,7 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O385" t="n">
@@ -46018,7 +46018,7 @@
       </c>
       <c r="N545" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O545" t="n">
@@ -47801,7 +47801,7 @@
       </c>
       <c r="N566" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O566" t="n">
@@ -64557,7 +64557,7 @@
       </c>
       <c r="N768" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O768" t="n">
@@ -71482,7 +71482,7 @@
       </c>
       <c r="N850" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O850" t="n">
@@ -72667,7 +72667,7 @@
       </c>
       <c r="N864" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O864" t="n">
@@ -74874,7 +74874,7 @@
       </c>
       <c r="N890" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O890" t="n">
@@ -76472,7 +76472,7 @@
       </c>
       <c r="N909" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O909" t="n">
@@ -80744,7 +80744,7 @@
       </c>
       <c r="N960" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O960" t="n">
@@ -86909,7 +86909,7 @@
       </c>
       <c r="N1032" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1032" t="n">
@@ -88725,7 +88725,7 @@
       </c>
       <c r="N1053" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1053" t="n">
@@ -94277,7 +94277,7 @@
       </c>
       <c r="N1118" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1118" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -6843,7 +6843,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O178" t="n">
@@ -65796,7 +65796,7 @@
       </c>
       <c r="N783" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O783" t="n">
@@ -87779,7 +87779,7 @@
       </c>
       <c r="N1042" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1042" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -15488,7 +15488,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O180" t="n">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O229" t="n">
@@ -26065,7 +26065,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O305" t="n">
@@ -38651,7 +38651,7 @@
       </c>
       <c r="N457" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O457" t="n">
@@ -47964,7 +47964,7 @@
       </c>
       <c r="N568" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O568" t="n">
@@ -62785,7 +62785,7 @@
       </c>
       <c r="N747" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O747" t="n">
@@ -70058,7 +70058,7 @@
       </c>
       <c r="N833" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O833" t="n">
@@ -75439,7 +75439,7 @@
       </c>
       <c r="N897" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O897" t="n">
@@ -79374,7 +79374,7 @@
       </c>
       <c r="N944" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O944" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1277,7 +1277,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O144" t="n">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O285" t="n">
@@ -26647,7 +26647,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O312" t="n">
@@ -30716,7 +30716,7 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O362" t="n">
@@ -30803,7 +30803,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O363" t="n">
@@ -34813,7 +34813,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O412" t="n">
@@ -38216,7 +38216,7 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O452" t="n">
@@ -38825,7 +38825,7 @@
       </c>
       <c r="N459" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O459" t="n">
@@ -52421,7 +52421,7 @@
       </c>
       <c r="N621" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O621" t="n">
@@ -56345,7 +56345,7 @@
       </c>
       <c r="N669" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O669" t="n">
@@ -59985,7 +59985,7 @@
       </c>
       <c r="N714" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O714" t="n">
@@ -72330,7 +72330,7 @@
       </c>
       <c r="N860" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O860" t="n">
@@ -89247,7 +89247,7 @@
       </c>
       <c r="N1059" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1059" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O111" t="n">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O187" t="n">
@@ -27582,7 +27582,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O323" t="n">
@@ -37618,7 +37618,7 @@
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O445" t="n">
@@ -39401,7 +39401,7 @@
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O466" t="n">
@@ -39836,7 +39836,7 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O471" t="n">
@@ -43858,7 +43858,7 @@
       </c>
       <c r="N519" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O519" t="n">
@@ -46105,7 +46105,7 @@
       </c>
       <c r="N546" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O546" t="n">
@@ -46692,7 +46692,7 @@
       </c>
       <c r="N553" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O553" t="n">
@@ -51236,7 +51236,7 @@
       </c>
       <c r="N607" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O607" t="n">
@@ -52508,7 +52508,7 @@
       </c>
       <c r="N622" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O622" t="n">
@@ -55823,7 +55823,7 @@
       </c>
       <c r="N663" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O663" t="n">
@@ -56084,7 +56084,7 @@
       </c>
       <c r="N666" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O666" t="n">
@@ -56171,7 +56171,7 @@
       </c>
       <c r="N667" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O667" t="n">
@@ -56606,7 +56606,7 @@
       </c>
       <c r="N672" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O672" t="n">
@@ -62372,7 +62372,7 @@
       </c>
       <c r="N742" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O742" t="n">
@@ -64383,7 +64383,7 @@
       </c>
       <c r="N766" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O766" t="n">
@@ -64894,7 +64894,7 @@
       </c>
       <c r="N772" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O772" t="n">
@@ -67960,7 +67960,7 @@
       </c>
       <c r="N808" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O808" t="n">
@@ -70895,7 +70895,7 @@
       </c>
       <c r="N843" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O843" t="n">
@@ -71656,7 +71656,7 @@
       </c>
       <c r="N852" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O852" t="n">
@@ -72156,7 +72156,7 @@
       </c>
       <c r="N858" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O858" t="n">
@@ -73950,7 +73950,7 @@
       </c>
       <c r="N879" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O879" t="n">
@@ -79635,7 +79635,7 @@
       </c>
       <c r="N947" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O947" t="n">
@@ -81440,7 +81440,7 @@
       </c>
       <c r="N968" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O968" t="n">
@@ -86996,7 +86996,7 @@
       </c>
       <c r="N1033" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1033" t="n">
@@ -91912,7 +91912,7 @@
       </c>
       <c r="N1090" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1090" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -15988,7 +15988,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O186" t="n">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O272" t="n">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O298" t="n">
@@ -34117,7 +34117,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O404" t="n">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O428" t="n">
@@ -41086,7 +41086,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O486" t="n">
@@ -49453,7 +49453,7 @@
       </c>
       <c r="N586" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O586" t="n">
@@ -51649,7 +51649,7 @@
       </c>
       <c r="N612" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O612" t="n">
@@ -61861,7 +61861,7 @@
       </c>
       <c r="N736" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O736" t="n">
@@ -72928,7 +72928,7 @@
       </c>
       <c r="N867" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O867" t="n">
@@ -73428,7 +73428,7 @@
       </c>
       <c r="N873" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O873" t="n">
@@ -75874,7 +75874,7 @@
       </c>
       <c r="N902" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O902" t="n">
@@ -79461,7 +79461,7 @@
       </c>
       <c r="N945" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O945" t="n">
@@ -80918,7 +80918,7 @@
       </c>
       <c r="N962" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O962" t="n">
@@ -85115,7 +85115,7 @@
       </c>
       <c r="N1011" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1011" t="n">
@@ -86148,7 +86148,7 @@
       </c>
       <c r="N1023" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1023" t="n">
@@ -94103,7 +94103,7 @@
       </c>
       <c r="N1116" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1116" t="n">
@@ -94777,7 +94777,7 @@
       </c>
       <c r="N1124" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1124" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3902,7 +3902,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -15151,7 +15151,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O176" t="n">
@@ -26315,7 +26315,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O308" t="n">
@@ -27832,7 +27832,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O326" t="n">
@@ -32140,7 +32140,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O379" t="n">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O408" t="n">
@@ -38042,7 +38042,7 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O450" t="n">
@@ -41782,7 +41782,7 @@
       </c>
       <c r="N494" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O494" t="n">
@@ -43434,7 +43434,7 @@
       </c>
       <c r="N514" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O514" t="n">
@@ -44782,7 +44782,7 @@
       </c>
       <c r="N530" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O530" t="n">
@@ -45680,7 +45680,7 @@
       </c>
       <c r="N541" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O541" t="n">
@@ -50149,7 +50149,7 @@
       </c>
       <c r="N594" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O594" t="n">
@@ -57800,7 +57800,7 @@
       </c>
       <c r="N688" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O688" t="n">
@@ -67873,7 +67873,7 @@
       </c>
       <c r="N807" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O807" t="n">
@@ -68971,7 +68971,7 @@
       </c>
       <c r="N820" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O820" t="n">
@@ -70634,7 +70634,7 @@
       </c>
       <c r="N840" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O840" t="n">
@@ -79287,7 +79287,7 @@
       </c>
       <c r="N943" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O943" t="n">
@@ -82310,7 +82310,7 @@
       </c>
       <c r="N978" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O978" t="n">
@@ -83419,7 +83419,7 @@
       </c>
       <c r="N991" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O991" t="n">
@@ -92586,7 +92586,7 @@
       </c>
       <c r="N1098" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1098" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -18897,7 +18897,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O220" t="n">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O230" t="n">
@@ -19930,7 +19930,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O232" t="n">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O280" t="n">
@@ -37107,7 +37107,7 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O439" t="n">
@@ -44032,7 +44032,7 @@
       </c>
       <c r="N521" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O521" t="n">
@@ -44380,7 +44380,7 @@
       </c>
       <c r="N525" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O525" t="n">
@@ -51823,7 +51823,7 @@
       </c>
       <c r="N614" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O614" t="n">
@@ -55910,7 +55910,7 @@
       </c>
       <c r="N664" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O664" t="n">
@@ -60143,7 +60143,7 @@
       </c>
       <c r="N716" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O716" t="n">
@@ -62959,7 +62959,7 @@
       </c>
       <c r="N749" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O749" t="n">
@@ -63622,7 +63622,7 @@
       </c>
       <c r="N757" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O757" t="n">
@@ -64296,7 +64296,7 @@
       </c>
       <c r="N765" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O765" t="n">
@@ -72754,7 +72754,7 @@
       </c>
       <c r="N865" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O865" t="n">
@@ -86572,7 +86572,7 @@
       </c>
       <c r="N1028" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1028" t="n">
@@ -86735,7 +86735,7 @@
       </c>
       <c r="N1030" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1030" t="n">
@@ -90454,7 +90454,7 @@
       </c>
       <c r="N1073" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1073" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -5250,7 +5250,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O138" t="n">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O199" t="n">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O218" t="n">
@@ -32901,7 +32901,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O388" t="n">
@@ -38303,7 +38303,7 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O453" t="n">
@@ -68134,7 +68134,7 @@
       </c>
       <c r="N810" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O810" t="n">
@@ -70808,7 +70808,7 @@
       </c>
       <c r="N842" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O842" t="n">
@@ -79026,7 +79026,7 @@
       </c>
       <c r="N940" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O940" t="n">
@@ -81614,7 +81614,7 @@
       </c>
       <c r="N970" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O970" t="n">
@@ -83582,7 +83582,7 @@
       </c>
       <c r="N993" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O993" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -8023,7 +8023,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O92" t="n">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O157" t="n">
@@ -47203,7 +47203,7 @@
       </c>
       <c r="N559" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O559" t="n">
@@ -65622,7 +65622,7 @@
       </c>
       <c r="N781" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O781" t="n">
@@ -70145,7 +70145,7 @@
       </c>
       <c r="N834" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O834" t="n">
@@ -82745,7 +82745,7 @@
       </c>
       <c r="N983" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O983" t="n">
@@ -88377,7 +88377,7 @@
       </c>
       <c r="N1049" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1049" t="n">
@@ -90106,7 +90106,7 @@
       </c>
       <c r="N1069" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1069" t="n">
@@ -92836,7 +92836,7 @@
       </c>
       <c r="N1101" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1101" t="n">
@@ -93331,7 +93331,7 @@
       </c>
       <c r="N1107" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1107" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4500,7 +4500,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O91" t="n">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O145" t="n">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O161" t="n">
@@ -16934,7 +16934,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O197" t="n">
@@ -21093,7 +21093,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O246" t="n">
@@ -21180,7 +21180,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O247" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O255" t="n">
@@ -23552,7 +23552,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O275" t="n">
@@ -28669,7 +28669,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O336" t="n">
@@ -29577,7 +29577,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O347" t="n">
@@ -33162,7 +33162,7 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O391" t="n">
@@ -34976,7 +34976,7 @@
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O414" t="n">
@@ -38912,7 +38912,7 @@
       </c>
       <c r="N460" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O460" t="n">
@@ -40097,7 +40097,7 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O474" t="n">
@@ -40999,7 +40999,7 @@
       </c>
       <c r="N485" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O485" t="n">
@@ -42684,7 +42684,7 @@
       </c>
       <c r="N505" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O505" t="n">
@@ -45854,7 +45854,7 @@
       </c>
       <c r="N543" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O543" t="n">
@@ -52595,7 +52595,7 @@
       </c>
       <c r="N623" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O623" t="n">
@@ -53617,7 +53617,7 @@
       </c>
       <c r="N635" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O635" t="n">
@@ -63883,7 +63883,7 @@
       </c>
       <c r="N760" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O760" t="n">
@@ -65970,7 +65970,7 @@
       </c>
       <c r="N785" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O785" t="n">
@@ -66492,7 +66492,7 @@
       </c>
       <c r="N791" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O791" t="n">
@@ -69221,7 +69221,7 @@
       </c>
       <c r="N823" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O823" t="n">
@@ -69308,7 +69308,7 @@
       </c>
       <c r="N824" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O824" t="n">
@@ -72069,7 +72069,7 @@
       </c>
       <c r="N857" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O857" t="n">
@@ -73515,7 +73515,7 @@
       </c>
       <c r="N874" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O874" t="n">
@@ -76037,7 +76037,7 @@
       </c>
       <c r="N904" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O904" t="n">
@@ -76211,7 +76211,7 @@
       </c>
       <c r="N906" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O906" t="n">
@@ -78222,7 +78222,7 @@
       </c>
       <c r="N930" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O930" t="n">
@@ -83832,7 +83832,7 @@
       </c>
       <c r="N996" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O996" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3554,7 +3554,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O64" t="n">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O71" t="n">
@@ -30629,7 +30629,7 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O361" t="n">
@@ -33075,7 +33075,7 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O390" t="n">
@@ -35661,7 +35661,7 @@
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O422" t="n">
@@ -49540,7 +49540,7 @@
       </c>
       <c r="N587" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O587" t="n">
@@ -52247,7 +52247,7 @@
       </c>
       <c r="N619" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O619" t="n">
@@ -57974,7 +57974,7 @@
       </c>
       <c r="N690" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O690" t="n">
@@ -68047,7 +68047,7 @@
       </c>
       <c r="N809" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O809" t="n">
@@ -71569,7 +71569,7 @@
       </c>
       <c r="N851" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O851" t="n">
@@ -92238,7 +92238,7 @@
       </c>
       <c r="N1094" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1094" t="n">
@@ -93010,7 +93010,7 @@
       </c>
       <c r="N1103" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1103" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -7343,7 +7343,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O84" t="n">
@@ -20767,7 +20767,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O242" t="n">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O262" t="n">
@@ -60654,7 +60654,7 @@
       </c>
       <c r="N722" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O722" t="n">
@@ -62459,7 +62459,7 @@
       </c>
       <c r="N743" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O743" t="n">
@@ -76559,7 +76559,7 @@
       </c>
       <c r="N910" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O910" t="n">
@@ -81266,7 +81266,7 @@
       </c>
       <c r="N966" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O966" t="n">
@@ -86061,7 +86061,7 @@
       </c>
       <c r="N1022" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1022" t="n">
@@ -88812,7 +88812,7 @@
       </c>
       <c r="N1054" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1054" t="n">
@@ -89160,7 +89160,7 @@
       </c>
       <c r="N1058" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1058" t="n">
@@ -91487,7 +91487,7 @@
       </c>
       <c r="N1085" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1085" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -5087,7 +5087,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O57" t="n">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O62" t="n">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O86" t="n">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O93" t="n">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O107" t="n">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O152" t="n">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O177" t="n">
@@ -15575,7 +15575,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O181" t="n">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O202" t="n">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O239" t="n">
@@ -22709,7 +22709,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O265" t="n">
@@ -23639,7 +23639,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O276" t="n">
@@ -25815,7 +25815,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O302" t="n">
@@ -32053,7 +32053,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O378" t="n">
@@ -34552,7 +34552,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O409" t="n">
@@ -35313,7 +35313,7 @@
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O418" t="n">
@@ -35922,7 +35922,7 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O425" t="n">
@@ -36933,7 +36933,7 @@
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O437" t="n">
@@ -37270,7 +37270,7 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O441" t="n">
@@ -37357,7 +37357,7 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O442" t="n">
@@ -38477,7 +38477,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O455" t="n">
@@ -39238,7 +39238,7 @@
       </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O464" t="n">
@@ -42521,7 +42521,7 @@
       </c>
       <c r="N503" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O503" t="n">
@@ -43184,7 +43184,7 @@
       </c>
       <c r="N511" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O511" t="n">
@@ -44293,7 +44293,7 @@
       </c>
       <c r="N524" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O524" t="n">
@@ -45119,7 +45119,7 @@
       </c>
       <c r="N534" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O534" t="n">
@@ -47377,7 +47377,7 @@
       </c>
       <c r="N561" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O561" t="n">
@@ -49627,7 +49627,7 @@
       </c>
       <c r="N588" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O588" t="n">
@@ -49714,7 +49714,7 @@
       </c>
       <c r="N589" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O589" t="n">
@@ -50399,7 +50399,7 @@
       </c>
       <c r="N597" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O597" t="n">
@@ -51062,7 +51062,7 @@
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O605" t="n">
@@ -58061,7 +58061,7 @@
       </c>
       <c r="N691" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O691" t="n">
@@ -59811,7 +59811,7 @@
       </c>
       <c r="N712" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O712" t="n">
@@ -60480,7 +60480,7 @@
       </c>
       <c r="N720" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O720" t="n">
@@ -60567,7 +60567,7 @@
       </c>
       <c r="N721" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O721" t="n">
@@ -60991,7 +60991,7 @@
       </c>
       <c r="N726" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O726" t="n">
@@ -62122,7 +62122,7 @@
       </c>
       <c r="N739" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O739" t="n">
@@ -62285,7 +62285,7 @@
       </c>
       <c r="N741" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O741" t="n">
@@ -63361,7 +63361,7 @@
       </c>
       <c r="N754" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O754" t="n">
@@ -63448,7 +63448,7 @@
       </c>
       <c r="N755" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O755" t="n">
@@ -63796,7 +63796,7 @@
       </c>
       <c r="N759" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O759" t="n">
@@ -65220,7 +65220,7 @@
       </c>
       <c r="N776" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O776" t="n">
@@ -66579,7 +66579,7 @@
       </c>
       <c r="N792" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O792" t="n">
@@ -67101,7 +67101,7 @@
       </c>
       <c r="N798" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O798" t="n">
@@ -67351,7 +67351,7 @@
       </c>
       <c r="N801" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O801" t="n">
@@ -67438,7 +67438,7 @@
       </c>
       <c r="N802" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O802" t="n">
@@ -69808,7 +69808,7 @@
       </c>
       <c r="N830" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O830" t="n">
@@ -69971,7 +69971,7 @@
       </c>
       <c r="N832" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O832" t="n">
@@ -70721,7 +70721,7 @@
       </c>
       <c r="N841" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O841" t="n">
@@ -70982,7 +70982,7 @@
       </c>
       <c r="N844" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O844" t="n">
@@ -72417,7 +72417,7 @@
       </c>
       <c r="N861" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O861" t="n">
@@ -75526,7 +75526,7 @@
       </c>
       <c r="N898" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O898" t="n">
@@ -75700,7 +75700,7 @@
       </c>
       <c r="N900" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O900" t="n">
@@ -76385,7 +76385,7 @@
       </c>
       <c r="N908" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O908" t="n">
@@ -77320,7 +77320,7 @@
       </c>
       <c r="N919" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O919" t="n">
@@ -77733,7 +77733,7 @@
       </c>
       <c r="N924" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O924" t="n">
@@ -78461,7 +78461,7 @@
       </c>
       <c r="N933" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O933" t="n">
@@ -79113,7 +79113,7 @@
       </c>
       <c r="N941" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O941" t="n">
@@ -80657,7 +80657,7 @@
       </c>
       <c r="N959" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O959" t="n">
@@ -82571,7 +82571,7 @@
       </c>
       <c r="N981" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O981" t="n">
@@ -83082,7 +83082,7 @@
       </c>
       <c r="N987" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O987" t="n">
@@ -84180,7 +84180,7 @@
       </c>
       <c r="N1000" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1000" t="n">
@@ -85202,7 +85202,7 @@
       </c>
       <c r="N1012" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1012" t="n">
@@ -86235,7 +86235,7 @@
       </c>
       <c r="N1024" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1024" t="n">
@@ -87605,7 +87605,7 @@
       </c>
       <c r="N1040" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1040" t="n">
@@ -90617,7 +90617,7 @@
       </c>
       <c r="N1075" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1075" t="n">
@@ -91738,7 +91738,7 @@
       </c>
       <c r="N1088" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1088" t="n">
@@ -92673,7 +92673,7 @@
       </c>
       <c r="N1099" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1099" t="n">
@@ -93668,7 +93668,7 @@
       </c>
       <c r="N1111" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1111" t="n">
@@ -93929,7 +93929,7 @@
       </c>
       <c r="N1114" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1114" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3641,7 +3641,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O95" t="n">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O137" t="n">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O141" t="n">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O147" t="n">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O170" t="n">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O183" t="n">
@@ -16162,7 +16162,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O188" t="n">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O192" t="n">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O194" t="n">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O253" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O254" t="n">
@@ -25167,7 +25167,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O294" t="n">
@@ -28245,7 +28245,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O331" t="n">
@@ -31303,7 +31303,7 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O369" t="n">
@@ -32477,7 +32477,7 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O383" t="n">
@@ -36498,7 +36498,7 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O432" t="n">
@@ -36672,7 +36672,7 @@
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O434" t="n">
@@ -44619,7 +44619,7 @@
       </c>
       <c r="N528" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O528" t="n">
@@ -45767,7 +45767,7 @@
       </c>
       <c r="N542" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O542" t="n">
@@ -47714,7 +47714,7 @@
       </c>
       <c r="N565" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O565" t="n">
@@ -49888,7 +49888,7 @@
       </c>
       <c r="N591" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O591" t="n">
@@ -59224,7 +59224,7 @@
       </c>
       <c r="N705" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O705" t="n">
@@ -59898,7 +59898,7 @@
       </c>
       <c r="N713" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O713" t="n">
@@ -66405,7 +66405,7 @@
       </c>
       <c r="N790" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O790" t="n">
@@ -73254,7 +73254,7 @@
       </c>
       <c r="N871" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O871" t="n">
@@ -73689,7 +73689,7 @@
       </c>
       <c r="N876" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O876" t="n">
@@ -74124,7 +74124,7 @@
       </c>
       <c r="N881" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O881" t="n">
@@ -79548,7 +79548,7 @@
       </c>
       <c r="N946" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O946" t="n">
@@ -82484,7 +82484,7 @@
       </c>
       <c r="N980" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O980" t="n">
@@ -83669,7 +83669,7 @@
       </c>
       <c r="N994" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O994" t="n">
@@ -84680,7 +84680,7 @@
       </c>
       <c r="N1006" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1006" t="n">
@@ -85637,7 +85637,7 @@
       </c>
       <c r="N1017" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1017" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -6011,7 +6011,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O90" t="n">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O106" t="n">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O112" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O155" t="n">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O221" t="n">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O224" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O288" t="n">
@@ -24835,7 +24835,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O290" t="n">
@@ -26821,7 +26821,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O314" t="n">
@@ -26995,7 +26995,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O316" t="n">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O317" t="n">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O392" t="n">
@@ -34204,7 +34204,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O405" t="n">
@@ -36585,7 +36585,7 @@
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O433" t="n">
@@ -46279,7 +46279,7 @@
       </c>
       <c r="N548" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O548" t="n">
@@ -49975,7 +49975,7 @@
       </c>
       <c r="N592" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O592" t="n">
@@ -50062,7 +50062,7 @@
       </c>
       <c r="N593" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O593" t="n">
@@ -57887,7 +57887,7 @@
       </c>
       <c r="N689" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O689" t="n">
@@ -58485,7 +58485,7 @@
       </c>
       <c r="N696" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O696" t="n">
@@ -59061,7 +59061,7 @@
       </c>
       <c r="N703" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O703" t="n">
@@ -61165,7 +61165,7 @@
       </c>
       <c r="N728" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O728" t="n">
@@ -62872,7 +62872,7 @@
       </c>
       <c r="N748" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O748" t="n">
@@ -65383,7 +65383,7 @@
       </c>
       <c r="N778" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O778" t="n">
@@ -66057,7 +66057,7 @@
       </c>
       <c r="N786" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O786" t="n">
@@ -66144,7 +66144,7 @@
       </c>
       <c r="N787" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O787" t="n">
@@ -66318,7 +66318,7 @@
       </c>
       <c r="N789" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O789" t="n">
@@ -81353,7 +81353,7 @@
       </c>
       <c r="N967" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O967" t="n">
@@ -82832,7 +82832,7 @@
       </c>
       <c r="N984" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O984" t="n">
@@ -89073,7 +89073,7 @@
       </c>
       <c r="N1057" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1057" t="n">
@@ -89421,7 +89421,7 @@
       </c>
       <c r="N1061" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1061" t="n">
@@ -89508,7 +89508,7 @@
       </c>
       <c r="N1062" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1062" t="n">
@@ -89758,7 +89758,7 @@
       </c>
       <c r="N1065" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1065" t="n">
@@ -90019,7 +90019,7 @@
       </c>
       <c r="N1068" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1068" t="n">
@@ -90367,7 +90367,7 @@
       </c>
       <c r="N1072" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1072" t="n">
@@ -91825,7 +91825,7 @@
       </c>
       <c r="N1089" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1089" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -10915,7 +10915,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O126" t="n">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O129" t="n">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O172" t="n">
@@ -45451,7 +45451,7 @@
       </c>
       <c r="N538" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O538" t="n">
@@ -53862,7 +53862,7 @@
       </c>
       <c r="N638" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O638" t="n">
@@ -54627,7 +54627,7 @@
       </c>
       <c r="N648" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O648" t="n">
@@ -54709,7 +54709,7 @@
       </c>
       <c r="N649" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O649" t="n">
@@ -54791,7 +54791,7 @@
       </c>
       <c r="N650" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O650" t="n">
@@ -54944,7 +54944,7 @@
       </c>
       <c r="N652" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O652" t="n">
@@ -55026,7 +55026,7 @@
       </c>
       <c r="N653" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O653" t="n">
@@ -55332,7 +55332,7 @@
       </c>
       <c r="N657" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O657" t="n">
@@ -55496,7 +55496,7 @@
       </c>
       <c r="N659" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O659" t="n">
@@ -55660,7 +55660,7 @@
       </c>
       <c r="N661" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O661" t="n">
@@ -84517,7 +84517,7 @@
       </c>
       <c r="N1004" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1004" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1032,7 +1032,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O65" t="n">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O109" t="n">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O118" t="n">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O121" t="n">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O135" t="n">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O184" t="n">
@@ -16760,7 +16760,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O195" t="n">
@@ -17603,7 +17603,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O205" t="n">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O209" t="n">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O210" t="n">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O212" t="n">
@@ -18549,7 +18549,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O216" t="n">
@@ -19147,7 +19147,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O223" t="n">
@@ -19495,7 +19495,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O227" t="n">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O249" t="n">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O256" t="n">
@@ -22361,7 +22361,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O261" t="n">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O263" t="n">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O264" t="n">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O320" t="n">
@@ -28419,7 +28419,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O333" t="n">
@@ -31064,7 +31064,7 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O366" t="n">
@@ -31390,7 +31390,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O370" t="n">
@@ -31629,7 +31629,7 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O373" t="n">
@@ -35835,7 +35835,7 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O424" t="n">
@@ -38564,7 +38564,7 @@
       </c>
       <c r="N456" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O456" t="n">
@@ -41347,7 +41347,7 @@
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O489" t="n">
@@ -43945,7 +43945,7 @@
       </c>
       <c r="N520" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O520" t="n">
@@ -46866,7 +46866,7 @@
       </c>
       <c r="N555" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O555" t="n">
@@ -55997,7 +55997,7 @@
       </c>
       <c r="N665" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O665" t="n">
@@ -58148,7 +58148,7 @@
       </c>
       <c r="N692" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O692" t="n">
@@ -64122,7 +64122,7 @@
       </c>
       <c r="N763" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O763" t="n">
@@ -75787,7 +75787,7 @@
       </c>
       <c r="N901" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O901" t="n">
@@ -76124,7 +76124,7 @@
       </c>
       <c r="N905" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O905" t="n">
@@ -76646,7 +76646,7 @@
       </c>
       <c r="N911" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O911" t="n">
@@ -77157,7 +77157,7 @@
       </c>
       <c r="N917" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O917" t="n">
@@ -80396,7 +80396,7 @@
       </c>
       <c r="N956" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O956" t="n">
@@ -81179,7 +81179,7 @@
       </c>
       <c r="N965" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O965" t="n">
@@ -82397,7 +82397,7 @@
       </c>
       <c r="N979" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O979" t="n">
@@ -82658,7 +82658,7 @@
       </c>
       <c r="N982" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O982" t="n">
@@ -82919,7 +82919,7 @@
       </c>
       <c r="N985" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O985" t="n">
@@ -85550,7 +85550,7 @@
       </c>
       <c r="N1016" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1016" t="n">
@@ -86398,7 +86398,7 @@
       </c>
       <c r="N1026" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1026" t="n">
@@ -89334,7 +89334,7 @@
       </c>
       <c r="N1060" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1060" t="n">
@@ -91400,7 +91400,7 @@
       </c>
       <c r="N1084" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1084" t="n">
@@ -92499,7 +92499,7 @@
       </c>
       <c r="N1097" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1097" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -41695,7 +41695,7 @@
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O493" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -8871,7 +8871,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O279" t="n">
@@ -25728,7 +25728,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O301" t="n">
@@ -30890,7 +30890,7 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O364" t="n">
@@ -40836,7 +40836,7 @@
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O483" t="n">
@@ -69134,7 +69134,7 @@
       </c>
       <c r="N822" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O822" t="n">
@@ -73602,7 +73602,7 @@
       </c>
       <c r="N875" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O875" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O156" t="n">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O162" t="n">
@@ -16412,7 +16412,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O191" t="n">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O196" t="n">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O269" t="n">
@@ -24313,7 +24313,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O284" t="n">
@@ -29006,7 +29006,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O340" t="n">
@@ -36846,7 +36846,7 @@
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O436" t="n">
@@ -38129,7 +38129,7 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O451" t="n">
@@ -45293,7 +45293,7 @@
       </c>
       <c r="N536" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O536" t="n">
@@ -50486,7 +50486,7 @@
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O598" t="n">
@@ -52943,7 +52943,7 @@
       </c>
       <c r="N627" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O627" t="n">
@@ -57637,7 +57637,7 @@
       </c>
       <c r="N686" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O686" t="n">
@@ -67188,7 +67188,7 @@
       </c>
       <c r="N799" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O799" t="n">
@@ -68710,7 +68710,7 @@
       </c>
       <c r="N817" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O817" t="n">
@@ -73776,7 +73776,7 @@
       </c>
       <c r="N877" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O877" t="n">
@@ -80222,7 +80222,7 @@
       </c>
       <c r="N954" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O954" t="n">
@@ -80570,7 +80570,7 @@
       </c>
       <c r="N958" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O958" t="n">
@@ -85463,7 +85463,7 @@
       </c>
       <c r="N1015" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1015" t="n">
@@ -87257,7 +87257,7 @@
       </c>
       <c r="N1036" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1036" t="n">
@@ -88638,7 +88638,7 @@
       </c>
       <c r="N1052" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1052" t="n">
@@ -89932,7 +89932,7 @@
       </c>
       <c r="N1067" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1067" t="n">
@@ -93755,7 +93755,7 @@
       </c>
       <c r="N1112" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1112" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -19582,7 +19582,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O228" t="n">
@@ -29827,7 +29827,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O350" t="n">
@@ -39575,7 +39575,7 @@
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O468" t="n">
@@ -39749,7 +39749,7 @@
       </c>
       <c r="N470" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O470" t="n">
@@ -64470,7 +64470,7 @@
       </c>
       <c r="N767" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O767" t="n">
@@ -69569,7 +69569,7 @@
       </c>
       <c r="N827" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O827" t="n">
@@ -93842,7 +93842,7 @@
       </c>
       <c r="N1113" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1113" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -9393,7 +9393,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O108" t="n">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O169" t="n">
@@ -24139,7 +24139,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O282" t="n">
@@ -28332,7 +28332,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O332" t="n">
@@ -34378,7 +34378,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O407" t="n">
@@ -34639,7 +34639,7 @@
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O410" t="n">
@@ -46192,7 +46192,7 @@
       </c>
       <c r="N547" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O547" t="n">
@@ -59311,7 +59311,7 @@
       </c>
       <c r="N706" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O706" t="n">
@@ -67525,7 +67525,7 @@
       </c>
       <c r="N803" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O803" t="n">
@@ -87953,7 +87953,7 @@
       </c>
       <c r="N1044" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1044" t="n">
@@ -90878,7 +90878,7 @@
       </c>
       <c r="N1078" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1078" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -37792,7 +37792,7 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O447" t="n">
@@ -56258,7 +56258,7 @@
       </c>
       <c r="N668" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O668" t="n">
@@ -76733,7 +76733,7 @@
       </c>
       <c r="N912" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O912" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -19843,7 +19843,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O231" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -26152,7 +26152,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O306" t="n">
@@ -26734,7 +26734,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O313" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -13068,7 +13068,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O151" t="n">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O158" t="n">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O260" t="n">
@@ -24748,7 +24748,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O289" t="n">
@@ -27419,7 +27419,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O321" t="n">
@@ -39488,7 +39488,7 @@
       </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O467" t="n">
@@ -42119,7 +42119,7 @@
       </c>
       <c r="N498" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O498" t="n">
@@ -45931,7 +45931,7 @@
       </c>
       <c r="N544" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O544" t="n">
@@ -60741,7 +60741,7 @@
       </c>
       <c r="N723" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O723" t="n">
@@ -71243,7 +71243,7 @@
       </c>
       <c r="N847" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O847" t="n">
@@ -78776,7 +78776,7 @@
       </c>
       <c r="N937" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O937" t="n">
@@ -82223,7 +82223,7 @@
       </c>
       <c r="N977" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O977" t="n">
@@ -92151,7 +92151,7 @@
       </c>
       <c r="N1093" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1093" t="n">
@@ -93173,7 +93173,7 @@
       </c>
       <c r="N1105" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1105" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -17777,7 +17777,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O207" t="n">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O245" t="n">
@@ -60230,7 +60230,7 @@
       </c>
       <c r="N717" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O717" t="n">
@@ -73341,7 +73341,7 @@
       </c>
       <c r="N872" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O872" t="n">
@@ -74298,7 +74298,7 @@
       </c>
       <c r="N883" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O883" t="n">
@@ -87692,7 +87692,7 @@
       </c>
       <c r="N1041" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1041" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -91574,7 +91574,7 @@
       </c>
       <c r="N1086" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1086" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -63535,7 +63535,7 @@
       </c>
       <c r="N756" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O756" t="n">
@@ -74961,7 +74961,7 @@
       </c>
       <c r="N891" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O891" t="n">
@@ -86822,7 +86822,7 @@
       </c>
       <c r="N1031" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1031" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -11263,7 +11263,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O130" t="n">
@@ -18810,7 +18810,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O219" t="n">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O270" t="n">
@@ -25978,7 +25978,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O304" t="n">
@@ -27669,7 +27669,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O324" t="n">
@@ -35487,7 +35487,7 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O420" t="n">
@@ -39923,7 +39923,7 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O472" t="n">
@@ -43521,7 +43521,7 @@
       </c>
       <c r="N515" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O515" t="n">
@@ -44945,7 +44945,7 @@
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O532" t="n">
@@ -50812,7 +50812,7 @@
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O602" t="n">
@@ -61513,7 +61513,7 @@
       </c>
       <c r="N732" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O732" t="n">
@@ -83169,7 +83169,7 @@
       </c>
       <c r="N988" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O988" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -12818,7 +12818,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O148" t="n">
@@ -66840,7 +66840,7 @@
       </c>
       <c r="N795" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O795" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -7767,7 +7767,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O89" t="n">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O226" t="n">
@@ -41521,7 +41521,7 @@
       </c>
       <c r="N491" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O491" t="n">
@@ -41608,7 +41608,7 @@
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O492" t="n">
@@ -52160,7 +52160,7 @@
       </c>
       <c r="N618" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O618" t="n">
@@ -52769,7 +52769,7 @@
       </c>
       <c r="N625" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O625" t="n">
@@ -53356,7 +53356,7 @@
       </c>
       <c r="N632" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O632" t="n">
@@ -59398,7 +59398,7 @@
       </c>
       <c r="N707" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O707" t="n">
@@ -61426,7 +61426,7 @@
       </c>
       <c r="N731" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O731" t="n">
@@ -71819,7 +71819,7 @@
       </c>
       <c r="N854" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O854" t="n">
@@ -74037,7 +74037,7 @@
       </c>
       <c r="N880" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O880" t="n">
@@ -74385,7 +74385,7 @@
       </c>
       <c r="N884" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O884" t="n">
@@ -77070,7 +77070,7 @@
       </c>
       <c r="N916" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O916" t="n">
@@ -79961,7 +79961,7 @@
       </c>
       <c r="N951" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O951" t="n">
@@ -80309,7 +80309,7 @@
       </c>
       <c r="N955" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O955" t="n">
@@ -84267,7 +84267,7 @@
       </c>
       <c r="N1001" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1001" t="n">
@@ -87344,7 +87344,7 @@
       </c>
       <c r="N1037" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1037" t="n">
@@ -87431,7 +87431,7 @@
       </c>
       <c r="N1038" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1038" t="n">
@@ -87518,7 +87518,7 @@
       </c>
       <c r="N1039" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1039" t="n">
@@ -88040,7 +88040,7 @@
       </c>
       <c r="N1045" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1045" t="n">
@@ -88127,7 +88127,7 @@
       </c>
       <c r="N1046" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1046" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -8197,7 +8197,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O94" t="n">
@@ -25080,7 +25080,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O293" t="n">
@@ -35139,7 +35139,7 @@
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O416" t="n">
@@ -42934,7 +42934,7 @@
       </c>
       <c r="N508" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O508" t="n">
@@ -61252,7 +61252,7 @@
       </c>
       <c r="N729" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O729" t="n">
@@ -76298,7 +76298,7 @@
       </c>
       <c r="N907" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O907" t="n">
@@ -78135,7 +78135,7 @@
       </c>
       <c r="N929" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O929" t="n">
@@ -80831,7 +80831,7 @@
       </c>
       <c r="N961" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O961" t="n">
@@ -83256,7 +83256,7 @@
       </c>
       <c r="N989" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O989" t="n">
@@ -86485,7 +86485,7 @@
       </c>
       <c r="N1027" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1027" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -20093,7 +20093,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O234" t="n">
@@ -51736,7 +51736,7 @@
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O613" t="n">
@@ -62035,7 +62035,7 @@
       </c>
       <c r="N738" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O738" t="n">
@@ -68623,7 +68623,7 @@
       </c>
       <c r="N816" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O816" t="n">
@@ -77407,7 +77407,7 @@
       </c>
       <c r="N920" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O920" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4152,7 +4152,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O83" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O96" t="n">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O98" t="n">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O99" t="n">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O164" t="n">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O208" t="n">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O225" t="n">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O236" t="n">
@@ -21441,7 +21441,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O250" t="n">
@@ -23215,7 +23215,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O271" t="n">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O273" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O311" t="n">
@@ -32814,7 +32814,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O387" t="n">
@@ -34291,7 +34291,7 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O406" t="n">
@@ -35226,7 +35226,7 @@
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O417" t="n">
@@ -40662,7 +40662,7 @@
       </c>
       <c r="N481" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O481" t="n">
@@ -40749,7 +40749,7 @@
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O482" t="n">
@@ -43021,7 +43021,7 @@
       </c>
       <c r="N509" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O509" t="n">
@@ -46529,7 +46529,7 @@
       </c>
       <c r="N551" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O551" t="n">
@@ -47627,7 +47627,7 @@
       </c>
       <c r="N564" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O564" t="n">
@@ -49366,7 +49366,7 @@
       </c>
       <c r="N585" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O585" t="n">
@@ -49801,7 +49801,7 @@
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O590" t="n">
@@ -50236,7 +50236,7 @@
       </c>
       <c r="N595" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O595" t="n">
@@ -52334,7 +52334,7 @@
       </c>
       <c r="N620" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O620" t="n">
@@ -63122,7 +63122,7 @@
       </c>
       <c r="N751" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O751" t="n">
@@ -67612,7 +67612,7 @@
       </c>
       <c r="N804" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O804" t="n">
@@ -67699,7 +67699,7 @@
       </c>
       <c r="N805" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O805" t="n">
@@ -83919,7 +83919,7 @@
       </c>
       <c r="N997" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O997" t="n">
@@ -85898,7 +85898,7 @@
       </c>
       <c r="N1020" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1020" t="n">
@@ -87083,7 +87083,7 @@
       </c>
       <c r="N1034" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1034" t="n">
@@ -92325,7 +92325,7 @@
       </c>
       <c r="N1095" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1095" t="n">
@@ -95027,7 +95027,7 @@
       </c>
       <c r="N1127" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O1127" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -604,17 +604,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -623,6 +623,17 @@
       <c r="P2" t="n">
         <v>-77.11141000000001</v>
       </c>
+      <c r="Q2" t="n">
+        <v>-12.04819</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-77.11141000000001</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -675,17 +686,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -694,6 +705,17 @@
       <c r="P3" t="n">
         <v>-77.11141000000001</v>
       </c>
+      <c r="Q3" t="n">
+        <v>-12.04819</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-77.11141000000001</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -746,17 +768,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -765,6 +787,17 @@
       <c r="P4" t="n">
         <v>-77.11141000000001</v>
       </c>
+      <c r="Q4" t="n">
+        <v>-12.04819</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-77.11141000000001</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1050,17 +1083,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1069,6 +1102,17 @@
       <c r="P8" t="n">
         <v>-77.20547999999999</v>
       </c>
+      <c r="Q8" t="n">
+        <v>-11.49353</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-77.20547999999999</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1354,17 +1398,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1373,6 +1417,17 @@
       <c r="P12" t="n">
         <v>-77.09483</v>
       </c>
+      <c r="Q12" t="n">
+        <v>-12.04235</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-77.09483</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1886,17 +1941,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -1905,6 +1960,17 @@
       <c r="P19" t="n">
         <v>-77.09125</v>
       </c>
+      <c r="Q19" t="n">
+        <v>-12.03965</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-77.09125</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1962,17 +2028,17 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -1981,6 +2047,17 @@
       <c r="P20" t="n">
         <v>-77.05362</v>
       </c>
+      <c r="Q20" t="n">
+        <v>-12.07519</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-77.05362</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2418,17 +2495,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -2437,6 +2514,17 @@
       <c r="P26" t="n">
         <v>-77.05362</v>
       </c>
+      <c r="Q26" t="n">
+        <v>-12.07519</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-77.05362</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4470,17 +4558,17 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O53" t="n">
@@ -4489,6 +4577,17 @@
       <c r="P53" t="n">
         <v>-77.30521</v>
       </c>
+      <c r="Q53" t="n">
+        <v>-11.48897</v>
+      </c>
+      <c r="R53" t="n">
+        <v>-77.30521</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4845,17 +4944,17 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O58" t="n">
@@ -4864,6 +4963,17 @@
       <c r="P58" t="n">
         <v>-77.21205</v>
       </c>
+      <c r="Q58" t="n">
+        <v>-11.4988</v>
+      </c>
+      <c r="R58" t="n">
+        <v>-77.21205</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5529,17 +5639,17 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O67" t="n">
@@ -5548,6 +5658,17 @@
       <c r="P67" t="n">
         <v>-77.05175</v>
       </c>
+      <c r="Q67" t="n">
+        <v>-12.07205</v>
+      </c>
+      <c r="R67" t="n">
+        <v>-77.05175</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5757,17 +5878,17 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -5776,6 +5897,17 @@
       <c r="P70" t="n">
         <v>-77.08637</v>
       </c>
+      <c r="Q70" t="n">
+        <v>-12.03793</v>
+      </c>
+      <c r="R70" t="n">
+        <v>-77.08637</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5985,17 +6117,17 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O73" t="n">
@@ -6004,6 +6136,17 @@
       <c r="P73" t="n">
         <v>-77.28274</v>
       </c>
+      <c r="Q73" t="n">
+        <v>-11.53767</v>
+      </c>
+      <c r="R73" t="n">
+        <v>-77.28274</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7136,17 +7279,17 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O88" t="n">
@@ -7155,6 +7298,17 @@
       <c r="P88" t="n">
         <v>-77.1007</v>
       </c>
+      <c r="Q88" t="n">
+        <v>-12.0543</v>
+      </c>
+      <c r="R88" t="n">
+        <v>-77.1007</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7744,17 +7898,17 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O96" t="n">
@@ -7763,6 +7917,17 @@
       <c r="P96" t="n">
         <v>-77.20243000000001</v>
       </c>
+      <c r="Q96" t="n">
+        <v>-11.49344</v>
+      </c>
+      <c r="R96" t="n">
+        <v>-77.20243000000001</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7820,17 +7985,17 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -7839,6 +8004,17 @@
       <c r="P97" t="n">
         <v>-77.26591999999999</v>
       </c>
+      <c r="Q97" t="n">
+        <v>-11.56206</v>
+      </c>
+      <c r="R97" t="n">
+        <v>-77.26591999999999</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8276,17 +8452,17 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -8295,6 +8471,17 @@
       <c r="P103" t="n">
         <v>-77.20744999999999</v>
       </c>
+      <c r="Q103" t="n">
+        <v>-11.49554</v>
+      </c>
+      <c r="R103" t="n">
+        <v>-77.20744999999999</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8732,17 +8919,17 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O109" t="n">
@@ -8751,6 +8938,17 @@
       <c r="P109" t="n">
         <v>-77.29152000000001</v>
       </c>
+      <c r="Q109" t="n">
+        <v>-11.52134</v>
+      </c>
+      <c r="R109" t="n">
+        <v>-77.29152000000001</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8808,17 +9006,17 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -8827,6 +9025,17 @@
       <c r="P110" t="n">
         <v>-77.27103</v>
       </c>
+      <c r="Q110" t="n">
+        <v>-11.56531</v>
+      </c>
+      <c r="R110" t="n">
+        <v>-77.27103</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10100,17 +10309,17 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -10119,6 +10328,17 @@
       <c r="P127" t="n">
         <v>-77.20529999999999</v>
       </c>
+      <c r="Q127" t="n">
+        <v>-11.49469</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-77.20529999999999</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10708,17 +10928,17 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O135" t="n">
@@ -10727,6 +10947,17 @@
       <c r="P135" t="n">
         <v>-77.04415</v>
       </c>
+      <c r="Q135" t="n">
+        <v>-12.06638</v>
+      </c>
+      <c r="R135" t="n">
+        <v>-77.04415</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11240,17 +11471,17 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O142" t="n">
@@ -11259,6 +11490,17 @@
       <c r="P142" t="n">
         <v>-77.20499</v>
       </c>
+      <c r="Q142" t="n">
+        <v>-11.49331</v>
+      </c>
+      <c r="R142" t="n">
+        <v>-77.20499</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12076,17 +12318,17 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O153" t="n">
@@ -12095,6 +12337,17 @@
       <c r="P153" t="n">
         <v>-77.26701</v>
       </c>
+      <c r="Q153" t="n">
+        <v>-11.569</v>
+      </c>
+      <c r="R153" t="n">
+        <v>-77.26701</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12380,17 +12633,17 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O157" t="n">
@@ -12399,6 +12652,17 @@
       <c r="P157" t="n">
         <v>-77.20465</v>
       </c>
+      <c r="Q157" t="n">
+        <v>-11.50231</v>
+      </c>
+      <c r="R157" t="n">
+        <v>-77.20465</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12608,17 +12872,17 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O160" t="n">
@@ -12627,6 +12891,17 @@
       <c r="P160" t="n">
         <v>-77.20708999999999</v>
       </c>
+      <c r="Q160" t="n">
+        <v>-11.49382</v>
+      </c>
+      <c r="R160" t="n">
+        <v>-77.20708999999999</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13444,17 +13719,17 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O171" t="n">
@@ -13463,6 +13738,17 @@
       <c r="P171" t="n">
         <v>-77.06688</v>
       </c>
+      <c r="Q171" t="n">
+        <v>-12.06962</v>
+      </c>
+      <c r="R171" t="n">
+        <v>-77.06688</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13520,17 +13806,17 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O172" t="n">
@@ -13539,6 +13825,17 @@
       <c r="P172" t="n">
         <v>-77.06688</v>
       </c>
+      <c r="Q172" t="n">
+        <v>-12.06962</v>
+      </c>
+      <c r="R172" t="n">
+        <v>-77.06688</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14280,17 +14577,17 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O182" t="n">
@@ -14299,6 +14596,17 @@
       <c r="P182" t="n">
         <v>-77.20480999999999</v>
       </c>
+      <c r="Q182" t="n">
+        <v>-11.4944</v>
+      </c>
+      <c r="R182" t="n">
+        <v>-77.20480999999999</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -14356,17 +14664,17 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O183" t="n">
@@ -14375,6 +14683,17 @@
       <c r="P183" t="n">
         <v>-77.27021999999999</v>
       </c>
+      <c r="Q183" t="n">
+        <v>-11.57415</v>
+      </c>
+      <c r="R183" t="n">
+        <v>-77.27021999999999</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -17776,17 +18095,17 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O228" t="n">
@@ -17795,6 +18114,17 @@
       <c r="P228" t="n">
         <v>-77.26899</v>
       </c>
+      <c r="Q228" t="n">
+        <v>-11.56419</v>
+      </c>
+      <c r="R228" t="n">
+        <v>-77.26899</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -21120,17 +21450,17 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O272" t="n">
@@ -21139,6 +21469,17 @@
       <c r="P272" t="n">
         <v>-77.26558</v>
       </c>
+      <c r="Q272" t="n">
+        <v>-11.56378</v>
+      </c>
+      <c r="R272" t="n">
+        <v>-77.26558</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -22032,17 +22373,17 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O284" t="n">
@@ -22051,6 +22392,17 @@
       <c r="P284" t="n">
         <v>-77.2046</v>
       </c>
+      <c r="Q284" t="n">
+        <v>-11.5022</v>
+      </c>
+      <c r="R284" t="n">
+        <v>-77.2046</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -23096,17 +23448,17 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O298" t="n">
@@ -23115,6 +23467,17 @@
       <c r="P298" t="n">
         <v>-77.30462</v>
       </c>
+      <c r="Q298" t="n">
+        <v>-11.489</v>
+      </c>
+      <c r="R298" t="n">
+        <v>-77.30462</v>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -24008,17 +24371,17 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O310" t="n">
@@ -24027,6 +24390,17 @@
       <c r="P310" t="n">
         <v>-77.0437</v>
       </c>
+      <c r="Q310" t="n">
+        <v>-12.07394</v>
+      </c>
+      <c r="R310" t="n">
+        <v>-77.0437</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -24692,17 +25066,17 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O319" t="n">
@@ -24711,6 +25085,17 @@
       <c r="P319" t="n">
         <v>-77.29062</v>
       </c>
+      <c r="Q319" t="n">
+        <v>-11.52408</v>
+      </c>
+      <c r="R319" t="n">
+        <v>-77.29062</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -24768,17 +25153,17 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O320" t="n">
@@ -24787,6 +25172,17 @@
       <c r="P320" t="n">
         <v>-77.26671</v>
       </c>
+      <c r="Q320" t="n">
+        <v>-11.57045</v>
+      </c>
+      <c r="R320" t="n">
+        <v>-77.26671</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -24844,17 +25240,17 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O321" t="n">
@@ -24863,6 +25259,17 @@
       <c r="P321" t="n">
         <v>-77.26705</v>
       </c>
+      <c r="Q321" t="n">
+        <v>-11.56875</v>
+      </c>
+      <c r="R321" t="n">
+        <v>-77.26705</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -25219,17 +25626,17 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O326" t="n">
@@ -25238,6 +25645,17 @@
       <c r="P326" t="n">
         <v>-77.2561</v>
       </c>
+      <c r="Q326" t="n">
+        <v>-11.59477</v>
+      </c>
+      <c r="R326" t="n">
+        <v>-77.2561</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -25523,17 +25941,17 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O330" t="n">
@@ -25542,6 +25960,17 @@
       <c r="P330" t="n">
         <v>-77.22461</v>
       </c>
+      <c r="Q330" t="n">
+        <v>-11.61802</v>
+      </c>
+      <c r="R330" t="n">
+        <v>-77.22461</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -26055,17 +26484,17 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O337" t="n">
@@ -26074,6 +26503,17 @@
       <c r="P337" t="n">
         <v>-77.2692</v>
       </c>
+      <c r="Q337" t="n">
+        <v>-11.56196</v>
+      </c>
+      <c r="R337" t="n">
+        <v>-77.2692</v>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -26207,17 +26647,17 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O339" t="n">
@@ -26226,6 +26666,17 @@
       <c r="P339" t="n">
         <v>-77.05812</v>
       </c>
+      <c r="Q339" t="n">
+        <v>-12.07852</v>
+      </c>
+      <c r="R339" t="n">
+        <v>-77.05812</v>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -26359,17 +26810,17 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O341" t="n">
@@ -26378,6 +26829,17 @@
       <c r="P341" t="n">
         <v>-77.20643</v>
       </c>
+      <c r="Q341" t="n">
+        <v>-11.49603</v>
+      </c>
+      <c r="R341" t="n">
+        <v>-77.20643</v>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -26435,17 +26897,17 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O342" t="n">
@@ -26454,6 +26916,17 @@
       <c r="P342" t="n">
         <v>-77.20426</v>
       </c>
+      <c r="Q342" t="n">
+        <v>-11.50188</v>
+      </c>
+      <c r="R342" t="n">
+        <v>-77.20426</v>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -26511,17 +26984,17 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O343" t="n">
@@ -26530,6 +27003,17 @@
       <c r="P343" t="n">
         <v>-77.20458000000001</v>
       </c>
+      <c r="Q343" t="n">
+        <v>-11.50216</v>
+      </c>
+      <c r="R343" t="n">
+        <v>-77.20458000000001</v>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -27028,17 +27512,17 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O350" t="n">
@@ -27047,6 +27531,17 @@
       <c r="P350" t="n">
         <v>-77.06871</v>
       </c>
+      <c r="Q350" t="n">
+        <v>-12.07229</v>
+      </c>
+      <c r="R350" t="n">
+        <v>-77.06871</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -27560,17 +28055,17 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O357" t="n">
@@ -27579,6 +28074,17 @@
       <c r="P357" t="n">
         <v>-77.04546999999999</v>
       </c>
+      <c r="Q357" t="n">
+        <v>-12.06886</v>
+      </c>
+      <c r="R357" t="n">
+        <v>-77.04546999999999</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -27864,17 +28370,17 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O361" t="n">
@@ -27883,6 +28389,17 @@
       <c r="P361" t="n">
         <v>-77.26130000000001</v>
       </c>
+      <c r="Q361" t="n">
+        <v>-11.58997</v>
+      </c>
+      <c r="R361" t="n">
+        <v>-77.26130000000001</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -28320,17 +28837,17 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O367" t="n">
@@ -28339,6 +28856,17 @@
       <c r="P367" t="n">
         <v>-77.20245</v>
       </c>
+      <c r="Q367" t="n">
+        <v>-11.4922</v>
+      </c>
+      <c r="R367" t="n">
+        <v>-77.20245</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -28624,17 +29152,17 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O371" t="n">
@@ -28643,6 +29171,17 @@
       <c r="P371" t="n">
         <v>-77.09242</v>
       </c>
+      <c r="Q371" t="n">
+        <v>-12.04156</v>
+      </c>
+      <c r="R371" t="n">
+        <v>-77.09242</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -29759,17 +30298,17 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O386" t="n">
@@ -29778,6 +30317,17 @@
       <c r="P386" t="n">
         <v>-77.26981000000001</v>
       </c>
+      <c r="Q386" t="n">
+        <v>-11.56207</v>
+      </c>
+      <c r="R386" t="n">
+        <v>-77.26981000000001</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -30443,17 +30993,17 @@
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O395" t="n">
@@ -30462,6 +31012,17 @@
       <c r="P395" t="n">
         <v>-77.06577</v>
       </c>
+      <c r="Q395" t="n">
+        <v>-12.07271</v>
+      </c>
+      <c r="R395" t="n">
+        <v>-77.06577</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -32267,17 +32828,17 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O419" t="n">
@@ -32286,6 +32847,17 @@
       <c r="P419" t="n">
         <v>-77.26658</v>
       </c>
+      <c r="Q419" t="n">
+        <v>-11.56849</v>
+      </c>
+      <c r="R419" t="n">
+        <v>-77.26658</v>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -32571,17 +33143,17 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O423" t="n">
@@ -32590,6 +33162,17 @@
       <c r="P423" t="n">
         <v>-77.05492</v>
       </c>
+      <c r="Q423" t="n">
+        <v>-12.0699</v>
+      </c>
+      <c r="R423" t="n">
+        <v>-77.05492</v>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -32647,17 +33230,17 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O424" t="n">
@@ -32666,6 +33249,17 @@
       <c r="P424" t="n">
         <v>-77.2088</v>
       </c>
+      <c r="Q424" t="n">
+        <v>-11.49595</v>
+      </c>
+      <c r="R424" t="n">
+        <v>-77.2088</v>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -32875,17 +33469,17 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O427" t="n">
@@ -32894,6 +33488,17 @@
       <c r="P427" t="n">
         <v>-77.20458000000001</v>
       </c>
+      <c r="Q427" t="n">
+        <v>-11.50209</v>
+      </c>
+      <c r="R427" t="n">
+        <v>-77.20458000000001</v>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -33711,17 +34316,17 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O438" t="n">
@@ -33730,6 +34335,17 @@
       <c r="P438" t="n">
         <v>-77.04541999999999</v>
       </c>
+      <c r="Q438" t="n">
+        <v>-12.06869</v>
+      </c>
+      <c r="R438" t="n">
+        <v>-77.04541999999999</v>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -33863,17 +34479,17 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O440" t="n">
@@ -33882,6 +34498,17 @@
       <c r="P440" t="n">
         <v>-77.26597</v>
       </c>
+      <c r="Q440" t="n">
+        <v>-11.55977</v>
+      </c>
+      <c r="R440" t="n">
+        <v>-77.26597</v>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -34775,17 +35402,17 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O452" t="n">
@@ -34794,6 +35421,17 @@
       <c r="P452" t="n">
         <v>-77.24769999999999</v>
       </c>
+      <c r="Q452" t="n">
+        <v>-11.60067</v>
+      </c>
+      <c r="R452" t="n">
+        <v>-77.24769999999999</v>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -35155,17 +35793,17 @@
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O457" t="n">
@@ -35174,6 +35812,17 @@
       <c r="P457" t="n">
         <v>-77.09748999999999</v>
       </c>
+      <c r="Q457" t="n">
+        <v>-12.05614</v>
+      </c>
+      <c r="R457" t="n">
+        <v>-77.09748999999999</v>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -35231,17 +35880,17 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O458" t="n">
@@ -35250,6 +35899,17 @@
       <c r="P458" t="n">
         <v>-77.1114</v>
       </c>
+      <c r="Q458" t="n">
+        <v>-12.04829</v>
+      </c>
+      <c r="R458" t="n">
+        <v>-77.1114</v>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -35763,17 +36423,17 @@
       </c>
       <c r="L465" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O465" t="n">
@@ -35782,6 +36442,17 @@
       <c r="P465" t="n">
         <v>-77.26667</v>
       </c>
+      <c r="Q465" t="n">
+        <v>-11.56865</v>
+      </c>
+      <c r="R465" t="n">
+        <v>-77.26667</v>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -36371,17 +37042,17 @@
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O473" t="n">
@@ -36390,6 +37061,17 @@
       <c r="P473" t="n">
         <v>-77.20458000000001</v>
       </c>
+      <c r="Q473" t="n">
+        <v>-11.50206</v>
+      </c>
+      <c r="R473" t="n">
+        <v>-77.20458000000001</v>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -36447,17 +37129,17 @@
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O474" t="n">
@@ -36466,6 +37148,17 @@
       <c r="P474" t="n">
         <v>-77.21061</v>
       </c>
+      <c r="Q474" t="n">
+        <v>-11.49873</v>
+      </c>
+      <c r="R474" t="n">
+        <v>-77.21061</v>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -38312,17 +39005,17 @@
       </c>
       <c r="L499" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O499" t="n">
@@ -38331,6 +39024,17 @@
       <c r="P499" t="n">
         <v>-77.06865999999999</v>
       </c>
+      <c r="Q499" t="n">
+        <v>-12.0718</v>
+      </c>
+      <c r="R499" t="n">
+        <v>-77.06865999999999</v>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -38768,17 +39472,17 @@
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M505" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N505" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O505" t="n">
@@ -38787,6 +39491,17 @@
       <c r="P505" t="n">
         <v>-77.2077</v>
       </c>
+      <c r="Q505" t="n">
+        <v>-11.49519</v>
+      </c>
+      <c r="R505" t="n">
+        <v>-77.2077</v>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -38920,17 +39635,17 @@
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N507" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O507" t="n">
@@ -38939,6 +39654,17 @@
       <c r="P507" t="n">
         <v>-77.26918000000001</v>
       </c>
+      <c r="Q507" t="n">
+        <v>-11.56293</v>
+      </c>
+      <c r="R507" t="n">
+        <v>-77.26918000000001</v>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -39680,17 +40406,17 @@
       </c>
       <c r="L517" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M517" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N517" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O517" t="n">
@@ -39699,6 +40425,17 @@
       <c r="P517" t="n">
         <v>-77.11060000000001</v>
       </c>
+      <c r="Q517" t="n">
+        <v>-12.05588</v>
+      </c>
+      <c r="R517" t="n">
+        <v>-77.11060000000001</v>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -39832,17 +40569,17 @@
       </c>
       <c r="L519" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N519" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O519" t="n">
@@ -39851,6 +40588,17 @@
       <c r="P519" t="n">
         <v>-77.20626</v>
       </c>
+      <c r="Q519" t="n">
+        <v>-11.49526</v>
+      </c>
+      <c r="R519" t="n">
+        <v>-77.20626</v>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -40212,17 +40960,17 @@
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M524" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N524" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O524" t="n">
@@ -40231,6 +40979,17 @@
       <c r="P524" t="n">
         <v>-77.09617</v>
       </c>
+      <c r="Q524" t="n">
+        <v>-12.04233</v>
+      </c>
+      <c r="R524" t="n">
+        <v>-77.09617</v>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -41124,17 +41883,17 @@
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M536" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N536" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O536" t="n">
@@ -41143,6 +41902,17 @@
       <c r="P536" t="n">
         <v>-77.04667999999999</v>
       </c>
+      <c r="Q536" t="n">
+        <v>-12.07275</v>
+      </c>
+      <c r="R536" t="n">
+        <v>-77.04667999999999</v>
+      </c>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -41276,17 +42046,17 @@
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M538" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N538" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O538" t="n">
@@ -41295,6 +42065,17 @@
       <c r="P538" t="n">
         <v>-77.26945000000001</v>
       </c>
+      <c r="Q538" t="n">
+        <v>-11.566</v>
+      </c>
+      <c r="R538" t="n">
+        <v>-77.26945000000001</v>
+      </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -41352,17 +42133,17 @@
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M539" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N539" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O539" t="n">
@@ -41371,6 +42152,17 @@
       <c r="P539" t="n">
         <v>-77.26945000000001</v>
       </c>
+      <c r="Q539" t="n">
+        <v>-11.566</v>
+      </c>
+      <c r="R539" t="n">
+        <v>-77.26945000000001</v>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -41428,17 +42220,17 @@
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M540" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N540" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O540" t="n">
@@ -41447,6 +42239,17 @@
       <c r="P540" t="n">
         <v>-77.20886</v>
       </c>
+      <c r="Q540" t="n">
+        <v>-11.49657</v>
+      </c>
+      <c r="R540" t="n">
+        <v>-77.20886</v>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -42188,17 +42991,17 @@
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M550" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N550" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O550" t="n">
@@ -42207,6 +43010,17 @@
       <c r="P550" t="n">
         <v>-77.26701</v>
       </c>
+      <c r="Q550" t="n">
+        <v>-11.569</v>
+      </c>
+      <c r="R550" t="n">
+        <v>-77.26701</v>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -42416,17 +43230,17 @@
       </c>
       <c r="L553" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M553" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N553" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O553" t="n">
@@ -42435,6 +43249,17 @@
       <c r="P553" t="n">
         <v>-77.09629</v>
       </c>
+      <c r="Q553" t="n">
+        <v>-12.04235</v>
+      </c>
+      <c r="R553" t="n">
+        <v>-77.09629</v>
+      </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -44230,17 +45055,17 @@
       </c>
       <c r="L577" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M577" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N577" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O577" t="n">
@@ -44249,6 +45074,17 @@
       <c r="P577" t="n">
         <v>-77.0508</v>
       </c>
+      <c r="Q577" t="n">
+        <v>-12.07526</v>
+      </c>
+      <c r="R577" t="n">
+        <v>-77.0508</v>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -45446,17 +46282,17 @@
       </c>
       <c r="L593" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M593" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N593" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O593" t="n">
@@ -45465,6 +46301,17 @@
       <c r="P593" t="n">
         <v>-77.27036</v>
       </c>
+      <c r="Q593" t="n">
+        <v>-11.57157</v>
+      </c>
+      <c r="R593" t="n">
+        <v>-77.27036</v>
+      </c>
+      <c r="S593" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -45522,17 +46369,17 @@
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N594" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O594" t="n">
@@ -45541,6 +46388,17 @@
       <c r="P594" t="n">
         <v>-77.11038000000001</v>
       </c>
+      <c r="Q594" t="n">
+        <v>-12.0456</v>
+      </c>
+      <c r="R594" t="n">
+        <v>-77.11038000000001</v>
+      </c>
+      <c r="S594" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -46282,17 +47140,17 @@
       </c>
       <c r="L604" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M604" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O604" t="n">
@@ -46301,6 +47159,17 @@
       <c r="P604" t="n">
         <v>-77.26976000000001</v>
       </c>
+      <c r="Q604" t="n">
+        <v>-11.56412</v>
+      </c>
+      <c r="R604" t="n">
+        <v>-77.26976000000001</v>
+      </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -46662,17 +47531,17 @@
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M609" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O609" t="n">
@@ -46681,6 +47550,17 @@
       <c r="P609" t="n">
         <v>-77.20626</v>
       </c>
+      <c r="Q609" t="n">
+        <v>-11.49526</v>
+      </c>
+      <c r="R609" t="n">
+        <v>-77.20626</v>
+      </c>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -46966,17 +47846,17 @@
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M613" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O613" t="n">
@@ -46985,6 +47865,17 @@
       <c r="P613" t="n">
         <v>-77.04195</v>
       </c>
+      <c r="Q613" t="n">
+        <v>-12.06434</v>
+      </c>
+      <c r="R613" t="n">
+        <v>-77.04195</v>
+      </c>
+      <c r="S613" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -47118,17 +48009,17 @@
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M615" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O615" t="n">
@@ -47137,6 +48028,17 @@
       <c r="P615" t="n">
         <v>-77.04478</v>
       </c>
+      <c r="Q615" t="n">
+        <v>-12.06624</v>
+      </c>
+      <c r="R615" t="n">
+        <v>-77.04478</v>
+      </c>
+      <c r="S615" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -47270,17 +48172,17 @@
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M617" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O617" t="n">
@@ -47289,6 +48191,17 @@
       <c r="P617" t="n">
         <v>-77.04607</v>
       </c>
+      <c r="Q617" t="n">
+        <v>-12.06807</v>
+      </c>
+      <c r="R617" t="n">
+        <v>-77.04607</v>
+      </c>
+      <c r="S617" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -47873,17 +48786,17 @@
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M625" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N625" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O625" t="n">
@@ -47892,6 +48805,17 @@
       <c r="P625" t="n">
         <v>-77.11538</v>
       </c>
+      <c r="Q625" t="n">
+        <v>-12.04283</v>
+      </c>
+      <c r="R625" t="n">
+        <v>-77.11538</v>
+      </c>
+      <c r="S625" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -48633,17 +49557,17 @@
       </c>
       <c r="L635" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M635" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N635" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O635" t="n">
@@ -48652,6 +49576,17 @@
       <c r="P635" t="n">
         <v>-77.20520999999999</v>
       </c>
+      <c r="Q635" t="n">
+        <v>-11.49339</v>
+      </c>
+      <c r="R635" t="n">
+        <v>-77.20520999999999</v>
+      </c>
+      <c r="S635" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -48785,17 +49720,17 @@
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M637" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N637" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O637" t="n">
@@ -48804,6 +49739,17 @@
       <c r="P637" t="n">
         <v>-77.20397</v>
       </c>
+      <c r="Q637" t="n">
+        <v>-11.49417</v>
+      </c>
+      <c r="R637" t="n">
+        <v>-77.20397</v>
+      </c>
+      <c r="S637" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -48937,17 +49883,17 @@
       </c>
       <c r="L639" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M639" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N639" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O639" t="n">
@@ -48956,6 +49902,17 @@
       <c r="P639" t="n">
         <v>-77.05812</v>
       </c>
+      <c r="Q639" t="n">
+        <v>-12.07852</v>
+      </c>
+      <c r="R639" t="n">
+        <v>-77.05812</v>
+      </c>
+      <c r="S639" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -49013,17 +49970,17 @@
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M640" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N640" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O640" t="n">
@@ -49032,6 +49989,17 @@
       <c r="P640" t="n">
         <v>-77.04094000000001</v>
       </c>
+      <c r="Q640" t="n">
+        <v>-12.06384</v>
+      </c>
+      <c r="R640" t="n">
+        <v>-77.04094000000001</v>
+      </c>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -49165,17 +50133,17 @@
       </c>
       <c r="L642" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M642" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N642" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O642" t="n">
@@ -49184,6 +50152,17 @@
       <c r="P642" t="n">
         <v>-77.10299999999999</v>
       </c>
+      <c r="Q642" t="n">
+        <v>-12.04352</v>
+      </c>
+      <c r="R642" t="n">
+        <v>-77.10299999999999</v>
+      </c>
+      <c r="S642" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -49393,17 +50372,17 @@
       </c>
       <c r="L645" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M645" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N645" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O645" t="n">
@@ -49412,6 +50391,17 @@
       <c r="P645" t="n">
         <v>-77.11526000000001</v>
       </c>
+      <c r="Q645" t="n">
+        <v>-12.04304</v>
+      </c>
+      <c r="R645" t="n">
+        <v>-77.11526000000001</v>
+      </c>
+      <c r="S645" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -49545,17 +50535,17 @@
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M647" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N647" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O647" t="n">
@@ -49564,6 +50554,17 @@
       <c r="P647" t="n">
         <v>-77.06144999999999</v>
       </c>
+      <c r="Q647" t="n">
+        <v>-12.07962</v>
+      </c>
+      <c r="R647" t="n">
+        <v>-77.06144999999999</v>
+      </c>
+      <c r="S647" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -49936,17 +50937,17 @@
       </c>
       <c r="L652" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M652" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N652" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O652" t="n">
@@ -49955,6 +50956,17 @@
       <c r="P652" t="n">
         <v>-77.04369</v>
       </c>
+      <c r="Q652" t="n">
+        <v>-12.06674</v>
+      </c>
+      <c r="R652" t="n">
+        <v>-77.04369</v>
+      </c>
+      <c r="S652" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -50392,17 +51404,17 @@
       </c>
       <c r="L658" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M658" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N658" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O658" t="n">
@@ -50411,6 +51423,17 @@
       <c r="P658" t="n">
         <v>-77.11815</v>
       </c>
+      <c r="Q658" t="n">
+        <v>-12.04228</v>
+      </c>
+      <c r="R658" t="n">
+        <v>-77.11815</v>
+      </c>
+      <c r="S658" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -51380,17 +52403,17 @@
       </c>
       <c r="L671" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N671" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O671" t="n">
@@ -51399,6 +52422,17 @@
       <c r="P671" t="n">
         <v>-77.26712999999999</v>
       </c>
+      <c r="Q671" t="n">
+        <v>-11.56889</v>
+      </c>
+      <c r="R671" t="n">
+        <v>-77.26712999999999</v>
+      </c>
+      <c r="S671" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -51532,17 +52566,17 @@
       </c>
       <c r="L673" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M673" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N673" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O673" t="n">
@@ -51551,6 +52585,17 @@
       <c r="P673" t="n">
         <v>-77.05179</v>
       </c>
+      <c r="Q673" t="n">
+        <v>-12.07357</v>
+      </c>
+      <c r="R673" t="n">
+        <v>-77.05179</v>
+      </c>
+      <c r="S673" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -51831,17 +52876,17 @@
       </c>
       <c r="L677" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M677" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N677" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O677" t="n">
@@ -51850,6 +52895,17 @@
       <c r="P677" t="n">
         <v>-77.09648</v>
       </c>
+      <c r="Q677" t="n">
+        <v>-12.04268</v>
+      </c>
+      <c r="R677" t="n">
+        <v>-77.09648</v>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -52059,17 +53115,17 @@
       </c>
       <c r="L680" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M680" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N680" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O680" t="n">
@@ -52078,6 +53134,17 @@
       <c r="P680" t="n">
         <v>-77.0414</v>
       </c>
+      <c r="Q680" t="n">
+        <v>-12.0624</v>
+      </c>
+      <c r="R680" t="n">
+        <v>-77.0414</v>
+      </c>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -52895,17 +53962,17 @@
       </c>
       <c r="L691" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M691" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N691" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O691" t="n">
@@ -52914,6 +53981,17 @@
       <c r="P691" t="n">
         <v>-77.26909000000001</v>
       </c>
+      <c r="Q691" t="n">
+        <v>-11.5641</v>
+      </c>
+      <c r="R691" t="n">
+        <v>-77.26909000000001</v>
+      </c>
+      <c r="S691" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -54035,17 +55113,17 @@
       </c>
       <c r="L706" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M706" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N706" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O706" t="n">
@@ -54054,6 +55132,17 @@
       <c r="P706" t="n">
         <v>-77.06746</v>
       </c>
+      <c r="Q706" t="n">
+        <v>-12.06783</v>
+      </c>
+      <c r="R706" t="n">
+        <v>-77.06746</v>
+      </c>
+      <c r="S706" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -55013,17 +56102,17 @@
       </c>
       <c r="L719" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M719" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N719" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O719" t="n">
@@ -55032,6 +56121,17 @@
       <c r="P719" t="n">
         <v>-77.26908</v>
       </c>
+      <c r="Q719" t="n">
+        <v>-11.56343</v>
+      </c>
+      <c r="R719" t="n">
+        <v>-77.26908</v>
+      </c>
+      <c r="S719" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -56001,17 +57101,17 @@
       </c>
       <c r="L732" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M732" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N732" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O732" t="n">
@@ -56020,6 +57120,17 @@
       <c r="P732" t="n">
         <v>-77.04286</v>
       </c>
+      <c r="Q732" t="n">
+        <v>-12.06413</v>
+      </c>
+      <c r="R732" t="n">
+        <v>-77.04286</v>
+      </c>
+      <c r="S732" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -56153,17 +57264,17 @@
       </c>
       <c r="L734" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M734" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N734" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O734" t="n">
@@ -56172,6 +57283,17 @@
       <c r="P734" t="n">
         <v>-77.20059999999999</v>
       </c>
+      <c r="Q734" t="n">
+        <v>-11.49392</v>
+      </c>
+      <c r="R734" t="n">
+        <v>-77.20059999999999</v>
+      </c>
+      <c r="S734" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -56609,17 +57731,17 @@
       </c>
       <c r="L740" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M740" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N740" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O740" t="n">
@@ -56628,6 +57750,17 @@
       <c r="P740" t="n">
         <v>-77.04689</v>
       </c>
+      <c r="Q740" t="n">
+        <v>-12.07092</v>
+      </c>
+      <c r="R740" t="n">
+        <v>-77.04689</v>
+      </c>
+      <c r="S740" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -57820,17 +58953,17 @@
       </c>
       <c r="L756" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M756" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N756" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O756" t="n">
@@ -57839,6 +58972,17 @@
       <c r="P756" t="n">
         <v>-77.26667</v>
       </c>
+      <c r="Q756" t="n">
+        <v>-11.56865</v>
+      </c>
+      <c r="R756" t="n">
+        <v>-77.26667</v>
+      </c>
+      <c r="S756" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -57896,17 +59040,17 @@
       </c>
       <c r="L757" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M757" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N757" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O757" t="n">
@@ -57915,6 +59059,17 @@
       <c r="P757" t="n">
         <v>-77.27055</v>
       </c>
+      <c r="Q757" t="n">
+        <v>-11.56237</v>
+      </c>
+      <c r="R757" t="n">
+        <v>-77.27055</v>
+      </c>
+      <c r="S757" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -58428,17 +59583,17 @@
       </c>
       <c r="L764" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M764" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N764" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O764" t="n">
@@ -58447,6 +59602,17 @@
       <c r="P764" t="n">
         <v>-77.20699</v>
       </c>
+      <c r="Q764" t="n">
+        <v>-11.50049</v>
+      </c>
+      <c r="R764" t="n">
+        <v>-77.20699</v>
+      </c>
+      <c r="S764" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -58884,17 +60050,17 @@
       </c>
       <c r="L770" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M770" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N770" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O770" t="n">
@@ -58903,6 +60069,17 @@
       <c r="P770" t="n">
         <v>-77.04187</v>
       </c>
+      <c r="Q770" t="n">
+        <v>-12.06433</v>
+      </c>
+      <c r="R770" t="n">
+        <v>-77.04187</v>
+      </c>
+      <c r="S770" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -59036,17 +60213,17 @@
       </c>
       <c r="L772" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M772" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N772" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O772" t="n">
@@ -59055,6 +60232,17 @@
       <c r="P772" t="n">
         <v>-77.10207</v>
       </c>
+      <c r="Q772" t="n">
+        <v>-12.04367</v>
+      </c>
+      <c r="R772" t="n">
+        <v>-77.10207</v>
+      </c>
+      <c r="S772" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -59791,17 +60979,17 @@
       </c>
       <c r="L782" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M782" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N782" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O782" t="n">
@@ -59810,6 +60998,17 @@
       <c r="P782" t="n">
         <v>-77.09265000000001</v>
       </c>
+      <c r="Q782" t="n">
+        <v>-12.04132</v>
+      </c>
+      <c r="R782" t="n">
+        <v>-77.09265000000001</v>
+      </c>
+      <c r="S782" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -60095,17 +61294,17 @@
       </c>
       <c r="L786" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M786" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N786" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O786" t="n">
@@ -60114,6 +61313,17 @@
       <c r="P786" t="n">
         <v>-77.209</v>
       </c>
+      <c r="Q786" t="n">
+        <v>-11.49645</v>
+      </c>
+      <c r="R786" t="n">
+        <v>-77.209</v>
+      </c>
+      <c r="S786" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -60475,17 +61685,17 @@
       </c>
       <c r="L791" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M791" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N791" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O791" t="n">
@@ -60494,6 +61704,17 @@
       <c r="P791" t="n">
         <v>-77.09477</v>
       </c>
+      <c r="Q791" t="n">
+        <v>-12.04164</v>
+      </c>
+      <c r="R791" t="n">
+        <v>-77.09477</v>
+      </c>
+      <c r="S791" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -61838,17 +63059,17 @@
       </c>
       <c r="L809" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M809" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N809" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O809" t="n">
@@ -61857,6 +63078,17 @@
       <c r="P809" t="n">
         <v>-77.05937</v>
       </c>
+      <c r="Q809" t="n">
+        <v>-12.07858</v>
+      </c>
+      <c r="R809" t="n">
+        <v>-77.05937</v>
+      </c>
+      <c r="S809" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -62522,17 +63754,17 @@
       </c>
       <c r="L818" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M818" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N818" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O818" t="n">
@@ -62541,6 +63773,17 @@
       <c r="P818" t="n">
         <v>-77.05172</v>
       </c>
+      <c r="Q818" t="n">
+        <v>-12.07337</v>
+      </c>
+      <c r="R818" t="n">
+        <v>-77.05172</v>
+      </c>
+      <c r="S818" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -62674,17 +63917,17 @@
       </c>
       <c r="L820" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M820" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N820" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O820" t="n">
@@ -62693,6 +63936,17 @@
       <c r="P820" t="n">
         <v>-77.04881</v>
       </c>
+      <c r="Q820" t="n">
+        <v>-12.07086</v>
+      </c>
+      <c r="R820" t="n">
+        <v>-77.04881</v>
+      </c>
+      <c r="S820" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -63130,17 +64384,17 @@
       </c>
       <c r="L826" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M826" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N826" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O826" t="n">
@@ -63149,6 +64403,17 @@
       <c r="P826" t="n">
         <v>-77.05005</v>
       </c>
+      <c r="Q826" t="n">
+        <v>-12.07456</v>
+      </c>
+      <c r="R826" t="n">
+        <v>-77.05005</v>
+      </c>
+      <c r="S826" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -63662,17 +64927,17 @@
       </c>
       <c r="L833" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M833" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N833" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O833" t="n">
@@ -63681,6 +64946,17 @@
       <c r="P833" t="n">
         <v>-77.04476</v>
       </c>
+      <c r="Q833" t="n">
+        <v>-12.06762</v>
+      </c>
+      <c r="R833" t="n">
+        <v>-77.04476</v>
+      </c>
+      <c r="S833" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -64498,17 +65774,17 @@
       </c>
       <c r="L844" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M844" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N844" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O844" t="n">
@@ -64517,6 +65793,17 @@
       <c r="P844" t="n">
         <v>-77.11183</v>
       </c>
+      <c r="Q844" t="n">
+        <v>-12.0479</v>
+      </c>
+      <c r="R844" t="n">
+        <v>-77.11183</v>
+      </c>
+      <c r="S844" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -65334,17 +66621,17 @@
       </c>
       <c r="L855" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M855" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N855" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O855" t="n">
@@ -65353,6 +66640,17 @@
       <c r="P855" t="n">
         <v>-77.26658</v>
       </c>
+      <c r="Q855" t="n">
+        <v>-11.56849</v>
+      </c>
+      <c r="R855" t="n">
+        <v>-77.26658</v>
+      </c>
+      <c r="S855" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -65942,17 +67240,17 @@
       </c>
       <c r="L863" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M863" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N863" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O863" t="n">
@@ -65961,6 +67259,17 @@
       <c r="P863" t="n">
         <v>-77.10402999999999</v>
       </c>
+      <c r="Q863" t="n">
+        <v>-12.05359</v>
+      </c>
+      <c r="R863" t="n">
+        <v>-77.10402999999999</v>
+      </c>
+      <c r="S863" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -66322,17 +67631,17 @@
       </c>
       <c r="L868" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M868" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N868" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O868" t="n">
@@ -66341,6 +67650,17 @@
       <c r="P868" t="n">
         <v>-77.10115999999999</v>
       </c>
+      <c r="Q868" t="n">
+        <v>-12.04515</v>
+      </c>
+      <c r="R868" t="n">
+        <v>-77.10115999999999</v>
+      </c>
+      <c r="S868" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
@@ -67148,17 +68468,17 @@
       </c>
       <c r="L879" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M879" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N879" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O879" t="n">
@@ -67167,6 +68487,17 @@
       <c r="P879" t="n">
         <v>-77.20950000000001</v>
       </c>
+      <c r="Q879" t="n">
+        <v>-11.49131</v>
+      </c>
+      <c r="R879" t="n">
+        <v>-77.20950000000001</v>
+      </c>
+      <c r="S879" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -67376,17 +68707,17 @@
       </c>
       <c r="L882" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M882" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N882" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O882" t="n">
@@ -67395,6 +68726,17 @@
       <c r="P882" t="n">
         <v>-77.26548</v>
       </c>
+      <c r="Q882" t="n">
+        <v>-11.56398</v>
+      </c>
+      <c r="R882" t="n">
+        <v>-77.26548</v>
+      </c>
+      <c r="S882" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
@@ -67452,17 +68794,17 @@
       </c>
       <c r="L883" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M883" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N883" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O883" t="n">
@@ -67471,6 +68813,17 @@
       <c r="P883" t="n">
         <v>-77.27238</v>
       </c>
+      <c r="Q883" t="n">
+        <v>-11.56166</v>
+      </c>
+      <c r="R883" t="n">
+        <v>-77.27238</v>
+      </c>
+      <c r="S883" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
@@ -67756,17 +69109,17 @@
       </c>
       <c r="L887" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M887" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N887" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O887" t="n">
@@ -67775,6 +69128,17 @@
       <c r="P887" t="n">
         <v>-77.11547</v>
       </c>
+      <c r="Q887" t="n">
+        <v>-12.05179</v>
+      </c>
+      <c r="R887" t="n">
+        <v>-77.11547</v>
+      </c>
+      <c r="S887" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
@@ -67984,17 +69348,17 @@
       </c>
       <c r="L890" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M890" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N890" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O890" t="n">
@@ -68003,6 +69367,17 @@
       <c r="P890" t="n">
         <v>-77.0962</v>
       </c>
+      <c r="Q890" t="n">
+        <v>-12.04163</v>
+      </c>
+      <c r="R890" t="n">
+        <v>-77.0962</v>
+      </c>
+      <c r="S890" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -68060,17 +69435,17 @@
       </c>
       <c r="L891" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M891" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N891" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O891" t="n">
@@ -68079,6 +69454,17 @@
       <c r="P891" t="n">
         <v>-77.04707999999999</v>
       </c>
+      <c r="Q891" t="n">
+        <v>-12.06885</v>
+      </c>
+      <c r="R891" t="n">
+        <v>-77.04707999999999</v>
+      </c>
+      <c r="S891" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -68212,17 +69598,17 @@
       </c>
       <c r="L893" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M893" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N893" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O893" t="n">
@@ -68231,6 +69617,17 @@
       <c r="P893" t="n">
         <v>-77.0474</v>
       </c>
+      <c r="Q893" t="n">
+        <v>-12.06946</v>
+      </c>
+      <c r="R893" t="n">
+        <v>-77.0474</v>
+      </c>
+      <c r="S893" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -68668,17 +70065,17 @@
       </c>
       <c r="L899" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M899" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N899" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O899" t="n">
@@ -68687,6 +70084,17 @@
       <c r="P899" t="n">
         <v>-77.20937000000001</v>
       </c>
+      <c r="Q899" t="n">
+        <v>-11.49445</v>
+      </c>
+      <c r="R899" t="n">
+        <v>-77.20937000000001</v>
+      </c>
+      <c r="S899" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
@@ -69656,17 +71064,17 @@
       </c>
       <c r="L912" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M912" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N912" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O912" t="n">
@@ -69675,6 +71083,17 @@
       <c r="P912" t="n">
         <v>-77.26924</v>
       </c>
+      <c r="Q912" t="n">
+        <v>-11.56523</v>
+      </c>
+      <c r="R912" t="n">
+        <v>-77.26924</v>
+      </c>
+      <c r="S912" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -74357,17 +75776,17 @@
       </c>
       <c r="L978" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M978" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N978" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O978" t="n">
@@ -74376,6 +75795,17 @@
       <c r="P978" t="n">
         <v>-77.04254</v>
       </c>
+      <c r="Q978" t="n">
+        <v>-12.06447</v>
+      </c>
+      <c r="R978" t="n">
+        <v>-77.04254</v>
+      </c>
+      <c r="S978" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
@@ -74585,17 +76015,17 @@
       </c>
       <c r="L981" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M981" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N981" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O981" t="n">
@@ -74604,6 +76034,17 @@
       <c r="P981" t="n">
         <v>-77.0479</v>
       </c>
+      <c r="Q981" t="n">
+        <v>-12.06982</v>
+      </c>
+      <c r="R981" t="n">
+        <v>-77.0479</v>
+      </c>
+      <c r="S981" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
@@ -75573,17 +77014,17 @@
       </c>
       <c r="L994" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M994" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N994" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O994" t="n">
@@ -75592,6 +77033,17 @@
       <c r="P994" t="n">
         <v>-77.06193</v>
       </c>
+      <c r="Q994" t="n">
+        <v>-12.07172</v>
+      </c>
+      <c r="R994" t="n">
+        <v>-77.06193</v>
+      </c>
+      <c r="S994" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
@@ -76789,17 +78241,17 @@
       </c>
       <c r="L1010" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1010" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1010" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1010" t="n">
@@ -76808,6 +78260,17 @@
       <c r="P1010" t="n">
         <v>-77.27055</v>
       </c>
+      <c r="Q1010" t="n">
+        <v>-11.56285</v>
+      </c>
+      <c r="R1010" t="n">
+        <v>-77.27055</v>
+      </c>
+      <c r="S1010" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
@@ -77853,17 +79316,17 @@
       </c>
       <c r="L1024" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1024" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1024" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1024" t="n">
@@ -77872,6 +79335,17 @@
       <c r="P1024" t="n">
         <v>-77.26703000000001</v>
       </c>
+      <c r="Q1024" t="n">
+        <v>-11.56462</v>
+      </c>
+      <c r="R1024" t="n">
+        <v>-77.26703000000001</v>
+      </c>
+      <c r="S1024" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
@@ -78385,17 +79859,17 @@
       </c>
       <c r="L1031" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1031" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1031" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1031" t="n">
@@ -78404,6 +79878,17 @@
       <c r="P1031" t="n">
         <v>-77.06126</v>
       </c>
+      <c r="Q1031" t="n">
+        <v>-12.07006</v>
+      </c>
+      <c r="R1031" t="n">
+        <v>-77.06126</v>
+      </c>
+      <c r="S1031" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
@@ -78537,17 +80022,17 @@
       </c>
       <c r="L1033" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1033" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1033" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1033" t="n">
@@ -78556,6 +80041,17 @@
       <c r="P1033" t="n">
         <v>-77.09623000000001</v>
       </c>
+      <c r="Q1033" t="n">
+        <v>-12.04228</v>
+      </c>
+      <c r="R1033" t="n">
+        <v>-77.09623000000001</v>
+      </c>
+      <c r="S1033" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
@@ -83367,17 +84863,17 @@
       </c>
       <c r="L1098" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1098" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1098" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1098" t="n">
@@ -83386,6 +84882,17 @@
       <c r="P1098" t="n">
         <v>-77.06412</v>
       </c>
+      <c r="Q1098" t="n">
+        <v>-12.07223</v>
+      </c>
+      <c r="R1098" t="n">
+        <v>-77.06412</v>
+      </c>
+      <c r="S1098" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
@@ -84279,17 +85786,17 @@
       </c>
       <c r="L1110" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1110" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1110" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1110" t="n">
@@ -84298,6 +85805,17 @@
       <c r="P1110" t="n">
         <v>-77.04447999999999</v>
       </c>
+      <c r="Q1110" t="n">
+        <v>-12.07396</v>
+      </c>
+      <c r="R1110" t="n">
+        <v>-77.04447999999999</v>
+      </c>
+      <c r="S1110" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
@@ -84431,17 +85949,17 @@
       </c>
       <c r="L1112" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1112" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1112" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1112" t="n">
@@ -84450,6 +85968,17 @@
       <c r="P1112" t="n">
         <v>-77.04501</v>
       </c>
+      <c r="Q1112" t="n">
+        <v>-12.07053</v>
+      </c>
+      <c r="R1112" t="n">
+        <v>-77.04501</v>
+      </c>
+      <c r="S1112" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
@@ -85647,17 +87176,17 @@
       </c>
       <c r="L1128" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1128" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1128" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1128" t="n">
@@ -85666,6 +87195,17 @@
       <c r="P1128" t="n">
         <v>-77.21447999999999</v>
       </c>
+      <c r="Q1128" t="n">
+        <v>-11.49686</v>
+      </c>
+      <c r="R1128" t="n">
+        <v>-77.21447999999999</v>
+      </c>
+      <c r="S1128" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
@@ -85951,17 +87491,17 @@
       </c>
       <c r="L1132" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1132" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1132" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1132" t="n">
@@ -85970,6 +87510,17 @@
       <c r="P1132" t="n">
         <v>-77.05107</v>
       </c>
+      <c r="Q1132" t="n">
+        <v>-12.07408</v>
+      </c>
+      <c r="R1132" t="n">
+        <v>-77.05107</v>
+      </c>
+      <c r="S1132" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
@@ -87471,17 +89022,17 @@
       </c>
       <c r="L1152" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1152" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1152" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1152" t="n">
@@ -87490,6 +89041,17 @@
       <c r="P1152" t="n">
         <v>-77.09007</v>
       </c>
+      <c r="Q1152" t="n">
+        <v>-12.03936</v>
+      </c>
+      <c r="R1152" t="n">
+        <v>-77.09007</v>
+      </c>
+      <c r="S1152" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
@@ -88991,17 +90553,17 @@
       </c>
       <c r="L1172" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1172" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1172" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1172" t="n">
@@ -89010,6 +90572,17 @@
       <c r="P1172" t="n">
         <v>-77.08559</v>
       </c>
+      <c r="Q1172" t="n">
+        <v>-12.04247</v>
+      </c>
+      <c r="R1172" t="n">
+        <v>-77.08559</v>
+      </c>
+      <c r="S1172" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
@@ -91727,17 +93300,17 @@
       </c>
       <c r="L1208" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1208" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1208" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1208" t="n">
@@ -91746,6 +93319,17 @@
       <c r="P1208" t="n">
         <v>-77.21012</v>
       </c>
+      <c r="Q1208" t="n">
+        <v>-11.49619</v>
+      </c>
+      <c r="R1208" t="n">
+        <v>-77.21012</v>
+      </c>
+      <c r="S1208" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
@@ -94007,17 +95591,17 @@
       </c>
       <c r="L1238" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1238" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1238" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1238" t="n">
@@ -94026,6 +95610,17 @@
       <c r="P1238" t="n">
         <v>-77.20783</v>
       </c>
+      <c r="Q1238" t="n">
+        <v>-11.49548</v>
+      </c>
+      <c r="R1238" t="n">
+        <v>-77.20783</v>
+      </c>
+      <c r="S1238" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
@@ -95299,17 +96894,17 @@
       </c>
       <c r="L1255" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1255" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1255" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1255" t="n">
@@ -95318,6 +96913,17 @@
       <c r="P1255" t="n">
         <v>-77.09599</v>
       </c>
+      <c r="Q1255" t="n">
+        <v>-12.05297</v>
+      </c>
+      <c r="R1255" t="n">
+        <v>-77.09599</v>
+      </c>
+      <c r="S1255" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
@@ -95679,17 +97285,17 @@
       </c>
       <c r="L1260" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1260" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1260" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1260" t="n">
@@ -95698,6 +97304,17 @@
       <c r="P1260" t="n">
         <v>-77.26548</v>
       </c>
+      <c r="Q1260" t="n">
+        <v>-11.56398</v>
+      </c>
+      <c r="R1260" t="n">
+        <v>-77.26548</v>
+      </c>
+      <c r="S1260" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
@@ -96287,17 +97904,17 @@
       </c>
       <c r="L1268" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1268" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1268" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1268" t="n">
@@ -96306,6 +97923,17 @@
       <c r="P1268" t="n">
         <v>-77.0975</v>
       </c>
+      <c r="Q1268" t="n">
+        <v>-12.05594</v>
+      </c>
+      <c r="R1268" t="n">
+        <v>-77.0975</v>
+      </c>
+      <c r="S1268" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
@@ -96667,17 +98295,17 @@
       </c>
       <c r="L1273" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1273" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1273" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1273" t="n">
@@ -96686,6 +98314,17 @@
       <c r="P1273" t="n">
         <v>-77.05029</v>
       </c>
+      <c r="Q1273" t="n">
+        <v>-12.07284</v>
+      </c>
+      <c r="R1273" t="n">
+        <v>-77.05029</v>
+      </c>
+      <c r="S1273" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
@@ -97579,17 +99218,17 @@
       </c>
       <c r="L1285" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1285" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1285" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1285" t="n">
@@ -97598,6 +99237,17 @@
       <c r="P1285" t="n">
         <v>-77.21509</v>
       </c>
+      <c r="Q1285" t="n">
+        <v>-11.4999</v>
+      </c>
+      <c r="R1285" t="n">
+        <v>-77.21509</v>
+      </c>
+      <c r="S1285" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
@@ -97731,17 +99381,17 @@
       </c>
       <c r="L1287" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1287" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1287" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1287" t="n">
@@ -97750,6 +99400,17 @@
       <c r="P1287" t="n">
         <v>-77.08524</v>
       </c>
+      <c r="Q1287" t="n">
+        <v>-12.04253</v>
+      </c>
+      <c r="R1287" t="n">
+        <v>-77.08524</v>
+      </c>
+      <c r="S1287" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
@@ -97883,17 +99544,17 @@
       </c>
       <c r="L1289" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1289" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1289" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1289" t="n">
@@ -97901,6 +99562,17 @@
       </c>
       <c r="P1289" t="n">
         <v>-77.11139</v>
+      </c>
+      <c r="Q1289" t="n">
+        <v>-12.04747</v>
+      </c>
+      <c r="R1289" t="n">
+        <v>-77.11139</v>
+      </c>
+      <c r="S1289" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
       </c>
     </row>
     <row r="1290">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -2349,7 +2349,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -31104,7 +31104,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -32735,7 +32735,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -35432,7 +35432,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -35954,7 +35954,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -36215,7 +36215,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -40380,7 +40380,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -42186,7 +42186,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -43443,7 +43443,7 @@
       </c>
       <c r="M508" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N508" t="inlineStr">
@@ -44400,7 +44400,7 @@
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N519" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="M522" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N522" t="inlineStr">
@@ -45444,7 +45444,7 @@
       </c>
       <c r="M531" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N531" t="inlineStr">
@@ -45792,7 +45792,7 @@
       </c>
       <c r="M535" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N535" t="inlineStr">
@@ -46140,7 +46140,7 @@
       </c>
       <c r="M539" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N539" t="inlineStr">
@@ -46227,7 +46227,7 @@
       </c>
       <c r="M540" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N540" t="inlineStr">
@@ -46314,7 +46314,7 @@
       </c>
       <c r="M541" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N541" t="inlineStr">
@@ -46836,7 +46836,7 @@
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N547" t="inlineStr">
@@ -49941,7 +49941,7 @@
       </c>
       <c r="M583" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N583" t="inlineStr">
@@ -51681,7 +51681,7 @@
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N603" t="inlineStr">
@@ -52377,7 +52377,7 @@
       </c>
       <c r="M611" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N611" t="inlineStr">
@@ -53334,7 +53334,7 @@
       </c>
       <c r="M622" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N622" t="inlineStr">
@@ -54966,7 +54966,7 @@
       </c>
       <c r="M641" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N641" t="inlineStr">
@@ -56604,7 +56604,7 @@
       </c>
       <c r="M661" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N661" t="inlineStr">
@@ -56691,7 +56691,7 @@
       </c>
       <c r="M662" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N662" t="inlineStr">
@@ -56865,7 +56865,7 @@
       </c>
       <c r="M664" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N664" t="inlineStr">
@@ -57387,7 +57387,7 @@
       </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N670" t="inlineStr">
@@ -59040,7 +59040,7 @@
       </c>
       <c r="M689" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N689" t="inlineStr">
@@ -60432,7 +60432,7 @@
       </c>
       <c r="M705" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N705" t="inlineStr">
@@ -60780,7 +60780,7 @@
       </c>
       <c r="M709" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N709" t="inlineStr">
@@ -61302,7 +61302,7 @@
       </c>
       <c r="M715" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N715" t="inlineStr">
@@ -65391,7 +65391,7 @@
       </c>
       <c r="M762" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N762" t="inlineStr">
@@ -66865,7 +66865,7 @@
       </c>
       <c r="M779" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N779" t="inlineStr">
@@ -69383,7 +69383,7 @@
       </c>
       <c r="M808" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N808" t="inlineStr">
@@ -69557,7 +69557,7 @@
       </c>
       <c r="M810" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N810" t="inlineStr">
@@ -70079,7 +70079,7 @@
       </c>
       <c r="M816" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N816" t="inlineStr">
@@ -70253,7 +70253,7 @@
       </c>
       <c r="M818" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N818" t="inlineStr">
@@ -72341,7 +72341,7 @@
       </c>
       <c r="M842" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N842" t="inlineStr">
@@ -72428,7 +72428,7 @@
       </c>
       <c r="M843" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N843" t="inlineStr">
@@ -74592,7 +74592,7 @@
       </c>
       <c r="M868" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N868" t="inlineStr">
@@ -77289,7 +77289,7 @@
       </c>
       <c r="M899" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N899" t="inlineStr">
@@ -77724,7 +77724,7 @@
       </c>
       <c r="M904" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N904" t="inlineStr">
@@ -78159,7 +78159,7 @@
       </c>
       <c r="M909" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N909" t="inlineStr">
@@ -78328,7 +78328,7 @@
       </c>
       <c r="M911" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N911" t="inlineStr">
@@ -78763,7 +78763,7 @@
       </c>
       <c r="M916" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N916" t="inlineStr">
@@ -79889,7 +79889,7 @@
       </c>
       <c r="M929" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N929" t="inlineStr">
@@ -80237,7 +80237,7 @@
       </c>
       <c r="M933" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N933" t="inlineStr">
@@ -80493,7 +80493,7 @@
       </c>
       <c r="M936" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N936" t="inlineStr">
@@ -80754,7 +80754,7 @@
       </c>
       <c r="M939" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N939" t="inlineStr">
@@ -80928,7 +80928,7 @@
       </c>
       <c r="M941" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N941" t="inlineStr">
@@ -81276,7 +81276,7 @@
       </c>
       <c r="M945" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N945" t="inlineStr">
@@ -81363,7 +81363,7 @@
       </c>
       <c r="M946" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N946" t="inlineStr">
@@ -81450,7 +81450,7 @@
       </c>
       <c r="M947" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N947" t="inlineStr">
@@ -83523,7 +83523,7 @@
       </c>
       <c r="M971" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N971" t="inlineStr">
@@ -84741,7 +84741,7 @@
       </c>
       <c r="M985" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N985" t="inlineStr">
@@ -86563,7 +86563,7 @@
       </c>
       <c r="M1006" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1006" t="inlineStr">
@@ -89260,7 +89260,7 @@
       </c>
       <c r="M1037" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1037" t="inlineStr">
@@ -89521,7 +89521,7 @@
       </c>
       <c r="M1040" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1040" t="inlineStr">
@@ -90130,7 +90130,7 @@
       </c>
       <c r="M1047" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1047" t="inlineStr">
@@ -91169,7 +91169,7 @@
       </c>
       <c r="M1059" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1059" t="inlineStr">
@@ -92295,7 +92295,7 @@
       </c>
       <c r="M1072" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1072" t="inlineStr">
@@ -92904,7 +92904,7 @@
       </c>
       <c r="M1079" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1079" t="inlineStr">
@@ -94030,7 +94030,7 @@
       </c>
       <c r="M1092" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1092" t="inlineStr">
@@ -94291,7 +94291,7 @@
       </c>
       <c r="M1095" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1095" t="inlineStr">
@@ -94726,7 +94726,7 @@
       </c>
       <c r="M1100" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1100" t="inlineStr">
@@ -95161,7 +95161,7 @@
       </c>
       <c r="M1105" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1105" t="inlineStr">
@@ -95683,7 +95683,7 @@
       </c>
       <c r="M1111" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1111" t="inlineStr">
@@ -95857,7 +95857,7 @@
       </c>
       <c r="M1113" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1113" t="inlineStr">
@@ -96379,7 +96379,7 @@
       </c>
       <c r="M1119" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1119" t="inlineStr">
@@ -97842,7 +97842,7 @@
       </c>
       <c r="M1136" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1136" t="inlineStr">
@@ -98016,7 +98016,7 @@
       </c>
       <c r="M1138" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1138" t="inlineStr">
@@ -99577,7 +99577,7 @@
       </c>
       <c r="M1156" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1156" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -25120,17 +25120,17 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O292" t="n">
@@ -25139,6 +25139,17 @@
       <c r="P292" t="n">
         <v>-76.8852</v>
       </c>
+      <c r="Q292" t="n">
+        <v>-12.2481</v>
+      </c>
+      <c r="R292" t="n">
+        <v>-76.8852</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -25457,17 +25468,17 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O296" t="n">
@@ -25476,6 +25487,17 @@
       <c r="P296" t="n">
         <v>-77.13114</v>
       </c>
+      <c r="Q296" t="n">
+        <v>-11.95196</v>
+      </c>
+      <c r="R296" t="n">
+        <v>-77.13114</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -25533,17 +25555,17 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O297" t="n">
@@ -25552,6 +25574,17 @@
       <c r="P297" t="n">
         <v>-77.13114</v>
       </c>
+      <c r="Q297" t="n">
+        <v>-11.95196</v>
+      </c>
+      <c r="R297" t="n">
+        <v>-77.13114</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -32132,17 +32165,17 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O377" t="n">
@@ -32151,6 +32184,17 @@
       <c r="P377" t="n">
         <v>-77.13114</v>
       </c>
+      <c r="Q377" t="n">
+        <v>-11.95196</v>
+      </c>
+      <c r="R377" t="n">
+        <v>-77.13114</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -42426,17 +42470,17 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O496" t="n">
@@ -42445,6 +42489,17 @@
       <c r="P496" t="n">
         <v>-77.13114</v>
       </c>
+      <c r="Q496" t="n">
+        <v>-11.95196</v>
+      </c>
+      <c r="R496" t="n">
+        <v>-77.13114</v>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -73380,17 +73435,17 @@
       </c>
       <c r="L854" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M854" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N854" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O854" t="n">
@@ -73399,6 +73454,17 @@
       <c r="P854" t="n">
         <v>-77.06480000000001</v>
       </c>
+      <c r="Q854" t="n">
+        <v>-11.97825</v>
+      </c>
+      <c r="R854" t="n">
+        <v>-77.06480000000001</v>
+      </c>
+      <c r="S854" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -96461,17 +96527,17 @@
       </c>
       <c r="L1120" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1120" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1120" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1120" t="n">
@@ -96480,6 +96546,17 @@
       <c r="P1120" t="n">
         <v>-77.06480000000001</v>
       </c>
+      <c r="Q1120" t="n">
+        <v>-11.97825</v>
+      </c>
+      <c r="R1120" t="n">
+        <v>-77.06480000000001</v>
+      </c>
+      <c r="S1120" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
@@ -100007,17 +100084,17 @@
       </c>
       <c r="L1161" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M1161" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N1161" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O1161" t="n">
@@ -100025,6 +100102,17 @@
       </c>
       <c r="P1161" t="n">
         <v>-77.06480000000001</v>
+      </c>
+      <c r="Q1161" t="n">
+        <v>-11.97825</v>
+      </c>
+      <c r="R1161" t="n">
+        <v>-77.06480000000001</v>
+      </c>
+      <c r="S1161" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
       </c>
     </row>
     <row r="1162">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -2262,7 +2262,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -17047,7 +17047,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -22359,7 +22359,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -29832,7 +29832,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -30093,7 +30093,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -30354,7 +30354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -30876,7 +30876,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -32692,7 +32692,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -36085,7 +36085,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -37738,7 +37738,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -39206,7 +39206,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -43846,7 +43846,7 @@
       </c>
       <c r="M512" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N512" t="inlineStr">
@@ -44194,7 +44194,7 @@
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N516" t="inlineStr">
@@ -45412,7 +45412,7 @@
       </c>
       <c r="M530" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N530" t="inlineStr">
@@ -47152,7 +47152,7 @@
       </c>
       <c r="M550" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N550" t="inlineStr">
@@ -48457,7 +48457,7 @@
       </c>
       <c r="M565" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N565" t="inlineStr">
@@ -50344,7 +50344,7 @@
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N587" t="inlineStr">
@@ -57094,7 +57094,7 @@
       </c>
       <c r="M666" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N666" t="inlineStr">
@@ -57877,7 +57877,7 @@
       </c>
       <c r="M675" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N675" t="inlineStr">
@@ -62488,7 +62488,7 @@
       </c>
       <c r="M728" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N728" t="inlineStr">
@@ -63010,7 +63010,7 @@
       </c>
       <c r="M734" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N734" t="inlineStr">
@@ -64837,7 +64837,7 @@
       </c>
       <c r="M755" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N755" t="inlineStr">
@@ -70743,7 +70743,7 @@
       </c>
       <c r="M823" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N823" t="inlineStr">
@@ -71352,7 +71352,7 @@
       </c>
       <c r="M830" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N830" t="inlineStr">
@@ -72222,7 +72222,7 @@
       </c>
       <c r="M840" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N840" t="inlineStr">
@@ -77877,7 +77877,7 @@
       </c>
       <c r="M905" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N905" t="inlineStr">
@@ -78138,7 +78138,7 @@
       </c>
       <c r="M908" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N908" t="inlineStr">
@@ -79003,7 +79003,7 @@
       </c>
       <c r="M918" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N918" t="inlineStr">
@@ -79177,7 +79177,7 @@
       </c>
       <c r="M920" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N920" t="inlineStr">
@@ -79264,7 +79264,7 @@
       </c>
       <c r="M921" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N921" t="inlineStr">
@@ -79694,7 +79694,7 @@
       </c>
       <c r="M926" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N926" t="inlineStr">
@@ -80390,7 +80390,7 @@
       </c>
       <c r="M934" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N934" t="inlineStr">
@@ -81081,7 +81081,7 @@
       </c>
       <c r="M942" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N942" t="inlineStr">
@@ -81946,7 +81946,7 @@
       </c>
       <c r="M952" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N952" t="inlineStr">
@@ -82120,7 +82120,7 @@
       </c>
       <c r="M954" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N954" t="inlineStr">
@@ -84894,7 +84894,7 @@
       </c>
       <c r="M986" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N986" t="inlineStr">
@@ -85933,7 +85933,7 @@
       </c>
       <c r="M998" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N998" t="inlineStr">
@@ -88108,7 +88108,7 @@
       </c>
       <c r="M1023" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1023" t="inlineStr">
@@ -88456,7 +88456,7 @@
       </c>
       <c r="M1027" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1027" t="inlineStr">
@@ -89500,7 +89500,7 @@
       </c>
       <c r="M1039" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1039" t="inlineStr">
@@ -89761,7 +89761,7 @@
       </c>
       <c r="M1042" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1042" t="inlineStr">
@@ -94879,7 +94879,7 @@
       </c>
       <c r="M1101" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1101" t="inlineStr">
@@ -96793,7 +96793,7 @@
       </c>
       <c r="M1123" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1123" t="inlineStr">
@@ -98006,7 +98006,7 @@
       </c>
       <c r="M1137" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1137" t="inlineStr">
@@ -98615,7 +98615,7 @@
       </c>
       <c r="M1144" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1144" t="inlineStr">
@@ -99311,7 +99311,7 @@
       </c>
       <c r="M1152" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1152" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -701,7 +701,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -31822,7 +31822,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -32083,7 +32083,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -33649,7 +33649,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -34519,7 +34519,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -34780,7 +34780,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -35215,7 +35215,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -35650,7 +35650,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -38260,7 +38260,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -38782,7 +38782,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -39293,7 +39293,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -39554,7 +39554,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -40767,7 +40767,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -41289,7 +41289,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -43759,7 +43759,7 @@
       </c>
       <c r="M511" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N511" t="inlineStr">
@@ -45586,7 +45586,7 @@
       </c>
       <c r="M532" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N532" t="inlineStr">
@@ -45673,7 +45673,7 @@
       </c>
       <c r="M533" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N533" t="inlineStr">
@@ -46456,7 +46456,7 @@
       </c>
       <c r="M542" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N542" t="inlineStr">
@@ -47065,7 +47065,7 @@
       </c>
       <c r="M549" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N549" t="inlineStr">
@@ -47674,7 +47674,7 @@
       </c>
       <c r="M556" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N556" t="inlineStr">
@@ -50779,7 +50779,7 @@
       </c>
       <c r="M592" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N592" t="inlineStr">
@@ -51301,7 +51301,7 @@
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N598" t="inlineStr">
@@ -51567,7 +51567,7 @@
       </c>
       <c r="N601" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O601" t="n">
@@ -54080,7 +54080,7 @@
       </c>
       <c r="M630" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N630" t="inlineStr">
@@ -54689,7 +54689,7 @@
       </c>
       <c r="M637" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N637" t="inlineStr">
@@ -58660,7 +58660,7 @@
       </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N684" t="inlineStr">
@@ -60052,7 +60052,7 @@
       </c>
       <c r="M700" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N700" t="inlineStr">
@@ -60661,7 +60661,7 @@
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N707" t="inlineStr">
@@ -62053,7 +62053,7 @@
       </c>
       <c r="M723" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N723" t="inlineStr">
@@ -63271,7 +63271,7 @@
       </c>
       <c r="M737" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N737" t="inlineStr">
@@ -64576,7 +64576,7 @@
       </c>
       <c r="M752" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N752" t="inlineStr">
@@ -64750,7 +64750,7 @@
       </c>
       <c r="M754" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N754" t="inlineStr">
@@ -66055,7 +66055,7 @@
       </c>
       <c r="M769" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N769" t="inlineStr">
@@ -66229,7 +66229,7 @@
       </c>
       <c r="M771" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N771" t="inlineStr">
@@ -66403,7 +66403,7 @@
       </c>
       <c r="M773" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N773" t="inlineStr">
@@ -68220,7 +68220,7 @@
       </c>
       <c r="M794" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N794" t="inlineStr">
@@ -68916,7 +68916,7 @@
       </c>
       <c r="M802" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N802" t="inlineStr">
@@ -71526,7 +71526,7 @@
       </c>
       <c r="M832" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N832" t="inlineStr">
@@ -73005,7 +73005,7 @@
       </c>
       <c r="M849" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N849" t="inlineStr">
@@ -73266,7 +73266,7 @@
       </c>
       <c r="M852" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N852" t="inlineStr">
@@ -76833,7 +76833,7 @@
       </c>
       <c r="M893" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N893" t="inlineStr">
@@ -77529,7 +77529,7 @@
       </c>
       <c r="M901" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N901" t="inlineStr">
@@ -82212,7 +82212,7 @@
       </c>
       <c r="N955" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O955" t="n">
@@ -86281,7 +86281,7 @@
       </c>
       <c r="M1002" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1002" t="inlineStr">
@@ -86368,7 +86368,7 @@
       </c>
       <c r="M1003" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1003" t="inlineStr">
@@ -86455,7 +86455,7 @@
       </c>
       <c r="M1004" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1004" t="inlineStr">
@@ -88630,7 +88630,7 @@
       </c>
       <c r="M1029" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1029" t="inlineStr">
@@ -90805,7 +90805,7 @@
       </c>
       <c r="M1054" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1054" t="inlineStr">
@@ -91752,7 +91752,7 @@
       </c>
       <c r="M1065" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1065" t="inlineStr">
@@ -94705,7 +94705,7 @@
       </c>
       <c r="M1099" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1099" t="inlineStr">
@@ -95053,7 +95053,7 @@
       </c>
       <c r="M1103" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1103" t="inlineStr">
@@ -96880,7 +96880,7 @@
       </c>
       <c r="M1124" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1124" t="inlineStr">
@@ -97054,7 +97054,7 @@
       </c>
       <c r="M1126" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1126" t="inlineStr">
@@ -99224,7 +99224,7 @@
       </c>
       <c r="M1151" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1151" t="inlineStr">
@@ -99741,7 +99741,7 @@
       </c>
       <c r="M1157" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1157" t="inlineStr">
@@ -99915,7 +99915,7 @@
       </c>
       <c r="M1159" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1159" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1044,7 +1044,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -15666,7 +15666,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -20445,7 +20445,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -23923,7 +23923,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -27016,7 +27016,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -27262,7 +27262,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -28082,7 +28082,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -28492,7 +28492,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -28656,7 +28656,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -28820,7 +28820,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -35737,7 +35737,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -36520,7 +36520,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -38608,7 +38608,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -39380,7 +39380,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -40593,7 +40593,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -43150,7 +43150,7 @@
       </c>
       <c r="M504" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N504" t="inlineStr">
@@ -44281,7 +44281,7 @@
       </c>
       <c r="M517" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N517" t="inlineStr">
@@ -51127,7 +51127,7 @@
       </c>
       <c r="M596" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N596" t="inlineStr">
@@ -51475,7 +51475,7 @@
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N600" t="inlineStr">
@@ -52519,7 +52519,7 @@
       </c>
       <c r="M612" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N612" t="inlineStr">
@@ -52867,7 +52867,7 @@
       </c>
       <c r="M616" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N616" t="inlineStr">
@@ -53645,7 +53645,7 @@
       </c>
       <c r="M625" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N625" t="inlineStr">
@@ -54934,7 +54934,7 @@
       </c>
       <c r="M640" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N640" t="inlineStr">
@@ -59530,7 +59530,7 @@
       </c>
       <c r="M694" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N694" t="inlineStr">
@@ -61444,7 +61444,7 @@
       </c>
       <c r="M716" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N716" t="inlineStr">
@@ -63880,7 +63880,7 @@
       </c>
       <c r="M744" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N744" t="inlineStr">
@@ -66659,7 +66659,7 @@
       </c>
       <c r="M776" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N776" t="inlineStr">
@@ -67002,7 +67002,7 @@
       </c>
       <c r="M780" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N780" t="inlineStr">
@@ -68481,7 +68481,7 @@
       </c>
       <c r="M797" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N797" t="inlineStr">
@@ -73788,7 +73788,7 @@
       </c>
       <c r="M858" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N858" t="inlineStr">
@@ -78307,7 +78307,7 @@
       </c>
       <c r="M910" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N910" t="inlineStr">
@@ -79433,7 +79433,7 @@
       </c>
       <c r="M923" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N923" t="inlineStr">
@@ -80472,7 +80472,7 @@
       </c>
       <c r="M935" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N935" t="inlineStr">
@@ -81859,7 +81859,7 @@
       </c>
       <c r="M951" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N951" t="inlineStr">
@@ -83333,7 +83333,7 @@
       </c>
       <c r="M968" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N968" t="inlineStr">
@@ -83415,7 +83415,7 @@
       </c>
       <c r="M969" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N969" t="inlineStr">
@@ -85237,7 +85237,7 @@
       </c>
       <c r="M990" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N990" t="inlineStr">
@@ -91148,7 +91148,7 @@
       </c>
       <c r="M1058" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1058" t="inlineStr">
@@ -91665,7 +91665,7 @@
       </c>
       <c r="M1064" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1064" t="inlineStr">
@@ -93400,7 +93400,7 @@
       </c>
       <c r="M1084" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1084" t="inlineStr">
@@ -97658,7 +97658,7 @@
       </c>
       <c r="M1133" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1133" t="inlineStr">
@@ -99393,7 +99393,7 @@
       </c>
       <c r="M1153" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1153" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1653,7 +1653,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O155" t="n">
@@ -20281,7 +20281,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -20363,7 +20363,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -22098,7 +22098,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -22185,7 +22185,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -22533,7 +22533,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -27098,7 +27098,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -27344,7 +27344,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -27426,7 +27426,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -27508,7 +27508,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -27590,7 +27590,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -27754,7 +27754,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -27836,7 +27836,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -27918,7 +27918,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -28000,7 +28000,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -28164,7 +28164,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -28246,7 +28246,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -28738,7 +28738,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -31050,7 +31050,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -32518,7 +32518,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -35041,7 +35041,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -35128,7 +35128,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -37129,7 +37129,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -38869,7 +38869,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -39641,7 +39641,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -41795,7 +41795,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -42633,7 +42633,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -48109,7 +48109,7 @@
       </c>
       <c r="M561" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N561" t="inlineStr">
@@ -48881,7 +48881,7 @@
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N570" t="inlineStr">
@@ -49735,7 +49735,7 @@
       </c>
       <c r="M580" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N580" t="inlineStr">
@@ -49822,7 +49822,7 @@
       </c>
       <c r="M581" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N581" t="inlineStr">
@@ -54167,7 +54167,7 @@
       </c>
       <c r="M631" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N631" t="inlineStr">
@@ -54428,7 +54428,7 @@
       </c>
       <c r="M634" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N634" t="inlineStr">
@@ -56833,7 +56833,7 @@
       </c>
       <c r="M663" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N663" t="inlineStr">
@@ -59791,7 +59791,7 @@
       </c>
       <c r="M697" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N697" t="inlineStr">
@@ -64228,7 +64228,7 @@
       </c>
       <c r="M748" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N748" t="inlineStr">
@@ -64489,7 +64489,7 @@
       </c>
       <c r="M751" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N751" t="inlineStr">
@@ -73353,7 +73353,7 @@
       </c>
       <c r="M853" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N853" t="inlineStr">
@@ -78742,7 +78742,7 @@
       </c>
       <c r="M915" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N915" t="inlineStr">
@@ -81603,7 +81603,7 @@
       </c>
       <c r="M948" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N948" t="inlineStr">
@@ -84459,7 +84459,7 @@
       </c>
       <c r="M981" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N981" t="inlineStr">
@@ -85068,7 +85068,7 @@
       </c>
       <c r="M988" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N988" t="inlineStr">
@@ -87412,7 +87412,7 @@
       </c>
       <c r="M1015" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1015" t="inlineStr">
@@ -90022,7 +90022,7 @@
       </c>
       <c r="M1045" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1045" t="inlineStr">
@@ -90631,7 +90631,7 @@
       </c>
       <c r="M1052" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1052" t="inlineStr">
@@ -93144,7 +93144,7 @@
       </c>
       <c r="M1081" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1081" t="inlineStr">
@@ -94531,7 +94531,7 @@
       </c>
       <c r="M1097" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1097" t="inlineStr">
@@ -95401,7 +95401,7 @@
       </c>
       <c r="M1107" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1107" t="inlineStr">
@@ -96358,7 +96358,7 @@
       </c>
       <c r="M1118" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1118" t="inlineStr">
@@ -96967,7 +96967,7 @@
       </c>
       <c r="M1125" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1125" t="inlineStr">
@@ -97402,7 +97402,7 @@
       </c>
       <c r="M1130" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1130" t="inlineStr">
@@ -99137,7 +99137,7 @@
       </c>
       <c r="M1150" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1150" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -20532,7 +20532,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -24951,7 +24951,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -25212,7 +25212,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -31311,7 +31311,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -32953,7 +32953,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -35911,7 +35911,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -36346,7 +36346,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -37390,7 +37390,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -38695,7 +38695,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -39902,7 +39902,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -41202,7 +41202,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -43237,7 +43237,7 @@
       </c>
       <c r="M505" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N505" t="inlineStr">
@@ -44803,7 +44803,7 @@
       </c>
       <c r="M523" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N523" t="inlineStr">
@@ -46804,7 +46804,7 @@
       </c>
       <c r="M546" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N546" t="inlineStr">
@@ -48631,7 +48631,7 @@
       </c>
       <c r="M567" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N567" t="inlineStr">
@@ -49213,7 +49213,7 @@
       </c>
       <c r="M574" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N574" t="inlineStr">
@@ -50953,7 +50953,7 @@
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N594" t="inlineStr">
@@ -53302,7 +53302,7 @@
       </c>
       <c r="M621" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N621" t="inlineStr">
@@ -57268,7 +57268,7 @@
       </c>
       <c r="M668" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N668" t="inlineStr">
@@ -60922,7 +60922,7 @@
       </c>
       <c r="M710" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N710" t="inlineStr">
@@ -61879,7 +61879,7 @@
       </c>
       <c r="M721" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N721" t="inlineStr">
@@ -62227,7 +62227,7 @@
       </c>
       <c r="M725" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N725" t="inlineStr">
@@ -65359,7 +65359,7 @@
       </c>
       <c r="M761" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N761" t="inlineStr">
@@ -68829,7 +68829,7 @@
       </c>
       <c r="M801" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N801" t="inlineStr">
@@ -69003,7 +69003,7 @@
       </c>
       <c r="M803" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N803" t="inlineStr">
@@ -70569,7 +70569,7 @@
       </c>
       <c r="M821" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N821" t="inlineStr">
@@ -72135,7 +72135,7 @@
       </c>
       <c r="M839" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N839" t="inlineStr">
@@ -72309,7 +72309,7 @@
       </c>
       <c r="M841" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N841" t="inlineStr">
@@ -76572,7 +76572,7 @@
       </c>
       <c r="M890" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N890" t="inlineStr">
@@ -78568,7 +78568,7 @@
       </c>
       <c r="M913" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N913" t="inlineStr">
@@ -78916,7 +78916,7 @@
       </c>
       <c r="M917" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N917" t="inlineStr">
@@ -80646,7 +80646,7 @@
       </c>
       <c r="M937" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N937" t="inlineStr">
@@ -80733,7 +80733,7 @@
       </c>
       <c r="M938" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N938" t="inlineStr">
@@ -82729,7 +82729,7 @@
       </c>
       <c r="M961" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N961" t="inlineStr">
@@ -84633,7 +84633,7 @@
       </c>
       <c r="M983" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N983" t="inlineStr">
@@ -85672,7 +85672,7 @@
       </c>
       <c r="M995" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N995" t="inlineStr">
@@ -85846,7 +85846,7 @@
       </c>
       <c r="M997" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N997" t="inlineStr">
@@ -87847,7 +87847,7 @@
       </c>
       <c r="M1020" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1020" t="inlineStr">
@@ -87934,7 +87934,7 @@
       </c>
       <c r="M1021" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1021" t="inlineStr">
@@ -88978,7 +88978,7 @@
       </c>
       <c r="M1033" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1033" t="inlineStr">
@@ -90892,7 +90892,7 @@
       </c>
       <c r="M1055" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1055" t="inlineStr">
@@ -91926,7 +91926,7 @@
       </c>
       <c r="M1067" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1067" t="inlineStr">
@@ -93574,7 +93574,7 @@
       </c>
       <c r="M1086" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1086" t="inlineStr">
@@ -93661,7 +93661,7 @@
       </c>
       <c r="M1087" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1087" t="inlineStr">
@@ -95314,7 +95314,7 @@
       </c>
       <c r="M1106" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1106" t="inlineStr">
@@ -96097,7 +96097,7 @@
       </c>
       <c r="M1115" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1115" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -2436,7 +2436,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -40941,7 +40941,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -44629,7 +44629,7 @@
       </c>
       <c r="M521" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N521" t="inlineStr">
@@ -49387,7 +49387,7 @@
       </c>
       <c r="M576" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N576" t="inlineStr">
@@ -50866,7 +50866,7 @@
       </c>
       <c r="M593" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N593" t="inlineStr">
@@ -56485,7 +56485,7 @@
       </c>
       <c r="M659" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N659" t="inlineStr">
@@ -60313,7 +60313,7 @@
       </c>
       <c r="M703" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N703" t="inlineStr">
@@ -61531,7 +61531,7 @@
       </c>
       <c r="M717" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N717" t="inlineStr">
@@ -71004,7 +71004,7 @@
       </c>
       <c r="M826" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N826" t="inlineStr">
@@ -76050,7 +76050,7 @@
       </c>
       <c r="M884" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N884" t="inlineStr">
@@ -76224,7 +76224,7 @@
       </c>
       <c r="M886" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N886" t="inlineStr">
@@ -76920,7 +76920,7 @@
       </c>
       <c r="M894" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N894" t="inlineStr">
@@ -83850,7 +83850,7 @@
       </c>
       <c r="M974" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N974" t="inlineStr">
@@ -88282,7 +88282,7 @@
       </c>
       <c r="M1025" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1025" t="inlineStr">
@@ -88891,7 +88891,7 @@
       </c>
       <c r="M1032" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1032" t="inlineStr">
@@ -89848,7 +89848,7 @@
       </c>
       <c r="M1043" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1043" t="inlineStr">
@@ -90283,7 +90283,7 @@
       </c>
       <c r="M1048" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1048" t="inlineStr">
@@ -92448,7 +92448,7 @@
       </c>
       <c r="M1073" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1073" t="inlineStr">
@@ -99828,7 +99828,7 @@
       </c>
       <c r="M1158" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1158" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1305,7 +1305,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -29745,7 +29745,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -31909,7 +31909,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -31996,7 +31996,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -35824,7 +35824,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -36781,7 +36781,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -36868,7 +36868,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -37042,7 +37042,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -37912,7 +37912,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -38347,7 +38347,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -40250,7 +40250,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -41463,7 +41463,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -43411,7 +43411,7 @@
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N507" t="inlineStr">
@@ -45330,7 +45330,7 @@
       </c>
       <c r="N529" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O529" t="n">
@@ -48283,7 +48283,7 @@
       </c>
       <c r="M563" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N563" t="inlineStr">
@@ -49561,7 +49561,7 @@
       </c>
       <c r="M578" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N578" t="inlineStr">
@@ -49648,7 +49648,7 @@
       </c>
       <c r="M579" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N579" t="inlineStr">
@@ -52693,7 +52693,7 @@
       </c>
       <c r="M614" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N614" t="inlineStr">
@@ -53476,7 +53476,7 @@
       </c>
       <c r="M623" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N623" t="inlineStr">
@@ -59356,7 +59356,7 @@
       </c>
       <c r="M692" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N692" t="inlineStr">
@@ -59704,7 +59704,7 @@
       </c>
       <c r="M696" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N696" t="inlineStr">
@@ -62314,7 +62314,7 @@
       </c>
       <c r="M726" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N726" t="inlineStr">
@@ -65011,7 +65011,7 @@
       </c>
       <c r="M757" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N757" t="inlineStr">
@@ -67089,7 +67089,7 @@
       </c>
       <c r="M781" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N781" t="inlineStr">
@@ -68655,7 +68655,7 @@
       </c>
       <c r="M799" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N799" t="inlineStr">
@@ -69356,7 +69356,7 @@
       </c>
       <c r="N807" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O807" t="n">
@@ -72918,7 +72918,7 @@
       </c>
       <c r="M848" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N848" t="inlineStr">
@@ -74484,7 +74484,7 @@
       </c>
       <c r="M866" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N866" t="inlineStr">
@@ -74832,7 +74832,7 @@
       </c>
       <c r="M870" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N870" t="inlineStr">
@@ -75093,7 +75093,7 @@
       </c>
       <c r="M873" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N873" t="inlineStr">
@@ -75180,7 +75180,7 @@
       </c>
       <c r="M874" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N874" t="inlineStr">
@@ -76311,7 +76311,7 @@
       </c>
       <c r="M887" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N887" t="inlineStr">
@@ -79008,7 +79008,7 @@
       </c>
       <c r="N918" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O918" t="n">
@@ -82033,7 +82033,7 @@
       </c>
       <c r="M953" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N953" t="inlineStr">
@@ -83502,7 +83502,7 @@
       </c>
       <c r="M970" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N970" t="inlineStr">
@@ -84111,7 +84111,7 @@
       </c>
       <c r="M977" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N977" t="inlineStr">
@@ -86716,7 +86716,7 @@
       </c>
       <c r="M1007" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1007" t="inlineStr">
@@ -94183,7 +94183,7 @@
       </c>
       <c r="M1093" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1093" t="inlineStr">
@@ -94275,7 +94275,7 @@
       </c>
       <c r="N1094" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1094" t="n">
@@ -100263,7 +100263,7 @@
       </c>
       <c r="M1163" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1163" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -962,7 +962,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O64" t="n">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -15405,7 +15405,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O190" t="n">
@@ -19803,17 +19803,17 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O228" t="n">
@@ -19822,6 +19822,17 @@
       <c r="P228" t="n">
         <v>-76.97635</v>
       </c>
+      <c r="Q228" t="n">
+        <v>-12.21215</v>
+      </c>
+      <c r="R228" t="n">
+        <v>-76.97635</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -19879,17 +19890,17 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>NO MIGRADO</t>
+          <t>MIGRADO</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>NO APLICA</t>
+          <t>SIN CONEXION</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>SIN INFORMACION</t>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="O229" t="n">
@@ -19898,6 +19909,17 @@
       <c r="P229" t="n">
         <v>-76.97635</v>
       </c>
+      <c r="Q229" t="n">
+        <v>-12.21215</v>
+      </c>
+      <c r="R229" t="n">
+        <v>-76.97635</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>PARADA</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -21489,7 +21511,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -21924,7 +21946,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -24516,7 +24538,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -24603,7 +24625,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -24777,7 +24799,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -28989,7 +29011,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -29571,7 +29593,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -29919,7 +29941,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -30615,7 +30637,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -31572,7 +31594,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -31735,7 +31757,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -33214,7 +33236,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -33475,7 +33497,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -33828,7 +33850,7 @@
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O396" t="n">
@@ -34606,7 +34628,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -34693,7 +34715,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -38086,7 +38108,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -39989,7 +40011,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -42056,7 +42078,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -42807,7 +42829,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -42894,7 +42916,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
@@ -42981,7 +43003,7 @@
       </c>
       <c r="M502" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N502" t="inlineStr">
@@ -43068,7 +43090,7 @@
       </c>
       <c r="M503" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N503" t="inlineStr">
@@ -43672,7 +43694,7 @@
       </c>
       <c r="M510" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N510" t="inlineStr">
@@ -44020,7 +44042,7 @@
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N514" t="inlineStr">
@@ -45064,7 +45086,7 @@
       </c>
       <c r="M526" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N526" t="inlineStr">
@@ -45934,7 +45956,7 @@
       </c>
       <c r="M536" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N536" t="inlineStr">
@@ -46717,7 +46739,7 @@
       </c>
       <c r="M545" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N545" t="inlineStr">
@@ -46978,7 +47000,7 @@
       </c>
       <c r="M548" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N548" t="inlineStr">
@@ -48022,7 +48044,7 @@
       </c>
       <c r="M560" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N560" t="inlineStr">
@@ -48794,7 +48816,7 @@
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N569" t="inlineStr">
@@ -49909,7 +49931,7 @@
       </c>
       <c r="M582" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N582" t="inlineStr">
@@ -51997,7 +52019,7 @@
       </c>
       <c r="M606" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N606" t="inlineStr">
@@ -52258,7 +52280,7 @@
       </c>
       <c r="M609" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N609" t="inlineStr">
@@ -52345,7 +52367,7 @@
       </c>
       <c r="M610" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N610" t="inlineStr">
@@ -52780,7 +52802,7 @@
       </c>
       <c r="M615" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N615" t="inlineStr">
@@ -53041,7 +53063,7 @@
       </c>
       <c r="M618" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N618" t="inlineStr">
@@ -53215,7 +53237,7 @@
       </c>
       <c r="M620" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N620" t="inlineStr">
@@ -53732,7 +53754,7 @@
       </c>
       <c r="M626" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N626" t="inlineStr">
@@ -54341,7 +54363,7 @@
       </c>
       <c r="M633" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N633" t="inlineStr">
@@ -55195,7 +55217,7 @@
       </c>
       <c r="M643" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N643" t="inlineStr">
@@ -55456,7 +55478,7 @@
       </c>
       <c r="M646" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N646" t="inlineStr">
@@ -55717,7 +55739,7 @@
       </c>
       <c r="M649" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N649" t="inlineStr">
@@ -56311,7 +56333,7 @@
       </c>
       <c r="M657" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N657" t="inlineStr">
@@ -57181,7 +57203,7 @@
       </c>
       <c r="M667" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N667" t="inlineStr">
@@ -57964,7 +57986,7 @@
       </c>
       <c r="M676" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N676" t="inlineStr">
@@ -58747,7 +58769,7 @@
       </c>
       <c r="M685" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N685" t="inlineStr">
@@ -60226,7 +60248,7 @@
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N702" t="inlineStr">
@@ -61705,7 +61727,7 @@
       </c>
       <c r="M719" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N719" t="inlineStr">
@@ -61966,7 +61988,7 @@
       </c>
       <c r="M722" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N722" t="inlineStr">
@@ -62575,7 +62597,7 @@
       </c>
       <c r="M729" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N729" t="inlineStr">
@@ -62749,7 +62771,7 @@
       </c>
       <c r="M731" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N731" t="inlineStr">
@@ -63097,7 +63119,7 @@
       </c>
       <c r="M735" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N735" t="inlineStr">
@@ -63358,7 +63380,7 @@
       </c>
       <c r="M738" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N738" t="inlineStr">
@@ -63445,7 +63467,7 @@
       </c>
       <c r="M739" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N739" t="inlineStr">
@@ -64402,7 +64424,7 @@
       </c>
       <c r="M750" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N750" t="inlineStr">
@@ -64663,7 +64685,7 @@
       </c>
       <c r="M753" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N753" t="inlineStr">
@@ -65185,7 +65207,7 @@
       </c>
       <c r="M759" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N759" t="inlineStr">
@@ -65272,7 +65294,7 @@
       </c>
       <c r="M760" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N760" t="inlineStr">
@@ -65707,7 +65729,7 @@
       </c>
       <c r="M765" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N765" t="inlineStr">
@@ -66142,7 +66164,7 @@
       </c>
       <c r="M770" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N770" t="inlineStr">
@@ -66321,7 +66343,7 @@
       </c>
       <c r="N772" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O772" t="n">
@@ -67263,7 +67285,7 @@
       </c>
       <c r="M783" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N783" t="inlineStr">
@@ -67350,7 +67372,7 @@
       </c>
       <c r="M784" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N784" t="inlineStr">
@@ -67437,7 +67459,7 @@
       </c>
       <c r="M785" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N785" t="inlineStr">
@@ -67959,7 +67981,7 @@
       </c>
       <c r="M791" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N791" t="inlineStr">
@@ -68046,7 +68068,7 @@
       </c>
       <c r="M792" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N792" t="inlineStr">
@@ -68394,7 +68416,7 @@
       </c>
       <c r="M796" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N796" t="inlineStr">
@@ -69090,7 +69112,7 @@
       </c>
       <c r="M804" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N804" t="inlineStr">
@@ -69960,7 +69982,7 @@
       </c>
       <c r="M814" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N814" t="inlineStr">
@@ -70395,7 +70417,7 @@
       </c>
       <c r="M819" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N819" t="inlineStr">
@@ -71091,7 +71113,7 @@
       </c>
       <c r="M827" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N827" t="inlineStr">
@@ -71700,7 +71722,7 @@
       </c>
       <c r="M834" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N834" t="inlineStr">
@@ -72048,7 +72070,7 @@
       </c>
       <c r="M838" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N838" t="inlineStr">
@@ -72657,7 +72679,7 @@
       </c>
       <c r="M845" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N845" t="inlineStr">
@@ -73179,7 +73201,7 @@
       </c>
       <c r="M851" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N851" t="inlineStr">
@@ -73614,7 +73636,7 @@
       </c>
       <c r="M856" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N856" t="inlineStr">
@@ -74223,7 +74245,7 @@
       </c>
       <c r="M863" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N863" t="inlineStr">
@@ -74924,7 +74946,7 @@
       </c>
       <c r="N871" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O871" t="n">
@@ -75006,7 +75028,7 @@
       </c>
       <c r="M872" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N872" t="inlineStr">
@@ -75446,7 +75468,7 @@
       </c>
       <c r="N877" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O877" t="n">
@@ -75615,7 +75637,7 @@
       </c>
       <c r="M879" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N879" t="inlineStr">
@@ -76137,7 +76159,7 @@
       </c>
       <c r="M885" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N885" t="inlineStr">
@@ -76398,7 +76420,7 @@
       </c>
       <c r="M888" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N888" t="inlineStr">
@@ -76659,7 +76681,7 @@
       </c>
       <c r="M891" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N891" t="inlineStr">
@@ -76746,7 +76768,7 @@
       </c>
       <c r="M892" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N892" t="inlineStr">
@@ -77181,7 +77203,7 @@
       </c>
       <c r="M897" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N897" t="inlineStr">
@@ -77442,7 +77464,7 @@
       </c>
       <c r="M900" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N900" t="inlineStr">
@@ -77616,7 +77638,7 @@
       </c>
       <c r="M902" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N902" t="inlineStr">
@@ -79090,7 +79112,7 @@
       </c>
       <c r="M919" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N919" t="inlineStr">
@@ -81951,7 +81973,7 @@
       </c>
       <c r="N952" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O952" t="n">
@@ -82642,7 +82664,7 @@
       </c>
       <c r="M960" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N960" t="inlineStr">
@@ -82816,7 +82838,7 @@
       </c>
       <c r="M962" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N962" t="inlineStr">
@@ -83763,7 +83785,7 @@
       </c>
       <c r="M973" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N973" t="inlineStr">
@@ -84285,7 +84307,7 @@
       </c>
       <c r="M979" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N979" t="inlineStr">
@@ -85155,7 +85177,7 @@
       </c>
       <c r="M989" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N989" t="inlineStr">
@@ -86803,7 +86825,7 @@
       </c>
       <c r="M1008" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1008" t="inlineStr">
@@ -86890,7 +86912,7 @@
       </c>
       <c r="M1009" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1009" t="inlineStr">
@@ -87064,7 +87086,7 @@
       </c>
       <c r="M1011" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1011" t="inlineStr">
@@ -87151,7 +87173,7 @@
       </c>
       <c r="M1012" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1012" t="inlineStr">
@@ -87499,7 +87521,7 @@
       </c>
       <c r="M1016" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1016" t="inlineStr">
@@ -89674,7 +89696,7 @@
       </c>
       <c r="M1041" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1041" t="inlineStr">
@@ -90109,7 +90131,7 @@
       </c>
       <c r="M1046" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1046" t="inlineStr">
@@ -91496,7 +91518,7 @@
       </c>
       <c r="M1062" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1062" t="inlineStr">
@@ -92013,7 +92035,7 @@
       </c>
       <c r="M1068" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1068" t="inlineStr">
@@ -92100,7 +92122,7 @@
       </c>
       <c r="M1069" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1069" t="inlineStr">
@@ -92535,7 +92557,7 @@
       </c>
       <c r="M1074" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1074" t="inlineStr">
@@ -93231,7 +93253,7 @@
       </c>
       <c r="M1082" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1082" t="inlineStr">
@@ -93835,7 +93857,7 @@
       </c>
       <c r="M1089" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1089" t="inlineStr">
@@ -93922,7 +93944,7 @@
       </c>
       <c r="M1090" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1090" t="inlineStr">
@@ -96010,7 +96032,7 @@
       </c>
       <c r="M1114" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1114" t="inlineStr">
@@ -96619,7 +96641,7 @@
       </c>
       <c r="M1121" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1121" t="inlineStr">
@@ -97489,7 +97511,7 @@
       </c>
       <c r="M1131" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1131" t="inlineStr">
@@ -97832,7 +97854,7 @@
       </c>
       <c r="M1135" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1135" t="inlineStr">
@@ -98011,7 +98033,7 @@
       </c>
       <c r="N1137" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1137" t="n">
@@ -98180,7 +98202,7 @@
       </c>
       <c r="M1139" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1139" t="inlineStr">
@@ -98702,7 +98724,7 @@
       </c>
       <c r="M1145" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1145" t="inlineStr">
@@ -98876,7 +98898,7 @@
       </c>
       <c r="M1147" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1147" t="inlineStr">
@@ -99050,7 +99072,7 @@
       </c>
       <c r="M1149" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1149" t="inlineStr">
@@ -100176,7 +100198,7 @@
       </c>
       <c r="M1162" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1162" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3459,7 +3459,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -16280,7 +16280,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O184" t="n">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O193" t="n">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -19803,17 +19803,17 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O228" t="n">
@@ -19822,17 +19822,6 @@
       <c r="P228" t="n">
         <v>-76.97635</v>
       </c>
-      <c r="Q228" t="n">
-        <v>-12.21215</v>
-      </c>
-      <c r="R228" t="n">
-        <v>-76.97635</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -19890,17 +19879,17 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O229" t="n">
@@ -19909,17 +19898,6 @@
       <c r="P229" t="n">
         <v>-76.97635</v>
       </c>
-      <c r="Q229" t="n">
-        <v>-12.21215</v>
-      </c>
-      <c r="R229" t="n">
-        <v>-76.97635</v>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -29506,7 +29484,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -30724,7 +30702,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -33937,7 +33915,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O397" t="n">
@@ -34193,7 +34171,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -37673,7 +37651,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -39750,7 +39728,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -43873,7 +43851,7 @@
       </c>
       <c r="N512" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O512" t="n">
@@ -47614,7 +47592,7 @@
       </c>
       <c r="N555" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O555" t="n">
@@ -47870,7 +47848,7 @@
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N558" t="inlineStr">
@@ -47957,7 +47935,7 @@
       </c>
       <c r="M559" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N559" t="inlineStr">
@@ -49148,7 +49126,7 @@
       </c>
       <c r="M573" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N573" t="inlineStr">
@@ -49936,7 +49914,7 @@
       </c>
       <c r="N582" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O582" t="n">
@@ -53585,7 +53563,7 @@
       </c>
       <c r="M624" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N624" t="inlineStr">
@@ -58334,7 +58312,7 @@
       </c>
       <c r="M680" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N680" t="inlineStr">
@@ -59465,7 +59443,7 @@
       </c>
       <c r="M693" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N693" t="inlineStr">
@@ -59987,7 +59965,7 @@
       </c>
       <c r="M699" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N699" t="inlineStr">
@@ -61118,7 +61096,7 @@
       </c>
       <c r="M712" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N712" t="inlineStr">
@@ -67377,7 +67355,7 @@
       </c>
       <c r="N784" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O784" t="n">
@@ -68590,7 +68568,7 @@
       </c>
       <c r="M798" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N798" t="inlineStr">
@@ -70069,7 +70047,7 @@
       </c>
       <c r="M815" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N815" t="inlineStr">
@@ -70678,7 +70656,7 @@
       </c>
       <c r="M822" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N822" t="inlineStr">
@@ -71809,7 +71787,7 @@
       </c>
       <c r="M835" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N835" t="inlineStr">
@@ -71896,7 +71874,7 @@
       </c>
       <c r="M836" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N836" t="inlineStr">
@@ -72766,7 +72744,7 @@
       </c>
       <c r="M846" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N846" t="inlineStr">
@@ -73549,7 +73527,7 @@
       </c>
       <c r="M855" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N855" t="inlineStr">
@@ -74332,7 +74310,7 @@
       </c>
       <c r="M864" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N864" t="inlineStr">
@@ -77029,7 +77007,7 @@
       </c>
       <c r="M895" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N895" t="inlineStr">
@@ -78073,7 +78051,7 @@
       </c>
       <c r="M907" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N907" t="inlineStr">
@@ -79542,7 +79520,7 @@
       </c>
       <c r="M924" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N924" t="inlineStr">
@@ -83273,7 +83251,7 @@
       </c>
       <c r="M967" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N967" t="inlineStr">
@@ -86216,7 +86194,7 @@
       </c>
       <c r="M1001" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1001" t="inlineStr">
@@ -86999,7 +86977,7 @@
       </c>
       <c r="M1010" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1010" t="inlineStr">
@@ -89957,7 +89935,7 @@
       </c>
       <c r="M1044" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1044" t="inlineStr">
@@ -90223,7 +90201,7 @@
       </c>
       <c r="N1047" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1047" t="n">
@@ -90392,7 +90370,7 @@
       </c>
       <c r="M1049" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1049" t="inlineStr">
@@ -91088,7 +91066,7 @@
       </c>
       <c r="M1057" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1057" t="inlineStr">
@@ -91344,7 +91322,7 @@
       </c>
       <c r="M1060" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1060" t="inlineStr">
@@ -91431,7 +91409,7 @@
       </c>
       <c r="M1061" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1061" t="inlineStr">
@@ -94031,7 +94009,7 @@
       </c>
       <c r="M1091" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1091" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -2093,7 +2093,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O38" t="n">
@@ -48549,7 +48549,7 @@
       </c>
       <c r="N566" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O566" t="n">
@@ -49653,7 +49653,7 @@
       </c>
       <c r="N579" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O579" t="n">
@@ -53481,7 +53481,7 @@
       </c>
       <c r="N623" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O623" t="n">
@@ -59361,7 +59361,7 @@
       </c>
       <c r="N692" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O692" t="n">
@@ -63015,7 +63015,7 @@
       </c>
       <c r="N734" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O734" t="n">
@@ -71183,7 +71183,7 @@
       </c>
       <c r="N828" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O828" t="n">
@@ -72923,7 +72923,7 @@
       </c>
       <c r="N848" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O848" t="n">
@@ -76316,7 +76316,7 @@
       </c>
       <c r="N887" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O887" t="n">
@@ -78486,7 +78486,7 @@
       </c>
       <c r="N912" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O912" t="n">
@@ -79356,7 +79356,7 @@
       </c>
       <c r="N922" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O922" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -33567,7 +33567,7 @@
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O393" t="n">
@@ -45504,7 +45504,7 @@
       </c>
       <c r="N531" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O531" t="n">
@@ -54852,7 +54852,7 @@
       </c>
       <c r="N639" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O639" t="n">
@@ -59187,7 +59187,7 @@
       </c>
       <c r="N690" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O690" t="n">
@@ -62232,7 +62232,7 @@
       </c>
       <c r="N725" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O725" t="n">
@@ -73706,7 +73706,7 @@
       </c>
       <c r="N857" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O857" t="n">
@@ -77882,7 +77882,7 @@
       </c>
       <c r="N905" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O905" t="n">
@@ -78230,7 +78230,7 @@
       </c>
       <c r="N909" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O909" t="n">
@@ -84899,7 +84899,7 @@
       </c>
       <c r="N986" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O986" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -7310,7 +7310,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O80" t="n">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O98" t="n">
@@ -25468,17 +25468,17 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O296" t="n">
@@ -25487,17 +25487,6 @@
       <c r="P296" t="n">
         <v>-77.13114</v>
       </c>
-      <c r="Q296" t="n">
-        <v>-11.95196</v>
-      </c>
-      <c r="R296" t="n">
-        <v>-77.13114</v>
-      </c>
-      <c r="S296" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -25555,17 +25544,17 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O297" t="n">
@@ -25574,17 +25563,6 @@
       <c r="P297" t="n">
         <v>-77.13114</v>
       </c>
-      <c r="Q297" t="n">
-        <v>-11.95196</v>
-      </c>
-      <c r="R297" t="n">
-        <v>-77.13114</v>
-      </c>
-      <c r="S297" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -25739,7 +25717,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O299" t="n">
@@ -26000,7 +25978,7 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O302" t="n">
@@ -32165,17 +32143,17 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O377" t="n">
@@ -32184,17 +32162,6 @@
       <c r="P377" t="n">
         <v>-77.13114</v>
       </c>
-      <c r="Q377" t="n">
-        <v>-11.95196</v>
-      </c>
-      <c r="R377" t="n">
-        <v>-77.13114</v>
-      </c>
-      <c r="S377" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -37395,7 +37362,7 @@
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O437" t="n">
@@ -42470,17 +42437,17 @@
       </c>
       <c r="L496" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O496" t="n">
@@ -42489,17 +42456,6 @@
       <c r="P496" t="n">
         <v>-77.13114</v>
       </c>
-      <c r="Q496" t="n">
-        <v>-11.95196</v>
-      </c>
-      <c r="R496" t="n">
-        <v>-77.13114</v>
-      </c>
-      <c r="S496" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -44199,7 +44155,7 @@
       </c>
       <c r="N516" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O516" t="n">
@@ -45852,7 +45808,7 @@
       </c>
       <c r="N535" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O535" t="n">
@@ -46113,7 +46069,7 @@
       </c>
       <c r="N538" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O538" t="n">
@@ -58491,7 +58447,7 @@
       </c>
       <c r="N682" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O682" t="n">
@@ -60492,7 +60448,7 @@
       </c>
       <c r="N705" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O705" t="n">
@@ -73967,7 +73923,7 @@
       </c>
       <c r="N860" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O860" t="n">
@@ -76925,7 +76881,7 @@
       </c>
       <c r="N894" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O894" t="n">
@@ -78834,7 +78790,7 @@
       </c>
       <c r="N916" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O916" t="n">
@@ -88200,7 +88156,7 @@
       </c>
       <c r="N1024" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1024" t="n">
@@ -92453,7 +92409,7 @@
       </c>
       <c r="N1073" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1073" t="n">
@@ -98098,7 +98054,7 @@
       </c>
       <c r="N1138" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1138" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -9045,7 +9045,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O100" t="n">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O175" t="n">
@@ -34752,7 +34752,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O407" t="n">
@@ -35187,7 +35187,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O412" t="n">
@@ -39526,7 +39526,7 @@
       </c>
       <c r="N462" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O462" t="n">
@@ -46417,7 +46417,7 @@
       </c>
       <c r="N542" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O542" t="n">
@@ -57055,7 +57055,7 @@
       </c>
       <c r="N666" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O666" t="n">
@@ -63232,7 +63232,7 @@
       </c>
       <c r="N737" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O737" t="n">
@@ -64537,7 +64537,7 @@
       </c>
       <c r="N752" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O752" t="n">
@@ -67572,7 +67572,7 @@
       </c>
       <c r="N787" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O787" t="n">
@@ -77490,7 +77490,7 @@
       </c>
       <c r="N901" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O901" t="n">
@@ -81477,7 +81477,7 @@
       </c>
       <c r="N947" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O947" t="n">
@@ -85372,7 +85372,7 @@
       </c>
       <c r="N992" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O992" t="n">
@@ -85459,7 +85459,7 @@
       </c>
       <c r="N993" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O993" t="n">
@@ -93535,7 +93535,7 @@
       </c>
       <c r="N1086" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1086" t="n">
@@ -94666,7 +94666,7 @@
       </c>
       <c r="N1099" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1099" t="n">
@@ -97537,7 +97537,7 @@
       </c>
       <c r="N1132" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1132" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -20117,7 +20117,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O232" t="n">
@@ -61231,7 +61231,7 @@
       </c>
       <c r="N714" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O714" t="n">
@@ -61840,7 +61840,7 @@
       </c>
       <c r="N721" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O721" t="n">
@@ -62362,7 +62362,7 @@
       </c>
       <c r="N727" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O727" t="n">
@@ -63580,7 +63580,7 @@
       </c>
       <c r="N741" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O741" t="n">
@@ -83550,7 +83550,7 @@
       </c>
       <c r="N971" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O971" t="n">
@@ -88069,7 +88069,7 @@
       </c>
       <c r="N1023" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1023" t="n">
@@ -88939,7 +88939,7 @@
       </c>
       <c r="N1033" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1033" t="n">
@@ -98924,7 +98924,7 @@
       </c>
       <c r="N1148" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1148" t="n">
@@ -99272,7 +99272,7 @@
       </c>
       <c r="N1152" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1152" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -2267,7 +2267,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O82" t="n">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O179" t="n">
@@ -28972,7 +28972,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O340" t="n">
@@ -32751,7 +32751,7 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O384" t="n">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O387" t="n">
@@ -39352,7 +39352,7 @@
       </c>
       <c r="N460" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O460" t="n">
@@ -49522,7 +49522,7 @@
       </c>
       <c r="N578" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O578" t="n">
@@ -58534,7 +58534,7 @@
       </c>
       <c r="N683" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O683" t="n">
@@ -60796,7 +60796,7 @@
       </c>
       <c r="N709" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O709" t="n">
@@ -68268,7 +68268,7 @@
       </c>
       <c r="N795" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O795" t="n">
@@ -69921,7 +69921,7 @@
       </c>
       <c r="N814" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O814" t="n">
@@ -80781,7 +80781,7 @@
       </c>
       <c r="N939" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O939" t="n">
@@ -81738,7 +81738,7 @@
       </c>
       <c r="N950" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O950" t="n">
@@ -90070,7 +90070,7 @@
       </c>
       <c r="N1046" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1046" t="n">
@@ -95188,7 +95188,7 @@
       </c>
       <c r="N1105" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1105" t="n">
@@ -95710,7 +95710,7 @@
       </c>
       <c r="N1111" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1111" t="n">
@@ -95884,7 +95884,7 @@
       </c>
       <c r="N1113" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1113" t="n">
@@ -98663,7 +98663,7 @@
       </c>
       <c r="N1145" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1145" t="n">
@@ -98837,7 +98837,7 @@
       </c>
       <c r="N1147" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1147" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -2866,12 +2866,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O74" t="n">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O156" t="n">
@@ -13941,12 +13941,12 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O157" t="n">
@@ -17139,7 +17139,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O194" t="n">
@@ -20619,7 +20619,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O260" t="n">
@@ -30772,7 +30772,7 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O361" t="n">
@@ -38580,7 +38580,7 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O451" t="n">
@@ -40647,7 +40647,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -41675,12 +41675,12 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O487" t="n">
@@ -42355,7 +42355,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -45194,7 +45194,7 @@
       </c>
       <c r="M528" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N528" t="inlineStr">
@@ -45716,7 +45716,7 @@
       </c>
       <c r="M534" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N534" t="inlineStr">
@@ -49174,7 +49174,7 @@
       </c>
       <c r="N574" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O574" t="n">
@@ -50474,7 +50474,7 @@
       </c>
       <c r="M589" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N589" t="inlineStr">
@@ -51349,7 +51349,7 @@
       </c>
       <c r="N599" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O599" t="n">
@@ -51610,7 +51610,7 @@
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O602" t="n">
@@ -55325,12 +55325,12 @@
       </c>
       <c r="M645" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N645" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O645" t="n">
@@ -59578,7 +59578,7 @@
       </c>
       <c r="N695" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O695" t="n">
@@ -62096,7 +62096,7 @@
       </c>
       <c r="M724" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N724" t="inlineStr">
@@ -66103,7 +66103,7 @@
       </c>
       <c r="N770" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O770" t="n">
@@ -67132,7 +67132,7 @@
       </c>
       <c r="M782" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N782" t="inlineStr">
@@ -70269,7 +70269,7 @@
       </c>
       <c r="N818" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O818" t="n">
@@ -70438,7 +70438,7 @@
       </c>
       <c r="M820" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N820" t="inlineStr">
@@ -73749,7 +73749,7 @@
       </c>
       <c r="N858" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O858" t="n">
@@ -81124,12 +81124,12 @@
       </c>
       <c r="M943" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N943" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O943" t="n">
@@ -81303,7 +81303,7 @@
       </c>
       <c r="N945" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O945" t="n">
@@ -85633,7 +85633,7 @@
       </c>
       <c r="N995" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O995" t="n">
@@ -91887,7 +91887,7 @@
       </c>
       <c r="N1067" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1067" t="n">
@@ -97097,7 +97097,7 @@
       </c>
       <c r="M1127" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1127" t="inlineStr">
@@ -98310,7 +98310,7 @@
       </c>
       <c r="M1141" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1141" t="inlineStr">
@@ -98576,7 +98576,7 @@
       </c>
       <c r="N1144" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1144" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -7745,7 +7745,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O85" t="n">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O147" t="n">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O152" t="n">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O177" t="n">
@@ -22364,7 +22364,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O258" t="n">
@@ -36492,7 +36492,7 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O427" t="n">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O441" t="n">
@@ -48842,7 +48842,7 @@
       </c>
       <c r="N570" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O570" t="n">
@@ -49696,7 +49696,7 @@
       </c>
       <c r="N580" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O580" t="n">
@@ -52567,7 +52567,7 @@
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O613" t="n">
@@ -52828,7 +52828,7 @@
       </c>
       <c r="N616" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O616" t="n">
@@ -54389,7 +54389,7 @@
       </c>
       <c r="N634" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O634" t="n">
@@ -56446,7 +56446,7 @@
       </c>
       <c r="N659" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O659" t="n">
@@ -64798,7 +64798,7 @@
       </c>
       <c r="N755" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O755" t="n">
@@ -75054,7 +75054,7 @@
       </c>
       <c r="N873" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O873" t="n">
@@ -76011,7 +76011,7 @@
       </c>
       <c r="N884" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O884" t="n">
@@ -79655,7 +79655,7 @@
       </c>
       <c r="N926" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O926" t="n">
@@ -85029,7 +85029,7 @@
       </c>
       <c r="N988" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O988" t="n">
@@ -88243,7 +88243,7 @@
       </c>
       <c r="N1025" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1025" t="n">
@@ -89722,7 +89722,7 @@
       </c>
       <c r="N1042" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1042" t="n">
@@ -89983,7 +89983,7 @@
       </c>
       <c r="N1045" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1045" t="n">
@@ -93709,7 +93709,7 @@
       </c>
       <c r="N1088" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1088" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -14453,12 +14453,12 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O163" t="n">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O167" t="n">
@@ -15231,7 +15231,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -17221,7 +17221,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O234" t="n">
@@ -22103,7 +22103,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O255" t="n">
@@ -27081,7 +27081,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O317" t="n">
@@ -27491,7 +27491,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O322" t="n">
@@ -27655,7 +27655,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O324" t="n">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O325" t="n">
@@ -27901,7 +27901,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O327" t="n">
@@ -28147,7 +28147,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O330" t="n">
@@ -28393,7 +28393,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O333" t="n">
@@ -28721,7 +28721,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O337" t="n">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -29989,7 +29989,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O352" t="n">
@@ -30859,7 +30859,7 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O362" t="n">
@@ -31207,7 +31207,7 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O366" t="n">
@@ -35530,12 +35530,12 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O416" t="n">
@@ -36661,12 +36661,12 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O429" t="n">
@@ -37183,7 +37183,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -37270,7 +37270,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -37444,12 +37444,12 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O438" t="n">
@@ -40135,7 +40135,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O469" t="n">
@@ -42855,7 +42855,7 @@
       </c>
       <c r="N501" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O501" t="n">
@@ -51436,7 +51436,7 @@
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O600" t="n">
@@ -51779,7 +51779,7 @@
       </c>
       <c r="M604" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N604" t="inlineStr">
@@ -52127,7 +52127,7 @@
       </c>
       <c r="M608" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N608" t="inlineStr">
@@ -52393,7 +52393,7 @@
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O611" t="n">
@@ -56528,7 +56528,7 @@
       </c>
       <c r="M660" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N660" t="inlineStr">
@@ -56963,7 +56963,7 @@
       </c>
       <c r="M665" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N665" t="inlineStr">
@@ -58181,7 +58181,7 @@
       </c>
       <c r="M679" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N679" t="inlineStr">
@@ -61139,7 +61139,7 @@
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N713" t="inlineStr">
@@ -63488,7 +63488,7 @@
       </c>
       <c r="M740" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N740" t="inlineStr">
@@ -67654,7 +67654,7 @@
       </c>
       <c r="M788" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N788" t="inlineStr">
@@ -67828,7 +67828,7 @@
       </c>
       <c r="M790" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N790" t="inlineStr">
@@ -68964,7 +68964,7 @@
       </c>
       <c r="N803" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O803" t="n">
@@ -75310,7 +75310,7 @@
       </c>
       <c r="M876" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N876" t="inlineStr">
@@ -79737,7 +79737,7 @@
       </c>
       <c r="M927" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N927" t="inlineStr">
@@ -79998,7 +79998,7 @@
       </c>
       <c r="M930" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N930" t="inlineStr">
@@ -80085,7 +80085,7 @@
       </c>
       <c r="M931" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N931" t="inlineStr">
@@ -80177,7 +80177,7 @@
       </c>
       <c r="N932" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O932" t="n">
@@ -82511,7 +82511,7 @@
       </c>
       <c r="M959" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N959" t="inlineStr">
@@ -83120,12 +83120,12 @@
       </c>
       <c r="M966" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N966" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O966" t="n">
@@ -84502,7 +84502,7 @@
       </c>
       <c r="M982" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N982" t="inlineStr">
@@ -85976,7 +85976,7 @@
       </c>
       <c r="M999" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N999" t="inlineStr">
@@ -87808,7 +87808,7 @@
       </c>
       <c r="N1020" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1020" t="n">
@@ -88673,7 +88673,7 @@
       </c>
       <c r="M1030" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1030" t="inlineStr">
@@ -89021,12 +89021,12 @@
       </c>
       <c r="M1034" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1034" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1034" t="n">
@@ -90500,7 +90500,7 @@
       </c>
       <c r="M1051" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1051" t="inlineStr">
@@ -90935,7 +90935,7 @@
       </c>
       <c r="M1056" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1056" t="inlineStr">
@@ -91795,7 +91795,7 @@
       </c>
       <c r="M1066" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1066" t="inlineStr">
@@ -92061,7 +92061,7 @@
       </c>
       <c r="N1069" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1069" t="n">
@@ -92230,7 +92230,7 @@
       </c>
       <c r="M1071" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1071" t="inlineStr">
@@ -92665,7 +92665,7 @@
       </c>
       <c r="M1076" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1076" t="inlineStr">
@@ -93443,7 +93443,7 @@
       </c>
       <c r="M1085" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1085" t="inlineStr">
@@ -95362,7 +95362,7 @@
       </c>
       <c r="N1107" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1107" t="n">
@@ -95792,7 +95792,7 @@
       </c>
       <c r="M1112" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1112" t="inlineStr">
@@ -96662,7 +96662,7 @@
       </c>
       <c r="M1122" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1122" t="inlineStr">
@@ -97184,12 +97184,12 @@
       </c>
       <c r="M1128" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1128" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1128" t="n">
@@ -97363,7 +97363,7 @@
       </c>
       <c r="N1130" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1130" t="n">
@@ -99958,7 +99958,7 @@
       </c>
       <c r="M1160" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1160" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3116,7 +3116,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O66" t="n">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O120" t="n">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O161" t="n">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O162" t="n">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O168" t="n">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O248" t="n">
@@ -25120,17 +25120,17 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O292" t="n">
@@ -25139,17 +25139,6 @@
       <c r="P292" t="n">
         <v>-76.8852</v>
       </c>
-      <c r="Q292" t="n">
-        <v>-12.2481</v>
-      </c>
-      <c r="R292" t="n">
-        <v>-76.8852</v>
-      </c>
-      <c r="S292" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -30337,7 +30326,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O356" t="n">
@@ -31294,7 +31283,7 @@
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O367" t="n">
@@ -36057,7 +36046,7 @@
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O422" t="n">
@@ -36144,7 +36133,7 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O423" t="n">
@@ -37884,7 +37873,7 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O443" t="n">
@@ -38058,7 +38047,7 @@
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O445" t="n">
@@ -38667,7 +38656,7 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O452" t="n">
@@ -39874,7 +39863,7 @@
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O466" t="n">
@@ -41854,7 +41843,7 @@
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O489" t="n">
@@ -51958,7 +51947,7 @@
       </c>
       <c r="N606" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O606" t="n">
@@ -52654,7 +52643,7 @@
       </c>
       <c r="N614" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O614" t="n">
@@ -53176,7 +53165,7 @@
       </c>
       <c r="N620" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O620" t="n">
@@ -60970,7 +60959,7 @@
       </c>
       <c r="N711" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O711" t="n">
@@ -61405,7 +61394,7 @@
       </c>
       <c r="N716" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O716" t="n">
@@ -63058,7 +63047,7 @@
       </c>
       <c r="N735" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O735" t="n">
@@ -68616,7 +68605,7 @@
       </c>
       <c r="N799" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O799" t="n">
@@ -73391,17 +73380,17 @@
       </c>
       <c r="L854" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M854" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N854" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O854" t="n">
@@ -73410,17 +73399,6 @@
       <c r="P854" t="n">
         <v>-77.06480000000001</v>
       </c>
-      <c r="Q854" t="n">
-        <v>-11.97825</v>
-      </c>
-      <c r="R854" t="n">
-        <v>-77.06480000000001</v>
-      </c>
-      <c r="S854" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -82081,7 +82059,7 @@
       </c>
       <c r="N954" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O954" t="n">
@@ -90418,7 +90396,7 @@
       </c>
       <c r="N1050" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1050" t="n">
@@ -94840,7 +94818,7 @@
       </c>
       <c r="N1101" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1101" t="n">
@@ -96483,17 +96461,17 @@
       </c>
       <c r="L1120" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1120" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1120" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1120" t="n">
@@ -96502,17 +96480,6 @@
       <c r="P1120" t="n">
         <v>-77.06480000000001</v>
       </c>
-      <c r="Q1120" t="n">
-        <v>-11.97825</v>
-      </c>
-      <c r="R1120" t="n">
-        <v>-77.06480000000001</v>
-      </c>
-      <c r="S1120" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
@@ -100040,17 +100007,17 @@
       </c>
       <c r="L1161" t="inlineStr">
         <is>
-          <t>MIGRADO</t>
+          <t>NO MIGRADO</t>
         </is>
       </c>
       <c r="M1161" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>NO APLICA</t>
         </is>
       </c>
       <c r="N1161" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O1161" t="n">
@@ -100059,17 +100026,6 @@
       <c r="P1161" t="n">
         <v>-77.06480000000001</v>
       </c>
-      <c r="Q1161" t="n">
-        <v>-11.97825</v>
-      </c>
-      <c r="R1161" t="n">
-        <v>-77.06480000000001</v>
-      </c>
-      <c r="S1161" t="inlineStr">
-        <is>
-          <t>PARADA</t>
-        </is>
-      </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
@@ -100224,7 +100180,7 @@
       </c>
       <c r="N1163" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1163" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1658,7 +1658,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O57" t="n">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O137" t="n">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O146" t="n">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O187" t="n">
@@ -20885,7 +20885,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O241" t="n">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O256" t="n">
@@ -30065,7 +30065,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O353" t="n">
@@ -31022,7 +31022,7 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O364" t="n">
@@ -31109,7 +31109,7 @@
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O365" t="n">
@@ -35002,7 +35002,7 @@
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O410" t="n">
@@ -38221,7 +38221,7 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O447" t="n">
@@ -39167,7 +39167,7 @@
       </c>
       <c r="N458" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O458" t="n">
@@ -40554,7 +40554,7 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O474" t="n">
@@ -40641,7 +40641,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O475" t="n">
@@ -43100,7 +43100,7 @@
       </c>
       <c r="N504" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O504" t="n">
@@ -43709,7 +43709,7 @@
       </c>
       <c r="N511" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O511" t="n">
@@ -50294,7 +50294,7 @@
       </c>
       <c r="N587" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O587" t="n">
@@ -54117,7 +54117,7 @@
       </c>
       <c r="N631" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O631" t="n">
@@ -56870,7 +56870,7 @@
       </c>
       <c r="N664" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O664" t="n">
@@ -61307,7 +61307,7 @@
       </c>
       <c r="N715" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O715" t="n">
@@ -64700,7 +64700,7 @@
       </c>
       <c r="N754" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O754" t="n">
@@ -66179,7 +66179,7 @@
       </c>
       <c r="N771" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O771" t="n">
@@ -66353,7 +66353,7 @@
       </c>
       <c r="N773" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O773" t="n">
@@ -69562,7 +69562,7 @@
       </c>
       <c r="N810" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O810" t="n">
@@ -71389,7 +71389,7 @@
       </c>
       <c r="N831" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O831" t="n">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="N833" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O833" t="n">
@@ -72085,7 +72085,7 @@
       </c>
       <c r="N839" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O839" t="n">
@@ -72955,7 +72955,7 @@
       </c>
       <c r="N849" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O849" t="n">
@@ -77294,7 +77294,7 @@
       </c>
       <c r="N899" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O899" t="n">
@@ -79372,7 +79372,7 @@
       </c>
       <c r="N923" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O923" t="n">
@@ -80242,7 +80242,7 @@
       </c>
       <c r="N933" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O933" t="n">
@@ -80411,7 +80411,7 @@
       </c>
       <c r="N935" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O935" t="n">
@@ -81194,7 +81194,7 @@
       </c>
       <c r="N944" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O944" t="n">
@@ -83272,7 +83272,7 @@
       </c>
       <c r="N968" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O968" t="n">
@@ -84746,7 +84746,7 @@
       </c>
       <c r="N985" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O985" t="n">
@@ -85176,7 +85176,7 @@
       </c>
       <c r="N990" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O990" t="n">
@@ -90744,7 +90744,7 @@
       </c>
       <c r="N1054" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1054" t="n">
@@ -91691,7 +91691,7 @@
       </c>
       <c r="N1065" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1065" t="n">
@@ -93600,7 +93600,7 @@
       </c>
       <c r="N1087" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1087" t="n">
@@ -97069,7 +97069,7 @@
       </c>
       <c r="N1127" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1127" t="n">
@@ -99065,7 +99065,7 @@
       </c>
       <c r="N1150" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1150" t="n">
@@ -99321,7 +99321,7 @@
       </c>
       <c r="N1153" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1153" t="n">
@@ -99582,7 +99582,7 @@
       </c>
       <c r="N1156" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1156" t="n">
@@ -99669,7 +99669,7 @@
       </c>
       <c r="N1157" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1157" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -12129,7 +12129,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O136" t="n">
@@ -14632,7 +14632,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O165" t="n">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O182" t="n">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O281" t="n">
@@ -36742,7 +36742,7 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O430" t="n">
@@ -36829,7 +36829,7 @@
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O431" t="n">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="N517" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O517" t="n">
@@ -59741,7 +59741,7 @@
       </c>
       <c r="N697" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O697" t="n">
@@ -78507,7 +78507,7 @@
       </c>
       <c r="N913" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O913" t="n">
@@ -81972,7 +81972,7 @@
       </c>
       <c r="N953" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O953" t="n">
@@ -94731,7 +94731,7 @@
       </c>
       <c r="N1100" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1100" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4743,7 +4743,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O158" t="n">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O159" t="n">
@@ -26988,7 +26988,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O316" t="n">
@@ -27234,7 +27234,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O319" t="n">
@@ -28054,7 +28054,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O329" t="n">
@@ -28300,7 +28300,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O332" t="n">
@@ -28464,7 +28464,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O334" t="n">
@@ -28628,7 +28628,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O336" t="n">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O338" t="n">
@@ -35872,7 +35872,7 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O420" t="n">
@@ -40472,7 +40472,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O473" t="n">
@@ -42349,7 +42349,7 @@
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O495" t="n">
@@ -48320,7 +48320,7 @@
       </c>
       <c r="N564" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O564" t="n">
@@ -53078,7 +53078,7 @@
       </c>
       <c r="N619" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O619" t="n">
@@ -55058,7 +55058,7 @@
       </c>
       <c r="N642" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O642" t="n">
@@ -90570,7 +90570,7 @@
       </c>
       <c r="N1052" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1052" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -793,7 +793,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -880,7 +880,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O54" t="n">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O67" t="n">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O86" t="n">
@@ -24956,7 +24956,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O290" t="n">
@@ -31544,7 +31544,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O370" t="n">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O404" t="n">
@@ -34567,7 +34567,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O405" t="n">
@@ -35698,7 +35698,7 @@
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O418" t="n">
@@ -43970,7 +43970,7 @@
       </c>
       <c r="N514" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O514" t="n">
@@ -45536,7 +45536,7 @@
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O532" t="n">
@@ -45623,7 +45623,7 @@
       </c>
       <c r="N533" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O533" t="n">
@@ -47711,7 +47711,7 @@
       </c>
       <c r="N557" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O557" t="n">
@@ -52469,7 +52469,7 @@
       </c>
       <c r="N612" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O612" t="n">
@@ -53682,7 +53682,7 @@
       </c>
       <c r="N626" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O626" t="n">
@@ -57827,7 +57827,7 @@
       </c>
       <c r="N675" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O675" t="n">
@@ -63395,7 +63395,7 @@
       </c>
       <c r="N739" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O739" t="n">
@@ -68344,7 +68344,7 @@
       </c>
       <c r="N796" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O796" t="n">
@@ -68866,7 +68866,7 @@
       </c>
       <c r="N802" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O802" t="n">
@@ -69040,7 +69040,7 @@
       </c>
       <c r="N804" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O804" t="n">
@@ -73216,7 +73216,7 @@
       </c>
       <c r="N852" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O852" t="n">
@@ -76772,7 +76772,7 @@
       </c>
       <c r="N893" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O893" t="n">
@@ -79116,7 +79116,7 @@
       </c>
       <c r="N920" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O920" t="n">
@@ -79203,7 +79203,7 @@
       </c>
       <c r="N921" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O921" t="n">
@@ -80329,7 +80329,7 @@
       </c>
       <c r="N934" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O934" t="n">
@@ -81368,7 +81368,7 @@
       </c>
       <c r="N946" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O946" t="n">
@@ -84920,7 +84920,7 @@
       </c>
       <c r="N987" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O987" t="n">
@@ -91174,7 +91174,7 @@
       </c>
       <c r="N1059" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1059" t="n">
@@ -93170,7 +93170,7 @@
       </c>
       <c r="N1082" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1082" t="n">
@@ -94992,7 +94992,7 @@
       </c>
       <c r="N1103" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1103" t="n">
@@ -96721,7 +96721,7 @@
       </c>
       <c r="N1123" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1123" t="n">
@@ -97417,7 +97417,7 @@
       </c>
       <c r="N1131" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1131" t="n">
@@ -99843,7 +99843,7 @@
       </c>
       <c r="N1159" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1159" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O138" t="n">
@@ -23928,7 +23928,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O278" t="n">
@@ -29717,7 +29717,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O349" t="n">
@@ -35785,7 +35785,7 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O419" t="n">
@@ -39776,7 +39776,7 @@
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O465" t="n">
@@ -41582,7 +41582,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O486" t="n">
@@ -43361,7 +43361,7 @@
       </c>
       <c r="N507" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O507" t="n">
@@ -45710,7 +45710,7 @@
       </c>
       <c r="N534" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O534" t="n">
@@ -50555,7 +50555,7 @@
       </c>
       <c r="N590" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O590" t="n">
@@ -58958,7 +58958,7 @@
       </c>
       <c r="N688" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O688" t="n">
@@ -62090,7 +62090,7 @@
       </c>
       <c r="N724" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O724" t="n">
@@ -70693,7 +70693,7 @@
       </c>
       <c r="N823" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O823" t="n">
@@ -81020,7 +81020,7 @@
       </c>
       <c r="N942" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O942" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -10840,7 +10840,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O121" t="n">
@@ -17558,7 +17558,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O199" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O200" t="n">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O201" t="n">
@@ -17804,7 +17804,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O202" t="n">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O206" t="n">
@@ -18272,7 +18272,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O208" t="n">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O211" t="n">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O212" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O215" t="n">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O220" t="n">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O221" t="n">
@@ -21233,7 +21233,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O245" t="n">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O253" t="n">
@@ -37003,7 +37003,7 @@
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O433" t="n">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O463" t="n">
@@ -53856,7 +53856,7 @@
       </c>
       <c r="N628" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O628" t="n">
@@ -61481,7 +61481,7 @@
       </c>
       <c r="N717" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O717" t="n">
@@ -62438,7 +62438,7 @@
       </c>
       <c r="N728" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O728" t="n">
@@ -68083,7 +68083,7 @@
       </c>
       <c r="N793" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O793" t="n">
@@ -68779,7 +68779,7 @@
       </c>
       <c r="N801" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O801" t="n">
@@ -85263,7 +85263,7 @@
       </c>
       <c r="N991" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O991" t="n">
@@ -94035,7 +94035,7 @@
       </c>
       <c r="N1092" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1092" t="n">
@@ -96895,7 +96895,7 @@
       </c>
       <c r="N1125" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1125" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -5613,7 +5613,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O60" t="n">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O99" t="n">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O238" t="n">
@@ -29804,7 +29804,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O350" t="n">
@@ -31370,7 +31370,7 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O368" t="n">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O392" t="n">
@@ -41163,7 +41163,7 @@
       </c>
       <c r="N481" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O481" t="n">
@@ -45188,7 +45188,7 @@
       </c>
       <c r="N528" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O528" t="n">
@@ -47972,7 +47972,7 @@
       </c>
       <c r="N560" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O560" t="n">
@@ -57914,7 +57914,7 @@
       </c>
       <c r="N676" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O676" t="n">
@@ -62786,7 +62786,7 @@
       </c>
       <c r="N732" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O732" t="n">
@@ -67126,7 +67126,7 @@
       </c>
       <c r="N782" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O782" t="n">
@@ -71302,7 +71302,7 @@
       </c>
       <c r="N830" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O830" t="n">
@@ -73814,7 +73814,7 @@
       </c>
       <c r="N859" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O859" t="n">
@@ -75641,7 +75641,7 @@
       </c>
       <c r="N880" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O880" t="n">
@@ -93083,7 +93083,7 @@
       </c>
       <c r="N1081" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1081" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1049,7 +1049,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O89" t="n">
@@ -20450,7 +20450,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O236" t="n">
@@ -67039,7 +67039,7 @@
       </c>
       <c r="N781" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O781" t="n">
@@ -73303,7 +73303,7 @@
       </c>
       <c r="N853" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O853" t="n">
@@ -97586,7 +97586,7 @@
       </c>
       <c r="N1133" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1133" t="n">
@@ -98717,7 +98717,7 @@
       </c>
       <c r="N1146" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1146" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1136,7 +1136,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O58" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O93" t="n">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O94" t="n">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O95" t="n">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O96" t="n">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O101" t="n">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O104" t="n">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O107" t="n">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O108" t="n">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O109" t="n">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O113" t="n">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O115" t="n">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O116" t="n">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O117" t="n">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O118" t="n">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O122" t="n">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O128" t="n">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O130" t="n">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O149" t="n">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O151" t="n">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O173" t="n">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O246" t="n">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O247" t="n">
@@ -21581,7 +21581,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O249" t="n">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O250" t="n">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O252" t="n">
@@ -22451,7 +22451,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O259" t="n">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O276" t="n">
@@ -24260,7 +24260,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O282" t="n">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O283" t="n">
@@ -25880,7 +25880,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O301" t="n">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O303" t="n">
@@ -29369,7 +29369,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O345" t="n">
@@ -33088,7 +33088,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O388" t="n">
@@ -33697,7 +33697,7 @@
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O395" t="n">
@@ -36220,7 +36220,7 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O424" t="n">
@@ -40211,7 +40211,7 @@
       </c>
       <c r="N470" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O470" t="n">
@@ -42583,7 +42583,7 @@
       </c>
       <c r="N498" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O498" t="n">
@@ -43187,7 +43187,7 @@
       </c>
       <c r="N505" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O505" t="n">
@@ -48407,7 +48407,7 @@
       </c>
       <c r="N565" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O565" t="n">
@@ -49424,7 +49424,7 @@
       </c>
       <c r="N577" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O577" t="n">
@@ -56348,7 +56348,7 @@
       </c>
       <c r="N658" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O658" t="n">
@@ -62612,7 +62612,7 @@
       </c>
       <c r="N730" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O730" t="n">
@@ -63830,7 +63830,7 @@
       </c>
       <c r="N744" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O744" t="n">
@@ -74597,7 +74597,7 @@
       </c>
       <c r="N868" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O868" t="n">
@@ -78333,7 +78333,7 @@
       </c>
       <c r="N911" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O911" t="n">
@@ -79807,7 +79807,7 @@
       </c>
       <c r="N928" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O928" t="n">
@@ -81629,7 +81629,7 @@
       </c>
       <c r="N949" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O949" t="n">
@@ -87612,7 +87612,7 @@
       </c>
       <c r="N1018" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1018" t="n">
@@ -88308,7 +88308,7 @@
       </c>
       <c r="N1026" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1026" t="n">
@@ -91522,7 +91522,7 @@
       </c>
       <c r="N1063" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1063" t="n">
@@ -94470,7 +94470,7 @@
       </c>
       <c r="N1097" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1097" t="n">
@@ -94557,7 +94557,7 @@
       </c>
       <c r="N1098" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1098" t="n">
@@ -95079,7 +95079,7 @@
       </c>
       <c r="N1104" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1104" t="n">
@@ -99408,7 +99408,7 @@
       </c>
       <c r="N1154" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1154" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4574,7 +4574,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O83" t="n">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O166" t="n">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O251" t="n">
@@ -31968,7 +31968,7 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O375" t="n">
@@ -37090,7 +37090,7 @@
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O434" t="n">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O448" t="n">
@@ -41424,7 +41424,7 @@
       </c>
       <c r="N484" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O484" t="n">
@@ -54884,7 +54884,7 @@
       </c>
       <c r="N640" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O640" t="n">
@@ -65309,7 +65309,7 @@
       </c>
       <c r="N761" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O761" t="n">
@@ -68431,7 +68431,7 @@
       </c>
       <c r="N797" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O797" t="n">
@@ -78855,7 +78855,7 @@
       </c>
       <c r="N917" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O917" t="n">
@@ -81542,7 +81542,7 @@
       </c>
       <c r="N948" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O948" t="n">
@@ -84398,7 +84398,7 @@
       </c>
       <c r="N981" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O981" t="n">
@@ -87351,7 +87351,7 @@
       </c>
       <c r="N1015" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1015" t="n">
@@ -90831,7 +90831,7 @@
       </c>
       <c r="N1055" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1055" t="n">
@@ -95253,7 +95253,7 @@
       </c>
       <c r="N1106" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1106" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1832,7 +1832,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O129" t="n">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O148" t="n">
@@ -32218,7 +32218,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O378" t="n">
@@ -44405,7 +44405,7 @@
       </c>
       <c r="N519" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O519" t="n">
@@ -44753,7 +44753,7 @@
       </c>
       <c r="N523" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O523" t="n">
@@ -49772,7 +49772,7 @@
       </c>
       <c r="N581" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O581" t="n">
@@ -51077,7 +51077,7 @@
       </c>
       <c r="N596" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O596" t="n">
@@ -51860,7 +51860,7 @@
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O605" t="n">
@@ -59480,7 +59480,7 @@
       </c>
       <c r="N694" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O694" t="n">
@@ -86394,7 +86394,7 @@
       </c>
       <c r="N1004" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1004" t="n">
@@ -88395,7 +88395,7 @@
       </c>
       <c r="N1027" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1027" t="n">
@@ -92126,7 +92126,7 @@
       </c>
       <c r="N1070" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1070" t="n">
@@ -96808,7 +96808,7 @@
       </c>
       <c r="N1124" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1124" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -5178,7 +5178,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O55" t="n">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O65" t="n">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O192" t="n">
@@ -31881,7 +31881,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O374" t="n">
@@ -39428,7 +39428,7 @@
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O461" t="n">
@@ -42104,7 +42104,7 @@
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O492" t="n">
@@ -44579,7 +44579,7 @@
       </c>
       <c r="N521" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O521" t="n">
@@ -48233,7 +48233,7 @@
       </c>
       <c r="N563" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O563" t="n">
@@ -50642,7 +50642,7 @@
       </c>
       <c r="N591" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O591" t="n">
@@ -52295,7 +52295,7 @@
       </c>
       <c r="N610" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O610" t="n">
@@ -54552,7 +54552,7 @@
       </c>
       <c r="N636" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O636" t="n">
@@ -54971,7 +54971,7 @@
       </c>
       <c r="N641" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O641" t="n">
@@ -56609,7 +56609,7 @@
       </c>
       <c r="N661" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O661" t="n">
@@ -62699,7 +62699,7 @@
       </c>
       <c r="N731" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O731" t="n">
@@ -62873,7 +62873,7 @@
       </c>
       <c r="N733" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O733" t="n">
@@ -64352,7 +64352,7 @@
       </c>
       <c r="N750" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O750" t="n">
@@ -69127,7 +69127,7 @@
       </c>
       <c r="N805" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O805" t="n">
@@ -74771,7 +74771,7 @@
       </c>
       <c r="N870" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O870" t="n">
@@ -75902,7 +75902,7 @@
       </c>
       <c r="N883" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O883" t="n">
@@ -76685,7 +76685,7 @@
       </c>
       <c r="N892" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O892" t="n">
@@ -87177,7 +87177,7 @@
       </c>
       <c r="N1013" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1013" t="n">
@@ -87264,7 +87264,7 @@
       </c>
       <c r="N1014" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1014" t="n">
@@ -88482,7 +88482,7 @@
       </c>
       <c r="N1028" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1028" t="n">
@@ -88830,7 +88830,7 @@
       </c>
       <c r="N1032" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1032" t="n">
@@ -89787,7 +89787,7 @@
       </c>
       <c r="N1043" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1043" t="n">
@@ -97243,7 +97243,7 @@
       </c>
       <c r="N1129" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1129" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -967,7 +967,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O53" t="n">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O176" t="n">
@@ -21146,7 +21146,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O244" t="n">
@@ -35437,7 +35437,7 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O415" t="n">
@@ -37525,7 +37525,7 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O439" t="n">
@@ -37786,7 +37786,7 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O442" t="n">
@@ -40385,7 +40385,7 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O472" t="n">
@@ -42191,7 +42191,7 @@
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O493" t="n">
@@ -43448,7 +43448,7 @@
       </c>
       <c r="N508" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O508" t="n">
@@ -44666,7 +44666,7 @@
       </c>
       <c r="N522" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O522" t="n">
@@ -45014,7 +45014,7 @@
       </c>
       <c r="N526" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O526" t="n">
@@ -45362,7 +45362,7 @@
       </c>
       <c r="N530" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O530" t="n">
@@ -46145,7 +46145,7 @@
       </c>
       <c r="N539" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O539" t="n">
@@ -46232,7 +46232,7 @@
       </c>
       <c r="N540" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O540" t="n">
@@ -46319,7 +46319,7 @@
       </c>
       <c r="N541" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O541" t="n">
@@ -49946,7 +49946,7 @@
       </c>
       <c r="N583" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O583" t="n">
@@ -53339,7 +53339,7 @@
       </c>
       <c r="N622" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O622" t="n">
@@ -55145,7 +55145,7 @@
       </c>
       <c r="N643" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O643" t="n">
@@ -55406,7 +55406,7 @@
       </c>
       <c r="N646" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O646" t="n">
@@ -56696,7 +56696,7 @@
       </c>
       <c r="N662" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O662" t="n">
@@ -57392,7 +57392,7 @@
       </c>
       <c r="N670" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O670" t="n">
@@ -60524,7 +60524,7 @@
       </c>
       <c r="N706" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O706" t="n">
@@ -64439,7 +64439,7 @@
       </c>
       <c r="N751" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O751" t="n">
@@ -64961,7 +64961,7 @@
       </c>
       <c r="N757" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O757" t="n">
@@ -67213,7 +67213,7 @@
       </c>
       <c r="N783" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O783" t="n">
@@ -69388,7 +69388,7 @@
       </c>
       <c r="N808" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O808" t="n">
@@ -71998,7 +71998,7 @@
       </c>
       <c r="N838" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O838" t="n">
@@ -72346,7 +72346,7 @@
       </c>
       <c r="N842" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O842" t="n">
@@ -72607,7 +72607,7 @@
       </c>
       <c r="N845" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O845" t="n">
@@ -72781,7 +72781,7 @@
       </c>
       <c r="N847" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O847" t="n">
@@ -73129,7 +73129,7 @@
       </c>
       <c r="N851" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O851" t="n">
@@ -74423,7 +74423,7 @@
       </c>
       <c r="N866" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O866" t="n">
@@ -74945,7 +74945,7 @@
       </c>
       <c r="N872" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O872" t="n">
@@ -75119,7 +75119,7 @@
       </c>
       <c r="N874" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O874" t="n">
@@ -76076,7 +76076,7 @@
       </c>
       <c r="N885" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O885" t="n">
@@ -76337,7 +76337,7 @@
       </c>
       <c r="N888" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O888" t="n">
@@ -76598,7 +76598,7 @@
       </c>
       <c r="N891" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O891" t="n">
@@ -77729,7 +77729,7 @@
       </c>
       <c r="N904" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O904" t="n">
@@ -80498,7 +80498,7 @@
       </c>
       <c r="N936" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O936" t="n">
@@ -82755,7 +82755,7 @@
       </c>
       <c r="N962" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O962" t="n">
@@ -83016,7 +83016,7 @@
       </c>
       <c r="N965" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O965" t="n">
@@ -84224,7 +84224,7 @@
       </c>
       <c r="N979" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O979" t="n">
@@ -85094,7 +85094,7 @@
       </c>
       <c r="N989" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O989" t="n">
@@ -86568,7 +86568,7 @@
       </c>
       <c r="N1006" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1006" t="n">
@@ -87003,7 +87003,7 @@
       </c>
       <c r="N1011" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1011" t="n">
@@ -89178,7 +89178,7 @@
       </c>
       <c r="N1036" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1036" t="n">
@@ -89265,7 +89265,7 @@
       </c>
       <c r="N1037" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1037" t="n">
@@ -89439,7 +89439,7 @@
       </c>
       <c r="N1039" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1039" t="n">
@@ -89526,7 +89526,7 @@
       </c>
       <c r="N1040" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1040" t="n">
@@ -91435,7 +91435,7 @@
       </c>
       <c r="N1062" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1062" t="n">
@@ -92300,7 +92300,7 @@
       </c>
       <c r="N1072" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1072" t="n">
@@ -92909,7 +92909,7 @@
       </c>
       <c r="N1079" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1079" t="n">
@@ -98108,7 +98108,7 @@
       </c>
       <c r="N1139" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1139" t="n">
@@ -98978,7 +98978,7 @@
       </c>
       <c r="N1149" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1149" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1223,7 +1223,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O150" t="n">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O178" t="n">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O188" t="n">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O233" t="n">
@@ -20368,7 +20368,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O235" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O242" t="n">
@@ -22625,7 +22625,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O261" t="n">
@@ -23841,7 +23841,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O277" t="n">
@@ -24086,7 +24086,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O280" t="n">
@@ -25043,7 +25043,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O291" t="n">
@@ -25293,7 +25293,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O294" t="n">
@@ -27152,7 +27152,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O318" t="n">
@@ -27316,7 +27316,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O320" t="n">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O321" t="n">
@@ -27562,7 +27562,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O323" t="n">
@@ -27808,7 +27808,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O326" t="n">
@@ -27972,7 +27972,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O328" t="n">
@@ -28218,7 +28218,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O331" t="n">
@@ -28546,7 +28546,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O335" t="n">
@@ -28874,7 +28874,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O339" t="n">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O363" t="n">
@@ -33958,7 +33958,7 @@
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O398" t="n">
@@ -34045,7 +34045,7 @@
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O399" t="n">
@@ -34219,7 +34219,7 @@
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O401" t="n">
@@ -35263,7 +35263,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O413" t="n">
@@ -35350,7 +35350,7 @@
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O414" t="n">
@@ -36916,7 +36916,7 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O432" t="n">
@@ -40298,7 +40298,7 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O471" t="n">
@@ -40902,7 +40902,7 @@
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O478" t="n">
@@ -41076,7 +41076,7 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O480" t="n">
@@ -41337,7 +41337,7 @@
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O483" t="n">
@@ -41930,7 +41930,7 @@
       </c>
       <c r="N490" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O490" t="n">
@@ -44318,7 +44318,7 @@
       </c>
       <c r="N518" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O518" t="n">
@@ -44927,7 +44927,7 @@
       </c>
       <c r="N525" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O525" t="n">
@@ -45971,7 +45971,7 @@
       </c>
       <c r="N537" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O537" t="n">
@@ -46580,7 +46580,7 @@
       </c>
       <c r="N544" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O544" t="n">
@@ -47276,7 +47276,7 @@
       </c>
       <c r="N552" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O552" t="n">
@@ -50468,7 +50468,7 @@
       </c>
       <c r="N589" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O589" t="n">
@@ -50990,7 +50990,7 @@
       </c>
       <c r="N595" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O595" t="n">
@@ -57218,7 +57218,7 @@
       </c>
       <c r="N668" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O668" t="n">
@@ -58001,7 +58001,7 @@
       </c>
       <c r="N677" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O677" t="n">
@@ -58349,7 +58349,7 @@
       </c>
       <c r="N681" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O681" t="n">
@@ -58871,7 +58871,7 @@
       </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O687" t="n">
@@ -60350,7 +60350,7 @@
       </c>
       <c r="N704" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O704" t="n">
@@ -60698,7 +60698,7 @@
       </c>
       <c r="N708" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O708" t="n">
@@ -65918,7 +65918,7 @@
       </c>
       <c r="N768" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O768" t="n">
@@ -70432,7 +70432,7 @@
       </c>
       <c r="N820" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O820" t="n">
@@ -71215,7 +71215,7 @@
       </c>
       <c r="N829" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O829" t="n">
@@ -74684,7 +74684,7 @@
       </c>
       <c r="N869" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O869" t="n">
@@ -75206,7 +75206,7 @@
       </c>
       <c r="N875" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O875" t="n">
@@ -80585,7 +80585,7 @@
       </c>
       <c r="N937" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O937" t="n">
@@ -80672,7 +80672,7 @@
       </c>
       <c r="N938" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O938" t="n">
@@ -82929,7 +82929,7 @@
       </c>
       <c r="N964" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O964" t="n">
@@ -83441,7 +83441,7 @@
       </c>
       <c r="N970" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O970" t="n">
@@ -84050,7 +84050,7 @@
       </c>
       <c r="N977" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O977" t="n">
@@ -90222,7 +90222,7 @@
       </c>
       <c r="N1048" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1048" t="n">
@@ -98282,7 +98282,7 @@
       </c>
       <c r="N1141" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1141" t="n">
@@ -99756,7 +99756,7 @@
       </c>
       <c r="N1158" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1158" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -5869,7 +5869,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O63" t="n">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O153" t="n">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O169" t="n">
@@ -53595,7 +53595,7 @@
       </c>
       <c r="N625" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O625" t="n">
@@ -66952,7 +66952,7 @@
       </c>
       <c r="N780" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O780" t="n">
@@ -91087,7 +91087,7 @@
       </c>
       <c r="N1058" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1058" t="n">
@@ -91604,7 +91604,7 @@
       </c>
       <c r="N1064" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1064" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -5787,7 +5787,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O62" t="n">
@@ -36307,7 +36307,7 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O425" t="n">
@@ -48581,7 +48581,7 @@
       </c>
       <c r="N567" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O567" t="n">
@@ -50903,7 +50903,7 @@
       </c>
       <c r="N594" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O594" t="n">
@@ -53252,7 +53252,7 @@
       </c>
       <c r="N621" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O621" t="n">
@@ -72433,7 +72433,7 @@
       </c>
       <c r="N843" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O843" t="n">
@@ -94122,7 +94122,7 @@
       </c>
       <c r="N1093" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1093" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -7658,7 +7658,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O84" t="n">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O105" t="n">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O123" t="n">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O133" t="n">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O174" t="n">
@@ -31707,7 +31707,7 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O372" t="n">
@@ -34654,7 +34654,7 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O406" t="n">
@@ -35959,7 +35959,7 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O421" t="n">
@@ -39950,7 +39950,7 @@
       </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O467" t="n">
@@ -43018,7 +43018,7 @@
       </c>
       <c r="N503" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O503" t="n">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="N510" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O510" t="n">
@@ -46667,7 +46667,7 @@
       </c>
       <c r="N545" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O545" t="n">
@@ -47885,7 +47885,7 @@
       </c>
       <c r="N559" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O559" t="n">
@@ -48744,7 +48744,7 @@
       </c>
       <c r="N569" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O569" t="n">
@@ -53513,7 +53513,7 @@
       </c>
       <c r="N624" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O624" t="n">
@@ -54291,7 +54291,7 @@
       </c>
       <c r="N633" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O633" t="n">
@@ -55667,7 +55667,7 @@
       </c>
       <c r="N649" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O649" t="n">
@@ -57131,7 +57131,7 @@
       </c>
       <c r="N667" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O667" t="n">
@@ -59045,7 +59045,7 @@
       </c>
       <c r="N689" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O689" t="n">
@@ -59654,7 +59654,7 @@
       </c>
       <c r="N696" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O696" t="n">
@@ -59915,7 +59915,7 @@
       </c>
       <c r="N699" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O699" t="n">
@@ -60176,7 +60176,7 @@
       </c>
       <c r="N702" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O702" t="n">
@@ -62264,7 +62264,7 @@
       </c>
       <c r="N726" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O726" t="n">
@@ -63308,7 +63308,7 @@
       </c>
       <c r="N738" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O738" t="n">
@@ -64613,7 +64613,7 @@
       </c>
       <c r="N753" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O753" t="n">
@@ -65396,7 +65396,7 @@
       </c>
       <c r="N762" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O762" t="n">
@@ -65657,7 +65657,7 @@
       </c>
       <c r="N765" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O765" t="n">
@@ -68518,7 +68518,7 @@
       </c>
       <c r="N798" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O798" t="n">
@@ -70084,7 +70084,7 @@
       </c>
       <c r="N816" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O816" t="n">
@@ -70606,7 +70606,7 @@
       </c>
       <c r="N822" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O822" t="n">
@@ -71041,7 +71041,7 @@
       </c>
       <c r="N827" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O827" t="n">
@@ -77120,7 +77120,7 @@
       </c>
       <c r="N897" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O897" t="n">
@@ -78077,7 +78077,7 @@
       </c>
       <c r="N908" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O908" t="n">
@@ -79459,7 +79459,7 @@
       </c>
       <c r="N924" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O924" t="n">
@@ -79894,7 +79894,7 @@
       </c>
       <c r="N929" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O929" t="n">
@@ -82581,7 +82581,7 @@
       </c>
       <c r="N960" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O960" t="n">
@@ -83702,7 +83702,7 @@
       </c>
       <c r="N973" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O973" t="n">
@@ -86133,7 +86133,7 @@
       </c>
       <c r="N1001" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1001" t="n">
@@ -87090,7 +87090,7 @@
       </c>
       <c r="N1012" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1012" t="n">
@@ -89613,7 +89613,7 @@
       </c>
       <c r="N1041" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1041" t="n">
@@ -93774,7 +93774,7 @@
       </c>
       <c r="N1089" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1089" t="n">
@@ -97760,7 +97760,7 @@
       </c>
       <c r="N1135" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1135" t="n">
@@ -100093,7 +100093,7 @@
       </c>
       <c r="N1162" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1162" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1745,7 +1745,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O69" t="n">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O119" t="n">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O126" t="n">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O132" t="n">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O141" t="n">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O145" t="n">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O181" t="n">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O185" t="n">
@@ -17313,7 +17313,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O196" t="n">
@@ -20798,7 +20798,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O240" t="n">
@@ -21059,7 +21059,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O243" t="n">
@@ -24434,7 +24434,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O284" t="n">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O295" t="n">
@@ -25793,7 +25793,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O300" t="n">
@@ -29195,7 +29195,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O343" t="n">
@@ -29456,7 +29456,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O346" t="n">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O360" t="n">
@@ -32827,7 +32827,7 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O385" t="n">
@@ -33262,7 +33262,7 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O390" t="n">
@@ -34132,7 +34132,7 @@
       </c>
       <c r="N400" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O400" t="n">
@@ -34306,7 +34306,7 @@
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O402" t="n">
@@ -34393,7 +34393,7 @@
       </c>
       <c r="N403" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O403" t="n">
@@ -34828,7 +34828,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O408" t="n">
@@ -34915,7 +34915,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O409" t="n">
@@ -36394,7 +36394,7 @@
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O426" t="n">
@@ -37612,7 +37612,7 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O440" t="n">
@@ -39689,7 +39689,7 @@
       </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O464" t="n">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O479" t="n">
@@ -42670,7 +42670,7 @@
       </c>
       <c r="N499" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O499" t="n">
@@ -44492,7 +44492,7 @@
       </c>
       <c r="N520" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O520" t="n">
@@ -45101,7 +45101,7 @@
       </c>
       <c r="N527" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O527" t="n">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="N543" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O543" t="n">
@@ -46841,7 +46841,7 @@
       </c>
       <c r="N547" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O547" t="n">
@@ -47798,7 +47798,7 @@
       </c>
       <c r="N558" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O558" t="n">
@@ -48146,7 +48146,7 @@
       </c>
       <c r="N562" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O562" t="n">
@@ -50120,7 +50120,7 @@
       </c>
       <c r="N585" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O585" t="n">
@@ -51686,7 +51686,7 @@
       </c>
       <c r="N603" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O603" t="n">
@@ -52034,7 +52034,7 @@
       </c>
       <c r="N607" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O607" t="n">
@@ -53943,7 +53943,7 @@
       </c>
       <c r="N629" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O629" t="n">
@@ -55232,7 +55232,7 @@
       </c>
       <c r="N644" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O644" t="n">
@@ -58262,7 +58262,7 @@
       </c>
       <c r="N680" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O680" t="n">
@@ -59393,7 +59393,7 @@
       </c>
       <c r="N693" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O693" t="n">
@@ -60089,7 +60089,7 @@
       </c>
       <c r="N701" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O701" t="n">
@@ -60872,7 +60872,7 @@
       </c>
       <c r="N710" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O710" t="n">
@@ -61046,7 +61046,7 @@
       </c>
       <c r="N712" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O712" t="n">
@@ -63134,7 +63134,7 @@
       </c>
       <c r="N736" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O736" t="n">
@@ -64874,7 +64874,7 @@
       </c>
       <c r="N756" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O756" t="n">
@@ -65570,7 +65570,7 @@
       </c>
       <c r="N764" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O764" t="n">
@@ -65744,7 +65744,7 @@
       </c>
       <c r="N766" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O766" t="n">
@@ -65831,7 +65831,7 @@
       </c>
       <c r="N767" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O767" t="n">
@@ -67735,7 +67735,7 @@
       </c>
       <c r="N789" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O789" t="n">
@@ -69736,7 +69736,7 @@
       </c>
       <c r="N812" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O812" t="n">
@@ -69997,7 +69997,7 @@
       </c>
       <c r="N815" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O815" t="n">
@@ -70171,7 +70171,7 @@
       </c>
       <c r="N817" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O817" t="n">
@@ -70780,7 +70780,7 @@
       </c>
       <c r="N824" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O824" t="n">
@@ -71737,7 +71737,7 @@
       </c>
       <c r="N835" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O835" t="n">
@@ -71824,7 +71824,7 @@
       </c>
       <c r="N836" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O836" t="n">
@@ -72172,7 +72172,7 @@
       </c>
       <c r="N840" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O840" t="n">
@@ -72520,7 +72520,7 @@
       </c>
       <c r="N844" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O844" t="n">
@@ -72694,7 +72694,7 @@
       </c>
       <c r="N846" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O846" t="n">
@@ -73042,7 +73042,7 @@
       </c>
       <c r="N850" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O850" t="n">
@@ -73466,7 +73466,7 @@
       </c>
       <c r="N855" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O855" t="n">
@@ -74249,7 +74249,7 @@
       </c>
       <c r="N864" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O864" t="n">
@@ -74336,7 +74336,7 @@
       </c>
       <c r="N865" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O865" t="n">
@@ -76424,7 +76424,7 @@
       </c>
       <c r="N889" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O889" t="n">
@@ -76946,7 +76946,7 @@
       </c>
       <c r="N895" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O895" t="n">
@@ -77642,7 +77642,7 @@
       </c>
       <c r="N903" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O903" t="n">
@@ -77903,7 +77903,7 @@
       </c>
       <c r="N906" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O906" t="n">
@@ -77990,7 +77990,7 @@
       </c>
       <c r="N907" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O907" t="n">
@@ -80846,7 +80846,7 @@
       </c>
       <c r="N940" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O940" t="n">
@@ -82233,7 +82233,7 @@
       </c>
       <c r="N956" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O956" t="n">
@@ -82668,7 +82668,7 @@
       </c>
       <c r="N961" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O961" t="n">
@@ -83190,7 +83190,7 @@
       </c>
       <c r="N967" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O967" t="n">
@@ -86481,7 +86481,7 @@
       </c>
       <c r="N1005" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1005" t="n">
@@ -86916,7 +86916,7 @@
       </c>
       <c r="N1010" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1010" t="n">
@@ -87525,7 +87525,7 @@
       </c>
       <c r="N1017" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1017" t="n">
@@ -87699,7 +87699,7 @@
       </c>
       <c r="N1019" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1019" t="n">
@@ -89091,7 +89091,7 @@
       </c>
       <c r="N1035" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1035" t="n">
@@ -89352,7 +89352,7 @@
       </c>
       <c r="N1038" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1038" t="n">
@@ -89874,7 +89874,7 @@
       </c>
       <c r="N1044" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1044" t="n">
@@ -90309,7 +90309,7 @@
       </c>
       <c r="N1049" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1049" t="n">
@@ -91005,7 +91005,7 @@
       </c>
       <c r="N1057" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1057" t="n">
@@ -91261,7 +91261,7 @@
       </c>
       <c r="N1060" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1060" t="n">
@@ -91348,7 +91348,7 @@
       </c>
       <c r="N1061" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1061" t="n">
@@ -93257,7 +93257,7 @@
       </c>
       <c r="N1083" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1083" t="n">
@@ -93948,7 +93948,7 @@
       </c>
       <c r="N1091" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1091" t="n">
@@ -94383,7 +94383,7 @@
       </c>
       <c r="N1096" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1096" t="n">
@@ -95427,7 +95427,7 @@
       </c>
       <c r="N1108" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1108" t="n">
@@ -95514,7 +95514,7 @@
       </c>
       <c r="N1109" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1109" t="n">
@@ -95601,7 +95601,7 @@
       </c>
       <c r="N1110" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1110" t="n">
@@ -97673,7 +97673,7 @@
       </c>
       <c r="N1134" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1134" t="n">
@@ -98456,7 +98456,7 @@
       </c>
       <c r="N1143" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1143" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3899,7 +3899,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O49" t="n">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O73" t="n">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O76" t="n">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O88" t="n">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O140" t="n">
@@ -15236,7 +15236,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O172" t="n">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O180" t="n">
@@ -16193,7 +16193,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O183" t="n">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O197" t="n">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O273" t="n">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O344" t="n">
@@ -29630,7 +29630,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O348" t="n">
@@ -30413,7 +30413,7 @@
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O357" t="n">
@@ -32479,7 +32479,7 @@
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O381" t="n">
@@ -33175,7 +33175,7 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O389" t="n">
@@ -35089,7 +35089,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O411" t="n">
@@ -37177,7 +37177,7 @@
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O435" t="n">
@@ -37264,7 +37264,7 @@
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O436" t="n">
@@ -38993,7 +38993,7 @@
       </c>
       <c r="N456" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O456" t="n">
@@ -41250,7 +41250,7 @@
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O482" t="n">
@@ -43274,7 +43274,7 @@
       </c>
       <c r="N506" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O506" t="n">
@@ -48059,7 +48059,7 @@
       </c>
       <c r="N561" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O561" t="n">
@@ -51773,7 +51773,7 @@
       </c>
       <c r="N604" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O604" t="n">
@@ -52121,7 +52121,7 @@
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O608" t="n">
@@ -53769,7 +53769,7 @@
       </c>
       <c r="N627" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O627" t="n">
@@ -54030,7 +54030,7 @@
       </c>
       <c r="N630" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O630" t="n">
@@ -55493,7 +55493,7 @@
       </c>
       <c r="N647" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O647" t="n">
@@ -55580,7 +55580,7 @@
       </c>
       <c r="N648" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O648" t="n">
@@ -56783,7 +56783,7 @@
       </c>
       <c r="N663" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O663" t="n">
@@ -56957,7 +56957,7 @@
       </c>
       <c r="N665" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O665" t="n">
@@ -58175,7 +58175,7 @@
       </c>
       <c r="N679" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O679" t="n">
@@ -58610,7 +58610,7 @@
       </c>
       <c r="N684" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O684" t="n">
@@ -58784,7 +58784,7 @@
       </c>
       <c r="N686" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O686" t="n">
@@ -62003,7 +62003,7 @@
       </c>
       <c r="N723" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O723" t="n">
@@ -64178,7 +64178,7 @@
       </c>
       <c r="N748" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O748" t="n">
@@ -65048,7 +65048,7 @@
       </c>
       <c r="N758" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O758" t="n">
@@ -66440,7 +66440,7 @@
       </c>
       <c r="N774" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O774" t="n">
@@ -66527,7 +66527,7 @@
       </c>
       <c r="N775" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O775" t="n">
@@ -68170,7 +68170,7 @@
       </c>
       <c r="N794" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O794" t="n">
@@ -68692,7 +68692,7 @@
       </c>
       <c r="N800" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O800" t="n">
@@ -69823,7 +69823,7 @@
       </c>
       <c r="N813" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O813" t="n">
@@ -75293,7 +75293,7 @@
       </c>
       <c r="N876" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O876" t="n">
@@ -75815,7 +75815,7 @@
       </c>
       <c r="N882" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O882" t="n">
@@ -77207,7 +77207,7 @@
       </c>
       <c r="N898" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O898" t="n">
@@ -79981,7 +79981,7 @@
       </c>
       <c r="N930" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O930" t="n">
@@ -80068,7 +80068,7 @@
       </c>
       <c r="N931" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O931" t="n">
@@ -82842,7 +82842,7 @@
       </c>
       <c r="N963" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O963" t="n">
@@ -84137,7 +84137,7 @@
       </c>
       <c r="N978" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O978" t="n">
@@ -84311,7 +84311,7 @@
       </c>
       <c r="N980" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O980" t="n">
@@ -84485,7 +84485,7 @@
       </c>
       <c r="N982" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O982" t="n">
@@ -86655,7 +86655,7 @@
       </c>
       <c r="N1007" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1007" t="n">
@@ -87960,7 +87960,7 @@
       </c>
       <c r="N1022" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1022" t="n">
@@ -88656,7 +88656,7 @@
       </c>
       <c r="N1030" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1030" t="n">
@@ -90657,7 +90657,7 @@
       </c>
       <c r="N1053" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1053" t="n">
@@ -91778,7 +91778,7 @@
       </c>
       <c r="N1066" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1066" t="n">
@@ -92561,7 +92561,7 @@
       </c>
       <c r="N1075" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1075" t="n">
@@ -92648,7 +92648,7 @@
       </c>
       <c r="N1076" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1076" t="n">
@@ -93426,7 +93426,7 @@
       </c>
       <c r="N1085" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1085" t="n">
@@ -96634,7 +96634,7 @@
       </c>
       <c r="N1122" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1122" t="n">
@@ -99152,7 +99152,7 @@
       </c>
       <c r="N1151" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1151" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O77" t="n">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -32055,7 +32055,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O376" t="n">
@@ -35611,7 +35611,7 @@
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O417" t="n">
@@ -38743,7 +38743,7 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O453" t="n">
@@ -46928,7 +46928,7 @@
       </c>
       <c r="N548" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O548" t="n">
@@ -50729,7 +50729,7 @@
       </c>
       <c r="N592" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O592" t="n">
@@ -51251,7 +51251,7 @@
       </c>
       <c r="N598" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O598" t="n">
@@ -54639,7 +54639,7 @@
       </c>
       <c r="N637" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O637" t="n">
@@ -57305,7 +57305,7 @@
       </c>
       <c r="N669" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O669" t="n">
@@ -71476,7 +71476,7 @@
       </c>
       <c r="N832" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O832" t="n">
@@ -78681,7 +78681,7 @@
       </c>
       <c r="N915" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O915" t="n">
@@ -88569,7 +88569,7 @@
       </c>
       <c r="N1029" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1029" t="n">
@@ -94296,7 +94296,7 @@
       </c>
       <c r="N1095" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1095" t="n">
@@ -96297,7 +96297,7 @@
       </c>
       <c r="N1118" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1118" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -10231,7 +10231,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O114" t="n">
@@ -24521,7 +24521,7 @@
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O285" t="n">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O286" t="n">
@@ -24782,7 +24782,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O288" t="n">
@@ -29543,7 +29543,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O347" t="n">
@@ -30587,7 +30587,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O359" t="n">
@@ -42931,7 +42931,7 @@
       </c>
       <c r="N502" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O502" t="n">
@@ -52730,7 +52730,7 @@
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O615" t="n">
@@ -56261,7 +56261,7 @@
       </c>
       <c r="N657" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>SIN INFORMACION</t>
         </is>
       </c>
       <c r="O657" t="n">
@@ -58697,7 +58697,7 @@
       </c>
       <c r="N685" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O685" t="n">
@@ -61568,7 +61568,7 @@
       </c>
       <c r="N718" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O718" t="n">
@@ -61916,7 +61916,7 @@
       </c>
       <c r="N722" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O722" t="n">
@@ -65135,7 +65135,7 @@
       </c>
       <c r="N759" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O759" t="n">
@@ -65222,7 +65222,7 @@
       </c>
       <c r="N760" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O760" t="n">
@@ -66696,7 +66696,7 @@
       </c>
       <c r="N777" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O777" t="n">
@@ -75554,7 +75554,7 @@
       </c>
       <c r="N879" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O879" t="n">
@@ -80933,7 +80933,7 @@
       </c>
       <c r="N941" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O941" t="n">
@@ -86307,7 +86307,7 @@
       </c>
       <c r="N1003" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1003" t="n">
@@ -92474,7 +92474,7 @@
       </c>
       <c r="N1074" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1074" t="n">
@@ -93861,7 +93861,7 @@
       </c>
       <c r="N1090" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1090" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -4231,7 +4231,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O52" t="n">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -13685,7 +13685,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O154" t="n">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O189" t="n">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O237" t="n">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O293" t="n">
@@ -32653,7 +32653,7 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O383" t="n">
@@ -42017,7 +42017,7 @@
       </c>
       <c r="N491" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O491" t="n">
@@ -42757,7 +42757,7 @@
       </c>
       <c r="N500" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O500" t="n">
@@ -47102,7 +47102,7 @@
       </c>
       <c r="N550" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O550" t="n">
@@ -54465,7 +54465,7 @@
       </c>
       <c r="N635" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O635" t="n">
@@ -62525,7 +62525,7 @@
       </c>
       <c r="N729" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O729" t="n">
@@ -70345,7 +70345,7 @@
       </c>
       <c r="N819" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O819" t="n">
@@ -71650,7 +71650,7 @@
       </c>
       <c r="N834" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O834" t="n">
@@ -73553,7 +73553,7 @@
       </c>
       <c r="N856" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O856" t="n">
@@ -77555,7 +77555,7 @@
       </c>
       <c r="N902" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O902" t="n">
@@ -79029,7 +79029,7 @@
       </c>
       <c r="N919" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O919" t="n">
@@ -84659,7 +84659,7 @@
       </c>
       <c r="N984" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O984" t="n">
@@ -86742,7 +86742,7 @@
       </c>
       <c r="N1008" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1008" t="n">
@@ -87438,7 +87438,7 @@
       </c>
       <c r="N1016" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1016" t="n">
@@ -91952,7 +91952,7 @@
       </c>
       <c r="N1068" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1068" t="n">
@@ -95949,7 +95949,7 @@
       </c>
       <c r="N1114" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1114" t="n">
@@ -96036,7 +96036,7 @@
       </c>
       <c r="N1115" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1115" t="n">
@@ -96547,7 +96547,7 @@
       </c>
       <c r="N1121" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1121" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -1571,7 +1571,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O91" t="n">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O144" t="n">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O160" t="n">
@@ -29891,7 +29891,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O351" t="n">
@@ -38830,7 +38830,7 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O454" t="n">
@@ -41756,7 +41756,7 @@
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O488" t="n">
@@ -45884,7 +45884,7 @@
       </c>
       <c r="N536" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O536" t="n">
@@ -52208,7 +52208,7 @@
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O609" t="n">
@@ -52991,7 +52991,7 @@
       </c>
       <c r="N618" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O618" t="n">
@@ -61655,7 +61655,7 @@
       </c>
       <c r="N719" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O719" t="n">
@@ -67387,7 +67387,7 @@
       </c>
       <c r="N785" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O785" t="n">
@@ -67909,7 +67909,7 @@
       </c>
       <c r="N791" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O791" t="n">
@@ -67996,7 +67996,7 @@
       </c>
       <c r="N792" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O792" t="n">
@@ -74162,7 +74162,7 @@
       </c>
       <c r="N863" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O863" t="n">
@@ -77381,7 +77381,7 @@
       </c>
       <c r="N900" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O900" t="n">
@@ -86046,7 +86046,7 @@
       </c>
       <c r="N1000" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1000" t="n">
@@ -86829,7 +86829,7 @@
       </c>
       <c r="N1009" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1009" t="n">
@@ -96123,7 +96123,7 @@
       </c>
       <c r="N1116" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1116" t="n">
@@ -96384,7 +96384,7 @@
       </c>
       <c r="N1119" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1119" t="n">
@@ -97847,7 +97847,7 @@
       </c>
       <c r="N1136" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1136" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -32914,7 +32914,7 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O386" t="n">
@@ -63482,7 +63482,7 @@
       </c>
       <c r="N740" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O740" t="n">
@@ -70519,7 +70519,7 @@
       </c>
       <c r="N821" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O821" t="n">
@@ -72259,7 +72259,7 @@
       </c>
       <c r="N841" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O841" t="n">
@@ -76511,7 +76511,7 @@
       </c>
       <c r="N890" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O890" t="n">
@@ -79720,7 +79720,7 @@
       </c>
       <c r="N927" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O927" t="n">
@@ -82407,7 +82407,7 @@
       </c>
       <c r="N958" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O958" t="n">
@@ -84572,7 +84572,7 @@
       </c>
       <c r="N983" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O983" t="n">
@@ -85785,7 +85785,7 @@
       </c>
       <c r="N997" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O997" t="n">
@@ -87873,7 +87873,7 @@
       </c>
       <c r="N1021" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1021" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3812,7 +3812,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O373" t="n">
@@ -39254,7 +39254,7 @@
       </c>
       <c r="N459" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O459" t="n">
@@ -40728,7 +40728,7 @@
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O476" t="n">
@@ -47015,7 +47015,7 @@
       </c>
       <c r="N549" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O549" t="n">
@@ -47624,7 +47624,7 @@
       </c>
       <c r="N556" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O556" t="n">
@@ -60611,7 +60611,7 @@
       </c>
       <c r="N707" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O707" t="n">
@@ -66783,7 +66783,7 @@
       </c>
       <c r="N778" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O778" t="n">
@@ -70867,7 +70867,7 @@
       </c>
       <c r="N825" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O825" t="n">
@@ -86220,7 +86220,7 @@
       </c>
       <c r="N1002" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1002" t="n">
@@ -96982,7 +96982,7 @@
       </c>
       <c r="N1126" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1126" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -8180,7 +8180,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O90" t="n">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O106" t="n">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O143" t="n">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O164" t="n">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O170" t="n">
@@ -36568,7 +36568,7 @@
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O428" t="n">
@@ -43535,7 +43535,7 @@
       </c>
       <c r="N509" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O509" t="n">
@@ -44057,7 +44057,7 @@
       </c>
       <c r="N515" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O515" t="n">
@@ -48918,7 +48918,7 @@
       </c>
       <c r="N571" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O571" t="n">
@@ -75467,7 +75467,7 @@
       </c>
       <c r="N878" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O878" t="n">
@@ -88743,7 +88743,7 @@
       </c>
       <c r="N1031" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1031" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -2523,7 +2523,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O92" t="n">
@@ -66609,7 +66609,7 @@
       </c>
       <c r="N776" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O776" t="n">
@@ -78246,7 +78246,7 @@
       </c>
       <c r="N910" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O910" t="n">
@@ -81798,7 +81798,7 @@
       </c>
       <c r="N951" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O951" t="n">
@@ -83354,7 +83354,7 @@
       </c>
       <c r="N969" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O969" t="n">
@@ -93339,7 +93339,7 @@
       </c>
       <c r="N1084" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1084" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -39080,7 +39080,7 @@
       </c>
       <c r="N457" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O457" t="n">
@@ -57740,7 +57740,7 @@
       </c>
       <c r="N674" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O674" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -46754,7 +46754,7 @@
       </c>
       <c r="N546" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O546" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -96210,7 +96210,7 @@
       </c>
       <c r="N1117" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1117" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -2441,7 +2441,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O139" t="n">
@@ -52904,7 +52904,7 @@
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O617" t="n">
@@ -76163,7 +76163,7 @@
       </c>
       <c r="N886" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O886" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -33610,7 +33610,7 @@
       </c>
       <c r="N394" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O394" t="n">
@@ -49337,7 +49337,7 @@
       </c>
       <c r="N576" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O576" t="n">
@@ -50816,7 +50816,7 @@
       </c>
       <c r="N593" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O593" t="n">
@@ -60002,7 +60002,7 @@
       </c>
       <c r="N700" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O700" t="n">
@@ -60263,7 +60263,7 @@
       </c>
       <c r="N703" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O703" t="n">
@@ -66005,7 +66005,7 @@
       </c>
       <c r="N769" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O769" t="n">
@@ -70954,7 +70954,7 @@
       </c>
       <c r="N826" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O826" t="n">
@@ -83789,7 +83789,7 @@
       </c>
       <c r="N974" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O974" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -6891,7 +6891,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O75" t="n">
@@ -49076,7 +49076,7 @@
       </c>
       <c r="N573" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O573" t="n">
@@ -74075,7 +74075,7 @@
       </c>
       <c r="N862" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O862" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -6304,7 +6304,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O87" t="n">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O124" t="n">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O171" t="n">
@@ -24695,7 +24695,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O287" t="n">
@@ -30152,7 +30152,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O354" t="n">
@@ -32305,7 +32305,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O379" t="n">
@@ -32392,7 +32392,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O380" t="n">
@@ -32566,7 +32566,7 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O382" t="n">
@@ -38134,7 +38134,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O446" t="n">
@@ -38482,7 +38482,7 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O450" t="n">
@@ -40037,7 +40037,7 @@
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O468" t="n">
@@ -47189,7 +47189,7 @@
       </c>
       <c r="N551" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O551" t="n">
@@ -50033,7 +50033,7 @@
       </c>
       <c r="N584" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O584" t="n">
@@ -58088,7 +58088,7 @@
       </c>
       <c r="N678" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O678" t="n">
@@ -59828,7 +59828,7 @@
       </c>
       <c r="N698" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O698" t="n">
@@ -64091,7 +64091,7 @@
       </c>
       <c r="N747" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O747" t="n">
@@ -73988,7 +73988,7 @@
       </c>
       <c r="N861" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O861" t="n">
@@ -75728,7 +75728,7 @@
       </c>
       <c r="N881" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O881" t="n">
@@ -92996,7 +92996,7 @@
       </c>
       <c r="N1080" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1080" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -2958,7 +2958,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O186" t="n">
@@ -23580,7 +23580,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O274" t="n">
@@ -23667,7 +23667,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O275" t="n">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O358" t="n">
@@ -50381,7 +50381,7 @@
       </c>
       <c r="N588" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O588" t="n">
@@ -61742,7 +61742,7 @@
       </c>
       <c r="N720" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O720" t="n">
@@ -64265,7 +64265,7 @@
       </c>
       <c r="N749" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O749" t="n">
@@ -69214,7 +69214,7 @@
       </c>
       <c r="N806" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O806" t="n">
@@ -74510,7 +74510,7 @@
       </c>
       <c r="N867" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O867" t="n">
@@ -79546,7 +79546,7 @@
       </c>
       <c r="N925" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O925" t="n">
@@ -83615,7 +83615,7 @@
       </c>
       <c r="N972" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O972" t="n">
@@ -92822,7 +92822,7 @@
       </c>
       <c r="N1078" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1078" t="n">
@@ -94905,7 +94905,7 @@
       </c>
       <c r="N1102" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1102" t="n">
@@ -99495,7 +99495,7 @@
       </c>
       <c r="N1155" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1155" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -82320,7 +82320,7 @@
       </c>
       <c r="N957" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O957" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -12646,7 +12646,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O142" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O195" t="n">
@@ -56522,7 +56522,7 @@
       </c>
       <c r="N660" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O660" t="n">
@@ -61133,7 +61133,7 @@
       </c>
       <c r="N713" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O713" t="n">
@@ -67648,7 +67648,7 @@
       </c>
       <c r="N788" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O788" t="n">
@@ -67822,7 +67822,7 @@
       </c>
       <c r="N790" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O790" t="n">
@@ -82494,7 +82494,7 @@
       </c>
       <c r="N959" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O959" t="n">
@@ -85959,7 +85959,7 @@
       </c>
       <c r="N999" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O999" t="n">
@@ -90483,7 +90483,7 @@
       </c>
       <c r="N1051" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1051" t="n">
@@ -90918,7 +90918,7 @@
       </c>
       <c r="N1056" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1056" t="n">
@@ -92213,7 +92213,7 @@
       </c>
       <c r="N1071" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1071" t="n">
@@ -95775,7 +95775,7 @@
       </c>
       <c r="N1112" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1112" t="n">
@@ -99930,7 +99930,7 @@
       </c>
       <c r="N1160" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O1160" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -66870,7 +66870,7 @@
       </c>
       <c r="N779" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O779" t="n">
@@ -85872,7 +85872,7 @@
       </c>
       <c r="N998" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>RECHAZADO</t>
         </is>
       </c>
       <c r="O998" t="n">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -875,7 +875,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -18135,7 +18135,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -18309,7 +18309,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -22959,7 +22959,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -30991,7 +30991,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -31078,7 +31078,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -31513,7 +31513,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -31948,7 +31948,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -32296,7 +32296,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -32383,7 +32383,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -32894,7 +32894,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -32981,7 +32981,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -34531,7 +34531,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -35787,7 +35787,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -36222,7 +36222,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -37929,7 +37929,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -38712,7 +38712,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -41801,7 +41801,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -42671,7 +42671,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
@@ -43367,7 +43367,7 @@
       </c>
       <c r="M509" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N509" t="inlineStr">
@@ -44237,7 +44237,7 @@
       </c>
       <c r="M519" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N519" t="inlineStr">
@@ -44574,7 +44574,7 @@
       </c>
       <c r="M523" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N523" t="inlineStr">
@@ -44911,7 +44911,7 @@
       </c>
       <c r="M527" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N527" t="inlineStr">
@@ -46287,7 +46287,7 @@
       </c>
       <c r="M543" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N543" t="inlineStr">
@@ -46548,12 +46548,12 @@
       </c>
       <c r="M546" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N546" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
+          <t>ENTREGADO</t>
         </is>
       </c>
       <c r="O546" t="n">
@@ -46896,7 +46896,7 @@
       </c>
       <c r="M550" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N550" t="inlineStr">
@@ -47315,7 +47315,7 @@
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N555" t="inlineStr">
@@ -50066,7 +50066,7 @@
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N587" t="inlineStr">
@@ -51197,7 +51197,7 @@
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N600" t="inlineStr">
@@ -52480,7 +52480,7 @@
       </c>
       <c r="M615" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N615" t="inlineStr">
@@ -55846,7 +55846,7 @@
       </c>
       <c r="M657" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N657" t="inlineStr">
@@ -56281,7 +56281,7 @@
       </c>
       <c r="M662" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N662" t="inlineStr">
@@ -56890,7 +56890,7 @@
       </c>
       <c r="M669" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N669" t="inlineStr">
@@ -56977,7 +56977,7 @@
       </c>
       <c r="M670" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N670" t="inlineStr">
@@ -57151,7 +57151,7 @@
       </c>
       <c r="M672" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N672" t="inlineStr">
@@ -57412,7 +57412,7 @@
       </c>
       <c r="M675" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N675" t="inlineStr">
@@ -57934,7 +57934,7 @@
       </c>
       <c r="M681" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N681" t="inlineStr">
@@ -59554,7 +59554,7 @@
       </c>
       <c r="M700" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N700" t="inlineStr">
@@ -60250,7 +60250,7 @@
       </c>
       <c r="M708" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N708" t="inlineStr">
@@ -64013,7 +64013,7 @@
       </c>
       <c r="M752" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N752" t="inlineStr">
@@ -64182,7 +64182,7 @@
       </c>
       <c r="M754" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N754" t="inlineStr">
@@ -69913,7 +69913,7 @@
       </c>
       <c r="M822" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N822" t="inlineStr">
@@ -71479,7 +71479,7 @@
       </c>
       <c r="M840" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N840" t="inlineStr">
@@ -72947,7 +72947,7 @@
       </c>
       <c r="M857" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N857" t="inlineStr">
@@ -74747,7 +74747,7 @@
       </c>
       <c r="M878" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N878" t="inlineStr">
@@ -75693,7 +75693,7 @@
       </c>
       <c r="M889" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N889" t="inlineStr">
@@ -77678,7 +77678,7 @@
       </c>
       <c r="M912" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N912" t="inlineStr">
@@ -78717,7 +78717,7 @@
       </c>
       <c r="M924" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N924" t="inlineStr">
@@ -78973,7 +78973,7 @@
       </c>
       <c r="M927" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N927" t="inlineStr">
@@ -79403,7 +79403,7 @@
       </c>
       <c r="M932" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N932" t="inlineStr">
@@ -80534,7 +80534,7 @@
       </c>
       <c r="M945" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N945" t="inlineStr">
@@ -81486,7 +81486,7 @@
       </c>
       <c r="M956" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N956" t="inlineStr">
@@ -82008,7 +82008,7 @@
       </c>
       <c r="M962" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N962" t="inlineStr">
@@ -84526,7 +84526,7 @@
       </c>
       <c r="M991" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N991" t="inlineStr">
@@ -87310,7 +87310,7 @@
       </c>
       <c r="M1023" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1023" t="inlineStr">
@@ -88425,7 +88425,7 @@
       </c>
       <c r="M1036" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1036" t="inlineStr">
@@ -88855,7 +88855,7 @@
       </c>
       <c r="M1041" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1041" t="inlineStr">
@@ -92471,7 +92471,7 @@
       </c>
       <c r="M1083" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1083" t="inlineStr">
@@ -94782,7 +94782,7 @@
       </c>
       <c r="M1110" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1110" t="inlineStr">
@@ -98257,7 +98257,7 @@
       </c>
       <c r="M1150" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1150" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -2773,7 +2773,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -25644,7 +25644,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -31426,7 +31426,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -38625,7 +38625,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -41371,7 +41371,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -42497,7 +42497,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -43802,7 +43802,7 @@
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N514" t="inlineStr">
@@ -43976,7 +43976,7 @@
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N516" t="inlineStr">
@@ -46200,7 +46200,7 @@
       </c>
       <c r="M542" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N542" t="inlineStr">
@@ -47489,7 +47489,7 @@
       </c>
       <c r="M557" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N557" t="inlineStr">
@@ -48696,7 +48696,7 @@
       </c>
       <c r="M571" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N571" t="inlineStr">
@@ -49468,7 +49468,7 @@
       </c>
       <c r="M580" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N580" t="inlineStr">
@@ -49631,7 +49631,7 @@
       </c>
       <c r="M582" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N582" t="inlineStr">
@@ -49718,7 +49718,7 @@
       </c>
       <c r="M583" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N583" t="inlineStr">
@@ -57760,7 +57760,7 @@
       </c>
       <c r="M679" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N679" t="inlineStr">
@@ -58195,7 +58195,7 @@
       </c>
       <c r="M684" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N684" t="inlineStr">
@@ -59391,7 +59391,7 @@
       </c>
       <c r="M698" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N698" t="inlineStr">
@@ -62034,7 +62034,7 @@
       </c>
       <c r="M729" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N729" t="inlineStr">
@@ -64954,7 +64954,7 @@
       </c>
       <c r="M763" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N763" t="inlineStr">
@@ -68967,7 +68967,7 @@
       </c>
       <c r="M811" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N811" t="inlineStr">
@@ -69054,7 +69054,7 @@
       </c>
       <c r="M812" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N812" t="inlineStr">
@@ -70174,7 +70174,7 @@
       </c>
       <c r="M825" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N825" t="inlineStr">
@@ -72088,7 +72088,7 @@
       </c>
       <c r="M847" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N847" t="inlineStr">
@@ -72175,7 +72175,7 @@
       </c>
       <c r="M848" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N848" t="inlineStr">
@@ -75954,7 +75954,7 @@
       </c>
       <c r="M892" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N892" t="inlineStr">
@@ -78026,7 +78026,7 @@
       </c>
       <c r="M916" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N916" t="inlineStr">
@@ -79147,7 +79147,7 @@
       </c>
       <c r="M929" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N929" t="inlineStr">
@@ -79925,7 +79925,7 @@
       </c>
       <c r="M938" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N938" t="inlineStr">
@@ -80012,7 +80012,7 @@
       </c>
       <c r="M939" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N939" t="inlineStr">
@@ -81404,7 +81404,7 @@
       </c>
       <c r="M955" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N955" t="inlineStr">
@@ -81921,7 +81921,7 @@
       </c>
       <c r="M961" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N961" t="inlineStr">
@@ -82182,7 +82182,7 @@
       </c>
       <c r="M964" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N964" t="inlineStr">
@@ -82356,7 +82356,7 @@
       </c>
       <c r="M966" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N966" t="inlineStr">
@@ -84700,7 +84700,7 @@
       </c>
       <c r="M993" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N993" t="inlineStr">
@@ -85135,7 +85135,7 @@
       </c>
       <c r="M998" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N998" t="inlineStr">
@@ -85483,7 +85483,7 @@
       </c>
       <c r="M1002" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1002" t="inlineStr">
@@ -86440,7 +86440,7 @@
       </c>
       <c r="M1013" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1013" t="inlineStr">
@@ -86701,7 +86701,7 @@
       </c>
       <c r="M1016" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1016" t="inlineStr">
@@ -87397,7 +87397,7 @@
       </c>
       <c r="M1024" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1024" t="inlineStr">
@@ -89366,7 +89366,7 @@
       </c>
       <c r="M1047" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1047" t="inlineStr">
@@ -90399,7 +90399,7 @@
       </c>
       <c r="M1059" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1059" t="inlineStr">
@@ -91269,7 +91269,7 @@
       </c>
       <c r="M1069" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1069" t="inlineStr">
@@ -92895,7 +92895,7 @@
       </c>
       <c r="M1088" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1088" t="inlineStr">
@@ -94439,7 +94439,7 @@
       </c>
       <c r="M1106" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1106" t="inlineStr">
@@ -96957,7 +96957,7 @@
       </c>
       <c r="M1135" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1135" t="inlineStr">
@@ -98953,7 +98953,7 @@
       </c>
       <c r="M1158" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1158" t="inlineStr">
@@ -100062,7 +100062,7 @@
       </c>
       <c r="M1171" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1171" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -701,7 +701,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -17276,7 +17276,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -24144,7 +24144,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -24394,7 +24394,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -27781,7 +27781,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -30300,7 +30300,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -30474,7 +30474,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -33405,7 +33405,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -33579,7 +33579,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -33840,7 +33840,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -34275,7 +34275,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -34694,7 +34694,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -34781,7 +34781,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -35531,7 +35531,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -37070,7 +37070,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -38016,7 +38016,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -38103,7 +38103,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -38538,7 +38538,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -39223,7 +39223,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -39310,7 +39310,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -39821,7 +39821,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -39995,7 +39995,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -40517,7 +40517,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -41126,7 +41126,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -41545,7 +41545,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -42062,7 +42062,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -42932,7 +42932,7 @@
       </c>
       <c r="M504" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N504" t="inlineStr">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="M511" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N511" t="inlineStr">
@@ -43715,7 +43715,7 @@
       </c>
       <c r="M513" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N513" t="inlineStr">
@@ -45346,7 +45346,7 @@
       </c>
       <c r="M532" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N532" t="inlineStr">
@@ -48261,7 +48261,7 @@
       </c>
       <c r="M566" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N566" t="inlineStr">
@@ -48522,7 +48522,7 @@
       </c>
       <c r="M569" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N569" t="inlineStr">
@@ -49207,7 +49207,7 @@
       </c>
       <c r="M577" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N577" t="inlineStr">
@@ -50675,7 +50675,7 @@
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N594" t="inlineStr">
@@ -50762,7 +50762,7 @@
       </c>
       <c r="M595" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N595" t="inlineStr">
@@ -51110,7 +51110,7 @@
       </c>
       <c r="M599" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N599" t="inlineStr">
@@ -51632,7 +51632,7 @@
       </c>
       <c r="M605" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N605" t="inlineStr">
@@ -51806,7 +51806,7 @@
       </c>
       <c r="M607" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N607" t="inlineStr">
@@ -52230,7 +52230,7 @@
       </c>
       <c r="M612" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N612" t="inlineStr">
@@ -52915,7 +52915,7 @@
       </c>
       <c r="M620" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N620" t="inlineStr">
@@ -54976,7 +54976,7 @@
       </c>
       <c r="M647" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N647" t="inlineStr">
@@ -55411,7 +55411,7 @@
       </c>
       <c r="M652" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N652" t="inlineStr">
@@ -55759,7 +55759,7 @@
       </c>
       <c r="M656" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N656" t="inlineStr">
@@ -55933,7 +55933,7 @@
       </c>
       <c r="M658" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N658" t="inlineStr">
@@ -56716,7 +56716,7 @@
       </c>
       <c r="M667" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N667" t="inlineStr">
@@ -57064,7 +57064,7 @@
       </c>
       <c r="M671" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N671" t="inlineStr">
@@ -57238,7 +57238,7 @@
       </c>
       <c r="M673" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N673" t="inlineStr">
@@ -58445,7 +58445,7 @@
       </c>
       <c r="M687" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N687" t="inlineStr">
@@ -58532,7 +58532,7 @@
       </c>
       <c r="M688" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N688" t="inlineStr">
@@ -59043,7 +59043,7 @@
       </c>
       <c r="M694" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N694" t="inlineStr">
@@ -59217,7 +59217,7 @@
       </c>
       <c r="M696" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N696" t="inlineStr">
@@ -59728,7 +59728,7 @@
       </c>
       <c r="M702" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N702" t="inlineStr">
@@ -60598,7 +60598,7 @@
       </c>
       <c r="M712" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N712" t="inlineStr">
@@ -60685,7 +60685,7 @@
       </c>
       <c r="M713" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N713" t="inlineStr">
@@ -60772,7 +60772,7 @@
       </c>
       <c r="M714" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N714" t="inlineStr">
@@ -60946,7 +60946,7 @@
       </c>
       <c r="M716" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N716" t="inlineStr">
@@ -62643,7 +62643,7 @@
       </c>
       <c r="M736" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N736" t="inlineStr">
@@ -63763,7 +63763,7 @@
       </c>
       <c r="M749" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N749" t="inlineStr">
@@ -63850,7 +63850,7 @@
       </c>
       <c r="M750" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N750" t="inlineStr">
@@ -65976,7 +65976,7 @@
       </c>
       <c r="M775" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N775" t="inlineStr">
@@ -68358,7 +68358,7 @@
       </c>
       <c r="M804" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N804" t="inlineStr">
@@ -68532,7 +68532,7 @@
       </c>
       <c r="M806" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N806" t="inlineStr">
@@ -69141,7 +69141,7 @@
       </c>
       <c r="M813" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N813" t="inlineStr">
@@ -69228,7 +69228,7 @@
       </c>
       <c r="M814" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N814" t="inlineStr">
@@ -69489,7 +69489,7 @@
       </c>
       <c r="M817" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N817" t="inlineStr">
@@ -70348,7 +70348,7 @@
       </c>
       <c r="M827" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N827" t="inlineStr">
@@ -71740,7 +71740,7 @@
       </c>
       <c r="M843" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N843" t="inlineStr">
@@ -71827,7 +71827,7 @@
       </c>
       <c r="M844" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N844" t="inlineStr">
@@ -72523,7 +72523,7 @@
       </c>
       <c r="M852" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N852" t="inlineStr">
@@ -72860,7 +72860,7 @@
       </c>
       <c r="M856" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N856" t="inlineStr">
@@ -73110,7 +73110,7 @@
       </c>
       <c r="M859" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N859" t="inlineStr">
@@ -73621,7 +73621,7 @@
       </c>
       <c r="M865" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N865" t="inlineStr">
@@ -73795,7 +73795,7 @@
       </c>
       <c r="M867" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N867" t="inlineStr">
@@ -73882,7 +73882,7 @@
       </c>
       <c r="M868" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N868" t="inlineStr">
@@ -74143,7 +74143,7 @@
       </c>
       <c r="M871" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N871" t="inlineStr">
@@ -74230,7 +74230,7 @@
       </c>
       <c r="M872" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N872" t="inlineStr">
@@ -75171,7 +75171,7 @@
       </c>
       <c r="M883" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N883" t="inlineStr">
@@ -76900,7 +76900,7 @@
       </c>
       <c r="M903" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N903" t="inlineStr">
@@ -77509,7 +77509,7 @@
       </c>
       <c r="M910" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N910" t="inlineStr">
@@ -77596,7 +77596,7 @@
       </c>
       <c r="M911" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N911" t="inlineStr">
@@ -78374,7 +78374,7 @@
       </c>
       <c r="M920" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N920" t="inlineStr">
@@ -78804,7 +78804,7 @@
       </c>
       <c r="M925" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N925" t="inlineStr">
@@ -80273,7 +80273,7 @@
       </c>
       <c r="M942" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N942" t="inlineStr">
@@ -80795,7 +80795,7 @@
       </c>
       <c r="M948" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N948" t="inlineStr">
@@ -81230,7 +81230,7 @@
       </c>
       <c r="M953" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N953" t="inlineStr">
@@ -81317,7 +81317,7 @@
       </c>
       <c r="M954" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N954" t="inlineStr">
@@ -82878,7 +82878,7 @@
       </c>
       <c r="M972" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N972" t="inlineStr">
@@ -83487,7 +83487,7 @@
       </c>
       <c r="M979" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N979" t="inlineStr">
@@ -84270,7 +84270,7 @@
       </c>
       <c r="M988" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N988" t="inlineStr">
@@ -85222,7 +85222,7 @@
       </c>
       <c r="M999" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N999" t="inlineStr">
@@ -85570,7 +85570,7 @@
       </c>
       <c r="M1003" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1003" t="inlineStr">
@@ -85657,7 +85657,7 @@
       </c>
       <c r="M1004" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1004" t="inlineStr">
@@ -86005,7 +86005,7 @@
       </c>
       <c r="M1008" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1008" t="inlineStr">
@@ -86614,7 +86614,7 @@
       </c>
       <c r="M1015" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1015" t="inlineStr">
@@ -86788,7 +86788,7 @@
       </c>
       <c r="M1017" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1017" t="inlineStr">
@@ -86962,7 +86962,7 @@
       </c>
       <c r="M1019" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1019" t="inlineStr">
@@ -88169,7 +88169,7 @@
       </c>
       <c r="M1033" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1033" t="inlineStr">
@@ -88686,7 +88686,7 @@
       </c>
       <c r="M1039" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1039" t="inlineStr">
@@ -89192,7 +89192,7 @@
       </c>
       <c r="M1045" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1045" t="inlineStr">
@@ -89453,7 +89453,7 @@
       </c>
       <c r="M1048" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1048" t="inlineStr">
@@ -89540,7 +89540,7 @@
       </c>
       <c r="M1049" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1049" t="inlineStr">
@@ -90062,7 +90062,7 @@
       </c>
       <c r="M1055" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1055" t="inlineStr">
@@ -90312,7 +90312,7 @@
       </c>
       <c r="M1058" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1058" t="inlineStr">
@@ -90573,7 +90573,7 @@
       </c>
       <c r="M1061" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1061" t="inlineStr">
@@ -90834,7 +90834,7 @@
       </c>
       <c r="M1064" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1064" t="inlineStr">
@@ -91095,7 +91095,7 @@
       </c>
       <c r="M1067" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1067" t="inlineStr">
@@ -91530,7 +91530,7 @@
       </c>
       <c r="M1072" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1072" t="inlineStr">
@@ -92389,7 +92389,7 @@
       </c>
       <c r="M1082" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1082" t="inlineStr">
@@ -94015,7 +94015,7 @@
       </c>
       <c r="M1101" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1101" t="inlineStr">
@@ -94352,7 +94352,7 @@
       </c>
       <c r="M1105" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1105" t="inlineStr">
@@ -94700,7 +94700,7 @@
       </c>
       <c r="M1109" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1109" t="inlineStr">
@@ -95304,7 +95304,7 @@
       </c>
       <c r="M1116" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1116" t="inlineStr">
@@ -95391,7 +95391,7 @@
       </c>
       <c r="M1117" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1117" t="inlineStr">
@@ -95478,7 +95478,7 @@
       </c>
       <c r="M1118" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1118" t="inlineStr">
@@ -96000,7 +96000,7 @@
       </c>
       <c r="M1124" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1124" t="inlineStr">
@@ -96435,7 +96435,7 @@
       </c>
       <c r="M1129" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1129" t="inlineStr">
@@ -96522,7 +96522,7 @@
       </c>
       <c r="M1130" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1130" t="inlineStr">
@@ -96609,7 +96609,7 @@
       </c>
       <c r="M1131" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1131" t="inlineStr">
@@ -97218,7 +97218,7 @@
       </c>
       <c r="M1138" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1138" t="inlineStr">
@@ -97653,7 +97653,7 @@
       </c>
       <c r="M1143" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1143" t="inlineStr">
@@ -98088,7 +98088,7 @@
       </c>
       <c r="M1148" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1148" t="inlineStr">
@@ -98175,7 +98175,7 @@
       </c>
       <c r="M1149" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1149" t="inlineStr">
@@ -98431,7 +98431,7 @@
       </c>
       <c r="M1152" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1152" t="inlineStr">
@@ -98866,7 +98866,7 @@
       </c>
       <c r="M1157" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1157" t="inlineStr">

--- a/PowerApp_Data.xlsx
+++ b/PowerApp_Data.xlsx
@@ -3034,7 +3034,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -15776,7 +15776,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -17363,7 +17363,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -25481,7 +25481,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -30822,7 +30822,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -30909,7 +30909,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -33318,7 +33318,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -34014,7 +34014,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -40169,7 +40169,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -41284,7 +41284,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -41632,7 +41632,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -43193,7 +43193,7 @@
       </c>
       <c r="M507" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N507" t="inlineStr">
@@ -46374,7 +46374,7 @@
       </c>
       <c r="M544" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N544" t="inlineStr">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="M554" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N554" t="inlineStr">
@@ -48609,7 +48609,7 @@
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N570" t="inlineStr">
@@ -48859,7 +48859,7 @@
       </c>
       <c r="M573" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N573" t="inlineStr">
@@ -49294,7 +49294,7 @@
       </c>
       <c r="M578" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N578" t="inlineStr">
@@ -50849,7 +50849,7 @@
       </c>
       <c r="M596" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N596" t="inlineStr">
@@ -55237,7 +55237,7 @@
       </c>
       <c r="M650" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N650" t="inlineStr">
@@ -55498,7 +55498,7 @@
       </c>
       <c r="M653" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N653" t="inlineStr">
@@ -55585,7 +55585,7 @@
       </c>
       <c r="M654" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N654" t="inlineStr">
@@ -56803,7 +56803,7 @@
       </c>
       <c r="M668" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N668" t="inlineStr">
@@ -61207,7 +61207,7 @@
       </c>
       <c r="M719" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N719" t="inlineStr">
@@ -62817,7 +62817,7 @@
       </c>
       <c r="M738" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N738" t="inlineStr">
@@ -64443,7 +64443,7 @@
       </c>
       <c r="M757" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N757" t="inlineStr">
@@ -70000,7 +70000,7 @@
       </c>
       <c r="M823" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N823" t="inlineStr">
@@ -70261,7 +70261,7 @@
       </c>
       <c r="M826" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N826" t="inlineStr">
@@ -70609,7 +70609,7 @@
       </c>
       <c r="M830" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N830" t="inlineStr">
@@ -70783,7 +70783,7 @@
       </c>
       <c r="M832" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N832" t="inlineStr">
@@ -72436,7 +72436,7 @@
       </c>
       <c r="M851" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N851" t="inlineStr">
@@ -76639,7 +76639,7 @@
       </c>
       <c r="M900" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N900" t="inlineStr">
@@ -78200,7 +78200,7 @@
       </c>
       <c r="M918" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N918" t="inlineStr">
@@ -83748,7 +83748,7 @@
       </c>
       <c r="M982" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N982" t="inlineStr">
@@ -84009,7 +84009,7 @@
       </c>
       <c r="M985" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N985" t="inlineStr">
@@ -89714,7 +89714,7 @@
       </c>
       <c r="M1051" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1051" t="inlineStr">
@@ -90921,7 +90921,7 @@
       </c>
       <c r="M1065" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1065" t="inlineStr">
@@ -91704,7 +91704,7 @@
       </c>
       <c r="M1074" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1074" t="inlineStr">
@@ -96348,7 +96348,7 @@
       </c>
       <c r="M1128" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1128" t="inlineStr">
@@ -97392,7 +97392,7 @@
       </c>
       <c r="M1140" t="inlineStr">
         <is>
-          <t>SIN CONEXION</t>
+          <t>CONECTADO</t>
         </is>
       </c>
       <c r="N1140" t="inlineStr">
